--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP91" headerRowCount="1">
-  <autoFilter ref="A1:EP91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP92" headerRowCount="1">
+  <autoFilter ref="A1:EP92"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP91"/>
+  <dimension ref="A1:EP92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -3229,7 +3229,7 @@
         <v>1.86</v>
       </c>
       <c r="DE5" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE11" t="n">
         <v>0.57</v>
@@ -10317,7 +10317,7 @@
         <v>1.43</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -11738,7 +11738,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE23" t="n">
         <v>1.13</v>
@@ -15565,7 +15565,7 @@
         <v>1.38</v>
       </c>
       <c r="DE31" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -16203,70 +16203,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>21</v>
+      </c>
+      <c r="V33" t="n">
         <v>11</v>
       </c>
-      <c r="L33" t="n">
-        <v>14</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>15</v>
-      </c>
-      <c r="U33" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>18</v>
-      </c>
       <c r="W33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -16276,97 +16276,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO33" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB33" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -16381,64 +16381,64 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK33" t="n">
         <v>3</v>
       </c>
-      <c r="BK33" t="n">
-        <v>1</v>
-      </c>
       <c r="BL33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO33" t="n">
         <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR33" t="n">
         <v>1</v>
       </c>
       <c r="BS33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU33" t="n">
         <v>1</v>
       </c>
       <c r="BV33" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW33" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX33" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY33" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA33" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -16471,7 +16471,7 @@
         <v>0</v>
       </c>
       <c r="CM33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
@@ -16486,73 +16486,73 @@
         <v>1</v>
       </c>
       <c r="CR33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS33" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT33" t="n">
         <v>1</v>
       </c>
       <c r="CU33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW33" t="n">
         <v>1</v>
       </c>
       <c r="CX33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CY33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB33" t="n">
         <v>67</v>
       </c>
-      <c r="DA33" t="n">
+      <c r="DC33" t="n">
         <v>100</v>
       </c>
-      <c r="DB33" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC33" t="n">
-        <v>67</v>
-      </c>
       <c r="DD33" t="n">
-        <v>0.88</v>
+        <v>2.25</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="DF33" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG33" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH33" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI33" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DJ33" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL33" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="DN33" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO33" t="n">
         <v>15</v>
@@ -16561,82 +16561,82 @@
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW33" t="n">
-        <v>16.01</v>
+        <v>16.08</v>
       </c>
       <c r="DX33" t="n">
-        <v>9.800000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EF33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EG33" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EH33" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EI33" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ33" t="inlineStr">
@@ -16656,12 +16656,12 @@
       </c>
       <c r="EM33" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN33" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EO33" t="inlineStr"/>
@@ -16683,70 +16683,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L34" t="n">
+        <v>14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>18</v>
+      </c>
+      <c r="W34" t="n">
         <v>10</v>
       </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>12</v>
-      </c>
-      <c r="R34" t="n">
-        <v>5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>9</v>
-      </c>
-      <c r="T34" t="n">
-        <v>6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>21</v>
-      </c>
-      <c r="V34" t="n">
-        <v>11</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
-      </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16756,97 +16756,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16861,178 +16861,178 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ34" t="n">
         <v>3</v>
       </c>
-      <c r="BJ34" t="n">
-        <v>2</v>
-      </c>
       <c r="BK34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR34" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY34" t="n">
         <v>5</v>
       </c>
-      <c r="BO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB34" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS34" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX34" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY34" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA34" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB34" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC34" t="n">
         <v>67</v>
       </c>
-      <c r="DC34" t="n">
-        <v>100</v>
-      </c>
       <c r="DD34" t="n">
-        <v>2.25</v>
+        <v>0.88</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF34" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ34" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK34" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL34" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN34" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO34" t="n">
         <v>15</v>
@@ -17041,107 +17041,107 @@
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW34" t="n">
-        <v>16.08</v>
+        <v>16.01</v>
       </c>
       <c r="DX34" t="n">
-        <v>8.460000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="ED34" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EE34" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EG34" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EH34" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ34" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EL34" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM34" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EN34" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="ED34" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EE34" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EF34" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EG34" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EH34" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EJ34" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK34" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EL34" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM34" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EN34" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EO34" t="inlineStr"/>
@@ -19402,7 +19402,7 @@
         <v>84</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE39" t="n">
         <v>1.13</v>
@@ -22741,7 +22741,7 @@
         <v>1.29</v>
       </c>
       <c r="DE46" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>84</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE48" t="n">
         <v>1.14</v>
@@ -28394,7 +28394,7 @@
         <v>75</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE58" t="n">
         <v>0.29</v>
@@ -28877,7 +28877,7 @@
         <v>1.29</v>
       </c>
       <c r="DE59" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF59" t="n">
         <v>1.5</v>
@@ -30423,22 +30423,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -30447,16 +30447,16 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -30465,120 +30465,128 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V63" t="n">
         <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X63" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y63" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z63" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AF63" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AN63" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AU63" t="n">
         <v>3</v>
       </c>
       <c r="AV63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX63" t="n">
         <v>0</v>
       </c>
       <c r="AY63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB63" t="n">
-        <v>2521</v>
+        <v>986</v>
       </c>
       <c r="BC63" t="n">
         <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="BE63" t="n">
         <v>0</v>
@@ -30593,178 +30601,178 @@
         <v>1</v>
       </c>
       <c r="BI63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK63" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU63" t="n">
         <v>3</v>
       </c>
-      <c r="BL63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV63" t="n">
-        <v>53</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>63</v>
-      </c>
-      <c r="BX63" t="n">
-        <v>84</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ63" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CA63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CB63" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM63" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS63" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU63" t="n">
-        <v>12</v>
-      </c>
       <c r="CV63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW63" t="n">
         <v>1</v>
       </c>
       <c r="CX63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ63" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA63" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DB63" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="DC63" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="DF63" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG63" t="n">
         <v>1.2</v>
       </c>
       <c r="DH63" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="DI63" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ63" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK63" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="DL63" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="DM63" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="DN63" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="DO63" t="n">
         <v>15</v>
@@ -30788,86 +30796,102 @@
         <v>0</v>
       </c>
       <c r="DV63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW63" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="DX63" t="n">
-        <v>9.65</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY63" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ63" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA63" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EB63" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EC63" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="ED63" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EE63" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EF63" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG63" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EH63" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EI63" t="inlineStr"/>
-      <c r="EJ63" t="inlineStr"/>
-      <c r="EK63" t="inlineStr"/>
-      <c r="EL63" t="inlineStr"/>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI63" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EJ63" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK63" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EL63" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EM63" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EN63" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EO63" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP63" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.34</t>
         </is>
       </c>
     </row>
@@ -30887,22 +30911,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>3</v>
@@ -30911,16 +30935,16 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -30929,128 +30953,120 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V64" t="n">
         <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y64" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z64" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE64" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF64" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL64" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AM64" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AN64" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AO64" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AS64" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AU64" t="n">
         <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX64" t="n">
         <v>0</v>
       </c>
       <c r="AY64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB64" t="n">
-        <v>986</v>
+        <v>2521</v>
       </c>
       <c r="BC64" t="n">
         <v>0</v>
       </c>
       <c r="BD64" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="BE64" t="n">
         <v>0</v>
@@ -31065,37 +31081,37 @@
         <v>1</v>
       </c>
       <c r="BI64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL64" t="n">
         <v>2</v>
       </c>
       <c r="BM64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN64" t="n">
         <v>5</v>
       </c>
-      <c r="BN64" t="n">
-        <v>6</v>
-      </c>
       <c r="BO64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP64" t="n">
         <v>0</v>
       </c>
       <c r="BQ64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT64" t="n">
         <v>2</v>
@@ -31104,25 +31120,25 @@
         <v>1</v>
       </c>
       <c r="BV64" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BW64" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="BX64" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BY64" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="BZ64" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="CB64" t="n">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="CC64" t="n">
         <v>0</v>
@@ -31155,7 +31171,7 @@
         <v>0</v>
       </c>
       <c r="CM64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
@@ -31170,73 +31186,73 @@
         <v>1</v>
       </c>
       <c r="CR64" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CS64" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT64" t="n">
         <v>1</v>
       </c>
       <c r="CU64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CV64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW64" t="n">
         <v>1</v>
       </c>
       <c r="CX64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ64" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="DA64" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DB64" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="DC64" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="DD64" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="DF64" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DG64" t="n">
         <v>1.2</v>
       </c>
       <c r="DH64" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="DI64" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ64" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK64" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="DL64" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="DM64" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="DN64" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="DO64" t="n">
         <v>15</v>
@@ -31260,102 +31276,86 @@
         <v>0</v>
       </c>
       <c r="DV64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW64" t="n">
-        <v>12.5</v>
+        <v>13.33</v>
       </c>
       <c r="DX64" t="n">
-        <v>9.859999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="DY64" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ64" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="EA64" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB64" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC64" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="ED64" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EE64" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EF64" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG64" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EH64" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EI64" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EJ64" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EK64" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EL64" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI64" t="inlineStr"/>
+      <c r="EJ64" t="inlineStr"/>
+      <c r="EK64" t="inlineStr"/>
+      <c r="EL64" t="inlineStr"/>
       <c r="EM64" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EN64" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EO64" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP64" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -31719,7 +31719,7 @@
         <v>3.44</v>
       </c>
       <c r="DO65" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -33110,7 +33110,7 @@
         <v>82</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE68" t="n">
         <v>1.88</v>
@@ -33263,12 +33263,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -33278,25 +33278,25 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>6</v>
+      </c>
+      <c r="K69" t="n">
         <v>3</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>9</v>
       </c>
-      <c r="K69" t="n">
-        <v>6</v>
-      </c>
-      <c r="L69" t="n">
-        <v>15</v>
-      </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -33305,101 +33305,101 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T69" t="n">
         <v>10</v>
       </c>
       <c r="U69" t="n">
+        <v>14</v>
+      </c>
+      <c r="V69" t="n">
+        <v>13</v>
+      </c>
+      <c r="W69" t="n">
         <v>10</v>
       </c>
-      <c r="V69" t="n">
-        <v>18</v>
-      </c>
-      <c r="W69" t="n">
-        <v>6</v>
-      </c>
       <c r="X69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y69" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="Z69" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AF69" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AG69" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL69" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AM69" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN69" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AO69" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR69" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AS69" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AU69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV69" t="n">
         <v>1</v>
@@ -33411,22 +33411,22 @@
         <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA69" t="n">
         <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>2523</v>
+        <v>986</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="BE69" t="n">
         <v>0</v>
@@ -33435,46 +33435,46 @@
         <v>-1</v>
       </c>
       <c r="BG69" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH69" t="n">
         <v>1</v>
       </c>
       <c r="BI69" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BJ69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL69" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM69" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BN69" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR69" t="n">
         <v>1</v>
       </c>
       <c r="BS69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
@@ -33483,22 +33483,22 @@
         <v>17</v>
       </c>
       <c r="BW69" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BX69" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BY69" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BZ69" t="n">
-        <v>0.89</v>
+        <v>1.49</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="CB69" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CC69" t="n">
         <v>0</v>
@@ -33525,16 +33525,16 @@
         <v>1</v>
       </c>
       <c r="CK69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL69" t="n">
         <v>0</v>
       </c>
       <c r="CM69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO69" t="n">
         <v>0</v>
@@ -33546,73 +33546,73 @@
         <v>1</v>
       </c>
       <c r="CR69" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="CS69" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT69" t="n">
         <v>1</v>
       </c>
       <c r="CU69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV69" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY69" t="n">
         <v>7</v>
       </c>
-      <c r="CW69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX69" t="n">
+      <c r="CZ69" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB69" t="n">
         <v>9</v>
       </c>
-      <c r="CY69" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ69" t="n">
-        <v>80</v>
-      </c>
-      <c r="DA69" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB69" t="n">
-        <v>80</v>
-      </c>
       <c r="DC69" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="DD69" t="n">
         <v>1.29</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="DF69" t="n">
         <v>1.2</v>
       </c>
       <c r="DG69" t="n">
-        <v>0.4</v>
+        <v>1.17</v>
       </c>
       <c r="DH69" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="DI69" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="DJ69" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK69" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="DL69" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="DN69" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="DO69" t="n">
         <v>15</v>
@@ -33621,10 +33621,10 @@
         <v>1</v>
       </c>
       <c r="DQ69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS69" t="b">
         <v>0</v>
@@ -33636,62 +33636,62 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW69" t="n">
-        <v>9.23</v>
+        <v>9.83</v>
       </c>
       <c r="DX69" t="n">
-        <v>6.84</v>
+        <v>5.78</v>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ69" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="EA69" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EB69" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC69" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="ED69" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EE69" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EF69" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="EC69" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="ED69" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="EE69" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EF69" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EG69" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH69" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI69" t="inlineStr"/>
@@ -33700,12 +33700,12 @@
       <c r="EL69" t="inlineStr"/>
       <c r="EM69" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EN69" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EO69" t="inlineStr"/>
@@ -33727,12 +33727,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -33742,25 +33742,25 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
+        <v>9</v>
+      </c>
+      <c r="K70" t="n">
         <v>6</v>
       </c>
-      <c r="K70" t="n">
-        <v>3</v>
-      </c>
       <c r="L70" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -33769,102 +33769,102 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T70" t="n">
         <v>10</v>
       </c>
       <c r="U70" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V70" t="n">
+        <v>18</v>
+      </c>
+      <c r="W70" t="n">
+        <v>6</v>
+      </c>
+      <c r="X70" t="n">
         <v>13</v>
       </c>
-      <c r="W70" t="n">
-        <v>10</v>
-      </c>
-      <c r="X70" t="n">
-        <v>11</v>
-      </c>
       <c r="Y70" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="Z70" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU70" t="n">
         <v>3</v>
       </c>
-      <c r="AD70" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ70" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR70" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT70" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU70" t="n">
-        <v>1</v>
-      </c>
       <c r="AV70" t="n">
         <v>1</v>
       </c>
@@ -33875,22 +33875,22 @@
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
       </c>
       <c r="BB70" t="n">
-        <v>986</v>
+        <v>2523</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -33899,46 +33899,46 @@
         <v>-1</v>
       </c>
       <c r="BG70" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH70" t="n">
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BJ70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL70" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM70" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BN70" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR70" t="n">
         <v>1</v>
       </c>
       <c r="BS70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU70" t="n">
         <v>1</v>
@@ -33947,136 +33947,136 @@
         <v>17</v>
       </c>
       <c r="BW70" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BX70" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>40</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR70" t="n">
         <v>35</v>
       </c>
-      <c r="BY70" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ70" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA70" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB70" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>16</v>
-      </c>
       <c r="CS70" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU70" t="n">
         <v>14</v>
       </c>
-      <c r="CT70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU70" t="n">
-        <v>12</v>
-      </c>
       <c r="CV70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW70" t="n">
         <v>1</v>
       </c>
       <c r="CX70" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CY70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ70" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA70" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="DB70" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="DC70" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="DD70" t="n">
         <v>1.29</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.88</v>
+        <v>1.14</v>
       </c>
       <c r="DF70" t="n">
         <v>1.2</v>
       </c>
       <c r="DG70" t="n">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="DH70" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="DI70" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="DJ70" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK70" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="DL70" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="DM70" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="DN70" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="DO70" t="n">
         <v>15</v>
@@ -34085,10 +34085,10 @@
         <v>1</v>
       </c>
       <c r="DQ70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS70" t="b">
         <v>0</v>
@@ -34100,62 +34100,62 @@
         <v>0</v>
       </c>
       <c r="DV70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW70" t="n">
-        <v>9.83</v>
+        <v>9.23</v>
       </c>
       <c r="DX70" t="n">
-        <v>5.78</v>
+        <v>6.84</v>
       </c>
       <c r="DY70" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ70" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA70" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EB70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC70" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="ED70" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EE70" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EF70" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EG70" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EH70" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI70" t="inlineStr"/>
@@ -34164,12 +34164,12 @@
       <c r="EL70" t="inlineStr"/>
       <c r="EM70" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EN70" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EO70" t="inlineStr"/>
@@ -34513,7 +34513,7 @@
         <v>2</v>
       </c>
       <c r="DE71" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF71" t="n">
         <v>2</v>
@@ -36071,146 +36071,146 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
         <v>4</v>
       </c>
-      <c r="I75" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="R75" t="n">
         <v>7</v>
       </c>
-      <c r="K75" t="n">
+      <c r="S75" t="n">
+        <v>9</v>
+      </c>
+      <c r="T75" t="n">
+        <v>7</v>
+      </c>
+      <c r="U75" t="n">
+        <v>13</v>
+      </c>
+      <c r="V75" t="n">
+        <v>14</v>
+      </c>
+      <c r="W75" t="n">
+        <v>15</v>
+      </c>
+      <c r="X75" t="n">
         <v>5</v>
       </c>
-      <c r="L75" t="n">
-        <v>12</v>
-      </c>
-      <c r="M75" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>5</v>
-      </c>
-      <c r="R75" t="n">
-        <v>12</v>
-      </c>
-      <c r="S75" t="n">
-        <v>5</v>
-      </c>
-      <c r="T75" t="n">
-        <v>9</v>
-      </c>
-      <c r="U75" t="n">
-        <v>10</v>
-      </c>
-      <c r="V75" t="n">
-        <v>21</v>
-      </c>
-      <c r="W75" t="n">
-        <v>6</v>
-      </c>
-      <c r="X75" t="n">
-        <v>11</v>
-      </c>
       <c r="Y75" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z75" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AF75" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AL75" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AM75" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AN75" t="n">
         <v>1.83</v>
       </c>
       <c r="AO75" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AR75" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AS75" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AU75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW75" t="n">
         <v>2</v>
@@ -36219,22 +36219,22 @@
         <v>0</v>
       </c>
       <c r="AY75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB75" t="n">
-        <v>955</v>
+        <v>2522</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -36252,175 +36252,175 @@
         <v>3</v>
       </c>
       <c r="BJ75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK75" t="n">
         <v>3</v>
       </c>
-      <c r="BK75" t="n">
+      <c r="BL75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX75" t="n">
         <v>4</v>
       </c>
-      <c r="BL75" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV75" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW75" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX75" t="n">
-        <v>63</v>
-      </c>
-      <c r="BY75" t="n">
-        <v>102</v>
-      </c>
-      <c r="BZ75" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CA75" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CB75" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="CC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM75" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU75" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV75" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX75" t="n">
+      <c r="CY75" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK75" t="n">
         <v>9</v>
       </c>
-      <c r="CY75" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ75" t="n">
-        <v>27</v>
-      </c>
-      <c r="DA75" t="n">
-        <v>72</v>
-      </c>
-      <c r="DB75" t="n">
-        <v>9</v>
-      </c>
-      <c r="DC75" t="n">
-        <v>45</v>
-      </c>
-      <c r="DD75" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DE75" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF75" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DG75" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DH75" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI75" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ75" t="n">
-        <v>74</v>
-      </c>
-      <c r="DK75" t="n">
-        <v>29</v>
-      </c>
       <c r="DL75" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="DO75" t="n">
         <v>15</v>
@@ -36435,7 +36435,7 @@
         <v>1</v>
       </c>
       <c r="DS75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT75" t="b">
         <v>0</v>
@@ -36444,88 +36444,88 @@
         <v>0</v>
       </c>
       <c r="DV75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW75" t="n">
-        <v>11.38</v>
+        <v>11.71</v>
       </c>
       <c r="DX75" t="n">
-        <v>11.66</v>
+        <v>9.65</v>
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EE75" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EF75" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EG75" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EH75" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EI75" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI75" t="inlineStr"/>
       <c r="EJ75" t="inlineStr"/>
       <c r="EK75" t="inlineStr"/>
-      <c r="EL75" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+      <c r="EL75" t="inlineStr"/>
       <c r="EM75" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EN75" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EO75" t="inlineStr"/>
-      <c r="EP75" t="inlineStr"/>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EO75" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EP75" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -36543,146 +36543,146 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
+        <v>7</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5</v>
+      </c>
+      <c r="L76" t="n">
+        <v>12</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>12</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="n">
+        <v>9</v>
+      </c>
+      <c r="U76" t="n">
+        <v>10</v>
+      </c>
+      <c r="V76" t="n">
+        <v>21</v>
+      </c>
+      <c r="W76" t="n">
         <v>6</v>
       </c>
-      <c r="K76" t="n">
-        <v>10</v>
-      </c>
-      <c r="L76" t="n">
-        <v>16</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>4</v>
-      </c>
-      <c r="R76" t="n">
+      <c r="X76" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
         <v>7</v>
       </c>
-      <c r="S76" t="n">
-        <v>9</v>
-      </c>
-      <c r="T76" t="n">
-        <v>7</v>
-      </c>
-      <c r="U76" t="n">
-        <v>13</v>
-      </c>
-      <c r="V76" t="n">
-        <v>14</v>
-      </c>
-      <c r="W76" t="n">
-        <v>15</v>
-      </c>
-      <c r="X76" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AF76" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL76" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN76" t="n">
         <v>1.83</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AS76" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AU76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW76" t="n">
         <v>2</v>
@@ -36691,22 +36691,22 @@
         <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB76" t="n">
-        <v>2522</v>
+        <v>955</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36724,19 +36724,19 @@
         <v>3</v>
       </c>
       <c r="BJ76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO76" t="n">
         <v>1</v>
@@ -36745,7 +36745,7 @@
         <v>0</v>
       </c>
       <c r="BQ76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR76" t="n">
         <v>0</v>
@@ -36754,31 +36754,31 @@
         <v>1</v>
       </c>
       <c r="BT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU76" t="n">
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BW76" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="BX76" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="BY76" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ76" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="CA76" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="CB76" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
@@ -36805,16 +36805,16 @@
         <v>1</v>
       </c>
       <c r="CK76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL76" t="n">
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO76" t="n">
         <v>0</v>
@@ -36826,73 +36826,73 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS76" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CV76" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY76" t="n">
         <v>4</v>
       </c>
-      <c r="CY76" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ76" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="DA76" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="DB76" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="DC76" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="DD76" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF76" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG76" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH76" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="DI76" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="DJ76" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="DK76" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="DL76" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="DO76" t="n">
         <v>15</v>
@@ -36907,7 +36907,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -36916,88 +36916,88 @@
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW76" t="n">
-        <v>11.71</v>
+        <v>11.38</v>
       </c>
       <c r="DX76" t="n">
-        <v>9.65</v>
+        <v>11.66</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EG76" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EH76" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EI76" t="inlineStr"/>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EI76" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
       <c r="EJ76" t="inlineStr"/>
       <c r="EK76" t="inlineStr"/>
-      <c r="EL76" t="inlineStr"/>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EM76" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EN76" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EO76" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EP76" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EO76" t="inlineStr"/>
+      <c r="EP76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -40674,7 +40674,7 @@
         <v>75</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DE84" t="n">
         <v>2.14</v>
@@ -41157,7 +41157,7 @@
         <v>2.25</v>
       </c>
       <c r="DE85" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DF85" t="n">
         <v>2.43</v>
@@ -41787,143 +41787,143 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" t="n">
+        <v>9</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
         <v>6</v>
       </c>
-      <c r="L87" t="n">
-        <v>10</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>6</v>
-      </c>
-      <c r="R87" t="n">
-        <v>3</v>
-      </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U87" t="n">
         <v>11</v>
       </c>
       <c r="V87" t="n">
+        <v>21</v>
+      </c>
+      <c r="W87" t="n">
         <v>14</v>
       </c>
-      <c r="W87" t="n">
-        <v>9</v>
-      </c>
       <c r="X87" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y87" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="Z87" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Vejle Stadion</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Roms Hule 3, Vejle</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD87" t="n">
         <v>1</v>
       </c>
       <c r="AE87" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="AF87" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG87" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL87" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AN87" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AO87" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AU87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV87" t="n">
         <v>0</v>
@@ -41932,25 +41932,25 @@
         <v>0</v>
       </c>
       <c r="AX87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA87" t="n">
         <v>0</v>
       </c>
       <c r="BB87" t="n">
-        <v>3647</v>
+        <v>2526</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -41968,175 +41968,175 @@
         <v>1</v>
       </c>
       <c r="BJ87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL87" t="n">
         <v>4</v>
       </c>
       <c r="BM87" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS87" t="n">
         <v>3</v>
       </c>
-      <c r="BN87" t="n">
+      <c r="BT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN87" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR87" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
         <v>7</v>
       </c>
-      <c r="BO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV87" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW87" t="n">
+      <c r="CY87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ87" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA87" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC87" t="n">
         <v>64</v>
       </c>
-      <c r="BX87" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY87" t="n">
-        <v>153</v>
-      </c>
-      <c r="BZ87" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CA87" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB87" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR87" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS87" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU87" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV87" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX87" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY87" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ87" t="n">
-        <v>79</v>
-      </c>
-      <c r="DA87" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB87" t="n">
+      <c r="DD87" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DE87" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI87" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ87" t="n">
         <v>57</v>
       </c>
-      <c r="DC87" t="n">
-        <v>79</v>
-      </c>
-      <c r="DD87" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE87" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DF87" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DG87" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DH87" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI87" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DJ87" t="n">
+      <c r="DK87" t="n">
         <v>22</v>
       </c>
-      <c r="DK87" t="n">
-        <v>0</v>
-      </c>
       <c r="DL87" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="DN87" t="n">
-        <v>3.26</v>
+        <v>2.68</v>
       </c>
       <c r="DO87" t="n">
         <v>15</v>
@@ -42148,7 +42148,7 @@
         <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS87" t="b">
         <v>0</v>
@@ -42163,83 +42163,83 @@
         <v>0</v>
       </c>
       <c r="DW87" t="n">
-        <v>9.470000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DX87" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EB87" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EC87" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="ED87" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EE87" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EF87" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EG87" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EH87" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI87" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EJ87" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EK87" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr"/>
+      <c r="EK87" t="inlineStr"/>
       <c r="EL87" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EM87" t="inlineStr"/>
-      <c r="EN87" t="inlineStr"/>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EN87" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EO87" t="inlineStr"/>
       <c r="EP87" t="inlineStr"/>
     </row>
@@ -42259,143 +42259,143 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" t="n">
+        <v>6</v>
+      </c>
+      <c r="L88" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>6</v>
+      </c>
+      <c r="R88" t="n">
         <v>3</v>
       </c>
-      <c r="I88" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" t="n">
-        <v>8</v>
-      </c>
-      <c r="L88" t="n">
-        <v>9</v>
-      </c>
-      <c r="M88" t="n">
-        <v>2</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>2</v>
-      </c>
-      <c r="R88" t="n">
-        <v>6</v>
-      </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T88" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U88" t="n">
         <v>11</v>
       </c>
       <c r="V88" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W88" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X88" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y88" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="Z88" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>1</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="AF88" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG88" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL88" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AN88" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AP88" t="n">
         <v>1.82</v>
       </c>
-      <c r="AO88" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP88" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AQ88" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AU88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV88" t="n">
         <v>0</v>
@@ -42404,25 +42404,25 @@
         <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA88" t="n">
         <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>2526</v>
+        <v>3647</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
@@ -42440,22 +42440,22 @@
         <v>1</v>
       </c>
       <c r="BJ88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL88" t="n">
         <v>4</v>
       </c>
       <c r="BM88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN88" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP88" t="n">
         <v>1</v>
@@ -42467,7 +42467,7 @@
         <v>0</v>
       </c>
       <c r="BS88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT88" t="n">
         <v>0</v>
@@ -42476,25 +42476,25 @@
         <v>1</v>
       </c>
       <c r="BV88" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW88" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BX88" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="BY88" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="BZ88" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="CA88" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="CB88" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="CC88" t="n">
         <v>0</v>
@@ -42527,10 +42527,10 @@
         <v>0</v>
       </c>
       <c r="CM88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO88" t="n">
         <v>0</v>
@@ -42542,73 +42542,73 @@
         <v>1</v>
       </c>
       <c r="CR88" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="CS88" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
         <v>10</v>
       </c>
-      <c r="CT88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU88" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV88" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX88" t="n">
+      <c r="CY88" t="n">
         <v>7</v>
       </c>
-      <c r="CY88" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ88" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="DA88" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC88" t="n">
         <v>79</v>
       </c>
-      <c r="DB88" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC88" t="n">
-        <v>64</v>
-      </c>
       <c r="DD88" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="DF88" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="DG88" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DH88" t="n">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="DI88" t="n">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="DJ88" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="DK88" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="DL88" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="DM88" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="DN88" t="n">
-        <v>2.68</v>
+        <v>3.26</v>
       </c>
       <c r="DO88" t="n">
         <v>15</v>
@@ -42620,7 +42620,7 @@
         <v>1</v>
       </c>
       <c r="DR88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS88" t="b">
         <v>0</v>
@@ -42635,83 +42635,83 @@
         <v>0</v>
       </c>
       <c r="DW88" t="n">
-        <v>8.84</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DX88" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="ED88" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EE88" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG88" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EH88" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="EC88" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="ED88" t="inlineStr">
-        <is>
-          <t>3.84</t>
-        </is>
-      </c>
-      <c r="EE88" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EF88" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EG88" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="EH88" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EI88" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EJ88" t="inlineStr"/>
-      <c r="EK88" t="inlineStr"/>
+      <c r="EK88" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
       <c r="EL88" t="inlineStr">
         <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EM88" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EN88" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr"/>
+      <c r="EN88" t="inlineStr"/>
       <c r="EO88" t="inlineStr"/>
       <c r="EP88" t="inlineStr"/>
     </row>
@@ -44098,6 +44098,478 @@
       <c r="EN91" t="inlineStr"/>
       <c r="EO91" t="inlineStr"/>
       <c r="EP91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>16</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>45982.75</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>4</v>
+      </c>
+      <c r="L92" t="n">
+        <v>9</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>4</v>
+      </c>
+      <c r="R92" t="n">
+        <v>4</v>
+      </c>
+      <c r="S92" t="n">
+        <v>3</v>
+      </c>
+      <c r="T92" t="n">
+        <v>12</v>
+      </c>
+      <c r="U92" t="n">
+        <v>7</v>
+      </c>
+      <c r="V92" t="n">
+        <v>16</v>
+      </c>
+      <c r="W92" t="n">
+        <v>6</v>
+      </c>
+      <c r="X92" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>2516</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ92" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK92" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>116</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>79</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>69</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV92" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX92" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY92" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ92" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA92" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB92" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC92" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD92" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE92" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DF92" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG92" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DH92" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI92" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DJ92" t="n">
+        <v>43</v>
+      </c>
+      <c r="DK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL92" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM92" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN92" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DO92" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ92" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV92" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW92" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DX92" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="DY92" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="DZ92" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="EA92" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EB92" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EC92" t="inlineStr">
+        <is>
+          <t>3.89</t>
+        </is>
+      </c>
+      <c r="ED92" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="EE92" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF92" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG92" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EH92" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI92" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EJ92" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EK92" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EL92" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EM92" t="inlineStr"/>
+      <c r="EN92" t="inlineStr"/>
+      <c r="EO92" t="inlineStr"/>
+      <c r="EP92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP92" headerRowCount="1">
-  <autoFilter ref="A1:EP92"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP97" headerRowCount="1">
+  <autoFilter ref="A1:EP97"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP92"/>
+  <dimension ref="A1:EP97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE2" t="n">
         <v>1.88</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE5" t="n">
         <v>2.25</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3701,7 +3701,7 @@
         <v>2.25</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4659,7 +4659,7 @@
         <v>0.76</v>
       </c>
       <c r="DO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5114,10 +5114,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6061,7 +6061,7 @@
         <v>1.25</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE12" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7035,7 +7035,7 @@
         <v>2.01</v>
       </c>
       <c r="DO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7507,7 +7507,7 @@
         <v>3.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7957,7 +7957,7 @@
         <v>1</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -7987,7 +7987,7 @@
         <v>2.69</v>
       </c>
       <c r="DO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8418,7 +8418,7 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE16" t="n">
         <v>1</v>
@@ -8451,7 +8451,7 @@
         <v>0.91</v>
       </c>
       <c r="DO16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8898,7 +8898,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE17" t="n">
         <v>1.13</v>
@@ -8931,7 +8931,7 @@
         <v>2.96</v>
       </c>
       <c r="DO17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9373,7 +9373,7 @@
         <v>2</v>
       </c>
       <c r="DE18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9403,7 +9403,7 @@
         <v>1.58</v>
       </c>
       <c r="DO18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP18" t="b">
         <v>0</v>
@@ -9883,7 +9883,7 @@
         <v>3.11</v>
       </c>
       <c r="DO19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10314,7 +10314,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE20" t="n">
         <v>2.25</v>
@@ -10347,7 +10347,7 @@
         <v>2.67</v>
       </c>
       <c r="DO20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10786,7 +10786,7 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE21" t="n">
         <v>1.13</v>
@@ -10819,7 +10819,7 @@
         <v>3.19</v>
       </c>
       <c r="DO21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11269,7 +11269,7 @@
         <v>2.25</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -11299,7 +11299,7 @@
         <v>3.1</v>
       </c>
       <c r="DO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11771,7 +11771,7 @@
         <v>3.75</v>
       </c>
       <c r="DO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12205,7 +12205,7 @@
         <v>2</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF24" t="n">
         <v>1.5</v>
@@ -12235,7 +12235,7 @@
         <v>2.85</v>
       </c>
       <c r="DO24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12707,7 +12707,7 @@
         <v>2.63</v>
       </c>
       <c r="DO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13154,7 +13154,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE26" t="n">
         <v>1.88</v>
@@ -13187,7 +13187,7 @@
         <v>4.08</v>
       </c>
       <c r="DO26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13667,7 +13667,7 @@
         <v>2.72</v>
       </c>
       <c r="DO27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14125,7 +14125,7 @@
         <v>1</v>
       </c>
       <c r="DE28" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF28" t="n">
         <v>2</v>
@@ -14155,7 +14155,7 @@
         <v>1.98</v>
       </c>
       <c r="DO28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14594,7 +14594,7 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE29" t="n">
         <v>1</v>
@@ -14627,7 +14627,7 @@
         <v>2.35</v>
       </c>
       <c r="DO29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15074,10 +15074,10 @@
         <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE30" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -15107,7 +15107,7 @@
         <v>1.96</v>
       </c>
       <c r="DO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15595,7 +15595,7 @@
         <v>2.43</v>
       </c>
       <c r="DO31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16042,10 +16042,10 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF32" t="n">
         <v>1.5</v>
@@ -16075,7 +16075,7 @@
         <v>2.68</v>
       </c>
       <c r="DO32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16203,70 +16203,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L33" t="n">
+        <v>14</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>15</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" t="n">
         <v>10</v>
       </c>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>12</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>9</v>
-      </c>
-      <c r="T33" t="n">
-        <v>6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>21</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>11</v>
-      </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -16276,97 +16276,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB33" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -16381,287 +16381,287 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ33" t="n">
         <v>3</v>
       </c>
-      <c r="BJ33" t="n">
-        <v>2</v>
-      </c>
       <c r="BK33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY33" t="n">
         <v>5</v>
       </c>
-      <c r="BO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB33" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS33" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA33" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB33" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC33" t="n">
         <v>67</v>
       </c>
-      <c r="DC33" t="n">
-        <v>100</v>
-      </c>
       <c r="DD33" t="n">
-        <v>2.25</v>
+        <v>0.88</v>
       </c>
       <c r="DE33" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DF33" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG33" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH33" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI33" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ33" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL33" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN33" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW33" t="n">
-        <v>16.08</v>
+        <v>16.01</v>
       </c>
       <c r="DX33" t="n">
-        <v>8.460000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EG33" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EH33" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK33" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EL33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM33" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EN33" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="ED33" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EE33" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EF33" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EG33" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EH33" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EJ33" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK33" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EL33" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM33" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EN33" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EO33" t="inlineStr"/>
@@ -16683,70 +16683,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>12</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>21</v>
+      </c>
+      <c r="V34" t="n">
         <v>11</v>
       </c>
-      <c r="L34" t="n">
-        <v>14</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>15</v>
-      </c>
-      <c r="U34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>18</v>
-      </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16756,97 +16756,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO34" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB34" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16861,64 +16861,64 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK34" t="n">
         <v>3</v>
       </c>
-      <c r="BK34" t="n">
-        <v>1</v>
-      </c>
       <c r="BL34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO34" t="n">
         <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR34" t="n">
         <v>1</v>
       </c>
       <c r="BS34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW34" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX34" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY34" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -16951,7 +16951,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -16966,157 +16966,157 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS34" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CY34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB34" t="n">
         <v>67</v>
       </c>
-      <c r="DA34" t="n">
+      <c r="DC34" t="n">
         <v>100</v>
       </c>
-      <c r="DB34" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC34" t="n">
-        <v>67</v>
-      </c>
       <c r="DD34" t="n">
-        <v>0.88</v>
+        <v>2.25</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="DF34" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG34" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DJ34" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK34" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW34" t="n">
-        <v>16.01</v>
+        <v>16.08</v>
       </c>
       <c r="DX34" t="n">
-        <v>9.800000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="EM34" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EO34" t="inlineStr"/>
@@ -17482,10 +17482,10 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE35" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -17515,7 +17515,7 @@
         <v>2.46</v>
       </c>
       <c r="DO35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17965,7 +17965,7 @@
         <v>2</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF36" t="n">
         <v>0.5</v>
@@ -17995,7 +17995,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18442,7 +18442,7 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE37" t="n">
         <v>1.25</v>
@@ -18475,7 +18475,7 @@
         <v>3.08</v>
       </c>
       <c r="DO37" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18947,7 +18947,7 @@
         <v>2.88</v>
       </c>
       <c r="DO38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19435,7 +19435,7 @@
         <v>3.56</v>
       </c>
       <c r="DO39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19869,7 +19869,7 @@
         <v>2</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF40" t="n">
         <v>1.33</v>
@@ -19899,7 +19899,7 @@
         <v>3.29</v>
       </c>
       <c r="DO40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20387,7 +20387,7 @@
         <v>3.25</v>
       </c>
       <c r="DO41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20818,7 +20818,7 @@
         <v>84</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE42" t="n">
         <v>1.88</v>
@@ -20851,7 +20851,7 @@
         <v>3.26</v>
       </c>
       <c r="DO42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21309,7 +21309,7 @@
         <v>2</v>
       </c>
       <c r="DE43" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -21339,7 +21339,7 @@
         <v>2.97</v>
       </c>
       <c r="DO43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21778,7 +21778,7 @@
         <v>71</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE44" t="n">
         <v>0.88</v>
@@ -21811,7 +21811,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22283,7 +22283,7 @@
         <v>3.76</v>
       </c>
       <c r="DO45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22738,7 +22738,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE46" t="n">
         <v>2.25</v>
@@ -22771,7 +22771,7 @@
         <v>2.56</v>
       </c>
       <c r="DO46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23210,10 +23210,10 @@
         <v>34</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE47" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -23243,7 +23243,7 @@
         <v>2.95</v>
       </c>
       <c r="DO47" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23693,7 +23693,7 @@
         <v>1.25</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF48" t="n">
         <v>1</v>
@@ -23723,7 +23723,7 @@
         <v>2.69</v>
       </c>
       <c r="DO48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24145,7 +24145,7 @@
         <v>0.88</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF49" t="n">
         <v>1.5</v>
@@ -24175,7 +24175,7 @@
         <v>2.22</v>
       </c>
       <c r="DO49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24625,7 +24625,7 @@
         <v>1.38</v>
       </c>
       <c r="DE50" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF50" t="n">
         <v>1.5</v>
@@ -24655,7 +24655,7 @@
         <v>2.69</v>
       </c>
       <c r="DO50" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -25127,7 +25127,7 @@
         <v>3.7</v>
       </c>
       <c r="DO51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25591,7 +25591,7 @@
         <v>3.05</v>
       </c>
       <c r="DO52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26038,7 +26038,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE53" t="n">
         <v>1</v>
@@ -26071,7 +26071,7 @@
         <v>3.35</v>
       </c>
       <c r="DO53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26513,7 +26513,7 @@
         <v>2</v>
       </c>
       <c r="DE54" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DF54" t="n">
         <v>1.75</v>
@@ -26543,7 +26543,7 @@
         <v>3.92</v>
       </c>
       <c r="DO54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26990,7 +26990,7 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE55" t="n">
         <v>1.13</v>
@@ -27023,7 +27023,7 @@
         <v>2.73</v>
       </c>
       <c r="DO55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27462,7 +27462,7 @@
         <v>65</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE56" t="n">
         <v>1.88</v>
@@ -27495,7 +27495,7 @@
         <v>2.8</v>
       </c>
       <c r="DO56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27922,10 +27922,10 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF57" t="n">
         <v>0.75</v>
@@ -27955,7 +27955,7 @@
         <v>2.67</v>
       </c>
       <c r="DO57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28397,7 +28397,7 @@
         <v>1.25</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF58" t="n">
         <v>1.5</v>
@@ -28427,7 +28427,7 @@
         <v>2.65</v>
       </c>
       <c r="DO58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28874,7 +28874,7 @@
         <v>88</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE59" t="n">
         <v>2.25</v>
@@ -28907,7 +28907,7 @@
         <v>2.98</v>
       </c>
       <c r="DO59" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29357,7 +29357,7 @@
         <v>2</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF60" t="n">
         <v>1.8</v>
@@ -29387,7 +29387,7 @@
         <v>2.73</v>
       </c>
       <c r="DO60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29843,7 +29843,7 @@
         <v>3.65</v>
       </c>
       <c r="DO61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30303,7 +30303,7 @@
         <v>3.02</v>
       </c>
       <c r="DO62" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30775,7 +30775,7 @@
         <v>2.95</v>
       </c>
       <c r="DO63" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31222,7 +31222,7 @@
         <v>78</v>
       </c>
       <c r="DD64" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE64" t="n">
         <v>1.25</v>
@@ -31255,7 +31255,7 @@
         <v>2.43</v>
       </c>
       <c r="DO64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -32158,10 +32158,10 @@
         <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE66" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF66" t="n">
         <v>1.25</v>
@@ -32191,7 +32191,7 @@
         <v>3.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -32649,7 +32649,7 @@
         <v>0.88</v>
       </c>
       <c r="DE67" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DF67" t="n">
         <v>1.4</v>
@@ -32679,7 +32679,7 @@
         <v>3.08</v>
       </c>
       <c r="DO67" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33143,7 +33143,7 @@
         <v>3.16</v>
       </c>
       <c r="DO68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33582,7 +33582,7 @@
         <v>55</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE69" t="n">
         <v>0.88</v>
@@ -33615,7 +33615,7 @@
         <v>2.94</v>
       </c>
       <c r="DO69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34046,10 +34046,10 @@
         <v>100</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF70" t="n">
         <v>1.2</v>
@@ -34079,7 +34079,7 @@
         <v>2.44</v>
       </c>
       <c r="DO70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34543,7 +34543,7 @@
         <v>3.14</v>
       </c>
       <c r="DO71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35001,7 +35001,7 @@
         <v>2.25</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF72" t="n">
         <v>2.33</v>
@@ -35031,7 +35031,7 @@
         <v>3.26</v>
       </c>
       <c r="DO72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35462,10 +35462,10 @@
         <v>80</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF73" t="n">
         <v>1.4</v>
@@ -35495,7 +35495,7 @@
         <v>2.18</v>
       </c>
       <c r="DO73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35943,7 +35943,7 @@
         <v>3.72</v>
       </c>
       <c r="DO74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36071,146 +36071,146 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>5</v>
+      </c>
+      <c r="R75" t="n">
+        <v>12</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="n">
+        <v>9</v>
+      </c>
+      <c r="U75" t="n">
+        <v>10</v>
+      </c>
+      <c r="V75" t="n">
+        <v>21</v>
+      </c>
+      <c r="W75" t="n">
         <v>6</v>
       </c>
-      <c r="K75" t="n">
-        <v>10</v>
-      </c>
-      <c r="L75" t="n">
-        <v>16</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>4</v>
-      </c>
-      <c r="R75" t="n">
+      <c r="X75" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
         <v>7</v>
       </c>
-      <c r="S75" t="n">
-        <v>9</v>
-      </c>
-      <c r="T75" t="n">
-        <v>7</v>
-      </c>
-      <c r="U75" t="n">
-        <v>13</v>
-      </c>
-      <c r="V75" t="n">
-        <v>14</v>
-      </c>
-      <c r="W75" t="n">
-        <v>15</v>
-      </c>
-      <c r="X75" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
-      <c r="AC75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AF75" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL75" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AM75" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN75" t="n">
         <v>1.83</v>
       </c>
       <c r="AO75" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AR75" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AS75" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AU75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW75" t="n">
         <v>2</v>
@@ -36219,22 +36219,22 @@
         <v>0</v>
       </c>
       <c r="AY75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB75" t="n">
-        <v>2522</v>
+        <v>955</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -36252,19 +36252,19 @@
         <v>3</v>
       </c>
       <c r="BJ75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO75" t="n">
         <v>1</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="BQ75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR75" t="n">
         <v>0</v>
@@ -36282,31 +36282,31 @@
         <v>1</v>
       </c>
       <c r="BT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU75" t="n">
         <v>1</v>
       </c>
       <c r="BV75" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BW75" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="BX75" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="BY75" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ75" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="CA75" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="CB75" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="CC75" t="n">
         <v>0</v>
@@ -36333,16 +36333,16 @@
         <v>1</v>
       </c>
       <c r="CK75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL75" t="n">
         <v>0</v>
       </c>
       <c r="CM75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO75" t="n">
         <v>0</v>
@@ -36354,76 +36354,76 @@
         <v>1</v>
       </c>
       <c r="CR75" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS75" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CT75" t="n">
         <v>1</v>
       </c>
       <c r="CU75" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CV75" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CW75" t="n">
         <v>1</v>
       </c>
       <c r="CX75" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY75" t="n">
         <v>4</v>
       </c>
-      <c r="CY75" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ75" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="DA75" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="DB75" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="DC75" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="DD75" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE75" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DF75" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG75" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH75" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="DI75" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="DJ75" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="DK75" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="DL75" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="DO75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36435,7 +36435,7 @@
         <v>1</v>
       </c>
       <c r="DS75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT75" t="b">
         <v>0</v>
@@ -36444,88 +36444,88 @@
         <v>0</v>
       </c>
       <c r="DV75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW75" t="n">
-        <v>11.71</v>
+        <v>11.38</v>
       </c>
       <c r="DX75" t="n">
-        <v>9.65</v>
+        <v>11.66</v>
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="EE75" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF75" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EG75" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EH75" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EI75" t="inlineStr"/>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EI75" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
       <c r="EJ75" t="inlineStr"/>
       <c r="EK75" t="inlineStr"/>
-      <c r="EL75" t="inlineStr"/>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EM75" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EN75" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EO75" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EP75" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EO75" t="inlineStr"/>
+      <c r="EP75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -36543,146 +36543,146 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" t="n">
+        <v>10</v>
+      </c>
+      <c r="L76" t="n">
+        <v>16</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
         <v>4</v>
       </c>
-      <c r="I76" t="n">
-        <v>4</v>
-      </c>
-      <c r="J76" t="n">
+      <c r="R76" t="n">
         <v>7</v>
       </c>
-      <c r="K76" t="n">
+      <c r="S76" t="n">
+        <v>9</v>
+      </c>
+      <c r="T76" t="n">
+        <v>7</v>
+      </c>
+      <c r="U76" t="n">
+        <v>13</v>
+      </c>
+      <c r="V76" t="n">
+        <v>14</v>
+      </c>
+      <c r="W76" t="n">
+        <v>15</v>
+      </c>
+      <c r="X76" t="n">
         <v>5</v>
       </c>
-      <c r="L76" t="n">
-        <v>12</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>5</v>
-      </c>
-      <c r="R76" t="n">
-        <v>12</v>
-      </c>
-      <c r="S76" t="n">
-        <v>5</v>
-      </c>
-      <c r="T76" t="n">
-        <v>9</v>
-      </c>
-      <c r="U76" t="n">
-        <v>10</v>
-      </c>
-      <c r="V76" t="n">
-        <v>21</v>
-      </c>
-      <c r="W76" t="n">
-        <v>6</v>
-      </c>
-      <c r="X76" t="n">
-        <v>11</v>
-      </c>
       <c r="Y76" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z76" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AF76" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AL76" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AN76" t="n">
         <v>1.83</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AS76" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AU76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW76" t="n">
         <v>2</v>
@@ -36691,22 +36691,22 @@
         <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB76" t="n">
-        <v>955</v>
+        <v>2522</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36724,178 +36724,178 @@
         <v>3</v>
       </c>
       <c r="BJ76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK76" t="n">
         <v>3</v>
       </c>
-      <c r="BK76" t="n">
+      <c r="BL76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
         <v>4</v>
       </c>
-      <c r="BL76" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM76" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN76" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV76" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW76" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX76" t="n">
-        <v>63</v>
-      </c>
-      <c r="BY76" t="n">
-        <v>102</v>
-      </c>
-      <c r="BZ76" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CA76" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CB76" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="CC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM76" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS76" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU76" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV76" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX76" t="n">
+      <c r="CY76" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF76" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK76" t="n">
         <v>9</v>
       </c>
-      <c r="CY76" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ76" t="n">
-        <v>27</v>
-      </c>
-      <c r="DA76" t="n">
-        <v>72</v>
-      </c>
-      <c r="DB76" t="n">
-        <v>9</v>
-      </c>
-      <c r="DC76" t="n">
-        <v>45</v>
-      </c>
-      <c r="DD76" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DE76" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF76" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DG76" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DH76" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI76" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ76" t="n">
-        <v>74</v>
-      </c>
-      <c r="DK76" t="n">
-        <v>29</v>
-      </c>
       <c r="DL76" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="DO76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36907,7 +36907,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -36916,88 +36916,88 @@
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW76" t="n">
-        <v>11.38</v>
+        <v>11.71</v>
       </c>
       <c r="DX76" t="n">
-        <v>11.66</v>
+        <v>9.65</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EG76" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EH76" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EI76" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI76" t="inlineStr"/>
       <c r="EJ76" t="inlineStr"/>
       <c r="EK76" t="inlineStr"/>
-      <c r="EL76" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+      <c r="EL76" t="inlineStr"/>
       <c r="EM76" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EN76" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EO76" t="inlineStr"/>
-      <c r="EP76" t="inlineStr"/>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EO76" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EP76" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -37326,7 +37326,7 @@
         <v>74</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE77" t="n">
         <v>1.13</v>
@@ -37359,7 +37359,7 @@
         <v>2.73</v>
       </c>
       <c r="DO77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -37798,7 +37798,7 @@
         <v>92</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE78" t="n">
         <v>1.25</v>
@@ -37831,7 +37831,7 @@
         <v>3.31</v>
       </c>
       <c r="DO78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP78" t="b">
         <v>0</v>
@@ -38289,7 +38289,7 @@
         <v>1.38</v>
       </c>
       <c r="DE79" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DF79" t="n">
         <v>1.67</v>
@@ -38319,7 +38319,7 @@
         <v>3.34</v>
       </c>
       <c r="DO79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38774,10 +38774,10 @@
         <v>92</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF80" t="n">
         <v>1.17</v>
@@ -38807,7 +38807,7 @@
         <v>3.11</v>
       </c>
       <c r="DO80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39254,7 +39254,7 @@
         <v>79</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE81" t="n">
         <v>0.88</v>
@@ -39287,7 +39287,7 @@
         <v>2.66</v>
       </c>
       <c r="DO81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39734,10 +39734,10 @@
         <v>75</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF82" t="n">
         <v>1.67</v>
@@ -39767,7 +39767,7 @@
         <v>2.34</v>
       </c>
       <c r="DO82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40194,10 +40194,10 @@
         <v>84</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DF83" t="n">
         <v>1.5</v>
@@ -40227,7 +40227,7 @@
         <v>2.73</v>
       </c>
       <c r="DO83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40677,7 +40677,7 @@
         <v>1.25</v>
       </c>
       <c r="DE84" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DF84" t="n">
         <v>1.67</v>
@@ -40707,7 +40707,7 @@
         <v>3.22</v>
       </c>
       <c r="DO84" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -41187,7 +41187,7 @@
         <v>3.51</v>
       </c>
       <c r="DO85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41659,7 +41659,7 @@
         <v>2.75</v>
       </c>
       <c r="DO86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41787,143 +41787,143 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>6</v>
+      </c>
+      <c r="R87" t="n">
         <v>3</v>
       </c>
-      <c r="I87" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>8</v>
-      </c>
-      <c r="L87" t="n">
-        <v>9</v>
-      </c>
-      <c r="M87" t="n">
-        <v>2</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>2</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6</v>
-      </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T87" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U87" t="n">
         <v>11</v>
       </c>
       <c r="V87" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W87" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X87" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y87" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="Z87" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>1</v>
       </c>
       <c r="AE87" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="AF87" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG87" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL87" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AN87" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AP87" t="n">
         <v>1.82</v>
       </c>
-      <c r="AO87" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP87" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AQ87" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
         <v>0</v>
@@ -41932,25 +41932,25 @@
         <v>0</v>
       </c>
       <c r="AX87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA87" t="n">
         <v>0</v>
       </c>
       <c r="BB87" t="n">
-        <v>2526</v>
+        <v>3647</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -41968,22 +41968,22 @@
         <v>1</v>
       </c>
       <c r="BJ87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL87" t="n">
         <v>4</v>
       </c>
       <c r="BM87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN87" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP87" t="n">
         <v>1</v>
@@ -41995,7 +41995,7 @@
         <v>0</v>
       </c>
       <c r="BS87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT87" t="n">
         <v>0</v>
@@ -42004,25 +42004,25 @@
         <v>1</v>
       </c>
       <c r="BV87" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW87" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BX87" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="BY87" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="BZ87" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="CA87" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="CB87" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="CC87" t="n">
         <v>0</v>
@@ -42055,10 +42055,10 @@
         <v>0</v>
       </c>
       <c r="CM87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO87" t="n">
         <v>0</v>
@@ -42070,76 +42070,76 @@
         <v>1</v>
       </c>
       <c r="CR87" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="CS87" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
         <v>10</v>
       </c>
-      <c r="CT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU87" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV87" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX87" t="n">
+      <c r="CY87" t="n">
         <v>7</v>
       </c>
-      <c r="CY87" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ87" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="DA87" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC87" t="n">
         <v>79</v>
       </c>
-      <c r="DB87" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC87" t="n">
-        <v>64</v>
-      </c>
       <c r="DD87" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="DF87" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="DG87" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DH87" t="n">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="DI87" t="n">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="DJ87" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="DK87" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="DL87" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="DN87" t="n">
-        <v>2.68</v>
+        <v>3.26</v>
       </c>
       <c r="DO87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42148,7 +42148,7 @@
         <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS87" t="b">
         <v>0</v>
@@ -42163,83 +42163,83 @@
         <v>0</v>
       </c>
       <c r="DW87" t="n">
-        <v>8.84</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DX87" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EB87" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EH87" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="EC87" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="ED87" t="inlineStr">
-        <is>
-          <t>3.84</t>
-        </is>
-      </c>
-      <c r="EE87" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EF87" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EG87" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="EH87" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EI87" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EJ87" t="inlineStr"/>
-      <c r="EK87" t="inlineStr"/>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
       <c r="EL87" t="inlineStr">
         <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EM87" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EN87" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr"/>
+      <c r="EN87" t="inlineStr"/>
       <c r="EO87" t="inlineStr"/>
       <c r="EP87" t="inlineStr"/>
     </row>
@@ -42259,143 +42259,143 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
+        <v>8</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2</v>
+      </c>
+      <c r="R88" t="n">
         <v>6</v>
       </c>
-      <c r="L88" t="n">
-        <v>10</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>6</v>
-      </c>
-      <c r="R88" t="n">
-        <v>3</v>
-      </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T88" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U88" t="n">
         <v>11</v>
       </c>
       <c r="V88" t="n">
+        <v>21</v>
+      </c>
+      <c r="W88" t="n">
         <v>14</v>
       </c>
-      <c r="W88" t="n">
-        <v>9</v>
-      </c>
       <c r="X88" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y88" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="Z88" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Vejle Stadion</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Roms Hule 3, Vejle</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD88" t="n">
         <v>1</v>
       </c>
       <c r="AE88" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="AF88" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AO88" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AU88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV88" t="n">
         <v>0</v>
@@ -42404,25 +42404,25 @@
         <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA88" t="n">
         <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>3647</v>
+        <v>2526</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
@@ -42440,178 +42440,178 @@
         <v>1</v>
       </c>
       <c r="BJ88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL88" t="n">
         <v>4</v>
       </c>
       <c r="BM88" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS88" t="n">
         <v>3</v>
       </c>
-      <c r="BN88" t="n">
+      <c r="BT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN88" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR88" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS88" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
         <v>7</v>
       </c>
-      <c r="BO88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV88" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW88" t="n">
+      <c r="CY88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ88" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA88" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC88" t="n">
         <v>64</v>
       </c>
-      <c r="BX88" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY88" t="n">
-        <v>153</v>
-      </c>
-      <c r="BZ88" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CA88" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB88" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CC88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR88" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS88" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU88" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV88" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX88" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY88" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ88" t="n">
-        <v>79</v>
-      </c>
-      <c r="DA88" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB88" t="n">
+      <c r="DD88" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DE88" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF88" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI88" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ88" t="n">
         <v>57</v>
       </c>
-      <c r="DC88" t="n">
-        <v>79</v>
-      </c>
-      <c r="DD88" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE88" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DF88" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DG88" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DH88" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI88" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DJ88" t="n">
+      <c r="DK88" t="n">
         <v>22</v>
       </c>
-      <c r="DK88" t="n">
-        <v>0</v>
-      </c>
       <c r="DL88" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="DM88" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="DN88" t="n">
-        <v>3.26</v>
+        <v>2.68</v>
       </c>
       <c r="DO88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42620,7 +42620,7 @@
         <v>1</v>
       </c>
       <c r="DR88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS88" t="b">
         <v>0</v>
@@ -42635,83 +42635,83 @@
         <v>0</v>
       </c>
       <c r="DW88" t="n">
-        <v>9.470000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DX88" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EC88" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="ED88" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EE88" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EF88" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EG88" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EH88" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI88" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EJ88" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EK88" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr"/>
+      <c r="EK88" t="inlineStr"/>
       <c r="EL88" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EM88" t="inlineStr"/>
-      <c r="EN88" t="inlineStr"/>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EN88" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EO88" t="inlineStr"/>
       <c r="EP88" t="inlineStr"/>
     </row>
@@ -43042,10 +43042,10 @@
         <v>59</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DE89" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DF89" t="n">
         <v>1.67</v>
@@ -43075,7 +43075,7 @@
         <v>2.65</v>
       </c>
       <c r="DO89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43531,7 +43531,7 @@
         <v>3.62</v>
       </c>
       <c r="DO90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43995,7 +43995,7 @@
         <v>3.1</v>
       </c>
       <c r="DO91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44570,6 +44570,2382 @@
       <c r="EN92" t="inlineStr"/>
       <c r="EO92" t="inlineStr"/>
       <c r="EP92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>16</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Brøndby</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>45984.45833333334</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>6</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4</v>
+      </c>
+      <c r="L93" t="n">
+        <v>10</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>6</v>
+      </c>
+      <c r="R93" t="n">
+        <v>4</v>
+      </c>
+      <c r="S93" t="n">
+        <v>13</v>
+      </c>
+      <c r="T93" t="n">
+        <v>7</v>
+      </c>
+      <c r="U93" t="n">
+        <v>19</v>
+      </c>
+      <c r="V93" t="n">
+        <v>11</v>
+      </c>
+      <c r="W93" t="n">
+        <v>16</v>
+      </c>
+      <c r="X93" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Parken</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>Øster Allé 50, København</t>
+        </is>
+      </c>
+      <c r="AC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK93" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>109</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY93" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>72</v>
+      </c>
+      <c r="DK93" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL93" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DM93" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DN93" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="DO93" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP93" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV93" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW93" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="DX93" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="DY93" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="DZ93" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA93" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EB93" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EC93" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="ED93" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EE93" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EF93" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG93" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EH93" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EI93" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EJ93" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EK93" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EL93" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EM93" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EN93" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EO93" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EP93" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>16</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Viborg</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>45984.54166666666</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" t="n">
+        <v>7</v>
+      </c>
+      <c r="J94" t="n">
+        <v>5</v>
+      </c>
+      <c r="K94" t="n">
+        <v>5</v>
+      </c>
+      <c r="L94" t="n">
+        <v>10</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>6</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2</v>
+      </c>
+      <c r="S94" t="n">
+        <v>4</v>
+      </c>
+      <c r="T94" t="n">
+        <v>9</v>
+      </c>
+      <c r="U94" t="n">
+        <v>10</v>
+      </c>
+      <c r="V94" t="n">
+        <v>11</v>
+      </c>
+      <c r="W94" t="n">
+        <v>8</v>
+      </c>
+      <c r="X94" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Energi Viborg Arena</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>Stadion Allé 7, Viborg</t>
+        </is>
+      </c>
+      <c r="AC94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>2526</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS94" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV94" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW94" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX94" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY94" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ94" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA94" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB94" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CC94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP94" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR94" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS94" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU94" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV94" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW94" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX94" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY94" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ94" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA94" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB94" t="n">
+        <v>64</v>
+      </c>
+      <c r="DC94" t="n">
+        <v>93</v>
+      </c>
+      <c r="DD94" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE94" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF94" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DG94" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DH94" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DI94" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DJ94" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK94" t="n">
+        <v>14</v>
+      </c>
+      <c r="DL94" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DM94" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DN94" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DO94" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV94" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW94" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="DX94" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="DY94" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="DZ94" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA94" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EB94" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EC94" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="ED94" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="EE94" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="EF94" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EG94" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EH94" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI94" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EJ94" t="inlineStr"/>
+      <c r="EK94" t="inlineStr"/>
+      <c r="EL94" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EM94" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="EN94" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EO94" t="inlineStr"/>
+      <c r="EP94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>16</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Nordsjælland</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>45984.625</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>10</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>11</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>12</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>14</v>
+      </c>
+      <c r="T95" t="n">
+        <v>3</v>
+      </c>
+      <c r="U95" t="n">
+        <v>26</v>
+      </c>
+      <c r="V95" t="n">
+        <v>4</v>
+      </c>
+      <c r="W95" t="n">
+        <v>9</v>
+      </c>
+      <c r="X95" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Right to Dream Park</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>Idrætsvænget 2, Farum</t>
+        </is>
+      </c>
+      <c r="AC95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>986</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI95" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK95" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT95" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV95" t="n">
+        <v>109</v>
+      </c>
+      <c r="BW95" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX95" t="n">
+        <v>158</v>
+      </c>
+      <c r="BY95" t="n">
+        <v>50</v>
+      </c>
+      <c r="BZ95" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CA95" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="CB95" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CC95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR95" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS95" t="n">
+        <v>9</v>
+      </c>
+      <c r="CT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU95" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV95" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW95" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX95" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY95" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ95" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA95" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB95" t="n">
+        <v>36</v>
+      </c>
+      <c r="DC95" t="n">
+        <v>86</v>
+      </c>
+      <c r="DD95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF95" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DG95" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DH95" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DI95" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DJ95" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK95" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL95" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DM95" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DN95" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="DO95" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT95" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV95" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW95" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DX95" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="DY95" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="DZ95" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA95" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EB95" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EC95" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="ED95" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="EE95" t="inlineStr">
+        <is>
+          <t>7.83</t>
+        </is>
+      </c>
+      <c r="EF95" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EG95" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EH95" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="EI95" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ95" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EK95" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="EL95" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EM95" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EN95" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EO95" t="inlineStr"/>
+      <c r="EP95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>16</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SønderjyskE</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>45984.70833333334</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>7</v>
+      </c>
+      <c r="K96" t="n">
+        <v>7</v>
+      </c>
+      <c r="L96" t="n">
+        <v>14</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5</v>
+      </c>
+      <c r="R96" t="n">
+        <v>2</v>
+      </c>
+      <c r="S96" t="n">
+        <v>7</v>
+      </c>
+      <c r="T96" t="n">
+        <v>6</v>
+      </c>
+      <c r="U96" t="n">
+        <v>12</v>
+      </c>
+      <c r="V96" t="n">
+        <v>8</v>
+      </c>
+      <c r="W96" t="n">
+        <v>9</v>
+      </c>
+      <c r="X96" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Sydbank Park</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>Stadionvej 7, Haderslev</t>
+        </is>
+      </c>
+      <c r="AC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>2519</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG96" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ96" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR96" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT96" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV96" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW96" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX96" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY96" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ96" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CA96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB96" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CC96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR96" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS96" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU96" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV96" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW96" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX96" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY96" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ96" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA96" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB96" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC96" t="n">
+        <v>57</v>
+      </c>
+      <c r="DD96" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE96" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DF96" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG96" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH96" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DI96" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DJ96" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK96" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL96" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DM96" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DN96" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DO96" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU96" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV96" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW96" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DX96" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="DY96" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="DZ96" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA96" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EB96" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EG96" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EH96" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI96" t="inlineStr"/>
+      <c r="EJ96" t="inlineStr"/>
+      <c r="EK96" t="inlineStr"/>
+      <c r="EL96" t="inlineStr"/>
+      <c r="EM96" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EO96" t="inlineStr"/>
+      <c r="EP96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>16</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>45985.75</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>11</v>
+      </c>
+      <c r="K97" t="n">
+        <v>6</v>
+      </c>
+      <c r="L97" t="n">
+        <v>17</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>4</v>
+      </c>
+      <c r="R97" t="n">
+        <v>3</v>
+      </c>
+      <c r="S97" t="n">
+        <v>12</v>
+      </c>
+      <c r="T97" t="n">
+        <v>11</v>
+      </c>
+      <c r="U97" t="n">
+        <v>16</v>
+      </c>
+      <c r="V97" t="n">
+        <v>14</v>
+      </c>
+      <c r="W97" t="n">
+        <v>7</v>
+      </c>
+      <c r="X97" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI97" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK97" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT97" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV97" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW97" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX97" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY97" t="n">
+        <v>110</v>
+      </c>
+      <c r="BZ97" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA97" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CB97" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR97" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS97" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU97" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV97" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW97" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX97" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY97" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ97" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA97" t="n">
+        <v>86</v>
+      </c>
+      <c r="DB97" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC97" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD97" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE97" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DF97" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DG97" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH97" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI97" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DJ97" t="n">
+        <v>36</v>
+      </c>
+      <c r="DK97" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL97" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM97" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DN97" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO97" t="n">
+        <v>16</v>
+      </c>
+      <c r="DP97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV97" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW97" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DX97" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="DY97" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="DZ97" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EA97" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EB97" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EE97" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EF97" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EG97" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EK97" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EL97" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EM97" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EN97" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EO97" t="inlineStr"/>
+      <c r="EP97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -45117,7 +45117,7 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R94" t="n">
         <v>2</v>
@@ -45129,7 +45129,7 @@
         <v>9</v>
       </c>
       <c r="U94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V94" t="n">
         <v>11</v>
@@ -45304,13 +45304,13 @@
         <v>90</v>
       </c>
       <c r="BZ94" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="CA94" t="n">
         <v>1.2</v>
       </c>
       <c r="CB94" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="CC94" t="n">
         <v>1</v>
@@ -46769,7 +46769,7 @@
         <v>16</v>
       </c>
       <c r="CS97" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CT97" t="n">
         <v>1</v>
@@ -46787,7 +46787,7 @@
         <v>8</v>
       </c>
       <c r="CY97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ97" t="n">
         <v>65</v>
@@ -46914,26 +46914,10 @@
           <t>1.22</t>
         </is>
       </c>
-      <c r="EI97" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EJ97" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EK97" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="EL97" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+      <c r="EI97" t="inlineStr"/>
+      <c r="EJ97" t="inlineStr"/>
+      <c r="EK97" t="inlineStr"/>
+      <c r="EL97" t="inlineStr"/>
       <c r="EM97" t="inlineStr">
         <is>
           <t>2.53</t>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP97" headerRowCount="1">
-  <autoFilter ref="A1:EP97"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP98" headerRowCount="1">
+  <autoFilter ref="A1:EP98"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP97"/>
+  <dimension ref="A1:EP98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE5" t="n">
         <v>2.25</v>
@@ -5589,7 +5589,7 @@
         <v>1.38</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -8898,7 +8898,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE17" t="n">
         <v>1.13</v>
@@ -9853,7 +9853,7 @@
         <v>2</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -10819,7 +10819,7 @@
         <v>3.19</v>
       </c>
       <c r="DO21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -17482,7 +17482,7 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE35" t="n">
         <v>1.88</v>
@@ -18445,7 +18445,7 @@
         <v>1.5</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -18917,7 +18917,7 @@
         <v>1</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF38" t="n">
         <v>1.33</v>
@@ -19083,170 +19083,162 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45900.5</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>10</v>
+      </c>
+      <c r="R39" t="n">
+        <v>5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>30</v>
+      </c>
+      <c r="V39" t="n">
         <v>9</v>
       </c>
-      <c r="K39" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="W39" t="n">
+        <v>12</v>
+      </c>
+      <c r="X39" t="n">
         <v>11</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7</v>
-      </c>
-      <c r="S39" t="n">
-        <v>9</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>13</v>
-      </c>
-      <c r="V39" t="n">
-        <v>10</v>
-      </c>
-      <c r="W39" t="n">
-        <v>8</v>
-      </c>
-      <c r="X39" t="n">
-        <v>7</v>
-      </c>
       <c r="Y39" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z39" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>JYSK park</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>Ansvej 104, Silkeborg</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
         <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AJ39" t="n">
         <v>2.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AO39" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW39" t="n">
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB39" t="n">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -19264,19 +19256,19 @@
         <v>4</v>
       </c>
       <c r="BJ39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL39" t="n">
         <v>1</v>
       </c>
       <c r="BM39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO39" t="n">
         <v>0</v>
@@ -19288,151 +19280,151 @@
         <v>0</v>
       </c>
       <c r="BR39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS39" t="n">
         <v>1</v>
       </c>
       <c r="BT39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
+        <v>69</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CB39" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="CC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR39" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS39" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU39" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX39" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY39" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ39" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA39" t="n">
         <v>67</v>
       </c>
-      <c r="BW39" t="n">
-        <v>28</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>141</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CA39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CB39" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM39" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS39" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU39" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV39" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX39" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY39" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ39" t="n">
-        <v>59</v>
-      </c>
-      <c r="DA39" t="n">
-        <v>84</v>
-      </c>
       <c r="DB39" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DC39" t="n">
         <v>84</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="DF39" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DG39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DH39" t="n">
-        <v>1</v>
+        <v>1.83</v>
       </c>
       <c r="DI39" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="DJ39" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="DK39" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL39" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DM39" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="DN39" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="DO39" t="n">
         <v>16</v>
@@ -19444,29 +19436,29 @@
         <v>1</v>
       </c>
       <c r="DR39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU39" t="b">
         <v>0</v>
       </c>
       <c r="DV39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>18.38</v>
+        <v>18.03</v>
       </c>
       <c r="DX39" t="n">
-        <v>6.62</v>
+        <v>5.37</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
@@ -19476,37 +19468,37 @@
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="EF39" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EH39" t="inlineStr">
@@ -19516,28 +19508,44 @@
       </c>
       <c r="EI39" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EM39" t="inlineStr"/>
-      <c r="EN39" t="inlineStr"/>
-      <c r="EO39" t="inlineStr"/>
-      <c r="EP39" t="inlineStr"/>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM39" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EN39" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EO39" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EP39" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -19555,162 +19563,170 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45900.5</v>
       </c>
       <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>9</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" t="n">
+      <c r="R40" t="n">
         <v>7</v>
       </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
+      <c r="S40" t="n">
+        <v>9</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>13</v>
+      </c>
+      <c r="V40" t="n">
+        <v>10</v>
+      </c>
+      <c r="W40" t="n">
         <v>8</v>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>10</v>
-      </c>
-      <c r="R40" t="n">
-        <v>5</v>
-      </c>
-      <c r="S40" t="n">
-        <v>20</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>30</v>
-      </c>
-      <c r="V40" t="n">
-        <v>9</v>
-      </c>
-      <c r="W40" t="n">
-        <v>12</v>
-      </c>
       <c r="X40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y40" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z40" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AF40" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AJ40" t="n">
         <v>2.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AO40" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AP40" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AU40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19728,95 +19744,95 @@
         <v>4</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>67</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>141</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CB40" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM40" t="n">
         <v>3</v>
       </c>
-      <c r="BL40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM40" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN40" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV40" t="n">
-        <v>69</v>
-      </c>
-      <c r="BW40" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX40" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>72</v>
-      </c>
-      <c r="BZ40" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CA40" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CB40" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="CC40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM40" t="n">
-        <v>0</v>
-      </c>
       <c r="CN40" t="n">
         <v>0</v>
       </c>
@@ -19830,73 +19846,73 @@
         <v>1</v>
       </c>
       <c r="CR40" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="CS40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CV40" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW40" t="n">
         <v>1</v>
       </c>
       <c r="CX40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="CY40" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CZ40" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="DA40" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB40" t="n">
         <v>67</v>
-      </c>
-      <c r="DB40" t="n">
-        <v>50</v>
       </c>
       <c r="DC40" t="n">
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="DF40" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DG40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DH40" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ40" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK40" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL40" t="n">
         <v>1.83</v>
       </c>
-      <c r="DI40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DJ40" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK40" t="n">
-        <v>34</v>
-      </c>
-      <c r="DL40" t="n">
-        <v>1.86</v>
-      </c>
       <c r="DM40" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="DN40" t="n">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="DO40" t="n">
         <v>16</v>
@@ -19908,29 +19924,29 @@
         <v>1</v>
       </c>
       <c r="DR40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU40" t="b">
         <v>0</v>
       </c>
       <c r="DV40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW40" t="n">
-        <v>18.03</v>
+        <v>18.38</v>
       </c>
       <c r="DX40" t="n">
-        <v>5.37</v>
+        <v>6.62</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -19940,37 +19956,37 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EB40" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EC40" t="inlineStr">
+        <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="EB40" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EC40" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="ED40" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
@@ -19980,44 +19996,28 @@
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EM40" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EN40" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EO40" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EP40" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EM40" t="inlineStr"/>
+      <c r="EN40" t="inlineStr"/>
+      <c r="EO40" t="inlineStr"/>
+      <c r="EP40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21778,7 +21778,7 @@
         <v>71</v>
       </c>
       <c r="DD44" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE44" t="n">
         <v>0.88</v>
@@ -25097,7 +25097,7 @@
         <v>2.25</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF51" t="n">
         <v>2</v>
@@ -27462,7 +27462,7 @@
         <v>65</v>
       </c>
       <c r="DD56" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE56" t="n">
         <v>1.88</v>
@@ -31225,7 +31225,7 @@
         <v>1.38</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF64" t="n">
         <v>1.5</v>
@@ -35462,7 +35462,7 @@
         <v>80</v>
       </c>
       <c r="DD73" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE73" t="n">
         <v>0.5</v>
@@ -36071,146 +36071,146 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
         <v>4</v>
       </c>
-      <c r="I75" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="R75" t="n">
         <v>7</v>
       </c>
-      <c r="K75" t="n">
+      <c r="S75" t="n">
+        <v>9</v>
+      </c>
+      <c r="T75" t="n">
+        <v>7</v>
+      </c>
+      <c r="U75" t="n">
+        <v>13</v>
+      </c>
+      <c r="V75" t="n">
+        <v>14</v>
+      </c>
+      <c r="W75" t="n">
+        <v>15</v>
+      </c>
+      <c r="X75" t="n">
         <v>5</v>
       </c>
-      <c r="L75" t="n">
-        <v>12</v>
-      </c>
-      <c r="M75" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>5</v>
-      </c>
-      <c r="R75" t="n">
-        <v>12</v>
-      </c>
-      <c r="S75" t="n">
-        <v>5</v>
-      </c>
-      <c r="T75" t="n">
-        <v>9</v>
-      </c>
-      <c r="U75" t="n">
-        <v>10</v>
-      </c>
-      <c r="V75" t="n">
-        <v>21</v>
-      </c>
-      <c r="W75" t="n">
-        <v>6</v>
-      </c>
-      <c r="X75" t="n">
-        <v>11</v>
-      </c>
       <c r="Y75" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z75" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AF75" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AL75" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AM75" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AN75" t="n">
         <v>1.83</v>
       </c>
       <c r="AO75" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AR75" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AS75" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AU75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW75" t="n">
         <v>2</v>
@@ -36219,22 +36219,22 @@
         <v>0</v>
       </c>
       <c r="AY75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB75" t="n">
-        <v>955</v>
+        <v>2522</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -36252,175 +36252,175 @@
         <v>3</v>
       </c>
       <c r="BJ75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK75" t="n">
         <v>3</v>
       </c>
-      <c r="BK75" t="n">
+      <c r="BL75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX75" t="n">
         <v>4</v>
       </c>
-      <c r="BL75" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV75" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW75" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX75" t="n">
-        <v>63</v>
-      </c>
-      <c r="BY75" t="n">
-        <v>102</v>
-      </c>
-      <c r="BZ75" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CA75" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CB75" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="CC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM75" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU75" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV75" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX75" t="n">
+      <c r="CY75" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK75" t="n">
         <v>9</v>
       </c>
-      <c r="CY75" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ75" t="n">
-        <v>27</v>
-      </c>
-      <c r="DA75" t="n">
-        <v>72</v>
-      </c>
-      <c r="DB75" t="n">
-        <v>9</v>
-      </c>
-      <c r="DC75" t="n">
-        <v>45</v>
-      </c>
-      <c r="DD75" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DE75" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DF75" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DG75" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DH75" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI75" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ75" t="n">
-        <v>74</v>
-      </c>
-      <c r="DK75" t="n">
-        <v>29</v>
-      </c>
       <c r="DL75" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="DO75" t="n">
         <v>16</v>
@@ -36435,7 +36435,7 @@
         <v>1</v>
       </c>
       <c r="DS75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT75" t="b">
         <v>0</v>
@@ -36444,88 +36444,88 @@
         <v>0</v>
       </c>
       <c r="DV75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW75" t="n">
-        <v>11.38</v>
+        <v>11.71</v>
       </c>
       <c r="DX75" t="n">
-        <v>11.66</v>
+        <v>9.65</v>
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EE75" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EF75" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EG75" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EH75" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EI75" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI75" t="inlineStr"/>
       <c r="EJ75" t="inlineStr"/>
       <c r="EK75" t="inlineStr"/>
-      <c r="EL75" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+      <c r="EL75" t="inlineStr"/>
       <c r="EM75" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EN75" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EO75" t="inlineStr"/>
-      <c r="EP75" t="inlineStr"/>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EO75" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EP75" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -36543,146 +36543,146 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
+        <v>7</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5</v>
+      </c>
+      <c r="L76" t="n">
+        <v>12</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>12</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="n">
+        <v>9</v>
+      </c>
+      <c r="U76" t="n">
+        <v>10</v>
+      </c>
+      <c r="V76" t="n">
+        <v>21</v>
+      </c>
+      <c r="W76" t="n">
         <v>6</v>
       </c>
-      <c r="K76" t="n">
-        <v>10</v>
-      </c>
-      <c r="L76" t="n">
-        <v>16</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>4</v>
-      </c>
-      <c r="R76" t="n">
+      <c r="X76" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
         <v>7</v>
       </c>
-      <c r="S76" t="n">
-        <v>9</v>
-      </c>
-      <c r="T76" t="n">
-        <v>7</v>
-      </c>
-      <c r="U76" t="n">
-        <v>13</v>
-      </c>
-      <c r="V76" t="n">
-        <v>14</v>
-      </c>
-      <c r="W76" t="n">
-        <v>15</v>
-      </c>
-      <c r="X76" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AF76" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL76" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN76" t="n">
         <v>1.83</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AS76" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AU76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW76" t="n">
         <v>2</v>
@@ -36691,22 +36691,22 @@
         <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB76" t="n">
-        <v>2522</v>
+        <v>955</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36724,19 +36724,19 @@
         <v>3</v>
       </c>
       <c r="BJ76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO76" t="n">
         <v>1</v>
@@ -36745,7 +36745,7 @@
         <v>0</v>
       </c>
       <c r="BQ76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR76" t="n">
         <v>0</v>
@@ -36754,31 +36754,31 @@
         <v>1</v>
       </c>
       <c r="BT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU76" t="n">
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BW76" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="BX76" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="BY76" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ76" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="CA76" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="CB76" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
@@ -36805,16 +36805,16 @@
         <v>1</v>
       </c>
       <c r="CK76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL76" t="n">
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO76" t="n">
         <v>0</v>
@@ -36826,73 +36826,73 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS76" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CV76" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY76" t="n">
         <v>4</v>
       </c>
-      <c r="CY76" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ76" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="DA76" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="DB76" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="DC76" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="DD76" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE76" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DF76" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG76" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH76" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="DI76" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="DJ76" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="DK76" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="DL76" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="DO76" t="n">
         <v>16</v>
@@ -36907,7 +36907,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -36916,88 +36916,88 @@
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW76" t="n">
-        <v>11.71</v>
+        <v>11.38</v>
       </c>
       <c r="DX76" t="n">
-        <v>9.65</v>
+        <v>11.66</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EG76" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EH76" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EI76" t="inlineStr"/>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EI76" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
       <c r="EJ76" t="inlineStr"/>
       <c r="EK76" t="inlineStr"/>
-      <c r="EL76" t="inlineStr"/>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EM76" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EN76" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EO76" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EP76" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EO76" t="inlineStr"/>
+      <c r="EP76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -37801,7 +37801,7 @@
         <v>1.63</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF78" t="n">
         <v>1.2</v>
@@ -39734,7 +39734,7 @@
         <v>75</v>
       </c>
       <c r="DD82" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE82" t="n">
         <v>0.25</v>
@@ -42581,7 +42581,7 @@
         <v>0.88</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DF88" t="n">
         <v>1</v>
@@ -46346,7 +46346,7 @@
         <v>57</v>
       </c>
       <c r="DD96" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DE96" t="n">
         <v>1.75</v>
@@ -46930,6 +46930,486 @@
       </c>
       <c r="EO97" t="inlineStr"/>
       <c r="EP97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>17</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SønderjyskE</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Viborg</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>45989.75</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" t="n">
+        <v>4</v>
+      </c>
+      <c r="J98" t="n">
+        <v>2</v>
+      </c>
+      <c r="K98" t="n">
+        <v>8</v>
+      </c>
+      <c r="L98" t="n">
+        <v>10</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>4</v>
+      </c>
+      <c r="R98" t="n">
+        <v>4</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="n">
+        <v>11</v>
+      </c>
+      <c r="U98" t="n">
+        <v>9</v>
+      </c>
+      <c r="V98" t="n">
+        <v>15</v>
+      </c>
+      <c r="W98" t="n">
+        <v>11</v>
+      </c>
+      <c r="X98" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>Sydbank Park</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>Stadionvej 7, Haderslev</t>
+        </is>
+      </c>
+      <c r="AC98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ98" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT98" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV98" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW98" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX98" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY98" t="n">
+        <v>135</v>
+      </c>
+      <c r="BZ98" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CA98" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CB98" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR98" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS98" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU98" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV98" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW98" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX98" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY98" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ98" t="n">
+        <v>57</v>
+      </c>
+      <c r="DA98" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB98" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC98" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD98" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE98" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF98" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG98" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH98" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DI98" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DJ98" t="n">
+        <v>44</v>
+      </c>
+      <c r="DK98" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL98" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DM98" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DN98" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DO98" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU98" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV98" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW98" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="DX98" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="DY98" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="DZ98" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA98" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EB98" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="EC98" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="ED98" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="EE98" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EF98" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG98" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EH98" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI98" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EJ98" t="inlineStr"/>
+      <c r="EK98" t="inlineStr"/>
+      <c r="EL98" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EM98" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EN98" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EO98" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP98" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP98" headerRowCount="1">
-  <autoFilter ref="A1:EP98"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP102" headerRowCount="1">
+  <autoFilter ref="A1:EP102"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP98"/>
+  <dimension ref="A1:EP102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1805,7 +1805,7 @@
         <v>1.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         <v>0.88</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE6" t="n">
         <v>1.13</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4626,10 +4626,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4659,7 +4659,7 @@
         <v>0.76</v>
       </c>
       <c r="DO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5117,7 +5117,7 @@
         <v>1.63</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5586,7 +5586,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE10" t="n">
         <v>1.22</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE11" t="n">
         <v>0.5</v>
@@ -7002,7 +7002,7 @@
         <v>50</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE13" t="n">
         <v>1.13</v>
@@ -7035,7 +7035,7 @@
         <v>2.01</v>
       </c>
       <c r="DO13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7477,7 +7477,7 @@
         <v>0.88</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
         <v>2.69</v>
       </c>
       <c r="DO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8107,162 +8107,170 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>45872.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
+      <c r="R16" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="n">
         <v>5</v>
       </c>
-      <c r="L16" t="n">
-        <v>9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
+        <v>17</v>
+      </c>
+      <c r="W16" t="n">
+        <v>11</v>
+      </c>
+      <c r="X16" t="n">
         <v>14</v>
       </c>
-      <c r="U16" t="n">
-        <v>10</v>
-      </c>
-      <c r="V16" t="n">
-        <v>18</v>
-      </c>
-      <c r="W16" t="n">
-        <v>5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>6</v>
-      </c>
       <c r="Y16" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Z16" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Sydbank Park</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Stadionvej 7, Haderslev</t>
+        </is>
+      </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.94</v>
+        <v>3.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.68</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AO16" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AP16" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB16" t="n">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -8277,73 +8285,73 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ16" t="n">
         <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS16" t="n">
         <v>2</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW16" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="BX16" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="BY16" t="n">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.23</v>
+        <v>0.8</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="CB16" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="CC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF16" t="n">
         <v>0</v>
@@ -8361,7 +8369,7 @@
         <v>1</v>
       </c>
       <c r="CK16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
@@ -8373,7 +8381,7 @@
         <v>1</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP16" t="n">
         <v>0</v>
@@ -8382,182 +8390,182 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CS16" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="CT16" t="n">
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CV16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CY16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="CZ16" t="n">
         <v>50</v>
       </c>
       <c r="DA16" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB16" t="n">
         <v>50</v>
       </c>
-      <c r="DB16" t="n">
-        <v>0</v>
-      </c>
       <c r="DC16" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ16" t="n">
         <v>50</v>
       </c>
-      <c r="DD16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>0</v>
-      </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.91</v>
+        <v>1.69</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.91</v>
+        <v>2.96</v>
       </c>
       <c r="DO16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
       </c>
       <c r="DQ16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU16" t="b">
         <v>0</v>
       </c>
       <c r="DV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW16" t="inlineStr"/>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EG16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EH16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr"/>
@@ -8579,170 +8587,162 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45872.5</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
         <v>5</v>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>14</v>
+      </c>
+      <c r="U17" t="n">
+        <v>10</v>
+      </c>
+      <c r="V17" t="n">
+        <v>18</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X17" t="n">
         <v>6</v>
       </c>
-      <c r="L17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>10</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" t="n">
-        <v>17</v>
-      </c>
-      <c r="W17" t="n">
-        <v>11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>14</v>
-      </c>
       <c r="Y17" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="Z17" t="n">
-        <v>68</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Sydbank Park</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Stadionvej 7, Haderslev</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.31</v>
+        <v>1.94</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>3.68</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AP17" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AU17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB17" t="n">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -8757,287 +8757,287 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL17" t="n">
         <v>4</v>
       </c>
-      <c r="BK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>2</v>
-      </c>
       <c r="BM17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU17" t="n">
         <v>5</v>
       </c>
-      <c r="BN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>65</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>136</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR17" t="n">
+      <c r="CV17" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX17" t="n">
         <v>11</v>
       </c>
-      <c r="CS17" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU17" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV17" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW17" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX17" t="n">
-        <v>8</v>
-      </c>
       <c r="CY17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CZ17" t="n">
         <v>50</v>
       </c>
       <c r="DA17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
         <v>50</v>
       </c>
-      <c r="DC17" t="n">
-        <v>100</v>
-      </c>
       <c r="DD17" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DI17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>1.69</v>
+        <v>0.91</v>
       </c>
       <c r="DN17" t="n">
-        <v>2.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
       </c>
       <c r="DQ17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU17" t="b">
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW17" t="inlineStr"/>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EG17" t="inlineStr">
         <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM17" t="inlineStr">
+        <is>
           <t>2.58</t>
         </is>
       </c>
-      <c r="EH17" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="EI17" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EJ17" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EK17" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EL17" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EM17" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr"/>
@@ -9370,7 +9370,7 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE18" t="n">
         <v>1.75</v>
@@ -9403,7 +9403,7 @@
         <v>1.58</v>
       </c>
       <c r="DO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP18" t="b">
         <v>0</v>
@@ -10347,7 +10347,7 @@
         <v>2.67</v>
       </c>
       <c r="DO20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -11266,7 +11266,7 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE22" t="n">
         <v>0.5</v>
@@ -11738,10 +11738,10 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>3.75</v>
       </c>
       <c r="DO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12205,7 +12205,7 @@
         <v>2</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF24" t="n">
         <v>1.5</v>
@@ -12674,10 +12674,10 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12707,7 +12707,7 @@
         <v>2.63</v>
       </c>
       <c r="DO25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13157,7 +13157,7 @@
         <v>1.5</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>4.08</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14155,7 +14155,7 @@
         <v>1.98</v>
       </c>
       <c r="DO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14627,7 +14627,7 @@
         <v>2.35</v>
       </c>
       <c r="DO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15562,7 +15562,7 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE31" t="n">
         <v>2.25</v>
@@ -15595,7 +15595,7 @@
         <v>2.43</v>
       </c>
       <c r="DO31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16075,7 +16075,7 @@
         <v>2.68</v>
       </c>
       <c r="DO32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16525,7 +16525,7 @@
         <v>0.88</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF33" t="n">
         <v>1</v>
@@ -17002,7 +17002,7 @@
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE34" t="n">
         <v>1</v>
@@ -17035,7 +17035,7 @@
         <v>3.63</v>
       </c>
       <c r="DO34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -17962,10 +17962,10 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF36" t="n">
         <v>0.5</v>
@@ -17995,7 +17995,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18475,7 +18475,7 @@
         <v>3.08</v>
       </c>
       <c r="DO37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18947,7 +18947,7 @@
         <v>2.88</v>
       </c>
       <c r="DO38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19394,7 +19394,7 @@
         <v>84</v>
       </c>
       <c r="DD39" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE39" t="n">
         <v>0.5</v>
@@ -19882,7 +19882,7 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE40" t="n">
         <v>1.13</v>
@@ -19915,7 +19915,7 @@
         <v>3.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20354,10 +20354,10 @@
         <v>100</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE41" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -20387,7 +20387,7 @@
         <v>3.25</v>
       </c>
       <c r="DO41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20821,7 +20821,7 @@
         <v>1.38</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF42" t="n">
         <v>1.5</v>
@@ -20851,7 +20851,7 @@
         <v>3.26</v>
       </c>
       <c r="DO42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21781,7 +21781,7 @@
         <v>1.89</v>
       </c>
       <c r="DE44" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF44" t="n">
         <v>2.33</v>
@@ -21811,7 +21811,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22253,7 +22253,7 @@
         <v>2</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -22771,7 +22771,7 @@
         <v>2.56</v>
       </c>
       <c r="DO46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23243,7 +23243,7 @@
         <v>2.95</v>
       </c>
       <c r="DO47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>84</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE48" t="n">
         <v>1.13</v>
@@ -23723,7 +23723,7 @@
         <v>2.69</v>
       </c>
       <c r="DO48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -24145,7 +24145,7 @@
         <v>0.88</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF49" t="n">
         <v>1.5</v>
@@ -24622,7 +24622,7 @@
         <v>100</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE50" t="n">
         <v>0.5</v>
@@ -25094,7 +25094,7 @@
         <v>100</v>
       </c>
       <c r="DD51" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE51" t="n">
         <v>1.22</v>
@@ -25127,7 +25127,7 @@
         <v>3.7</v>
       </c>
       <c r="DO51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25591,7 +25591,7 @@
         <v>3.05</v>
       </c>
       <c r="DO52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26071,7 +26071,7 @@
         <v>3.35</v>
       </c>
       <c r="DO53" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26510,7 +26510,7 @@
         <v>71</v>
       </c>
       <c r="DD54" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE54" t="n">
         <v>1.88</v>
@@ -26993,7 +26993,7 @@
         <v>1.38</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF55" t="n">
         <v>1</v>
@@ -27023,7 +27023,7 @@
         <v>2.73</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27465,7 +27465,7 @@
         <v>1.89</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF56" t="n">
         <v>1.75</v>
@@ -27495,7 +27495,7 @@
         <v>2.8</v>
       </c>
       <c r="DO56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -28394,10 +28394,10 @@
         <v>75</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF58" t="n">
         <v>1.5</v>
@@ -28427,7 +28427,7 @@
         <v>2.65</v>
       </c>
       <c r="DO58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -28907,7 +28907,7 @@
         <v>2.98</v>
       </c>
       <c r="DO59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29810,10 +29810,10 @@
         <v>70</v>
       </c>
       <c r="DD61" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF61" t="n">
         <v>2.2</v>
@@ -29843,7 +29843,7 @@
         <v>3.65</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30270,7 +30270,7 @@
         <v>80</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE62" t="n">
         <v>1.13</v>
@@ -30303,7 +30303,7 @@
         <v>3.02</v>
       </c>
       <c r="DO62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30745,7 +30745,7 @@
         <v>1</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF63" t="n">
         <v>1</v>
@@ -30775,7 +30775,7 @@
         <v>2.95</v>
       </c>
       <c r="DO63" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31255,7 +31255,7 @@
         <v>2.43</v>
       </c>
       <c r="DO64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31686,7 +31686,7 @@
         <v>90</v>
       </c>
       <c r="DD65" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE65" t="n">
         <v>1</v>
@@ -31719,7 +31719,7 @@
         <v>3.44</v>
       </c>
       <c r="DO65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32191,7 +32191,7 @@
         <v>3.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33110,10 +33110,10 @@
         <v>82</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF68" t="n">
         <v>1.4</v>
@@ -33143,7 +33143,7 @@
         <v>3.16</v>
       </c>
       <c r="DO68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33585,7 +33585,7 @@
         <v>1.5</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF69" t="n">
         <v>1.2</v>
@@ -33615,7 +33615,7 @@
         <v>2.94</v>
       </c>
       <c r="DO69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -34079,7 +34079,7 @@
         <v>2.44</v>
       </c>
       <c r="DO70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -34998,10 +34998,10 @@
         <v>74</v>
       </c>
       <c r="DD72" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF72" t="n">
         <v>2.33</v>
@@ -35031,7 +35031,7 @@
         <v>3.26</v>
       </c>
       <c r="DO72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35910,10 +35910,10 @@
         <v>83</v>
       </c>
       <c r="DD74" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF74" t="n">
         <v>2.17</v>
@@ -35943,7 +35943,7 @@
         <v>3.72</v>
       </c>
       <c r="DO74" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36071,146 +36071,146 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>5</v>
+      </c>
+      <c r="R75" t="n">
+        <v>12</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="n">
+        <v>9</v>
+      </c>
+      <c r="U75" t="n">
+        <v>10</v>
+      </c>
+      <c r="V75" t="n">
+        <v>21</v>
+      </c>
+      <c r="W75" t="n">
         <v>6</v>
       </c>
-      <c r="K75" t="n">
-        <v>10</v>
-      </c>
-      <c r="L75" t="n">
-        <v>16</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>4</v>
-      </c>
-      <c r="R75" t="n">
+      <c r="X75" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
         <v>7</v>
       </c>
-      <c r="S75" t="n">
-        <v>9</v>
-      </c>
-      <c r="T75" t="n">
-        <v>7</v>
-      </c>
-      <c r="U75" t="n">
-        <v>13</v>
-      </c>
-      <c r="V75" t="n">
-        <v>14</v>
-      </c>
-      <c r="W75" t="n">
-        <v>15</v>
-      </c>
-      <c r="X75" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
-      <c r="AC75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AF75" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL75" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AM75" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN75" t="n">
         <v>1.83</v>
       </c>
       <c r="AO75" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AR75" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AS75" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AU75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW75" t="n">
         <v>2</v>
@@ -36219,22 +36219,22 @@
         <v>0</v>
       </c>
       <c r="AY75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB75" t="n">
-        <v>2522</v>
+        <v>955</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -36252,19 +36252,19 @@
         <v>3</v>
       </c>
       <c r="BJ75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO75" t="n">
         <v>1</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="BQ75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR75" t="n">
         <v>0</v>
@@ -36282,31 +36282,31 @@
         <v>1</v>
       </c>
       <c r="BT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU75" t="n">
         <v>1</v>
       </c>
       <c r="BV75" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BW75" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="BX75" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="BY75" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ75" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="CA75" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="CB75" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="CC75" t="n">
         <v>0</v>
@@ -36333,16 +36333,16 @@
         <v>1</v>
       </c>
       <c r="CK75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL75" t="n">
         <v>0</v>
       </c>
       <c r="CM75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO75" t="n">
         <v>0</v>
@@ -36354,73 +36354,73 @@
         <v>1</v>
       </c>
       <c r="CR75" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS75" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CT75" t="n">
         <v>1</v>
       </c>
       <c r="CU75" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CV75" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CW75" t="n">
         <v>1</v>
       </c>
       <c r="CX75" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY75" t="n">
         <v>4</v>
       </c>
-      <c r="CY75" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ75" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="DA75" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="DB75" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="DC75" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="DD75" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DE75" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DF75" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG75" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH75" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="DI75" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="DJ75" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="DK75" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="DL75" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="DO75" t="n">
         <v>16</v>
@@ -36435,7 +36435,7 @@
         <v>1</v>
       </c>
       <c r="DS75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT75" t="b">
         <v>0</v>
@@ -36444,88 +36444,88 @@
         <v>0</v>
       </c>
       <c r="DV75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW75" t="n">
-        <v>11.71</v>
+        <v>11.38</v>
       </c>
       <c r="DX75" t="n">
-        <v>9.65</v>
+        <v>11.66</v>
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="EE75" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EF75" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EG75" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EH75" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EI75" t="inlineStr"/>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EI75" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
       <c r="EJ75" t="inlineStr"/>
       <c r="EK75" t="inlineStr"/>
-      <c r="EL75" t="inlineStr"/>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EM75" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EN75" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EO75" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EP75" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EO75" t="inlineStr"/>
+      <c r="EP75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -36543,146 +36543,146 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" t="n">
+        <v>10</v>
+      </c>
+      <c r="L76" t="n">
+        <v>16</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
         <v>4</v>
       </c>
-      <c r="I76" t="n">
-        <v>4</v>
-      </c>
-      <c r="J76" t="n">
+      <c r="R76" t="n">
         <v>7</v>
       </c>
-      <c r="K76" t="n">
+      <c r="S76" t="n">
+        <v>9</v>
+      </c>
+      <c r="T76" t="n">
+        <v>7</v>
+      </c>
+      <c r="U76" t="n">
+        <v>13</v>
+      </c>
+      <c r="V76" t="n">
+        <v>14</v>
+      </c>
+      <c r="W76" t="n">
+        <v>15</v>
+      </c>
+      <c r="X76" t="n">
         <v>5</v>
       </c>
-      <c r="L76" t="n">
-        <v>12</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>5</v>
-      </c>
-      <c r="R76" t="n">
-        <v>12</v>
-      </c>
-      <c r="S76" t="n">
-        <v>5</v>
-      </c>
-      <c r="T76" t="n">
-        <v>9</v>
-      </c>
-      <c r="U76" t="n">
-        <v>10</v>
-      </c>
-      <c r="V76" t="n">
-        <v>21</v>
-      </c>
-      <c r="W76" t="n">
-        <v>6</v>
-      </c>
-      <c r="X76" t="n">
-        <v>11</v>
-      </c>
       <c r="Y76" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z76" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AF76" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AL76" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AN76" t="n">
         <v>1.83</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AS76" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AU76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW76" t="n">
         <v>2</v>
@@ -36691,22 +36691,22 @@
         <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB76" t="n">
-        <v>955</v>
+        <v>2522</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36724,178 +36724,178 @@
         <v>3</v>
       </c>
       <c r="BJ76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK76" t="n">
         <v>3</v>
       </c>
-      <c r="BK76" t="n">
+      <c r="BL76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
         <v>4</v>
       </c>
-      <c r="BL76" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM76" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN76" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV76" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW76" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX76" t="n">
-        <v>63</v>
-      </c>
-      <c r="BY76" t="n">
-        <v>102</v>
-      </c>
-      <c r="BZ76" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CA76" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CB76" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="CC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM76" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS76" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU76" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV76" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX76" t="n">
+      <c r="CY76" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF76" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK76" t="n">
         <v>9</v>
       </c>
-      <c r="CY76" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ76" t="n">
-        <v>27</v>
-      </c>
-      <c r="DA76" t="n">
-        <v>72</v>
-      </c>
-      <c r="DB76" t="n">
-        <v>9</v>
-      </c>
-      <c r="DC76" t="n">
-        <v>45</v>
-      </c>
-      <c r="DD76" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DE76" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DF76" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DG76" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DH76" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI76" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ76" t="n">
-        <v>74</v>
-      </c>
-      <c r="DK76" t="n">
-        <v>29</v>
-      </c>
       <c r="DL76" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="DO76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36907,7 +36907,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -36916,88 +36916,88 @@
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW76" t="n">
-        <v>11.38</v>
+        <v>11.71</v>
       </c>
       <c r="DX76" t="n">
-        <v>11.66</v>
+        <v>9.65</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EG76" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EH76" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EI76" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI76" t="inlineStr"/>
       <c r="EJ76" t="inlineStr"/>
       <c r="EK76" t="inlineStr"/>
-      <c r="EL76" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+      <c r="EL76" t="inlineStr"/>
       <c r="EM76" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EN76" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EO76" t="inlineStr"/>
-      <c r="EP76" t="inlineStr"/>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EO76" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EP76" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -37359,7 +37359,7 @@
         <v>2.73</v>
       </c>
       <c r="DO77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -37831,7 +37831,7 @@
         <v>3.31</v>
       </c>
       <c r="DO78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP78" t="b">
         <v>0</v>
@@ -38286,7 +38286,7 @@
         <v>80</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE79" t="n">
         <v>1.88</v>
@@ -39257,7 +39257,7 @@
         <v>1.5</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -39287,7 +39287,7 @@
         <v>2.66</v>
       </c>
       <c r="DO81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -39737,7 +39737,7 @@
         <v>1.89</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF82" t="n">
         <v>1.67</v>
@@ -39767,7 +39767,7 @@
         <v>2.34</v>
       </c>
       <c r="DO82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40227,7 +40227,7 @@
         <v>2.73</v>
       </c>
       <c r="DO83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40674,7 +40674,7 @@
         <v>75</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE84" t="n">
         <v>1.88</v>
@@ -41154,7 +41154,7 @@
         <v>77</v>
       </c>
       <c r="DD85" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DE85" t="n">
         <v>2.25</v>
@@ -41187,7 +41187,7 @@
         <v>3.51</v>
       </c>
       <c r="DO85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41626,7 +41626,7 @@
         <v>100</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DE86" t="n">
         <v>1</v>
@@ -41659,7 +41659,7 @@
         <v>2.75</v>
       </c>
       <c r="DO86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -42109,7 +42109,7 @@
         <v>1</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF87" t="n">
         <v>0.71</v>
@@ -42139,7 +42139,7 @@
         <v>3.26</v>
       </c>
       <c r="DO87" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -43075,7 +43075,7 @@
         <v>2.65</v>
       </c>
       <c r="DO89" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43498,7 +43498,7 @@
         <v>64</v>
       </c>
       <c r="DD90" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DE90" t="n">
         <v>1.13</v>
@@ -43531,7 +43531,7 @@
         <v>3.62</v>
       </c>
       <c r="DO90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -43965,7 +43965,7 @@
         <v>2</v>
       </c>
       <c r="DE91" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="DF91" t="n">
         <v>1.86</v>
@@ -44434,7 +44434,7 @@
         <v>86</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DE92" t="n">
         <v>2.25</v>
@@ -44467,7 +44467,7 @@
         <v>2.83</v>
       </c>
       <c r="DO92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45397,7 +45397,7 @@
         <v>1.5</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF94" t="n">
         <v>1.29</v>
@@ -45427,7 +45427,7 @@
         <v>2.31</v>
       </c>
       <c r="DO94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46379,7 +46379,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46835,7 +46835,7 @@
         <v>2.56</v>
       </c>
       <c r="DO97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -47410,6 +47410,1910 @@
           <t>3.36</t>
         </is>
       </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>17</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>2</v>
+      </c>
+      <c r="J99" t="n">
+        <v>8</v>
+      </c>
+      <c r="K99" t="n">
+        <v>6</v>
+      </c>
+      <c r="L99" t="n">
+        <v>14</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2</v>
+      </c>
+      <c r="N99" t="n">
+        <v>4</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>4</v>
+      </c>
+      <c r="R99" t="n">
+        <v>3</v>
+      </c>
+      <c r="S99" t="n">
+        <v>7</v>
+      </c>
+      <c r="T99" t="n">
+        <v>7</v>
+      </c>
+      <c r="U99" t="n">
+        <v>11</v>
+      </c>
+      <c r="V99" t="n">
+        <v>10</v>
+      </c>
+      <c r="W99" t="n">
+        <v>14</v>
+      </c>
+      <c r="X99" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>2516</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK99" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR99" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT99" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>69</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD99" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DE99" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK99" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL99" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DM99" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DN99" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="DO99" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ99" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV99" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW99" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="DX99" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="DZ99" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG99" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EN99" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EO99" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EP99" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>17</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>45991.54166666666</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>9</v>
+      </c>
+      <c r="K100" t="n">
+        <v>6</v>
+      </c>
+      <c r="L100" t="n">
+        <v>15</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>4</v>
+      </c>
+      <c r="R100" t="n">
+        <v>4</v>
+      </c>
+      <c r="S100" t="n">
+        <v>14</v>
+      </c>
+      <c r="T100" t="n">
+        <v>10</v>
+      </c>
+      <c r="U100" t="n">
+        <v>18</v>
+      </c>
+      <c r="V100" t="n">
+        <v>14</v>
+      </c>
+      <c r="W100" t="n">
+        <v>10</v>
+      </c>
+      <c r="X100" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
+      <c r="AC100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI100" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK100" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT100" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV100" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>41</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD100" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE100" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ100" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK100" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL100" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM100" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DN100" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DO100" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV100" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW100" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="DX100" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="DY100" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="DZ100" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA100" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="ED100" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ100" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EL100" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EM100" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EN100" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EO100" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP100" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>17</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Nordsjælland</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>45991.625</v>
+      </c>
+      <c r="G101" t="n">
+        <v>6</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>6</v>
+      </c>
+      <c r="J101" t="n">
+        <v>6</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>7</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>2</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>9</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>6</v>
+      </c>
+      <c r="T101" t="n">
+        <v>4</v>
+      </c>
+      <c r="U101" t="n">
+        <v>15</v>
+      </c>
+      <c r="V101" t="n">
+        <v>4</v>
+      </c>
+      <c r="W101" t="n">
+        <v>12</v>
+      </c>
+      <c r="X101" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>MCH Arena</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Kaj Zartows Vej 5, Herning</t>
+        </is>
+      </c>
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>955</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI101" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV101" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX101" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY101" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>63</v>
+      </c>
+      <c r="DC101" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE101" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI101" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DJ101" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK101" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL101" t="n">
+        <v>2</v>
+      </c>
+      <c r="DM101" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DN101" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DO101" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU101" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV101" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW101" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="DX101" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="DY101" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="DZ101" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA101" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EB101" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EC101" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="ED101" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="EE101" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EF101" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EG101" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH101" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="EJ101" t="inlineStr"/>
+      <c r="EK101" t="inlineStr"/>
+      <c r="EL101" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EM101" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EN101" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EO101" t="inlineStr"/>
+      <c r="EP101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>17</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>45991.70833333334</v>
+      </c>
+      <c r="G102" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>4</v>
+      </c>
+      <c r="K102" t="n">
+        <v>5</v>
+      </c>
+      <c r="L102" t="n">
+        <v>9</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>2</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>6</v>
+      </c>
+      <c r="R102" t="n">
+        <v>5</v>
+      </c>
+      <c r="S102" t="n">
+        <v>4</v>
+      </c>
+      <c r="T102" t="n">
+        <v>7</v>
+      </c>
+      <c r="U102" t="n">
+        <v>10</v>
+      </c>
+      <c r="V102" t="n">
+        <v>12</v>
+      </c>
+      <c r="W102" t="n">
+        <v>10</v>
+      </c>
+      <c r="X102" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>Nature Energy Park</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>Højstrupvej 7B, Odense</t>
+        </is>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>2523</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI102" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV102" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW102" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX102" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY102" t="n">
+        <v>107</v>
+      </c>
+      <c r="BZ102" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CA102" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB102" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR102" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS102" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU102" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV102" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW102" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX102" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY102" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ102" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA102" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB102" t="n">
+        <v>51</v>
+      </c>
+      <c r="DC102" t="n">
+        <v>94</v>
+      </c>
+      <c r="DD102" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DE102" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DF102" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG102" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH102" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI102" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DJ102" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK102" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL102" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM102" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN102" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DO102" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR102" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV102" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW102" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="DX102" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="DY102" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="DZ102" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA102" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="EB102" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EC102" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="ED102" t="inlineStr">
+        <is>
+          <t>4.03</t>
+        </is>
+      </c>
+      <c r="EE102" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="EF102" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EG102" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EH102" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EI102" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EJ102" t="inlineStr"/>
+      <c r="EK102" t="inlineStr"/>
+      <c r="EL102" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EM102" t="inlineStr"/>
+      <c r="EN102" t="inlineStr"/>
+      <c r="EO102" t="inlineStr"/>
+      <c r="EP102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP102" headerRowCount="1">
-  <autoFilter ref="A1:EP102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP103" headerRowCount="1">
+  <autoFilter ref="A1:EP103"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP102"/>
+  <dimension ref="A1:EP103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -4162,7 +4162,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE7" t="n">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -6061,7 +6061,7 @@
         <v>1.22</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7507,7 +7507,7 @@
         <v>3.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8107,170 +8107,162 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>45872.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10</v>
+      </c>
+      <c r="V16" t="n">
+        <v>18</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5</v>
+      </c>
+      <c r="X16" t="n">
         <v>6</v>
       </c>
-      <c r="L16" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>17</v>
-      </c>
-      <c r="W16" t="n">
-        <v>11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14</v>
-      </c>
       <c r="Y16" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="Z16" t="n">
-        <v>68</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Sydbank Park</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Stadionvej 7, Haderslev</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.31</v>
+        <v>1.94</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>3.68</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AP16" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AU16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB16" t="n">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -8285,178 +8277,178 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL16" t="n">
         <v>4</v>
       </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>2</v>
-      </c>
       <c r="BM16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU16" t="n">
         <v>5</v>
       </c>
-      <c r="BN16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>65</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>136</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR16" t="n">
+      <c r="CV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX16" t="n">
         <v>11</v>
       </c>
-      <c r="CS16" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>8</v>
-      </c>
       <c r="CY16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CZ16" t="n">
         <v>50</v>
       </c>
       <c r="DA16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
         <v>50</v>
       </c>
-      <c r="DC16" t="n">
-        <v>100</v>
-      </c>
       <c r="DD16" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="DE16" t="n">
         <v>1</v>
       </c>
       <c r="DF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DI16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>1.69</v>
+        <v>0.91</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO16" t="n">
         <v>17</v>
@@ -8465,107 +8457,107 @@
         <v>1</v>
       </c>
       <c r="DQ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU16" t="b">
         <v>0</v>
       </c>
       <c r="DV16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="inlineStr"/>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EG16" t="inlineStr">
         <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EJ16" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK16" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EL16" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EM16" t="inlineStr">
+        <is>
           <t>2.58</t>
         </is>
       </c>
-      <c r="EH16" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EJ16" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EK16" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EL16" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EM16" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr"/>
@@ -8587,162 +8579,170 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45872.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="R17" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10</v>
+      </c>
+      <c r="U17" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="n">
-        <v>9</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
+        <v>17</v>
+      </c>
+      <c r="W17" t="n">
+        <v>11</v>
+      </c>
+      <c r="X17" t="n">
         <v>14</v>
       </c>
-      <c r="U17" t="n">
-        <v>10</v>
-      </c>
-      <c r="V17" t="n">
-        <v>18</v>
-      </c>
-      <c r="W17" t="n">
-        <v>5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6</v>
-      </c>
       <c r="Y17" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Sydbank Park</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Stadionvej 7, Haderslev</t>
+        </is>
+      </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.94</v>
+        <v>3.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.68</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AP17" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -8757,73 +8757,73 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS17" t="n">
         <v>2</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW17" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="BX17" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="BY17" t="n">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.23</v>
+        <v>0.8</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="CB17" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="CC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -8841,7 +8841,7 @@
         <v>1</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
@@ -8853,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP17" t="n">
         <v>0</v>
@@ -8862,73 +8862,73 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CS17" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CV17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CY17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="CZ17" t="n">
         <v>50</v>
       </c>
       <c r="DA17" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB17" t="n">
         <v>50</v>
       </c>
-      <c r="DB17" t="n">
-        <v>0</v>
-      </c>
       <c r="DC17" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ17" t="n">
         <v>50</v>
       </c>
-      <c r="DD17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DE17" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>0</v>
-      </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.91</v>
+        <v>1.69</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.91</v>
+        <v>2.96</v>
       </c>
       <c r="DO17" t="n">
         <v>17</v>
@@ -8937,107 +8937,107 @@
         <v>1</v>
       </c>
       <c r="DQ17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU17" t="b">
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW17" t="inlineStr"/>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr"/>
@@ -9850,7 +9850,7 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE19" t="n">
         <v>1.22</v>
@@ -9883,7 +9883,7 @@
         <v>3.11</v>
       </c>
       <c r="DO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -11269,7 +11269,7 @@
         <v>2.33</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -11299,7 +11299,7 @@
         <v>3.1</v>
       </c>
       <c r="DO22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -12202,7 +12202,7 @@
         <v>100</v>
       </c>
       <c r="DD24" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE24" t="n">
         <v>0.22</v>
@@ -12235,7 +12235,7 @@
         <v>2.85</v>
       </c>
       <c r="DO24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -13667,7 +13667,7 @@
         <v>2.72</v>
       </c>
       <c r="DO27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -15107,7 +15107,7 @@
         <v>1.96</v>
       </c>
       <c r="DO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -16203,70 +16203,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>21</v>
+      </c>
+      <c r="V33" t="n">
         <v>11</v>
       </c>
-      <c r="L33" t="n">
-        <v>14</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>15</v>
-      </c>
-      <c r="U33" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>18</v>
-      </c>
       <c r="W33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -16276,97 +16276,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO33" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB33" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -16381,64 +16381,64 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK33" t="n">
         <v>3</v>
       </c>
-      <c r="BK33" t="n">
-        <v>1</v>
-      </c>
       <c r="BL33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO33" t="n">
         <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR33" t="n">
         <v>1</v>
       </c>
       <c r="BS33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU33" t="n">
         <v>1</v>
       </c>
       <c r="BV33" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW33" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX33" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY33" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA33" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -16471,7 +16471,7 @@
         <v>0</v>
       </c>
       <c r="CM33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
@@ -16486,157 +16486,157 @@
         <v>1</v>
       </c>
       <c r="CR33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS33" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT33" t="n">
         <v>1</v>
       </c>
       <c r="CU33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW33" t="n">
         <v>1</v>
       </c>
       <c r="CX33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CY33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB33" t="n">
         <v>67</v>
       </c>
-      <c r="DA33" t="n">
+      <c r="DC33" t="n">
         <v>100</v>
       </c>
-      <c r="DB33" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC33" t="n">
-        <v>67</v>
-      </c>
       <c r="DD33" t="n">
-        <v>0.88</v>
+        <v>2.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DF33" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG33" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH33" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI33" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DJ33" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL33" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="DN33" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW33" t="n">
-        <v>16.01</v>
+        <v>16.08</v>
       </c>
       <c r="DX33" t="n">
-        <v>9.800000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EF33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EG33" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EH33" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EI33" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ33" t="inlineStr">
@@ -16656,12 +16656,12 @@
       </c>
       <c r="EM33" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN33" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EO33" t="inlineStr"/>
@@ -16683,70 +16683,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L34" t="n">
+        <v>14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>18</v>
+      </c>
+      <c r="W34" t="n">
         <v>10</v>
       </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>12</v>
-      </c>
-      <c r="R34" t="n">
-        <v>5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>9</v>
-      </c>
-      <c r="T34" t="n">
-        <v>6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>21</v>
-      </c>
-      <c r="V34" t="n">
-        <v>11</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
-      </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16756,97 +16756,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16861,178 +16861,178 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ34" t="n">
         <v>3</v>
       </c>
-      <c r="BJ34" t="n">
-        <v>2</v>
-      </c>
       <c r="BK34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR34" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY34" t="n">
         <v>5</v>
       </c>
-      <c r="BO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB34" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS34" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX34" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY34" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA34" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB34" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC34" t="n">
         <v>67</v>
       </c>
-      <c r="DC34" t="n">
-        <v>100</v>
-      </c>
       <c r="DD34" t="n">
-        <v>2.33</v>
+        <v>0.88</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF34" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ34" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK34" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL34" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN34" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO34" t="n">
         <v>17</v>
@@ -17041,107 +17041,107 @@
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW34" t="n">
-        <v>16.08</v>
+        <v>16.01</v>
       </c>
       <c r="DX34" t="n">
-        <v>8.460000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="ED34" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EE34" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EG34" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EH34" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ34" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EL34" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM34" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EN34" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="ED34" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EE34" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EF34" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EG34" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EH34" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EJ34" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK34" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EL34" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM34" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EN34" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EO34" t="inlineStr"/>
@@ -17515,7 +17515,7 @@
         <v>2.46</v>
       </c>
       <c r="DO35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -19397,7 +19397,7 @@
         <v>2.11</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF39" t="n">
         <v>1.33</v>
@@ -19427,7 +19427,7 @@
         <v>3.29</v>
       </c>
       <c r="DO39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -21306,7 +21306,7 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE43" t="n">
         <v>1.75</v>
@@ -21339,7 +21339,7 @@
         <v>2.97</v>
       </c>
       <c r="DO43" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22250,7 +22250,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE45" t="n">
         <v>1.67</v>
@@ -22283,7 +22283,7 @@
         <v>3.76</v>
       </c>
       <c r="DO45" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -24175,7 +24175,7 @@
         <v>2.22</v>
       </c>
       <c r="DO49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24625,7 +24625,7 @@
         <v>1.56</v>
       </c>
       <c r="DE50" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF50" t="n">
         <v>1.5</v>
@@ -24655,7 +24655,7 @@
         <v>2.69</v>
       </c>
       <c r="DO50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26543,7 +26543,7 @@
         <v>3.92</v>
       </c>
       <c r="DO54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -27925,7 +27925,7 @@
         <v>1.5</v>
       </c>
       <c r="DE57" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF57" t="n">
         <v>0.75</v>
@@ -27955,7 +27955,7 @@
         <v>2.67</v>
       </c>
       <c r="DO57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -29354,7 +29354,7 @@
         <v>90</v>
       </c>
       <c r="DD60" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE60" t="n">
         <v>1.13</v>
@@ -29387,7 +29387,7 @@
         <v>2.73</v>
       </c>
       <c r="DO60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30423,22 +30423,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -30447,16 +30447,16 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -30465,128 +30465,120 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V63" t="n">
         <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y63" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z63" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE63" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF63" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AN63" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AU63" t="n">
         <v>3</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX63" t="n">
         <v>0</v>
       </c>
       <c r="AY63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB63" t="n">
-        <v>986</v>
+        <v>2521</v>
       </c>
       <c r="BC63" t="n">
         <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="BE63" t="n">
         <v>0</v>
@@ -30601,37 +30593,37 @@
         <v>1</v>
       </c>
       <c r="BI63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL63" t="n">
         <v>2</v>
       </c>
       <c r="BM63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN63" t="n">
         <v>5</v>
       </c>
-      <c r="BN63" t="n">
-        <v>6</v>
-      </c>
       <c r="BO63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP63" t="n">
         <v>0</v>
       </c>
       <c r="BQ63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT63" t="n">
         <v>2</v>
@@ -30640,25 +30632,25 @@
         <v>1</v>
       </c>
       <c r="BV63" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BW63" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="BX63" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BY63" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="BZ63" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="CB63" t="n">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="CC63" t="n">
         <v>0</v>
@@ -30691,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="CM63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN63" t="n">
         <v>0</v>
@@ -30706,73 +30698,73 @@
         <v>1</v>
       </c>
       <c r="CR63" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CS63" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT63" t="n">
         <v>1</v>
       </c>
       <c r="CU63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CV63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW63" t="n">
         <v>1</v>
       </c>
       <c r="CX63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ63" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="DA63" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DB63" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="DC63" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="DD63" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="DE63" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF63" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DG63" t="n">
         <v>1.2</v>
       </c>
       <c r="DH63" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="DI63" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ63" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK63" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="DL63" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="DM63" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="DN63" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="DO63" t="n">
         <v>17</v>
@@ -30796,102 +30788,86 @@
         <v>0</v>
       </c>
       <c r="DV63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW63" t="n">
-        <v>12.5</v>
+        <v>13.33</v>
       </c>
       <c r="DX63" t="n">
-        <v>9.859999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="DY63" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ63" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="EA63" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB63" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC63" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="ED63" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EE63" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EF63" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG63" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EH63" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EI63" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EJ63" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EK63" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EL63" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI63" t="inlineStr"/>
+      <c r="EJ63" t="inlineStr"/>
+      <c r="EK63" t="inlineStr"/>
+      <c r="EL63" t="inlineStr"/>
       <c r="EM63" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EN63" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EO63" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP63" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -30911,22 +30887,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
         <v>3</v>
@@ -30935,16 +30911,16 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -30953,120 +30929,128 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V64" t="n">
         <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X64" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y64" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z64" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AF64" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL64" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AM64" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AN64" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AO64" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AS64" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AU64" t="n">
         <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX64" t="n">
         <v>0</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB64" t="n">
-        <v>2521</v>
+        <v>986</v>
       </c>
       <c r="BC64" t="n">
         <v>0</v>
       </c>
       <c r="BD64" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="BE64" t="n">
         <v>0</v>
@@ -31081,178 +31065,178 @@
         <v>1</v>
       </c>
       <c r="BI64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK64" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB64" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR64" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS64" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU64" t="n">
         <v>3</v>
       </c>
-      <c r="BL64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN64" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU64" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV64" t="n">
-        <v>53</v>
-      </c>
-      <c r="BW64" t="n">
-        <v>63</v>
-      </c>
-      <c r="BX64" t="n">
-        <v>84</v>
-      </c>
-      <c r="BY64" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ64" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CA64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CB64" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM64" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS64" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU64" t="n">
-        <v>12</v>
-      </c>
       <c r="CV64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW64" t="n">
         <v>1</v>
       </c>
       <c r="CX64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ64" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA64" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DB64" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="DC64" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="DD64" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="DF64" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG64" t="n">
         <v>1.2</v>
       </c>
       <c r="DH64" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="DI64" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ64" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK64" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="DL64" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="DM64" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="DN64" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="DO64" t="n">
         <v>17</v>
@@ -31276,86 +31260,102 @@
         <v>0</v>
       </c>
       <c r="DV64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW64" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="DX64" t="n">
-        <v>9.65</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY64" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ64" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA64" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EB64" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EC64" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="ED64" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EE64" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EF64" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG64" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EH64" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EI64" t="inlineStr"/>
-      <c r="EJ64" t="inlineStr"/>
-      <c r="EK64" t="inlineStr"/>
-      <c r="EL64" t="inlineStr"/>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI64" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EJ64" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK64" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EL64" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EM64" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EN64" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EO64" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP64" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.34</t>
         </is>
       </c>
     </row>
@@ -32679,7 +32679,7 @@
         <v>3.08</v>
       </c>
       <c r="DO67" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -33263,12 +33263,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -33278,25 +33278,25 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
+        <v>9</v>
+      </c>
+      <c r="K69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" t="n">
-        <v>3</v>
-      </c>
       <c r="L69" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -33305,102 +33305,102 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T69" t="n">
         <v>10</v>
       </c>
       <c r="U69" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V69" t="n">
+        <v>18</v>
+      </c>
+      <c r="W69" t="n">
+        <v>6</v>
+      </c>
+      <c r="X69" t="n">
         <v>13</v>
       </c>
-      <c r="W69" t="n">
-        <v>10</v>
-      </c>
-      <c r="X69" t="n">
-        <v>11</v>
-      </c>
       <c r="Y69" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="Z69" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU69" t="n">
         <v>3</v>
       </c>
-      <c r="AD69" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN69" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO69" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP69" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ69" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU69" t="n">
-        <v>1</v>
-      </c>
       <c r="AV69" t="n">
         <v>1</v>
       </c>
@@ -33411,22 +33411,22 @@
         <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA69" t="n">
         <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>986</v>
+        <v>2523</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="BE69" t="n">
         <v>0</v>
@@ -33435,46 +33435,46 @@
         <v>-1</v>
       </c>
       <c r="BG69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH69" t="n">
         <v>1</v>
       </c>
       <c r="BI69" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BJ69" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK69" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM69" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BN69" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR69" t="n">
         <v>1</v>
       </c>
       <c r="BS69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
@@ -33483,136 +33483,136 @@
         <v>17</v>
       </c>
       <c r="BW69" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BX69" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>40</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR69" t="n">
         <v>35</v>
       </c>
-      <c r="BY69" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ69" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB69" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>16</v>
-      </c>
       <c r="CS69" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU69" t="n">
         <v>14</v>
       </c>
-      <c r="CT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU69" t="n">
-        <v>12</v>
-      </c>
       <c r="CV69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW69" t="n">
         <v>1</v>
       </c>
       <c r="CX69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CY69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ69" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA69" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="DB69" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="DC69" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="DD69" t="n">
         <v>1.5</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="DF69" t="n">
         <v>1.2</v>
       </c>
       <c r="DG69" t="n">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="DH69" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="DI69" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="DJ69" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK69" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="DL69" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="DN69" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="DO69" t="n">
         <v>17</v>
@@ -33621,10 +33621,10 @@
         <v>1</v>
       </c>
       <c r="DQ69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS69" t="b">
         <v>0</v>
@@ -33636,62 +33636,62 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW69" t="n">
-        <v>9.83</v>
+        <v>9.23</v>
       </c>
       <c r="DX69" t="n">
-        <v>5.78</v>
+        <v>6.84</v>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ69" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA69" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EB69" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC69" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="ED69" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EE69" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EF69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EG69" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EH69" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI69" t="inlineStr"/>
@@ -33700,12 +33700,12 @@
       <c r="EL69" t="inlineStr"/>
       <c r="EM69" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EN69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EO69" t="inlineStr"/>
@@ -33727,12 +33727,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -33742,25 +33742,25 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" t="n">
         <v>3</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>9</v>
       </c>
-      <c r="K70" t="n">
-        <v>6</v>
-      </c>
-      <c r="L70" t="n">
-        <v>15</v>
-      </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -33769,101 +33769,101 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R70" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="n">
         <v>10</v>
       </c>
       <c r="U70" t="n">
+        <v>14</v>
+      </c>
+      <c r="V70" t="n">
+        <v>13</v>
+      </c>
+      <c r="W70" t="n">
         <v>10</v>
       </c>
-      <c r="V70" t="n">
-        <v>18</v>
-      </c>
-      <c r="W70" t="n">
-        <v>6</v>
-      </c>
       <c r="X70" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y70" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="Z70" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AK70" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL70" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AM70" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN70" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AO70" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AS70" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AU70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV70" t="n">
         <v>1</v>
@@ -33875,22 +33875,22 @@
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
       </c>
       <c r="BB70" t="n">
-        <v>2523</v>
+        <v>986</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -33899,46 +33899,46 @@
         <v>-1</v>
       </c>
       <c r="BG70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH70" t="n">
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BJ70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM70" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BN70" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR70" t="n">
         <v>1</v>
       </c>
       <c r="BS70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU70" t="n">
         <v>1</v>
@@ -33947,22 +33947,22 @@
         <v>17</v>
       </c>
       <c r="BW70" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BX70" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BY70" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BZ70" t="n">
-        <v>0.89</v>
+        <v>1.49</v>
       </c>
       <c r="CA70" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CC70" t="n">
         <v>0</v>
@@ -33989,16 +33989,16 @@
         <v>1</v>
       </c>
       <c r="CK70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL70" t="n">
         <v>0</v>
       </c>
       <c r="CM70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO70" t="n">
         <v>0</v>
@@ -34010,73 +34010,73 @@
         <v>1</v>
       </c>
       <c r="CR70" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="CS70" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT70" t="n">
         <v>1</v>
       </c>
       <c r="CU70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV70" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY70" t="n">
         <v>7</v>
       </c>
-      <c r="CW70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX70" t="n">
+      <c r="CZ70" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB70" t="n">
         <v>9</v>
       </c>
-      <c r="CY70" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ70" t="n">
-        <v>80</v>
-      </c>
-      <c r="DA70" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB70" t="n">
-        <v>80</v>
-      </c>
       <c r="DC70" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="DD70" t="n">
         <v>1.5</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.13</v>
+        <v>0.89</v>
       </c>
       <c r="DF70" t="n">
         <v>1.2</v>
       </c>
       <c r="DG70" t="n">
-        <v>0.4</v>
+        <v>1.17</v>
       </c>
       <c r="DH70" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="DI70" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="DJ70" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK70" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="DL70" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="DM70" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="DN70" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="DO70" t="n">
         <v>17</v>
@@ -34085,10 +34085,10 @@
         <v>1</v>
       </c>
       <c r="DQ70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS70" t="b">
         <v>0</v>
@@ -34100,62 +34100,62 @@
         <v>0</v>
       </c>
       <c r="DV70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW70" t="n">
-        <v>9.23</v>
+        <v>9.83</v>
       </c>
       <c r="DX70" t="n">
-        <v>6.84</v>
+        <v>5.78</v>
       </c>
       <c r="DY70" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ70" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="EA70" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EB70" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC70" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="ED70" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EE70" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EF70" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="EC70" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="ED70" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="EE70" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EF70" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EG70" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH70" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI70" t="inlineStr"/>
@@ -34164,12 +34164,12 @@
       <c r="EL70" t="inlineStr"/>
       <c r="EM70" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EN70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EO70" t="inlineStr"/>
@@ -34510,7 +34510,7 @@
         <v>82</v>
       </c>
       <c r="DD71" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE71" t="n">
         <v>2.25</v>
@@ -34543,7 +34543,7 @@
         <v>3.14</v>
       </c>
       <c r="DO71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35465,7 +35465,7 @@
         <v>1.89</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF73" t="n">
         <v>1.4</v>
@@ -35495,7 +35495,7 @@
         <v>2.18</v>
       </c>
       <c r="DO73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -36423,7 +36423,7 @@
         <v>2.51</v>
       </c>
       <c r="DO75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -38319,7 +38319,7 @@
         <v>3.34</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38777,7 +38777,7 @@
         <v>1.63</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF80" t="n">
         <v>1.17</v>
@@ -38807,7 +38807,7 @@
         <v>3.11</v>
       </c>
       <c r="DO80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -40707,7 +40707,7 @@
         <v>3.22</v>
       </c>
       <c r="DO84" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -42611,7 +42611,7 @@
         <v>2.68</v>
       </c>
       <c r="DO88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -43962,7 +43962,7 @@
         <v>79</v>
       </c>
       <c r="DD91" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DE91" t="n">
         <v>1</v>
@@ -43995,7 +43995,7 @@
         <v>3.1</v>
       </c>
       <c r="DO91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44939,7 +44939,7 @@
         <v>3.71</v>
       </c>
       <c r="DO93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45869,7 +45869,7 @@
         <v>1.5</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="DF95" t="n">
         <v>1.29</v>
@@ -45899,7 +45899,7 @@
         <v>2.79</v>
       </c>
       <c r="DO95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -47427,40 +47427,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K99" t="n">
         <v>6</v>
       </c>
       <c r="L99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M99" t="n">
         <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -47472,117 +47472,125 @@
         <v>4</v>
       </c>
       <c r="R99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U99" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V99" t="n">
+        <v>14</v>
+      </c>
+      <c r="W99" t="n">
         <v>10</v>
       </c>
-      <c r="W99" t="n">
-        <v>14</v>
-      </c>
       <c r="X99" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y99" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z99" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
       <c r="AC99" t="n">
         <v>2</v>
       </c>
       <c r="AD99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE99" t="n">
         <v>2.37</v>
       </c>
       <c r="AF99" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL99" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AN99" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AU99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW99" t="n">
         <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
         <v>0</v>
       </c>
       <c r="AZ99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>2516</v>
+        <v>-1</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47597,19 +47605,19 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK99" t="n">
         <v>3</v>
       </c>
-      <c r="BJ99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK99" t="n">
-        <v>5</v>
-      </c>
       <c r="BL99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BM99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN99" t="n">
         <v>9</v>
@@ -47618,166 +47626,166 @@
         <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ99" t="n">
         <v>2</v>
       </c>
       <c r="BR99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BW99" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="BX99" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="BY99" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BZ99" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD99" t="n">
         <v>1.22</v>
       </c>
-      <c r="CA99" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="CB99" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CC99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN99" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>12</v>
-      </c>
-      <c r="CS99" t="n">
+      <c r="DE99" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK99" t="n">
         <v>19</v>
       </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV99" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX99" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY99" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ99" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA99" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB99" t="n">
-        <v>38</v>
-      </c>
-      <c r="DC99" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD99" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE99" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF99" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG99" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DH99" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DI99" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DJ99" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK99" t="n">
-        <v>25</v>
-      </c>
       <c r="DL99" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="DN99" t="n">
-        <v>4.05</v>
+        <v>2.78</v>
       </c>
       <c r="DO99" t="n">
         <v>17</v>
       </c>
       <c r="DP99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR99" t="b">
         <v>0</v>
@@ -47795,10 +47803,10 @@
         <v>0</v>
       </c>
       <c r="DW99" t="n">
-        <v>6.46</v>
+        <v>6.66</v>
       </c>
       <c r="DX99" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
@@ -47812,82 +47820,82 @@
       </c>
       <c r="EA99" t="inlineStr">
         <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG99" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="EB99" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EC99" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="ED99" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EE99" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EF99" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG99" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="EH99" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EI99" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EJ99" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EK99" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EM99" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EN99" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EO99" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP99" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.38</t>
         </is>
       </c>
     </row>
@@ -47907,40 +47915,40 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K100" t="n">
         <v>6</v>
       </c>
       <c r="L100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M100" t="n">
         <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -47952,125 +47960,117 @@
         <v>4</v>
       </c>
       <c r="R100" t="n">
+        <v>3</v>
+      </c>
+      <c r="S100" t="n">
+        <v>7</v>
+      </c>
+      <c r="T100" t="n">
+        <v>7</v>
+      </c>
+      <c r="U100" t="n">
+        <v>11</v>
+      </c>
+      <c r="V100" t="n">
+        <v>10</v>
+      </c>
+      <c r="W100" t="n">
+        <v>14</v>
+      </c>
+      <c r="X100" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD100" t="n">
         <v>4</v>
-      </c>
-      <c r="S100" t="n">
-        <v>14</v>
-      </c>
-      <c r="T100" t="n">
-        <v>10</v>
-      </c>
-      <c r="U100" t="n">
-        <v>18</v>
-      </c>
-      <c r="V100" t="n">
-        <v>14</v>
-      </c>
-      <c r="W100" t="n">
-        <v>10</v>
-      </c>
-      <c r="X100" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>JYSK park</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>Ansvej 104, Silkeborg</t>
-        </is>
-      </c>
-      <c r="AC100" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>2</v>
       </c>
       <c r="AE100" t="n">
         <v>2.37</v>
       </c>
       <c r="AF100" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AJ100" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL100" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW100" t="n">
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB100" t="n">
-        <v>-1</v>
+        <v>2516</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48085,19 +48085,19 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BJ100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BM100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN100" t="n">
         <v>9</v>
@@ -48106,43 +48106,43 @@
         <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ100" t="n">
         <v>2</v>
       </c>
       <c r="BR100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BW100" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="BX100" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="BY100" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BZ100" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="CB100" t="n">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="CC100" t="n">
         <v>0</v>
@@ -48169,16 +48169,16 @@
         <v>1</v>
       </c>
       <c r="CK100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL100" t="n">
         <v>0</v>
       </c>
       <c r="CM100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO100" t="n">
         <v>0</v>
@@ -48190,82 +48190,82 @@
         <v>1</v>
       </c>
       <c r="CR100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
         <v>16</v>
       </c>
-      <c r="CS100" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
+      <c r="CV100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY100" t="n">
         <v>12</v>
       </c>
-      <c r="CV100" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY100" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ100" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="DA100" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="DB100" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="DC100" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="DF100" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DG100" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DH100" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="DI100" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="DJ100" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="DK100" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="DN100" t="n">
-        <v>2.78</v>
+        <v>4.05</v>
       </c>
       <c r="DO100" t="n">
         <v>17</v>
       </c>
       <c r="DP100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR100" t="b">
         <v>0</v>
@@ -48283,10 +48283,10 @@
         <v>0</v>
       </c>
       <c r="DW100" t="n">
-        <v>6.66</v>
+        <v>6.46</v>
       </c>
       <c r="DX100" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
@@ -48300,82 +48300,82 @@
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC100" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="ED100" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EE100" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EF100" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EK100" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM100" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN100" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -49314,6 +49314,470 @@
       <c r="EN102" t="inlineStr"/>
       <c r="EO102" t="inlineStr"/>
       <c r="EP102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>17</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Brøndby</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>45992.75</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3</v>
+      </c>
+      <c r="I103" t="n">
+        <v>4</v>
+      </c>
+      <c r="J103" t="n">
+        <v>8</v>
+      </c>
+      <c r="K103" t="n">
+        <v>3</v>
+      </c>
+      <c r="L103" t="n">
+        <v>11</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="n">
+        <v>2</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>4</v>
+      </c>
+      <c r="R103" t="n">
+        <v>5</v>
+      </c>
+      <c r="S103" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" t="n">
+        <v>6</v>
+      </c>
+      <c r="U103" t="n">
+        <v>19</v>
+      </c>
+      <c r="V103" t="n">
+        <v>11</v>
+      </c>
+      <c r="W103" t="n">
+        <v>11</v>
+      </c>
+      <c r="X103" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Brøndby Stadion</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>Brøndby Stadion 8, Brøndby</t>
+        </is>
+      </c>
+      <c r="AC103" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>3649</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>114</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>137</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>40</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU103" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY103" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ103" t="n">
+        <v>82</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>94</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DJ103" t="n">
+        <v>19</v>
+      </c>
+      <c r="DK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL103" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DM103" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DN103" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DO103" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW103" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="DX103" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="DY103" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="DZ103" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="EA103" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EB103" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EC103" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="ED103" t="inlineStr">
+        <is>
+          <t>6.56</t>
+        </is>
+      </c>
+      <c r="EE103" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
+      </c>
+      <c r="EF103" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EG103" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EH103" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="EI103" t="inlineStr"/>
+      <c r="EJ103" t="inlineStr"/>
+      <c r="EK103" t="inlineStr"/>
+      <c r="EL103" t="inlineStr"/>
+      <c r="EM103" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EN103" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EO103" t="inlineStr"/>
+      <c r="EP103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP103" headerRowCount="1">
-  <autoFilter ref="A1:EP103"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP104" headerRowCount="1">
+  <autoFilter ref="A1:EP104"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP103"/>
+  <dimension ref="A1:EP104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE3" t="n">
         <v>1</v>
@@ -3701,7 +3701,7 @@
         <v>2.33</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>100</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE14" t="n">
         <v>1.67</v>
@@ -7957,7 +7957,7 @@
         <v>1</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -13634,7 +13634,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE27" t="n">
         <v>1.13</v>
@@ -16045,7 +16045,7 @@
         <v>1.63</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF32" t="n">
         <v>1.5</v>
@@ -16203,70 +16203,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L33" t="n">
+        <v>14</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>15</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" t="n">
         <v>10</v>
       </c>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>12</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>9</v>
-      </c>
-      <c r="T33" t="n">
-        <v>6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>21</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>11</v>
-      </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -16276,97 +16276,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB33" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -16381,178 +16381,178 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ33" t="n">
         <v>3</v>
       </c>
-      <c r="BJ33" t="n">
-        <v>2</v>
-      </c>
       <c r="BK33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY33" t="n">
         <v>5</v>
       </c>
-      <c r="BO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB33" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS33" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA33" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB33" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC33" t="n">
         <v>67</v>
       </c>
-      <c r="DC33" t="n">
-        <v>100</v>
-      </c>
       <c r="DD33" t="n">
-        <v>2.33</v>
+        <v>0.78</v>
       </c>
       <c r="DE33" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF33" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG33" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH33" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI33" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ33" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL33" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN33" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO33" t="n">
         <v>17</v>
@@ -16561,107 +16561,107 @@
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW33" t="n">
-        <v>16.08</v>
+        <v>16.01</v>
       </c>
       <c r="DX33" t="n">
-        <v>8.460000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EG33" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EH33" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK33" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EL33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM33" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EN33" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="ED33" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EE33" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EF33" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EG33" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EH33" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EJ33" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK33" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EL33" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM33" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EN33" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EO33" t="inlineStr"/>
@@ -16683,70 +16683,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>12</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>21</v>
+      </c>
+      <c r="V34" t="n">
         <v>11</v>
       </c>
-      <c r="L34" t="n">
-        <v>14</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>15</v>
-      </c>
-      <c r="U34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>18</v>
-      </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16756,97 +16756,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO34" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB34" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16861,64 +16861,64 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK34" t="n">
         <v>3</v>
       </c>
-      <c r="BK34" t="n">
-        <v>1</v>
-      </c>
       <c r="BL34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO34" t="n">
         <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR34" t="n">
         <v>1</v>
       </c>
       <c r="BS34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW34" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX34" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY34" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -16951,7 +16951,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -16966,73 +16966,73 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS34" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CY34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB34" t="n">
         <v>67</v>
       </c>
-      <c r="DA34" t="n">
+      <c r="DC34" t="n">
         <v>100</v>
       </c>
-      <c r="DB34" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC34" t="n">
-        <v>67</v>
-      </c>
       <c r="DD34" t="n">
-        <v>0.88</v>
+        <v>2.33</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DF34" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG34" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DJ34" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK34" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO34" t="n">
         <v>17</v>
@@ -17041,82 +17041,82 @@
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW34" t="n">
-        <v>16.01</v>
+        <v>16.08</v>
       </c>
       <c r="DX34" t="n">
-        <v>9.800000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="EM34" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EO34" t="inlineStr"/>
@@ -23693,7 +23693,7 @@
         <v>1.22</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF48" t="n">
         <v>1</v>
@@ -24142,7 +24142,7 @@
         <v>88</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE49" t="n">
         <v>0.22</v>
@@ -24655,7 +24655,7 @@
         <v>2.69</v>
       </c>
       <c r="DO50" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -29357,7 +29357,7 @@
         <v>1.78</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF60" t="n">
         <v>1.8</v>
@@ -32646,7 +32646,7 @@
         <v>68</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE67" t="n">
         <v>1.88</v>
@@ -33263,12 +33263,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -33278,25 +33278,25 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>6</v>
+      </c>
+      <c r="K69" t="n">
         <v>3</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>9</v>
       </c>
-      <c r="K69" t="n">
-        <v>6</v>
-      </c>
-      <c r="L69" t="n">
-        <v>15</v>
-      </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -33305,101 +33305,101 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T69" t="n">
         <v>10</v>
       </c>
       <c r="U69" t="n">
+        <v>14</v>
+      </c>
+      <c r="V69" t="n">
+        <v>13</v>
+      </c>
+      <c r="W69" t="n">
         <v>10</v>
       </c>
-      <c r="V69" t="n">
-        <v>18</v>
-      </c>
-      <c r="W69" t="n">
-        <v>6</v>
-      </c>
       <c r="X69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y69" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="Z69" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AF69" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AG69" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL69" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AM69" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN69" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AO69" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR69" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AS69" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AU69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV69" t="n">
         <v>1</v>
@@ -33411,22 +33411,22 @@
         <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA69" t="n">
         <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>2523</v>
+        <v>986</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="BE69" t="n">
         <v>0</v>
@@ -33435,46 +33435,46 @@
         <v>-1</v>
       </c>
       <c r="BG69" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH69" t="n">
         <v>1</v>
       </c>
       <c r="BI69" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BJ69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL69" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM69" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BN69" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR69" t="n">
         <v>1</v>
       </c>
       <c r="BS69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
@@ -33483,22 +33483,22 @@
         <v>17</v>
       </c>
       <c r="BW69" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BX69" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BY69" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BZ69" t="n">
-        <v>0.89</v>
+        <v>1.49</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="CB69" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CC69" t="n">
         <v>0</v>
@@ -33525,16 +33525,16 @@
         <v>1</v>
       </c>
       <c r="CK69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL69" t="n">
         <v>0</v>
       </c>
       <c r="CM69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO69" t="n">
         <v>0</v>
@@ -33546,73 +33546,73 @@
         <v>1</v>
       </c>
       <c r="CR69" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="CS69" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT69" t="n">
         <v>1</v>
       </c>
       <c r="CU69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV69" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY69" t="n">
         <v>7</v>
       </c>
-      <c r="CW69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX69" t="n">
+      <c r="CZ69" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB69" t="n">
         <v>9</v>
       </c>
-      <c r="CY69" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ69" t="n">
-        <v>80</v>
-      </c>
-      <c r="DA69" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB69" t="n">
-        <v>80</v>
-      </c>
       <c r="DC69" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="DD69" t="n">
         <v>1.5</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.13</v>
+        <v>0.89</v>
       </c>
       <c r="DF69" t="n">
         <v>1.2</v>
       </c>
       <c r="DG69" t="n">
-        <v>0.4</v>
+        <v>1.17</v>
       </c>
       <c r="DH69" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="DI69" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="DJ69" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK69" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="DL69" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="DN69" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="DO69" t="n">
         <v>17</v>
@@ -33621,10 +33621,10 @@
         <v>1</v>
       </c>
       <c r="DQ69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS69" t="b">
         <v>0</v>
@@ -33636,62 +33636,62 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW69" t="n">
-        <v>9.23</v>
+        <v>9.83</v>
       </c>
       <c r="DX69" t="n">
-        <v>6.84</v>
+        <v>5.78</v>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ69" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="EA69" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EB69" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC69" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="ED69" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EE69" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EF69" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="EC69" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="ED69" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="EE69" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EF69" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EG69" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH69" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI69" t="inlineStr"/>
@@ -33700,12 +33700,12 @@
       <c r="EL69" t="inlineStr"/>
       <c r="EM69" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EN69" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EO69" t="inlineStr"/>
@@ -33727,12 +33727,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -33742,25 +33742,25 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
+        <v>9</v>
+      </c>
+      <c r="K70" t="n">
         <v>6</v>
       </c>
-      <c r="K70" t="n">
-        <v>3</v>
-      </c>
       <c r="L70" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -33769,102 +33769,102 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T70" t="n">
         <v>10</v>
       </c>
       <c r="U70" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V70" t="n">
+        <v>18</v>
+      </c>
+      <c r="W70" t="n">
+        <v>6</v>
+      </c>
+      <c r="X70" t="n">
         <v>13</v>
       </c>
-      <c r="W70" t="n">
-        <v>10</v>
-      </c>
-      <c r="X70" t="n">
-        <v>11</v>
-      </c>
       <c r="Y70" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="Z70" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU70" t="n">
         <v>3</v>
       </c>
-      <c r="AD70" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ70" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR70" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT70" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU70" t="n">
-        <v>1</v>
-      </c>
       <c r="AV70" t="n">
         <v>1</v>
       </c>
@@ -33875,22 +33875,22 @@
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
       </c>
       <c r="BB70" t="n">
-        <v>986</v>
+        <v>2523</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -33899,46 +33899,46 @@
         <v>-1</v>
       </c>
       <c r="BG70" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH70" t="n">
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BJ70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL70" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM70" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BN70" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR70" t="n">
         <v>1</v>
       </c>
       <c r="BS70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU70" t="n">
         <v>1</v>
@@ -33947,136 +33947,136 @@
         <v>17</v>
       </c>
       <c r="BW70" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BX70" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>40</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR70" t="n">
         <v>35</v>
       </c>
-      <c r="BY70" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ70" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA70" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB70" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>16</v>
-      </c>
       <c r="CS70" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU70" t="n">
         <v>14</v>
       </c>
-      <c r="CT70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU70" t="n">
-        <v>12</v>
-      </c>
       <c r="CV70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW70" t="n">
         <v>1</v>
       </c>
       <c r="CX70" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CY70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ70" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA70" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="DB70" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="DC70" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="DD70" t="n">
         <v>1.5</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="DF70" t="n">
         <v>1.2</v>
       </c>
       <c r="DG70" t="n">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="DH70" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="DI70" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="DJ70" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK70" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="DL70" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="DM70" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="DN70" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="DO70" t="n">
         <v>17</v>
@@ -34085,10 +34085,10 @@
         <v>1</v>
       </c>
       <c r="DQ70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS70" t="b">
         <v>0</v>
@@ -34100,62 +34100,62 @@
         <v>0</v>
       </c>
       <c r="DV70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW70" t="n">
-        <v>9.83</v>
+        <v>9.23</v>
       </c>
       <c r="DX70" t="n">
-        <v>5.78</v>
+        <v>6.84</v>
       </c>
       <c r="DY70" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ70" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA70" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EB70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC70" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="ED70" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EE70" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EF70" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EG70" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EH70" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI70" t="inlineStr"/>
@@ -34164,12 +34164,12 @@
       <c r="EL70" t="inlineStr"/>
       <c r="EM70" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EN70" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EO70" t="inlineStr"/>
@@ -36390,7 +36390,7 @@
         <v>45</v>
       </c>
       <c r="DD75" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DE75" t="n">
         <v>1.75</v>
@@ -40197,7 +40197,7 @@
         <v>1.5</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF83" t="n">
         <v>1.5</v>
@@ -41787,143 +41787,143 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" t="n">
+        <v>9</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
         <v>6</v>
       </c>
-      <c r="L87" t="n">
-        <v>10</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>6</v>
-      </c>
-      <c r="R87" t="n">
-        <v>3</v>
-      </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U87" t="n">
         <v>11</v>
       </c>
       <c r="V87" t="n">
+        <v>21</v>
+      </c>
+      <c r="W87" t="n">
         <v>14</v>
       </c>
-      <c r="W87" t="n">
-        <v>9</v>
-      </c>
       <c r="X87" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y87" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="Z87" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Vejle Stadion</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Roms Hule 3, Vejle</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD87" t="n">
         <v>1</v>
       </c>
       <c r="AE87" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="AF87" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG87" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL87" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AN87" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AO87" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AU87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV87" t="n">
         <v>0</v>
@@ -41932,25 +41932,25 @@
         <v>0</v>
       </c>
       <c r="AX87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA87" t="n">
         <v>0</v>
       </c>
       <c r="BB87" t="n">
-        <v>3647</v>
+        <v>2526</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -41968,175 +41968,175 @@
         <v>1</v>
       </c>
       <c r="BJ87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL87" t="n">
         <v>4</v>
       </c>
       <c r="BM87" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS87" t="n">
         <v>3</v>
       </c>
-      <c r="BN87" t="n">
+      <c r="BT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN87" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR87" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
         <v>7</v>
       </c>
-      <c r="BO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV87" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW87" t="n">
+      <c r="CY87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ87" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA87" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC87" t="n">
         <v>64</v>
       </c>
-      <c r="BX87" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY87" t="n">
-        <v>153</v>
-      </c>
-      <c r="BZ87" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CA87" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB87" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR87" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS87" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU87" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV87" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX87" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY87" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ87" t="n">
-        <v>79</v>
-      </c>
-      <c r="DA87" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB87" t="n">
+      <c r="DD87" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE87" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI87" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ87" t="n">
         <v>57</v>
       </c>
-      <c r="DC87" t="n">
-        <v>79</v>
-      </c>
-      <c r="DD87" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE87" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF87" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DG87" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DH87" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI87" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DJ87" t="n">
+      <c r="DK87" t="n">
         <v>22</v>
       </c>
-      <c r="DK87" t="n">
-        <v>0</v>
-      </c>
       <c r="DL87" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="DN87" t="n">
-        <v>3.26</v>
+        <v>2.68</v>
       </c>
       <c r="DO87" t="n">
         <v>17</v>
@@ -42148,7 +42148,7 @@
         <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS87" t="b">
         <v>0</v>
@@ -42163,83 +42163,83 @@
         <v>0</v>
       </c>
       <c r="DW87" t="n">
-        <v>9.470000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DX87" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EB87" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EC87" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="ED87" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EE87" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EF87" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EG87" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EH87" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI87" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EJ87" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EK87" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr"/>
+      <c r="EK87" t="inlineStr"/>
       <c r="EL87" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EM87" t="inlineStr"/>
-      <c r="EN87" t="inlineStr"/>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EN87" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EO87" t="inlineStr"/>
       <c r="EP87" t="inlineStr"/>
     </row>
@@ -42259,143 +42259,143 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" t="n">
+        <v>6</v>
+      </c>
+      <c r="L88" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>6</v>
+      </c>
+      <c r="R88" t="n">
         <v>3</v>
       </c>
-      <c r="I88" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" t="n">
-        <v>8</v>
-      </c>
-      <c r="L88" t="n">
-        <v>9</v>
-      </c>
-      <c r="M88" t="n">
-        <v>2</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>2</v>
-      </c>
-      <c r="R88" t="n">
-        <v>6</v>
-      </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T88" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U88" t="n">
         <v>11</v>
       </c>
       <c r="V88" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W88" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X88" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y88" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="Z88" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>1</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="AF88" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG88" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL88" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AN88" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AP88" t="n">
         <v>1.82</v>
       </c>
-      <c r="AO88" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP88" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AQ88" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AU88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV88" t="n">
         <v>0</v>
@@ -42404,25 +42404,25 @@
         <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA88" t="n">
         <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>2526</v>
+        <v>3647</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
@@ -42440,22 +42440,22 @@
         <v>1</v>
       </c>
       <c r="BJ88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL88" t="n">
         <v>4</v>
       </c>
       <c r="BM88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN88" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP88" t="n">
         <v>1</v>
@@ -42467,7 +42467,7 @@
         <v>0</v>
       </c>
       <c r="BS88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT88" t="n">
         <v>0</v>
@@ -42476,25 +42476,25 @@
         <v>1</v>
       </c>
       <c r="BV88" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW88" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BX88" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="BY88" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="BZ88" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="CA88" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="CB88" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="CC88" t="n">
         <v>0</v>
@@ -42527,10 +42527,10 @@
         <v>0</v>
       </c>
       <c r="CM88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO88" t="n">
         <v>0</v>
@@ -42542,73 +42542,73 @@
         <v>1</v>
       </c>
       <c r="CR88" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="CS88" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
         <v>10</v>
       </c>
-      <c r="CT88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU88" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV88" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX88" t="n">
+      <c r="CY88" t="n">
         <v>7</v>
       </c>
-      <c r="CY88" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ88" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="DA88" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC88" t="n">
         <v>79</v>
       </c>
-      <c r="DB88" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC88" t="n">
-        <v>64</v>
-      </c>
       <c r="DD88" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="DF88" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="DG88" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DH88" t="n">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="DI88" t="n">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="DJ88" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="DK88" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="DL88" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="DM88" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="DN88" t="n">
-        <v>2.68</v>
+        <v>3.26</v>
       </c>
       <c r="DO88" t="n">
         <v>17</v>
@@ -42620,7 +42620,7 @@
         <v>1</v>
       </c>
       <c r="DR88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS88" t="b">
         <v>0</v>
@@ -42635,83 +42635,83 @@
         <v>0</v>
       </c>
       <c r="DW88" t="n">
-        <v>8.84</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DX88" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="ED88" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EE88" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG88" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EH88" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="EC88" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="ED88" t="inlineStr">
-        <is>
-          <t>3.84</t>
-        </is>
-      </c>
-      <c r="EE88" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EF88" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EG88" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="EH88" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EI88" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EJ88" t="inlineStr"/>
-      <c r="EK88" t="inlineStr"/>
+      <c r="EK88" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
       <c r="EL88" t="inlineStr">
         <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EM88" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EN88" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr"/>
+      <c r="EN88" t="inlineStr"/>
       <c r="EO88" t="inlineStr"/>
       <c r="EP88" t="inlineStr"/>
     </row>
@@ -46805,7 +46805,7 @@
         <v>1.38</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF97" t="n">
         <v>1.43</v>
@@ -47427,40 +47427,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K99" t="n">
         <v>6</v>
       </c>
       <c r="L99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M99" t="n">
         <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -47472,125 +47472,117 @@
         <v>4</v>
       </c>
       <c r="R99" t="n">
+        <v>3</v>
+      </c>
+      <c r="S99" t="n">
+        <v>7</v>
+      </c>
+      <c r="T99" t="n">
+        <v>7</v>
+      </c>
+      <c r="U99" t="n">
+        <v>11</v>
+      </c>
+      <c r="V99" t="n">
+        <v>10</v>
+      </c>
+      <c r="W99" t="n">
+        <v>14</v>
+      </c>
+      <c r="X99" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD99" t="n">
         <v>4</v>
-      </c>
-      <c r="S99" t="n">
-        <v>14</v>
-      </c>
-      <c r="T99" t="n">
-        <v>10</v>
-      </c>
-      <c r="U99" t="n">
-        <v>18</v>
-      </c>
-      <c r="V99" t="n">
-        <v>14</v>
-      </c>
-      <c r="W99" t="n">
-        <v>10</v>
-      </c>
-      <c r="X99" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>JYSK park</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>Ansvej 104, Silkeborg</t>
-        </is>
-      </c>
-      <c r="AC99" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>2</v>
       </c>
       <c r="AE99" t="n">
         <v>2.37</v>
       </c>
       <c r="AF99" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL99" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AN99" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AU99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
         <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY99" t="n">
         <v>0</v>
       </c>
       <c r="AZ99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB99" t="n">
-        <v>-1</v>
+        <v>2516</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47605,19 +47597,19 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BJ99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BM99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN99" t="n">
         <v>9</v>
@@ -47626,43 +47618,43 @@
         <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ99" t="n">
         <v>2</v>
       </c>
       <c r="BR99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BW99" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="BX99" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="BY99" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="CB99" t="n">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="CC99" t="n">
         <v>0</v>
@@ -47689,16 +47681,16 @@
         <v>1</v>
       </c>
       <c r="CK99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL99" t="n">
         <v>0</v>
       </c>
       <c r="CM99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO99" t="n">
         <v>0</v>
@@ -47710,82 +47702,82 @@
         <v>1</v>
       </c>
       <c r="CR99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
         <v>16</v>
       </c>
-      <c r="CS99" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
+      <c r="CV99" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY99" t="n">
         <v>12</v>
       </c>
-      <c r="CV99" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX99" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY99" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ99" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="DA99" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="DB99" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="DC99" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="DE99" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="DF99" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DG99" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DH99" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="DI99" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="DJ99" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="DK99" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="DN99" t="n">
-        <v>2.78</v>
+        <v>4.05</v>
       </c>
       <c r="DO99" t="n">
         <v>17</v>
       </c>
       <c r="DP99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR99" t="b">
         <v>0</v>
@@ -47803,10 +47795,10 @@
         <v>0</v>
       </c>
       <c r="DW99" t="n">
-        <v>6.66</v>
+        <v>6.46</v>
       </c>
       <c r="DX99" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
@@ -47820,82 +47812,82 @@
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EF99" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EI99" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EJ99" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM99" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN99" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EO99" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EP99" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -47915,40 +47907,40 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K100" t="n">
         <v>6</v>
       </c>
       <c r="L100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M100" t="n">
         <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -47960,117 +47952,125 @@
         <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U100" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V100" t="n">
+        <v>14</v>
+      </c>
+      <c r="W100" t="n">
         <v>10</v>
       </c>
-      <c r="W100" t="n">
-        <v>14</v>
-      </c>
       <c r="X100" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y100" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z100" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
       <c r="AC100" t="n">
         <v>2</v>
       </c>
       <c r="AD100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE100" t="n">
         <v>2.37</v>
       </c>
       <c r="AF100" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AJ100" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL100" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AN100" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AU100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW100" t="n">
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>2516</v>
+        <v>-1</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48085,19 +48085,19 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK100" t="n">
         <v>3</v>
       </c>
-      <c r="BJ100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK100" t="n">
-        <v>5</v>
-      </c>
       <c r="BL100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BM100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN100" t="n">
         <v>9</v>
@@ -48106,166 +48106,166 @@
         <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ100" t="n">
         <v>2</v>
       </c>
       <c r="BR100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BW100" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="BX100" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="BY100" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BZ100" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD100" t="n">
         <v>1.22</v>
       </c>
-      <c r="CA100" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CS100" t="n">
+      <c r="DE100" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ100" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK100" t="n">
         <v>19</v>
       </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV100" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ100" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA100" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB100" t="n">
-        <v>38</v>
-      </c>
-      <c r="DC100" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD100" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE100" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF100" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG100" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DH100" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DI100" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DJ100" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK100" t="n">
-        <v>25</v>
-      </c>
       <c r="DL100" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="DN100" t="n">
-        <v>4.05</v>
+        <v>2.78</v>
       </c>
       <c r="DO100" t="n">
         <v>17</v>
       </c>
       <c r="DP100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR100" t="b">
         <v>0</v>
@@ -48283,10 +48283,10 @@
         <v>0</v>
       </c>
       <c r="DW100" t="n">
-        <v>6.46</v>
+        <v>6.66</v>
       </c>
       <c r="DX100" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
@@ -48300,82 +48300,82 @@
       </c>
       <c r="EA100" t="inlineStr">
         <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="ED100" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ100" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="EB100" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EC100" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="ED100" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EE100" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EF100" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG100" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EI100" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EJ100" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EK100" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EM100" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EN100" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.38</t>
         </is>
       </c>
     </row>
@@ -49778,6 +49778,470 @@
       </c>
       <c r="EO103" t="inlineStr"/>
       <c r="EP103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>18</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>45996.75</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" t="n">
+        <v>4</v>
+      </c>
+      <c r="J104" t="n">
+        <v>7</v>
+      </c>
+      <c r="K104" t="n">
+        <v>6</v>
+      </c>
+      <c r="L104" t="n">
+        <v>13</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>3</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6</v>
+      </c>
+      <c r="S104" t="n">
+        <v>7</v>
+      </c>
+      <c r="T104" t="n">
+        <v>6</v>
+      </c>
+      <c r="U104" t="n">
+        <v>10</v>
+      </c>
+      <c r="V104" t="n">
+        <v>12</v>
+      </c>
+      <c r="W104" t="n">
+        <v>9</v>
+      </c>
+      <c r="X104" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>2523</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>65</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU104" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX104" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY104" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ104" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB104" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC104" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD104" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE104" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF104" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DG104" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH104" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DI104" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DJ104" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK104" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL104" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DM104" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN104" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO104" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW104" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="DX104" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="DZ104" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="EA104" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EC104" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="ED104" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="EE104" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EF104" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EG104" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EH104" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EJ104" t="inlineStr"/>
+      <c r="EK104" t="inlineStr"/>
+      <c r="EL104" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EM104" t="inlineStr"/>
+      <c r="EN104" t="inlineStr"/>
+      <c r="EO104" t="inlineStr"/>
+      <c r="EP104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP104" headerRowCount="1">
-  <autoFilter ref="A1:EP104"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP108" headerRowCount="1">
+  <autoFilter ref="A1:EP108"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP104"/>
+  <dimension ref="A1:EP108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE2" t="n">
         <v>1.67</v>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3229,7 +3229,7 @@
         <v>1.89</v>
       </c>
       <c r="DE5" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3731,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4165,7 +4165,7 @@
         <v>1.78</v>
       </c>
       <c r="DE7" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4659,7 +4659,7 @@
         <v>0.76</v>
       </c>
       <c r="DO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE9" t="n">
         <v>0.22</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE12" t="n">
         <v>1.88</v>
@@ -7005,7 +7005,7 @@
         <v>2.33</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF13" t="n">
         <v>1</v>
@@ -7035,7 +7035,7 @@
         <v>2.01</v>
       </c>
       <c r="DO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7507,7 +7507,7 @@
         <v>3.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8418,10 +8418,10 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE16" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8451,7 +8451,7 @@
         <v>0.91</v>
       </c>
       <c r="DO16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8931,7 +8931,7 @@
         <v>2.96</v>
       </c>
       <c r="DO17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9373,7 +9373,7 @@
         <v>2.11</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9403,7 +9403,7 @@
         <v>1.58</v>
       </c>
       <c r="DO18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP18" t="b">
         <v>0</v>
@@ -10314,10 +10314,10 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10347,7 +10347,7 @@
         <v>2.67</v>
       </c>
       <c r="DO20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10786,10 +10786,10 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10819,7 +10819,7 @@
         <v>3.19</v>
       </c>
       <c r="DO21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -11299,7 +11299,7 @@
         <v>3.1</v>
       </c>
       <c r="DO22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11771,7 +11771,7 @@
         <v>3.75</v>
       </c>
       <c r="DO23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12707,7 +12707,7 @@
         <v>2.63</v>
       </c>
       <c r="DO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13154,7 +13154,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE26" t="n">
         <v>1.67</v>
@@ -13187,7 +13187,7 @@
         <v>4.08</v>
       </c>
       <c r="DO26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13637,7 +13637,7 @@
         <v>0.78</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13667,7 +13667,7 @@
         <v>2.72</v>
       </c>
       <c r="DO27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14125,7 +14125,7 @@
         <v>1</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DF28" t="n">
         <v>2</v>
@@ -14594,10 +14594,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE29" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF29" t="n">
         <v>1.5</v>
@@ -14627,7 +14627,7 @@
         <v>2.35</v>
       </c>
       <c r="DO29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -15074,7 +15074,7 @@
         <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE30" t="n">
         <v>1.88</v>
@@ -15565,7 +15565,7 @@
         <v>1.56</v>
       </c>
       <c r="DE31" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15595,7 +15595,7 @@
         <v>2.43</v>
       </c>
       <c r="DO31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16042,7 +16042,7 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE32" t="n">
         <v>1.33</v>
@@ -16075,7 +16075,7 @@
         <v>2.68</v>
       </c>
       <c r="DO32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -16555,7 +16555,7 @@
         <v>2.55</v>
       </c>
       <c r="DO33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17005,7 +17005,7 @@
         <v>2.33</v>
       </c>
       <c r="DE34" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF34" t="n">
         <v>1.67</v>
@@ -17035,7 +17035,7 @@
         <v>3.63</v>
       </c>
       <c r="DO34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -18442,7 +18442,7 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE37" t="n">
         <v>1.22</v>
@@ -18475,7 +18475,7 @@
         <v>3.08</v>
       </c>
       <c r="DO37" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -19427,7 +19427,7 @@
         <v>3.29</v>
       </c>
       <c r="DO39" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19885,7 +19885,7 @@
         <v>1.22</v>
       </c>
       <c r="DE40" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF40" t="n">
         <v>1.5</v>
@@ -19915,7 +19915,7 @@
         <v>3.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20387,7 +20387,7 @@
         <v>3.25</v>
       </c>
       <c r="DO41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20818,7 +20818,7 @@
         <v>84</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE42" t="n">
         <v>1.67</v>
@@ -20851,7 +20851,7 @@
         <v>3.26</v>
       </c>
       <c r="DO42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -21309,7 +21309,7 @@
         <v>1.78</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -21811,7 +21811,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -22738,10 +22738,10 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE46" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22771,7 +22771,7 @@
         <v>2.56</v>
       </c>
       <c r="DO46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23210,10 +23210,10 @@
         <v>34</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -23243,7 +23243,7 @@
         <v>2.95</v>
       </c>
       <c r="DO47" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23723,7 +23723,7 @@
         <v>2.69</v>
       </c>
       <c r="DO48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -25127,7 +25127,7 @@
         <v>3.7</v>
       </c>
       <c r="DO51" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -25561,7 +25561,7 @@
         <v>1</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF52" t="n">
         <v>1</v>
@@ -26038,10 +26038,10 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE53" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF53" t="n">
         <v>1.33</v>
@@ -26071,7 +26071,7 @@
         <v>3.35</v>
       </c>
       <c r="DO53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -26990,7 +26990,7 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE55" t="n">
         <v>1</v>
@@ -27023,7 +27023,7 @@
         <v>2.73</v>
       </c>
       <c r="DO55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27495,7 +27495,7 @@
         <v>2.8</v>
       </c>
       <c r="DO56" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27922,7 +27922,7 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE57" t="n">
         <v>0.78</v>
@@ -27955,7 +27955,7 @@
         <v>2.67</v>
       </c>
       <c r="DO57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -28874,10 +28874,10 @@
         <v>88</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE59" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF59" t="n">
         <v>1.5</v>
@@ -28907,7 +28907,7 @@
         <v>2.98</v>
       </c>
       <c r="DO59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -29843,7 +29843,7 @@
         <v>3.65</v>
       </c>
       <c r="DO61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -30273,7 +30273,7 @@
         <v>1.56</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF62" t="n">
         <v>1.8</v>
@@ -30303,7 +30303,7 @@
         <v>3.02</v>
       </c>
       <c r="DO62" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30423,22 +30423,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -30447,16 +30447,16 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -30465,120 +30465,128 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V63" t="n">
         <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X63" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y63" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z63" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AF63" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AN63" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AU63" t="n">
         <v>3</v>
       </c>
       <c r="AV63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX63" t="n">
         <v>0</v>
       </c>
       <c r="AY63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB63" t="n">
-        <v>2521</v>
+        <v>986</v>
       </c>
       <c r="BC63" t="n">
         <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="BE63" t="n">
         <v>0</v>
@@ -30593,178 +30601,178 @@
         <v>1</v>
       </c>
       <c r="BI63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK63" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU63" t="n">
         <v>3</v>
       </c>
-      <c r="BL63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV63" t="n">
-        <v>53</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>63</v>
-      </c>
-      <c r="BX63" t="n">
-        <v>84</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ63" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CA63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CB63" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM63" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS63" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU63" t="n">
-        <v>12</v>
-      </c>
       <c r="CV63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW63" t="n">
         <v>1</v>
       </c>
       <c r="CX63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ63" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA63" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DB63" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="DC63" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="DF63" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG63" t="n">
         <v>1.2</v>
       </c>
       <c r="DH63" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="DI63" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ63" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK63" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="DL63" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="DM63" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="DN63" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="DO63" t="n">
         <v>17</v>
@@ -30788,86 +30796,102 @@
         <v>0</v>
       </c>
       <c r="DV63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW63" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="DX63" t="n">
-        <v>9.65</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY63" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ63" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA63" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EB63" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EC63" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="ED63" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EE63" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EF63" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG63" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EH63" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EI63" t="inlineStr"/>
-      <c r="EJ63" t="inlineStr"/>
-      <c r="EK63" t="inlineStr"/>
-      <c r="EL63" t="inlineStr"/>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI63" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EJ63" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK63" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EL63" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EM63" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EN63" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EO63" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP63" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.34</t>
         </is>
       </c>
     </row>
@@ -30887,22 +30911,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>3</v>
@@ -30911,16 +30935,16 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -30929,128 +30953,120 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V64" t="n">
         <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y64" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z64" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE64" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF64" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL64" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AM64" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AN64" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AO64" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AS64" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AU64" t="n">
         <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX64" t="n">
         <v>0</v>
       </c>
       <c r="AY64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB64" t="n">
-        <v>986</v>
+        <v>2521</v>
       </c>
       <c r="BC64" t="n">
         <v>0</v>
       </c>
       <c r="BD64" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="BE64" t="n">
         <v>0</v>
@@ -31065,37 +31081,37 @@
         <v>1</v>
       </c>
       <c r="BI64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL64" t="n">
         <v>2</v>
       </c>
       <c r="BM64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN64" t="n">
         <v>5</v>
       </c>
-      <c r="BN64" t="n">
-        <v>6</v>
-      </c>
       <c r="BO64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP64" t="n">
         <v>0</v>
       </c>
       <c r="BQ64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT64" t="n">
         <v>2</v>
@@ -31104,25 +31120,25 @@
         <v>1</v>
       </c>
       <c r="BV64" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BW64" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="BX64" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BY64" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="BZ64" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="CB64" t="n">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="CC64" t="n">
         <v>0</v>
@@ -31155,7 +31171,7 @@
         <v>0</v>
       </c>
       <c r="CM64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
@@ -31170,76 +31186,76 @@
         <v>1</v>
       </c>
       <c r="CR64" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CS64" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT64" t="n">
         <v>1</v>
       </c>
       <c r="CU64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CV64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW64" t="n">
         <v>1</v>
       </c>
       <c r="CX64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ64" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="DA64" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DB64" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="DC64" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="DD64" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE64" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF64" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DG64" t="n">
         <v>1.2</v>
       </c>
       <c r="DH64" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="DI64" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ64" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK64" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="DL64" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="DM64" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="DN64" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="DO64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -31260,102 +31276,86 @@
         <v>0</v>
       </c>
       <c r="DV64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW64" t="n">
-        <v>12.5</v>
+        <v>13.33</v>
       </c>
       <c r="DX64" t="n">
-        <v>9.859999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="DY64" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ64" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="EA64" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB64" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC64" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="ED64" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EE64" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EF64" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG64" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EH64" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EI64" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EJ64" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EK64" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EL64" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI64" t="inlineStr"/>
+      <c r="EJ64" t="inlineStr"/>
+      <c r="EK64" t="inlineStr"/>
+      <c r="EL64" t="inlineStr"/>
       <c r="EM64" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EN64" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EO64" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP64" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -31689,7 +31689,7 @@
         <v>2.11</v>
       </c>
       <c r="DE65" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF65" t="n">
         <v>2</v>
@@ -31719,7 +31719,7 @@
         <v>3.44</v>
       </c>
       <c r="DO65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32158,10 +32158,10 @@
         <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DF66" t="n">
         <v>1.25</v>
@@ -32191,7 +32191,7 @@
         <v>3.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33143,7 +33143,7 @@
         <v>3.16</v>
       </c>
       <c r="DO68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33263,12 +33263,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -33278,25 +33278,25 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
+        <v>9</v>
+      </c>
+      <c r="K69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" t="n">
-        <v>3</v>
-      </c>
       <c r="L69" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -33305,102 +33305,102 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T69" t="n">
         <v>10</v>
       </c>
       <c r="U69" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V69" t="n">
+        <v>18</v>
+      </c>
+      <c r="W69" t="n">
+        <v>6</v>
+      </c>
+      <c r="X69" t="n">
         <v>13</v>
       </c>
-      <c r="W69" t="n">
-        <v>10</v>
-      </c>
-      <c r="X69" t="n">
-        <v>11</v>
-      </c>
       <c r="Y69" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="Z69" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU69" t="n">
         <v>3</v>
       </c>
-      <c r="AD69" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN69" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO69" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP69" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ69" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU69" t="n">
-        <v>1</v>
-      </c>
       <c r="AV69" t="n">
         <v>1</v>
       </c>
@@ -33411,22 +33411,22 @@
         <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA69" t="n">
         <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>986</v>
+        <v>2523</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="BE69" t="n">
         <v>0</v>
@@ -33435,46 +33435,46 @@
         <v>-1</v>
       </c>
       <c r="BG69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH69" t="n">
         <v>1</v>
       </c>
       <c r="BI69" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BJ69" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK69" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM69" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BN69" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR69" t="n">
         <v>1</v>
       </c>
       <c r="BS69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
@@ -33483,148 +33483,148 @@
         <v>17</v>
       </c>
       <c r="BW69" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BX69" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>40</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR69" t="n">
         <v>35</v>
       </c>
-      <c r="BY69" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ69" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB69" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>16</v>
-      </c>
       <c r="CS69" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU69" t="n">
         <v>14</v>
       </c>
-      <c r="CT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU69" t="n">
-        <v>12</v>
-      </c>
       <c r="CV69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW69" t="n">
         <v>1</v>
       </c>
       <c r="CX69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CY69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ69" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA69" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="DB69" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="DC69" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="DF69" t="n">
         <v>1.2</v>
       </c>
       <c r="DG69" t="n">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="DH69" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="DI69" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="DJ69" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK69" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="DL69" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="DN69" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="DO69" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
       </c>
       <c r="DQ69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS69" t="b">
         <v>0</v>
@@ -33636,62 +33636,62 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW69" t="n">
-        <v>9.83</v>
+        <v>9.23</v>
       </c>
       <c r="DX69" t="n">
-        <v>5.78</v>
+        <v>6.84</v>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ69" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA69" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EB69" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC69" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="ED69" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EE69" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EF69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EG69" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EH69" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EI69" t="inlineStr"/>
@@ -33700,12 +33700,12 @@
       <c r="EL69" t="inlineStr"/>
       <c r="EM69" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EN69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EO69" t="inlineStr"/>
@@ -33727,12 +33727,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -33742,25 +33742,25 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" t="n">
         <v>3</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>9</v>
       </c>
-      <c r="K70" t="n">
-        <v>6</v>
-      </c>
-      <c r="L70" t="n">
-        <v>15</v>
-      </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -33769,101 +33769,101 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R70" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="n">
         <v>10</v>
       </c>
       <c r="U70" t="n">
+        <v>14</v>
+      </c>
+      <c r="V70" t="n">
+        <v>13</v>
+      </c>
+      <c r="W70" t="n">
         <v>10</v>
       </c>
-      <c r="V70" t="n">
-        <v>18</v>
-      </c>
-      <c r="W70" t="n">
-        <v>6</v>
-      </c>
       <c r="X70" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y70" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="Z70" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AK70" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL70" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AM70" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN70" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AO70" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AS70" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AU70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV70" t="n">
         <v>1</v>
@@ -33875,22 +33875,22 @@
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
       </c>
       <c r="BB70" t="n">
-        <v>2523</v>
+        <v>986</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -33899,46 +33899,46 @@
         <v>-1</v>
       </c>
       <c r="BG70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH70" t="n">
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BJ70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM70" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BN70" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR70" t="n">
         <v>1</v>
       </c>
       <c r="BS70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU70" t="n">
         <v>1</v>
@@ -33947,148 +33947,148 @@
         <v>17</v>
       </c>
       <c r="BW70" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BX70" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BY70" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BZ70" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR70" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS70" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU70" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV70" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY70" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ70" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB70" t="n">
+        <v>9</v>
+      </c>
+      <c r="DC70" t="n">
+        <v>55</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE70" t="n">
         <v>0.89</v>
-      </c>
-      <c r="CA70" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CB70" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM70" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN70" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>35</v>
-      </c>
-      <c r="CS70" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU70" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV70" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX70" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY70" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ70" t="n">
-        <v>80</v>
-      </c>
-      <c r="DA70" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB70" t="n">
-        <v>80</v>
-      </c>
-      <c r="DC70" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD70" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE70" t="n">
-        <v>1.33</v>
       </c>
       <c r="DF70" t="n">
         <v>1.2</v>
       </c>
       <c r="DG70" t="n">
-        <v>0.4</v>
+        <v>1.17</v>
       </c>
       <c r="DH70" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="DI70" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="DJ70" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK70" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="DL70" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="DM70" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="DN70" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="DO70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
       </c>
       <c r="DQ70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS70" t="b">
         <v>0</v>
@@ -34100,62 +34100,62 @@
         <v>0</v>
       </c>
       <c r="DV70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW70" t="n">
-        <v>9.23</v>
+        <v>9.83</v>
       </c>
       <c r="DX70" t="n">
-        <v>6.84</v>
+        <v>5.78</v>
       </c>
       <c r="DY70" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ70" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="EA70" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EB70" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC70" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="ED70" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EE70" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EF70" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="EC70" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="ED70" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="EE70" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EF70" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EG70" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EH70" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI70" t="inlineStr"/>
@@ -34164,12 +34164,12 @@
       <c r="EL70" t="inlineStr"/>
       <c r="EM70" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EN70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EO70" t="inlineStr"/>
@@ -34513,7 +34513,7 @@
         <v>1.78</v>
       </c>
       <c r="DE71" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF71" t="n">
         <v>2</v>
@@ -35495,7 +35495,7 @@
         <v>2.18</v>
       </c>
       <c r="DO73" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -35943,7 +35943,7 @@
         <v>3.72</v>
       </c>
       <c r="DO74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -36393,7 +36393,7 @@
         <v>0.78</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DF75" t="n">
         <v>1.17</v>
@@ -36423,7 +36423,7 @@
         <v>2.51</v>
       </c>
       <c r="DO75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -36865,7 +36865,7 @@
         <v>1</v>
       </c>
       <c r="DE76" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF76" t="n">
         <v>0.83</v>
@@ -37326,10 +37326,10 @@
         <v>74</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF77" t="n">
         <v>1.8</v>
@@ -37359,7 +37359,7 @@
         <v>2.73</v>
       </c>
       <c r="DO77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -37798,7 +37798,7 @@
         <v>92</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE78" t="n">
         <v>1.22</v>
@@ -37831,7 +37831,7 @@
         <v>3.31</v>
       </c>
       <c r="DO78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP78" t="b">
         <v>0</v>
@@ -38774,7 +38774,7 @@
         <v>92</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE80" t="n">
         <v>0.78</v>
@@ -38807,7 +38807,7 @@
         <v>3.11</v>
       </c>
       <c r="DO80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39254,7 +39254,7 @@
         <v>79</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE81" t="n">
         <v>0.89</v>
@@ -39287,7 +39287,7 @@
         <v>2.66</v>
       </c>
       <c r="DO81" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40194,7 +40194,7 @@
         <v>84</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE83" t="n">
         <v>1.33</v>
@@ -40227,7 +40227,7 @@
         <v>2.73</v>
       </c>
       <c r="DO83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -41157,7 +41157,7 @@
         <v>2.33</v>
       </c>
       <c r="DE85" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF85" t="n">
         <v>2.43</v>
@@ -41187,7 +41187,7 @@
         <v>3.51</v>
       </c>
       <c r="DO85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41629,7 +41629,7 @@
         <v>1.56</v>
       </c>
       <c r="DE86" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF86" t="n">
         <v>1.43</v>
@@ -41659,7 +41659,7 @@
         <v>2.75</v>
       </c>
       <c r="DO86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41787,143 +41787,143 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>6</v>
+      </c>
+      <c r="R87" t="n">
         <v>3</v>
       </c>
-      <c r="I87" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>8</v>
-      </c>
-      <c r="L87" t="n">
-        <v>9</v>
-      </c>
-      <c r="M87" t="n">
-        <v>2</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>2</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6</v>
-      </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T87" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U87" t="n">
         <v>11</v>
       </c>
       <c r="V87" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W87" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X87" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y87" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="Z87" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>1</v>
       </c>
       <c r="AE87" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="AF87" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG87" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL87" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AN87" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AP87" t="n">
         <v>1.82</v>
       </c>
-      <c r="AO87" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP87" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AQ87" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
         <v>0</v>
@@ -41932,25 +41932,25 @@
         <v>0</v>
       </c>
       <c r="AX87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA87" t="n">
         <v>0</v>
       </c>
       <c r="BB87" t="n">
-        <v>2526</v>
+        <v>3647</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -41968,22 +41968,22 @@
         <v>1</v>
       </c>
       <c r="BJ87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL87" t="n">
         <v>4</v>
       </c>
       <c r="BM87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN87" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP87" t="n">
         <v>1</v>
@@ -41995,7 +41995,7 @@
         <v>0</v>
       </c>
       <c r="BS87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT87" t="n">
         <v>0</v>
@@ -42004,25 +42004,25 @@
         <v>1</v>
       </c>
       <c r="BV87" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW87" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BX87" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="BY87" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="BZ87" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="CA87" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="CB87" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="CC87" t="n">
         <v>0</v>
@@ -42055,10 +42055,10 @@
         <v>0</v>
       </c>
       <c r="CM87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO87" t="n">
         <v>0</v>
@@ -42070,73 +42070,73 @@
         <v>1</v>
       </c>
       <c r="CR87" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="CS87" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
         <v>10</v>
       </c>
-      <c r="CT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU87" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV87" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX87" t="n">
+      <c r="CY87" t="n">
         <v>7</v>
       </c>
-      <c r="CY87" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ87" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="DA87" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC87" t="n">
         <v>79</v>
       </c>
-      <c r="DB87" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC87" t="n">
-        <v>64</v>
-      </c>
       <c r="DD87" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="DF87" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="DG87" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DH87" t="n">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="DI87" t="n">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="DJ87" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="DK87" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="DL87" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="DN87" t="n">
-        <v>2.68</v>
+        <v>3.26</v>
       </c>
       <c r="DO87" t="n">
         <v>17</v>
@@ -42148,7 +42148,7 @@
         <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS87" t="b">
         <v>0</v>
@@ -42163,83 +42163,83 @@
         <v>0</v>
       </c>
       <c r="DW87" t="n">
-        <v>8.84</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DX87" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EB87" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="EH87" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="EC87" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="ED87" t="inlineStr">
-        <is>
-          <t>3.84</t>
-        </is>
-      </c>
-      <c r="EE87" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EF87" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EG87" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="EH87" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EI87" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EJ87" t="inlineStr"/>
-      <c r="EK87" t="inlineStr"/>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
       <c r="EL87" t="inlineStr">
         <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EM87" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EN87" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr"/>
+      <c r="EN87" t="inlineStr"/>
       <c r="EO87" t="inlineStr"/>
       <c r="EP87" t="inlineStr"/>
     </row>
@@ -42259,143 +42259,143 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
+        <v>8</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2</v>
+      </c>
+      <c r="R88" t="n">
         <v>6</v>
       </c>
-      <c r="L88" t="n">
-        <v>10</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>6</v>
-      </c>
-      <c r="R88" t="n">
-        <v>3</v>
-      </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T88" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U88" t="n">
         <v>11</v>
       </c>
       <c r="V88" t="n">
+        <v>21</v>
+      </c>
+      <c r="W88" t="n">
         <v>14</v>
       </c>
-      <c r="W88" t="n">
-        <v>9</v>
-      </c>
       <c r="X88" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y88" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="Z88" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Vejle Stadion</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Roms Hule 3, Vejle</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD88" t="n">
         <v>1</v>
       </c>
       <c r="AE88" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="AF88" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AO88" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AU88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV88" t="n">
         <v>0</v>
@@ -42404,25 +42404,25 @@
         <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA88" t="n">
         <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>3647</v>
+        <v>2526</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
@@ -42440,178 +42440,178 @@
         <v>1</v>
       </c>
       <c r="BJ88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL88" t="n">
         <v>4</v>
       </c>
       <c r="BM88" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS88" t="n">
         <v>3</v>
       </c>
-      <c r="BN88" t="n">
+      <c r="BT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN88" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR88" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS88" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
         <v>7</v>
       </c>
-      <c r="BO88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV88" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW88" t="n">
+      <c r="CY88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ88" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA88" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC88" t="n">
         <v>64</v>
       </c>
-      <c r="BX88" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY88" t="n">
-        <v>153</v>
-      </c>
-      <c r="BZ88" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CA88" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB88" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CC88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR88" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS88" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU88" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV88" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX88" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY88" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ88" t="n">
-        <v>79</v>
-      </c>
-      <c r="DA88" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB88" t="n">
+      <c r="DD88" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE88" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF88" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI88" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ88" t="n">
         <v>57</v>
       </c>
-      <c r="DC88" t="n">
-        <v>79</v>
-      </c>
-      <c r="DD88" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE88" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF88" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DG88" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DH88" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI88" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DJ88" t="n">
+      <c r="DK88" t="n">
         <v>22</v>
       </c>
-      <c r="DK88" t="n">
-        <v>0</v>
-      </c>
       <c r="DL88" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="DM88" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="DN88" t="n">
-        <v>3.26</v>
+        <v>2.68</v>
       </c>
       <c r="DO88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -42620,7 +42620,7 @@
         <v>1</v>
       </c>
       <c r="DR88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS88" t="b">
         <v>0</v>
@@ -42635,83 +42635,83 @@
         <v>0</v>
       </c>
       <c r="DW88" t="n">
-        <v>9.470000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="DX88" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EC88" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="ED88" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EE88" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EF88" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EG88" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EH88" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EI88" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EJ88" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EK88" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr"/>
+      <c r="EK88" t="inlineStr"/>
       <c r="EL88" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EM88" t="inlineStr"/>
-      <c r="EN88" t="inlineStr"/>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EN88" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EO88" t="inlineStr"/>
       <c r="EP88" t="inlineStr"/>
     </row>
@@ -43042,10 +43042,10 @@
         <v>59</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DF89" t="n">
         <v>1.67</v>
@@ -43075,7 +43075,7 @@
         <v>2.65</v>
       </c>
       <c r="DO89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -43501,7 +43501,7 @@
         <v>2.11</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="DF90" t="n">
         <v>2.29</v>
@@ -43531,7 +43531,7 @@
         <v>3.62</v>
       </c>
       <c r="DO90" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -44437,7 +44437,7 @@
         <v>1.22</v>
       </c>
       <c r="DE92" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DF92" t="n">
         <v>1.43</v>
@@ -44467,7 +44467,7 @@
         <v>2.83</v>
       </c>
       <c r="DO92" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -44906,7 +44906,7 @@
         <v>79</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="DE93" t="n">
         <v>1.88</v>
@@ -45394,7 +45394,7 @@
         <v>93</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DE94" t="n">
         <v>0.22</v>
@@ -45866,7 +45866,7 @@
         <v>86</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE95" t="n">
         <v>0.78</v>
@@ -45899,7 +45899,7 @@
         <v>2.79</v>
       </c>
       <c r="DO95" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -46349,7 +46349,7 @@
         <v>1.89</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DF96" t="n">
         <v>1.86</v>
@@ -46379,7 +46379,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -46802,7 +46802,7 @@
         <v>79</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE97" t="n">
         <v>1.33</v>
@@ -46835,7 +46835,7 @@
         <v>2.56</v>
       </c>
       <c r="DO97" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -47299,7 +47299,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -47427,40 +47427,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K99" t="n">
         <v>6</v>
       </c>
       <c r="L99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M99" t="n">
         <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -47472,117 +47472,125 @@
         <v>4</v>
       </c>
       <c r="R99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U99" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V99" t="n">
+        <v>14</v>
+      </c>
+      <c r="W99" t="n">
         <v>10</v>
       </c>
-      <c r="W99" t="n">
-        <v>14</v>
-      </c>
       <c r="X99" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y99" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z99" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
       <c r="AC99" t="n">
         <v>2</v>
       </c>
       <c r="AD99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE99" t="n">
         <v>2.37</v>
       </c>
       <c r="AF99" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL99" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AN99" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AU99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW99" t="n">
         <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
         <v>0</v>
       </c>
       <c r="AZ99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>2516</v>
+        <v>-1</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47597,19 +47605,19 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK99" t="n">
         <v>3</v>
       </c>
-      <c r="BJ99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK99" t="n">
-        <v>5</v>
-      </c>
       <c r="BL99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BM99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN99" t="n">
         <v>9</v>
@@ -47618,166 +47626,166 @@
         <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ99" t="n">
         <v>2</v>
       </c>
       <c r="BR99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BW99" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="BX99" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="BY99" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BZ99" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR99" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV99" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD99" t="n">
         <v>1.22</v>
       </c>
-      <c r="CA99" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="CB99" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CC99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN99" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP99" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>12</v>
-      </c>
-      <c r="CS99" t="n">
+      <c r="DE99" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK99" t="n">
         <v>19</v>
       </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV99" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX99" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY99" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ99" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA99" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB99" t="n">
-        <v>38</v>
-      </c>
-      <c r="DC99" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD99" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE99" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF99" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG99" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DH99" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DI99" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DJ99" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK99" t="n">
-        <v>25</v>
-      </c>
       <c r="DL99" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="DN99" t="n">
-        <v>4.05</v>
+        <v>2.78</v>
       </c>
       <c r="DO99" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR99" t="b">
         <v>0</v>
@@ -47795,10 +47803,10 @@
         <v>0</v>
       </c>
       <c r="DW99" t="n">
-        <v>6.46</v>
+        <v>6.66</v>
       </c>
       <c r="DX99" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
@@ -47812,82 +47820,82 @@
       </c>
       <c r="EA99" t="inlineStr">
         <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG99" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="EB99" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EC99" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="ED99" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EE99" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EF99" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG99" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="EH99" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EI99" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EJ99" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EK99" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EM99" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EN99" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EO99" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP99" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.38</t>
         </is>
       </c>
     </row>
@@ -47907,40 +47915,40 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K100" t="n">
         <v>6</v>
       </c>
       <c r="L100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M100" t="n">
         <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -47952,125 +47960,117 @@
         <v>4</v>
       </c>
       <c r="R100" t="n">
+        <v>3</v>
+      </c>
+      <c r="S100" t="n">
+        <v>7</v>
+      </c>
+      <c r="T100" t="n">
+        <v>7</v>
+      </c>
+      <c r="U100" t="n">
+        <v>11</v>
+      </c>
+      <c r="V100" t="n">
+        <v>10</v>
+      </c>
+      <c r="W100" t="n">
+        <v>14</v>
+      </c>
+      <c r="X100" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD100" t="n">
         <v>4</v>
-      </c>
-      <c r="S100" t="n">
-        <v>14</v>
-      </c>
-      <c r="T100" t="n">
-        <v>10</v>
-      </c>
-      <c r="U100" t="n">
-        <v>18</v>
-      </c>
-      <c r="V100" t="n">
-        <v>14</v>
-      </c>
-      <c r="W100" t="n">
-        <v>10</v>
-      </c>
-      <c r="X100" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>JYSK park</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>Ansvej 104, Silkeborg</t>
-        </is>
-      </c>
-      <c r="AC100" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>2</v>
       </c>
       <c r="AE100" t="n">
         <v>2.37</v>
       </c>
       <c r="AF100" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AJ100" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL100" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW100" t="n">
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB100" t="n">
-        <v>-1</v>
+        <v>2516</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48085,19 +48085,19 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BJ100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BM100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN100" t="n">
         <v>9</v>
@@ -48106,43 +48106,43 @@
         <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ100" t="n">
         <v>2</v>
       </c>
       <c r="BR100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BW100" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="BX100" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="BY100" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BZ100" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="CB100" t="n">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="CC100" t="n">
         <v>0</v>
@@ -48169,16 +48169,16 @@
         <v>1</v>
       </c>
       <c r="CK100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL100" t="n">
         <v>0</v>
       </c>
       <c r="CM100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO100" t="n">
         <v>0</v>
@@ -48190,82 +48190,82 @@
         <v>1</v>
       </c>
       <c r="CR100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
         <v>16</v>
       </c>
-      <c r="CS100" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
+      <c r="CV100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY100" t="n">
         <v>12</v>
       </c>
-      <c r="CV100" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY100" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ100" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="DA100" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="DB100" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="DC100" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="DF100" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DG100" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DH100" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="DI100" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="DJ100" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="DK100" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="DN100" t="n">
-        <v>2.78</v>
+        <v>4.05</v>
       </c>
       <c r="DO100" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR100" t="b">
         <v>0</v>
@@ -48283,10 +48283,10 @@
         <v>0</v>
       </c>
       <c r="DW100" t="n">
-        <v>6.66</v>
+        <v>6.46</v>
       </c>
       <c r="DX100" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
@@ -48300,82 +48300,82 @@
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC100" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="ED100" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EE100" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EF100" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EK100" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM100" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN100" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -48747,7 +48747,7 @@
         <v>3.44</v>
       </c>
       <c r="DO101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -50242,6 +50242,1894 @@
       <c r="EN104" t="inlineStr"/>
       <c r="EO104" t="inlineStr"/>
       <c r="EP104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>18</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Nordsjælland</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>45998.54166666666</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>7</v>
+      </c>
+      <c r="K105" t="n">
+        <v>4</v>
+      </c>
+      <c r="L105" t="n">
+        <v>11</v>
+      </c>
+      <c r="M105" t="n">
+        <v>4</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>10</v>
+      </c>
+      <c r="R105" t="n">
+        <v>3</v>
+      </c>
+      <c r="S105" t="n">
+        <v>7</v>
+      </c>
+      <c r="T105" t="n">
+        <v>9</v>
+      </c>
+      <c r="U105" t="n">
+        <v>17</v>
+      </c>
+      <c r="V105" t="n">
+        <v>12</v>
+      </c>
+      <c r="W105" t="n">
+        <v>11</v>
+      </c>
+      <c r="X105" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Right to Dream Park</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>Idrætsvænget 2, Farum</t>
+        </is>
+      </c>
+      <c r="AC105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>986</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI105" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>82</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY105" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ105" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA105" t="n">
+        <v>69</v>
+      </c>
+      <c r="DB105" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC105" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD105" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE105" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF105" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG105" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH105" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DI105" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DJ105" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK105" t="n">
+        <v>32</v>
+      </c>
+      <c r="DL105" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DM105" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN105" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="DO105" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT105" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV105" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW105" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="DX105" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="DY105" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="DZ105" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA105" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EB105" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC105" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="ED105" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="EE105" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EG105" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EH105" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EI105" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EJ105" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK105" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EL105" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EM105" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EN105" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EO105" t="inlineStr"/>
+      <c r="EP105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>18</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Viborg</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>45998.54166666666</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>6</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2</v>
+      </c>
+      <c r="K106" t="n">
+        <v>9</v>
+      </c>
+      <c r="L106" t="n">
+        <v>11</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2</v>
+      </c>
+      <c r="N106" t="n">
+        <v>4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>3</v>
+      </c>
+      <c r="R106" t="n">
+        <v>5</v>
+      </c>
+      <c r="S106" t="n">
+        <v>7</v>
+      </c>
+      <c r="T106" t="n">
+        <v>14</v>
+      </c>
+      <c r="U106" t="n">
+        <v>10</v>
+      </c>
+      <c r="V106" t="n">
+        <v>19</v>
+      </c>
+      <c r="W106" t="n">
+        <v>16</v>
+      </c>
+      <c r="X106" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>Energi Viborg Arena</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>Stadion Allé 7, Viborg</t>
+        </is>
+      </c>
+      <c r="AC106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL106" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN106" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>64</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>69</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>93</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>2</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR106" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS106" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU106" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV106" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX106" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY106" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ106" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA106" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB106" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC106" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD106" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE106" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF106" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG106" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH106" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DI106" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DJ106" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK106" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL106" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DM106" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="DN106" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DO106" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV106" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW106" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="DX106" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="DY106" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="DZ106" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA106" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EB106" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EC106" t="inlineStr">
+        <is>
+          <t>5.32</t>
+        </is>
+      </c>
+      <c r="ED106" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="EE106" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EG106" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EH106" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EI106" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EJ106" t="inlineStr"/>
+      <c r="EK106" t="inlineStr"/>
+      <c r="EL106" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EM106" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EN106" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EO106" t="inlineStr"/>
+      <c r="EP106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>18</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>45998.625</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3</v>
+      </c>
+      <c r="J107" t="n">
+        <v>3</v>
+      </c>
+      <c r="K107" t="n">
+        <v>4</v>
+      </c>
+      <c r="L107" t="n">
+        <v>7</v>
+      </c>
+      <c r="M107" t="n">
+        <v>3</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>4</v>
+      </c>
+      <c r="R107" t="n">
+        <v>5</v>
+      </c>
+      <c r="S107" t="n">
+        <v>11</v>
+      </c>
+      <c r="T107" t="n">
+        <v>7</v>
+      </c>
+      <c r="U107" t="n">
+        <v>15</v>
+      </c>
+      <c r="V107" t="n">
+        <v>12</v>
+      </c>
+      <c r="W107" t="n">
+        <v>17</v>
+      </c>
+      <c r="X107" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>2516</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM107" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN107" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT107" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV107" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW107" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX107" t="n">
+        <v>114</v>
+      </c>
+      <c r="BY107" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ107" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CA107" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CB107" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR107" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS107" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU107" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV107" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX107" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY107" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ107" t="n">
+        <v>51</v>
+      </c>
+      <c r="DA107" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB107" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC107" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD107" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE107" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DF107" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG107" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH107" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DI107" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DJ107" t="n">
+        <v>51</v>
+      </c>
+      <c r="DK107" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL107" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DM107" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN107" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO107" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU107" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV107" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW107" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="DX107" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="DY107" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="DZ107" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA107" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="EB107" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EC107" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="ED107" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EE107" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EF107" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG107" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EH107" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EI107" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EJ107" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK107" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EL107" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EM107" t="inlineStr"/>
+      <c r="EN107" t="inlineStr"/>
+      <c r="EO107" t="inlineStr"/>
+      <c r="EP107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>18</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>SønderjyskE</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>45998.70833333334</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" t="n">
+        <v>8</v>
+      </c>
+      <c r="K108" t="n">
+        <v>4</v>
+      </c>
+      <c r="L108" t="n">
+        <v>12</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>2</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>5</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="n">
+        <v>3</v>
+      </c>
+      <c r="U108" t="n">
+        <v>20</v>
+      </c>
+      <c r="V108" t="n">
+        <v>9</v>
+      </c>
+      <c r="W108" t="n">
+        <v>8</v>
+      </c>
+      <c r="X108" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Parken</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>Øster Allé 50, København</t>
+        </is>
+      </c>
+      <c r="AC108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>2519</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ108" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK108" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM108" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN108" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>57</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>151</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV108" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY108" t="n">
+        <v>15</v>
+      </c>
+      <c r="CZ108" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA108" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB108" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC108" t="n">
+        <v>69</v>
+      </c>
+      <c r="DD108" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE108" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DG108" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DH108" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DI108" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DJ108" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL108" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="DM108" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN108" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DO108" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ108" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV108" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW108" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="DX108" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="DY108" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="DZ108" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC108" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="ED108" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="EE108" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="EF108" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EH108" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr"/>
+      <c r="EJ108" t="inlineStr"/>
+      <c r="EK108" t="inlineStr"/>
+      <c r="EL108" t="inlineStr"/>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EO108" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EP108" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP108" headerRowCount="1">
-  <autoFilter ref="A1:EP108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP109" headerRowCount="1">
+  <autoFilter ref="A1:EP109"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP108"/>
+  <dimension ref="A1:EP109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE4" t="n">
         <v>0.89</v>
@@ -2787,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -6533,7 +6533,7 @@
         <v>1.67</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6563,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="DD15" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE15" t="n">
         <v>1.33</v>
@@ -7987,7 +7987,7 @@
         <v>2.69</v>
       </c>
       <c r="DO15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -9883,7 +9883,7 @@
         <v>3.11</v>
       </c>
       <c r="DO19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -12235,7 +12235,7 @@
         <v>2.85</v>
       </c>
       <c r="DO24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -14122,7 +14122,7 @@
         <v>25</v>
       </c>
       <c r="DD28" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE28" t="n">
         <v>1.67</v>
@@ -14155,7 +14155,7 @@
         <v>1.98</v>
       </c>
       <c r="DO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -15077,7 +15077,7 @@
         <v>1.22</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -15107,7 +15107,7 @@
         <v>1.96</v>
       </c>
       <c r="DO30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -16203,70 +16203,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>21</v>
+      </c>
+      <c r="V33" t="n">
         <v>11</v>
       </c>
-      <c r="L33" t="n">
-        <v>14</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>15</v>
-      </c>
-      <c r="U33" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>18</v>
-      </c>
       <c r="W33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -16276,97 +16276,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO33" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB33" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -16381,64 +16381,64 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK33" t="n">
         <v>3</v>
       </c>
-      <c r="BK33" t="n">
-        <v>1</v>
-      </c>
       <c r="BL33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO33" t="n">
         <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR33" t="n">
         <v>1</v>
       </c>
       <c r="BS33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU33" t="n">
         <v>1</v>
       </c>
       <c r="BV33" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW33" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX33" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY33" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA33" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -16471,7 +16471,7 @@
         <v>0</v>
       </c>
       <c r="CM33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
@@ -16486,73 +16486,73 @@
         <v>1</v>
       </c>
       <c r="CR33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS33" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT33" t="n">
         <v>1</v>
       </c>
       <c r="CU33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW33" t="n">
         <v>1</v>
       </c>
       <c r="CX33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CY33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB33" t="n">
         <v>67</v>
       </c>
-      <c r="DA33" t="n">
+      <c r="DC33" t="n">
         <v>100</v>
       </c>
-      <c r="DB33" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC33" t="n">
-        <v>67</v>
-      </c>
       <c r="DD33" t="n">
-        <v>0.78</v>
+        <v>2.33</v>
       </c>
       <c r="DE33" t="n">
         <v>0.89</v>
       </c>
       <c r="DF33" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG33" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH33" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI33" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DJ33" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL33" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="DN33" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO33" t="n">
         <v>18</v>
@@ -16561,82 +16561,82 @@
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW33" t="n">
-        <v>16.01</v>
+        <v>16.08</v>
       </c>
       <c r="DX33" t="n">
-        <v>9.800000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EF33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EG33" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EH33" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EI33" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ33" t="inlineStr">
@@ -16656,12 +16656,12 @@
       </c>
       <c r="EM33" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EN33" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EO33" t="inlineStr"/>
@@ -16683,70 +16683,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L34" t="n">
+        <v>14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>18</v>
+      </c>
+      <c r="W34" t="n">
         <v>10</v>
       </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>12</v>
-      </c>
-      <c r="R34" t="n">
-        <v>5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>9</v>
-      </c>
-      <c r="T34" t="n">
-        <v>6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>21</v>
-      </c>
-      <c r="V34" t="n">
-        <v>11</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
-      </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16756,97 +16756,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16861,178 +16861,178 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ34" t="n">
         <v>3</v>
       </c>
-      <c r="BJ34" t="n">
-        <v>2</v>
-      </c>
       <c r="BK34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR34" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY34" t="n">
         <v>5</v>
       </c>
-      <c r="BO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB34" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS34" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX34" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY34" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA34" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB34" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC34" t="n">
         <v>67</v>
       </c>
-      <c r="DC34" t="n">
-        <v>100</v>
-      </c>
       <c r="DD34" t="n">
-        <v>2.33</v>
+        <v>0.78</v>
       </c>
       <c r="DE34" t="n">
         <v>0.89</v>
       </c>
       <c r="DF34" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ34" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK34" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL34" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN34" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO34" t="n">
         <v>18</v>
@@ -17041,107 +17041,107 @@
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW34" t="n">
-        <v>16.08</v>
+        <v>16.01</v>
       </c>
       <c r="DX34" t="n">
-        <v>8.460000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="ED34" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EE34" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EG34" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EH34" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ34" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EL34" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EM34" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EN34" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="ED34" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EE34" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EF34" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EG34" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EH34" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EJ34" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK34" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EL34" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EM34" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EN34" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EO34" t="inlineStr"/>
@@ -17485,7 +17485,7 @@
         <v>1.89</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -17515,7 +17515,7 @@
         <v>2.46</v>
       </c>
       <c r="DO35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17995,7 +17995,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18914,7 +18914,7 @@
         <v>67</v>
       </c>
       <c r="DD38" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE38" t="n">
         <v>1.22</v>
@@ -18947,7 +18947,7 @@
         <v>2.88</v>
       </c>
       <c r="DO38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -21339,7 +21339,7 @@
         <v>2.97</v>
       </c>
       <c r="DO43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -22283,7 +22283,7 @@
         <v>3.76</v>
       </c>
       <c r="DO45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -24175,7 +24175,7 @@
         <v>2.22</v>
       </c>
       <c r="DO49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -25558,7 +25558,7 @@
         <v>50</v>
       </c>
       <c r="DD52" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE52" t="n">
         <v>1.33</v>
@@ -25591,7 +25591,7 @@
         <v>3.05</v>
       </c>
       <c r="DO52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -26513,7 +26513,7 @@
         <v>2.11</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF54" t="n">
         <v>1.75</v>
@@ -26543,7 +26543,7 @@
         <v>3.92</v>
       </c>
       <c r="DO54" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -28427,7 +28427,7 @@
         <v>2.65</v>
       </c>
       <c r="DO58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29387,7 +29387,7 @@
         <v>2.73</v>
       </c>
       <c r="DO60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -30423,22 +30423,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -30447,16 +30447,16 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -30465,128 +30465,120 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V63" t="n">
         <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y63" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z63" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE63" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF63" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AN63" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AU63" t="n">
         <v>3</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX63" t="n">
         <v>0</v>
       </c>
       <c r="AY63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB63" t="n">
-        <v>986</v>
+        <v>2521</v>
       </c>
       <c r="BC63" t="n">
         <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="BE63" t="n">
         <v>0</v>
@@ -30601,37 +30593,37 @@
         <v>1</v>
       </c>
       <c r="BI63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL63" t="n">
         <v>2</v>
       </c>
       <c r="BM63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN63" t="n">
         <v>5</v>
       </c>
-      <c r="BN63" t="n">
-        <v>6</v>
-      </c>
       <c r="BO63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP63" t="n">
         <v>0</v>
       </c>
       <c r="BQ63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT63" t="n">
         <v>2</v>
@@ -30640,25 +30632,25 @@
         <v>1</v>
       </c>
       <c r="BV63" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BW63" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="BX63" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BY63" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="BZ63" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="CB63" t="n">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="CC63" t="n">
         <v>0</v>
@@ -30691,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="CM63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN63" t="n">
         <v>0</v>
@@ -30706,76 +30698,76 @@
         <v>1</v>
       </c>
       <c r="CR63" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CS63" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT63" t="n">
         <v>1</v>
       </c>
       <c r="CU63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CV63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW63" t="n">
         <v>1</v>
       </c>
       <c r="CX63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ63" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="DA63" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DB63" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="DC63" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="DD63" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE63" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DF63" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DG63" t="n">
         <v>1.2</v>
       </c>
       <c r="DH63" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="DI63" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ63" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK63" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="DL63" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="DM63" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="DN63" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="DO63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30796,102 +30788,86 @@
         <v>0</v>
       </c>
       <c r="DV63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW63" t="n">
-        <v>12.5</v>
+        <v>13.33</v>
       </c>
       <c r="DX63" t="n">
-        <v>9.859999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="DY63" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ63" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="EA63" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB63" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC63" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="ED63" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EE63" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EF63" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG63" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EH63" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EI63" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EJ63" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EK63" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EL63" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI63" t="inlineStr"/>
+      <c r="EJ63" t="inlineStr"/>
+      <c r="EK63" t="inlineStr"/>
+      <c r="EL63" t="inlineStr"/>
       <c r="EM63" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EN63" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EO63" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP63" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -30911,22 +30887,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
         <v>3</v>
@@ -30935,16 +30911,16 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -30953,120 +30929,128 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V64" t="n">
         <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X64" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y64" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z64" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AF64" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL64" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AM64" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AN64" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AO64" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AS64" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AU64" t="n">
         <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX64" t="n">
         <v>0</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB64" t="n">
-        <v>2521</v>
+        <v>986</v>
       </c>
       <c r="BC64" t="n">
         <v>0</v>
       </c>
       <c r="BD64" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="BE64" t="n">
         <v>0</v>
@@ -31081,178 +31065,178 @@
         <v>1</v>
       </c>
       <c r="BI64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK64" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB64" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR64" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS64" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU64" t="n">
         <v>3</v>
       </c>
-      <c r="BL64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN64" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU64" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV64" t="n">
-        <v>53</v>
-      </c>
-      <c r="BW64" t="n">
-        <v>63</v>
-      </c>
-      <c r="BX64" t="n">
-        <v>84</v>
-      </c>
-      <c r="BY64" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ64" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CA64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CB64" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM64" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS64" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU64" t="n">
-        <v>12</v>
-      </c>
       <c r="CV64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW64" t="n">
         <v>1</v>
       </c>
       <c r="CX64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ64" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA64" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DB64" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="DC64" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="DD64" t="n">
         <v>1.22</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="DF64" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG64" t="n">
         <v>1.2</v>
       </c>
       <c r="DH64" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="DI64" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ64" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK64" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="DL64" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="DM64" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="DN64" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="DO64" t="n">
         <v>18</v>
@@ -31276,86 +31260,102 @@
         <v>0</v>
       </c>
       <c r="DV64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW64" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="DX64" t="n">
-        <v>9.65</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY64" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ64" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EA64" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EB64" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EC64" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="ED64" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EE64" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EF64" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG64" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EH64" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EI64" t="inlineStr"/>
-      <c r="EJ64" t="inlineStr"/>
-      <c r="EK64" t="inlineStr"/>
-      <c r="EL64" t="inlineStr"/>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EI64" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EJ64" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK64" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EL64" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EM64" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EN64" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EO64" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP64" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.34</t>
         </is>
       </c>
     </row>
@@ -32649,7 +32649,7 @@
         <v>0.78</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF67" t="n">
         <v>1.4</v>
@@ -32679,7 +32679,7 @@
         <v>3.08</v>
       </c>
       <c r="DO67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -34543,7 +34543,7 @@
         <v>3.14</v>
       </c>
       <c r="DO71" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -35031,7 +35031,7 @@
         <v>3.26</v>
       </c>
       <c r="DO72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -36862,7 +36862,7 @@
         <v>84</v>
       </c>
       <c r="DD76" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE76" t="n">
         <v>0.89</v>
@@ -36895,7 +36895,7 @@
         <v>2.66</v>
       </c>
       <c r="DO76" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -38289,7 +38289,7 @@
         <v>1.56</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF79" t="n">
         <v>1.67</v>
@@ -38319,7 +38319,7 @@
         <v>3.34</v>
       </c>
       <c r="DO79" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39767,7 +39767,7 @@
         <v>2.34</v>
       </c>
       <c r="DO82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -40677,7 +40677,7 @@
         <v>1.22</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF84" t="n">
         <v>1.67</v>
@@ -40707,7 +40707,7 @@
         <v>3.22</v>
       </c>
       <c r="DO84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -42106,7 +42106,7 @@
         <v>79</v>
       </c>
       <c r="DD87" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DE87" t="n">
         <v>1.67</v>
@@ -42139,7 +42139,7 @@
         <v>3.26</v>
       </c>
       <c r="DO87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -43995,7 +43995,7 @@
         <v>3.1</v>
       </c>
       <c r="DO91" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -44909,7 +44909,7 @@
         <v>1.44</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DF93" t="n">
         <v>1.43</v>
@@ -44939,7 +44939,7 @@
         <v>3.71</v>
       </c>
       <c r="DO93" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -45427,7 +45427,7 @@
         <v>2.31</v>
       </c>
       <c r="DO94" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -47427,40 +47427,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K99" t="n">
         <v>6</v>
       </c>
       <c r="L99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M99" t="n">
         <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -47472,125 +47472,117 @@
         <v>4</v>
       </c>
       <c r="R99" t="n">
+        <v>3</v>
+      </c>
+      <c r="S99" t="n">
+        <v>7</v>
+      </c>
+      <c r="T99" t="n">
+        <v>7</v>
+      </c>
+      <c r="U99" t="n">
+        <v>11</v>
+      </c>
+      <c r="V99" t="n">
+        <v>10</v>
+      </c>
+      <c r="W99" t="n">
+        <v>14</v>
+      </c>
+      <c r="X99" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD99" t="n">
         <v>4</v>
-      </c>
-      <c r="S99" t="n">
-        <v>14</v>
-      </c>
-      <c r="T99" t="n">
-        <v>10</v>
-      </c>
-      <c r="U99" t="n">
-        <v>18</v>
-      </c>
-      <c r="V99" t="n">
-        <v>14</v>
-      </c>
-      <c r="W99" t="n">
-        <v>10</v>
-      </c>
-      <c r="X99" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>JYSK park</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>Ansvej 104, Silkeborg</t>
-        </is>
-      </c>
-      <c r="AC99" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>2</v>
       </c>
       <c r="AE99" t="n">
         <v>2.37</v>
       </c>
       <c r="AF99" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL99" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AN99" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AU99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
         <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY99" t="n">
         <v>0</v>
       </c>
       <c r="AZ99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB99" t="n">
-        <v>-1</v>
+        <v>2516</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47605,19 +47597,19 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BJ99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BM99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN99" t="n">
         <v>9</v>
@@ -47626,43 +47618,43 @@
         <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ99" t="n">
         <v>2</v>
       </c>
       <c r="BR99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BW99" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="BX99" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="BY99" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="CB99" t="n">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="CC99" t="n">
         <v>0</v>
@@ -47689,16 +47681,16 @@
         <v>1</v>
       </c>
       <c r="CK99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL99" t="n">
         <v>0</v>
       </c>
       <c r="CM99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO99" t="n">
         <v>0</v>
@@ -47710,82 +47702,82 @@
         <v>1</v>
       </c>
       <c r="CR99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
         <v>16</v>
       </c>
-      <c r="CS99" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
+      <c r="CV99" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY99" t="n">
         <v>12</v>
       </c>
-      <c r="CV99" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX99" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY99" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ99" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="DA99" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="DB99" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="DC99" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="DE99" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="DF99" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DG99" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DH99" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="DI99" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="DJ99" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="DK99" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="DN99" t="n">
-        <v>2.78</v>
+        <v>4.05</v>
       </c>
       <c r="DO99" t="n">
         <v>18</v>
       </c>
       <c r="DP99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR99" t="b">
         <v>0</v>
@@ -47803,10 +47795,10 @@
         <v>0</v>
       </c>
       <c r="DW99" t="n">
-        <v>6.66</v>
+        <v>6.46</v>
       </c>
       <c r="DX99" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
@@ -47820,82 +47812,82 @@
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EF99" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EI99" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EJ99" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EM99" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EN99" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EO99" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EP99" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -47915,40 +47907,40 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K100" t="n">
         <v>6</v>
       </c>
       <c r="L100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M100" t="n">
         <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -47960,117 +47952,125 @@
         <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U100" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V100" t="n">
+        <v>14</v>
+      </c>
+      <c r="W100" t="n">
         <v>10</v>
       </c>
-      <c r="W100" t="n">
-        <v>14</v>
-      </c>
       <c r="X100" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y100" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z100" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
       <c r="AC100" t="n">
         <v>2</v>
       </c>
       <c r="AD100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE100" t="n">
         <v>2.37</v>
       </c>
       <c r="AF100" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AJ100" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL100" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AN100" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AU100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW100" t="n">
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>2516</v>
+        <v>-1</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48085,19 +48085,19 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK100" t="n">
         <v>3</v>
       </c>
-      <c r="BJ100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK100" t="n">
-        <v>5</v>
-      </c>
       <c r="BL100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BM100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN100" t="n">
         <v>9</v>
@@ -48106,166 +48106,166 @@
         <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ100" t="n">
         <v>2</v>
       </c>
       <c r="BR100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BW100" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="BX100" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="BY100" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BZ100" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD100" t="n">
         <v>1.22</v>
       </c>
-      <c r="CA100" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CS100" t="n">
+      <c r="DE100" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ100" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK100" t="n">
         <v>19</v>
       </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV100" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ100" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA100" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB100" t="n">
-        <v>38</v>
-      </c>
-      <c r="DC100" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD100" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE100" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF100" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG100" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DH100" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DI100" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DJ100" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK100" t="n">
-        <v>25</v>
-      </c>
       <c r="DL100" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="DN100" t="n">
-        <v>4.05</v>
+        <v>2.78</v>
       </c>
       <c r="DO100" t="n">
         <v>18</v>
       </c>
       <c r="DP100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR100" t="b">
         <v>0</v>
@@ -48283,10 +48283,10 @@
         <v>0</v>
       </c>
       <c r="DW100" t="n">
-        <v>6.46</v>
+        <v>6.66</v>
       </c>
       <c r="DX100" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
@@ -48300,82 +48300,82 @@
       </c>
       <c r="EA100" t="inlineStr">
         <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="ED100" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ100" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK100" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="EB100" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EC100" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="ED100" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EE100" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EF100" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG100" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EI100" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EJ100" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EK100" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EM100" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EN100" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.38</t>
         </is>
       </c>
     </row>
@@ -49219,7 +49219,7 @@
         <v>2.62</v>
       </c>
       <c r="DO102" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -49683,7 +49683,7 @@
         <v>2.76</v>
       </c>
       <c r="DO103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -52128,6 +52128,478 @@
       <c r="EP108" t="inlineStr">
         <is>
           <t>3.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>18</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Brøndby</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>45999.75</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>3</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>5</v>
+      </c>
+      <c r="L109" t="n">
+        <v>6</v>
+      </c>
+      <c r="M109" t="n">
+        <v>5</v>
+      </c>
+      <c r="N109" t="n">
+        <v>5</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>2</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="n">
+        <v>9</v>
+      </c>
+      <c r="U109" t="n">
+        <v>7</v>
+      </c>
+      <c r="V109" t="n">
+        <v>11</v>
+      </c>
+      <c r="W109" t="n">
+        <v>17</v>
+      </c>
+      <c r="X109" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
+      <c r="AC109" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>3647</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ109" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR109" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT109" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV109" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW109" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX109" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY109" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ109" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CA109" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CB109" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR109" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS109" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU109" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV109" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
+        <v>16</v>
+      </c>
+      <c r="CY109" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ109" t="n">
+        <v>38</v>
+      </c>
+      <c r="DA109" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB109" t="n">
+        <v>51</v>
+      </c>
+      <c r="DC109" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD109" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE109" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF109" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG109" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DH109" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="DI109" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DJ109" t="n">
+        <v>63</v>
+      </c>
+      <c r="DK109" t="n">
+        <v>19</v>
+      </c>
+      <c r="DL109" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM109" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DN109" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DO109" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU109" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV109" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW109" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="DX109" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="DY109" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="DZ109" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="EA109" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EC109" t="inlineStr">
+        <is>
+          <t>4.31</t>
+        </is>
+      </c>
+      <c r="ED109" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="EE109" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EF109" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG109" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EH109" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI109" t="inlineStr"/>
+      <c r="EJ109" t="inlineStr"/>
+      <c r="EK109" t="inlineStr"/>
+      <c r="EL109" t="inlineStr"/>
+      <c r="EM109" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EN109" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EO109" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP109" t="inlineStr">
+        <is>
+          <t>3.39</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -43217,7 +43217,7 @@
         <v>12</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
         <v>1</v>
@@ -43261,7 +43261,7 @@
       <c r="AA90" t="inlineStr"/>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>1</v>
@@ -43375,7 +43375,7 @@
         <v>9</v>
       </c>
       <c r="BO90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP90" t="n">
         <v>0</v>
@@ -43387,7 +43387,7 @@
         <v>1</v>
       </c>
       <c r="BS90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT90" t="n">
         <v>1</v>
@@ -43453,7 +43453,7 @@
         <v>0</v>
       </c>
       <c r="CO90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP90" t="n">
         <v>0</v>
@@ -46057,10 +46057,10 @@
         <v>14</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -46109,10 +46109,10 @@
         </is>
       </c>
       <c r="AC96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE96" t="n">
         <v>4.74</v>
@@ -46229,16 +46229,16 @@
         <v>1</v>
       </c>
       <c r="BQ96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BS96" t="n">
         <v>1</v>
       </c>
       <c r="BT96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU96" t="n">
         <v>1</v>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL115" headerRowCount="1">
-  <autoFilter ref="A1:EL115"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL117" headerRowCount="1">
+  <autoFilter ref="A1:EL117"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL115"/>
+  <dimension ref="A1:EL117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -2233,7 +2233,7 @@
         <v>0.78</v>
       </c>
       <c r="DE3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -4974,10 +4974,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -7855,170 +7855,162 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>45872.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10</v>
+      </c>
+      <c r="V16" t="n">
+        <v>18</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5</v>
+      </c>
+      <c r="X16" t="n">
         <v>6</v>
       </c>
-      <c r="L16" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>17</v>
-      </c>
-      <c r="W16" t="n">
-        <v>11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14</v>
-      </c>
       <c r="Y16" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="Z16" t="n">
-        <v>68</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Sydbank Park</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Stadionvej 7, Haderslev</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.31</v>
+        <v>1.94</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>3.68</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AP16" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AU16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB16" t="n">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -8033,178 +8025,178 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL16" t="n">
         <v>4</v>
       </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>2</v>
-      </c>
       <c r="BM16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU16" t="n">
         <v>5</v>
       </c>
-      <c r="BN16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>65</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>136</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR16" t="n">
+      <c r="CV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX16" t="n">
         <v>11</v>
       </c>
-      <c r="CS16" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>8</v>
-      </c>
       <c r="CY16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CZ16" t="n">
         <v>50</v>
       </c>
       <c r="DA16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
         <v>50</v>
       </c>
-      <c r="DC16" t="n">
-        <v>100</v>
-      </c>
       <c r="DD16" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="DE16" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DI16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>1.69</v>
+        <v>0.91</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO16" t="n">
         <v>19</v>
@@ -8213,91 +8205,91 @@
         <v>1</v>
       </c>
       <c r="DQ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU16" t="b">
         <v>0</v>
       </c>
       <c r="DV16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr">
+        <is>
           <t>2.58</t>
         </is>
       </c>
-      <c r="ED16" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EH16" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr"/>
@@ -8319,162 +8311,170 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45872.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="R17" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10</v>
+      </c>
+      <c r="U17" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="n">
-        <v>9</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
+        <v>17</v>
+      </c>
+      <c r="W17" t="n">
+        <v>11</v>
+      </c>
+      <c r="X17" t="n">
         <v>14</v>
       </c>
-      <c r="U17" t="n">
-        <v>10</v>
-      </c>
-      <c r="V17" t="n">
-        <v>18</v>
-      </c>
-      <c r="W17" t="n">
-        <v>5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6</v>
-      </c>
       <c r="Y17" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Sydbank Park</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Stadionvej 7, Haderslev</t>
+        </is>
+      </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.94</v>
+        <v>3.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.68</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AP17" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -8489,73 +8489,73 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS17" t="n">
         <v>2</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW17" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="BX17" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="BY17" t="n">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.23</v>
+        <v>0.8</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="CB17" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="CC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -8573,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
         <v>1</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP17" t="n">
         <v>0</v>
@@ -8594,73 +8594,73 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CS17" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CV17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CY17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="CZ17" t="n">
         <v>50</v>
       </c>
       <c r="DA17" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB17" t="n">
         <v>50</v>
       </c>
-      <c r="DB17" t="n">
-        <v>0</v>
-      </c>
       <c r="DC17" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ17" t="n">
         <v>50</v>
       </c>
-      <c r="DD17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DE17" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>0</v>
-      </c>
       <c r="DK17" t="n">
         <v>0</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.91</v>
+        <v>1.69</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.91</v>
+        <v>2.96</v>
       </c>
       <c r="DO17" t="n">
         <v>19</v>
@@ -8669,91 +8669,91 @@
         <v>1</v>
       </c>
       <c r="DQ17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU17" t="b">
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr"/>
@@ -9998,7 +9998,7 @@
         <v>100</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE20" t="n">
         <v>2.33</v>
@@ -11377,7 +11377,7 @@
         <v>1.1</v>
       </c>
       <c r="DE23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -11825,7 +11825,7 @@
         <v>1.7</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF24" t="n">
         <v>1.5</v>
@@ -12775,7 +12775,7 @@
         <v>4.08</v>
       </c>
       <c r="DO26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14598,7 +14598,7 @@
         <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE30" t="n">
         <v>1.67</v>
@@ -15534,7 +15534,7 @@
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE32" t="n">
         <v>1.2</v>
@@ -17393,7 +17393,7 @@
         <v>2.2</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF36" t="n">
         <v>0.5</v>
@@ -19705,7 +19705,7 @@
         <v>1.56</v>
       </c>
       <c r="DE41" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF41" t="n">
         <v>2</v>
@@ -20150,7 +20150,7 @@
         <v>84</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE42" t="n">
         <v>1.5</v>
@@ -20183,7 +20183,7 @@
         <v>3.26</v>
       </c>
       <c r="DO42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -23365,7 +23365,7 @@
         <v>0.78</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF49" t="n">
         <v>1.5</v>
@@ -25194,7 +25194,7 @@
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE53" t="n">
         <v>0.89</v>
@@ -26114,10 +26114,10 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE55" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF55" t="n">
         <v>1</v>
@@ -26147,7 +26147,7 @@
         <v>2.73</v>
       </c>
       <c r="DO55" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27473,7 +27473,7 @@
         <v>1.1</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF58" t="n">
         <v>1.5</v>
@@ -29419,22 +29419,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -29443,16 +29443,16 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -29461,128 +29461,120 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T63" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V63" t="n">
         <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y63" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z63" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE63" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF63" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AN63" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AU63" t="n">
         <v>3</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX63" t="n">
         <v>0</v>
       </c>
       <c r="AY63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB63" t="n">
-        <v>986</v>
+        <v>2521</v>
       </c>
       <c r="BC63" t="n">
         <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="BE63" t="n">
         <v>0</v>
@@ -29597,37 +29589,37 @@
         <v>1</v>
       </c>
       <c r="BI63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL63" t="n">
         <v>2</v>
       </c>
       <c r="BM63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN63" t="n">
         <v>5</v>
       </c>
-      <c r="BN63" t="n">
-        <v>6</v>
-      </c>
       <c r="BO63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP63" t="n">
         <v>0</v>
       </c>
       <c r="BQ63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT63" t="n">
         <v>2</v>
@@ -29636,25 +29628,25 @@
         <v>1</v>
       </c>
       <c r="BV63" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BW63" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="BX63" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BY63" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="BZ63" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="CA63" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="CB63" t="n">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="CC63" t="n">
         <v>0</v>
@@ -29687,7 +29679,7 @@
         <v>0</v>
       </c>
       <c r="CM63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN63" t="n">
         <v>0</v>
@@ -29702,73 +29694,73 @@
         <v>1</v>
       </c>
       <c r="CR63" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CS63" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT63" t="n">
         <v>1</v>
       </c>
       <c r="CU63" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CV63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW63" t="n">
         <v>1</v>
       </c>
       <c r="CX63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ63" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="DA63" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DB63" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="DC63" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="DE63" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="DF63" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DG63" t="n">
         <v>1.2</v>
       </c>
       <c r="DH63" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="DI63" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ63" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK63" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="DL63" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="DM63" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="DN63" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="DO63" t="n">
         <v>19</v>
@@ -29792,86 +29784,70 @@
         <v>0</v>
       </c>
       <c r="DV63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW63" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="DX63" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY63" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="DZ63" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EA63" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EB63" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EC63" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED63" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EE63" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EF63" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EG63" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EH63" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EE63" t="inlineStr"/>
+      <c r="EF63" t="inlineStr"/>
+      <c r="EG63" t="inlineStr"/>
+      <c r="EH63" t="inlineStr"/>
       <c r="EI63" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EJ63" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EK63" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL63" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -29891,22 +29867,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64" t="n">
         <v>3</v>
@@ -29915,16 +29891,16 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -29933,120 +29909,128 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V64" t="n">
         <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X64" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y64" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z64" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AF64" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL64" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AM64" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AN64" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AO64" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AS64" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AU64" t="n">
         <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX64" t="n">
         <v>0</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB64" t="n">
-        <v>2521</v>
+        <v>986</v>
       </c>
       <c r="BC64" t="n">
         <v>0</v>
       </c>
       <c r="BD64" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="BE64" t="n">
         <v>0</v>
@@ -30061,181 +30045,181 @@
         <v>1</v>
       </c>
       <c r="BI64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK64" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY64" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ64" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA64" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB64" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR64" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS64" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT64" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU64" t="n">
         <v>3</v>
       </c>
-      <c r="BL64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN64" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT64" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU64" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV64" t="n">
-        <v>53</v>
-      </c>
-      <c r="BW64" t="n">
-        <v>63</v>
-      </c>
-      <c r="BX64" t="n">
-        <v>84</v>
-      </c>
-      <c r="BY64" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ64" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CA64" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CB64" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM64" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP64" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS64" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT64" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU64" t="n">
-        <v>12</v>
-      </c>
       <c r="CV64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW64" t="n">
         <v>1</v>
       </c>
       <c r="CX64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ64" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA64" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DB64" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="DC64" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="DD64" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DF64" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG64" t="n">
         <v>1.2</v>
       </c>
       <c r="DH64" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="DI64" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ64" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK64" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="DL64" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="DM64" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="DN64" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="DO64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30256,70 +30240,86 @@
         <v>0</v>
       </c>
       <c r="DV64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW64" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="DX64" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="DY64" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="DZ64" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EA64" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EB64" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EC64" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="ED64" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EE64" t="inlineStr"/>
-      <c r="EF64" t="inlineStr"/>
-      <c r="EG64" t="inlineStr"/>
-      <c r="EH64" t="inlineStr"/>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EE64" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF64" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG64" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH64" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EI64" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EJ64" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK64" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EL64" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.34</t>
         </is>
       </c>
     </row>
@@ -31106,7 +31106,7 @@
         <v>63</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE66" t="n">
         <v>1.67</v>
@@ -32515,7 +32515,7 @@
         <v>2.94</v>
       </c>
       <c r="DO69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
@@ -33853,7 +33853,7 @@
         <v>2.4</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF72" t="n">
         <v>2.33</v>
@@ -34733,7 +34733,7 @@
         <v>2.2</v>
       </c>
       <c r="DE74" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF74" t="n">
         <v>2.17</v>
@@ -34875,146 +34875,146 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
         <v>4</v>
       </c>
-      <c r="I75" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="R75" t="n">
         <v>7</v>
       </c>
-      <c r="K75" t="n">
+      <c r="S75" t="n">
+        <v>9</v>
+      </c>
+      <c r="T75" t="n">
+        <v>7</v>
+      </c>
+      <c r="U75" t="n">
+        <v>13</v>
+      </c>
+      <c r="V75" t="n">
+        <v>14</v>
+      </c>
+      <c r="W75" t="n">
+        <v>15</v>
+      </c>
+      <c r="X75" t="n">
         <v>5</v>
       </c>
-      <c r="L75" t="n">
-        <v>12</v>
-      </c>
-      <c r="M75" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>5</v>
-      </c>
-      <c r="R75" t="n">
-        <v>12</v>
-      </c>
-      <c r="S75" t="n">
-        <v>5</v>
-      </c>
-      <c r="T75" t="n">
-        <v>9</v>
-      </c>
-      <c r="U75" t="n">
-        <v>10</v>
-      </c>
-      <c r="V75" t="n">
-        <v>21</v>
-      </c>
-      <c r="W75" t="n">
-        <v>6</v>
-      </c>
-      <c r="X75" t="n">
-        <v>11</v>
-      </c>
       <c r="Y75" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z75" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AF75" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AL75" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AM75" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AN75" t="n">
         <v>1.83</v>
       </c>
       <c r="AO75" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AR75" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AS75" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AU75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW75" t="n">
         <v>2</v>
@@ -35023,22 +35023,22 @@
         <v>0</v>
       </c>
       <c r="AY75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB75" t="n">
-        <v>955</v>
+        <v>2522</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -35056,175 +35056,175 @@
         <v>3</v>
       </c>
       <c r="BJ75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK75" t="n">
         <v>3</v>
       </c>
-      <c r="BK75" t="n">
+      <c r="BL75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX75" t="n">
         <v>4</v>
       </c>
-      <c r="BL75" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV75" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW75" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX75" t="n">
-        <v>63</v>
-      </c>
-      <c r="BY75" t="n">
-        <v>102</v>
-      </c>
-      <c r="BZ75" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CA75" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CB75" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="CC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM75" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU75" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV75" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX75" t="n">
+      <c r="CY75" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK75" t="n">
         <v>9</v>
       </c>
-      <c r="CY75" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ75" t="n">
-        <v>27</v>
-      </c>
-      <c r="DA75" t="n">
-        <v>72</v>
-      </c>
-      <c r="DB75" t="n">
-        <v>9</v>
-      </c>
-      <c r="DC75" t="n">
-        <v>45</v>
-      </c>
-      <c r="DD75" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DE75" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF75" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DG75" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DH75" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI75" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ75" t="n">
-        <v>74</v>
-      </c>
-      <c r="DK75" t="n">
-        <v>29</v>
-      </c>
       <c r="DL75" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="DO75" t="n">
         <v>19</v>
@@ -35239,7 +35239,7 @@
         <v>1</v>
       </c>
       <c r="DS75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT75" t="b">
         <v>0</v>
@@ -35248,72 +35248,72 @@
         <v>0</v>
       </c>
       <c r="DV75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW75" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="DX75" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EE75" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EE75" t="inlineStr"/>
       <c r="EF75" t="inlineStr"/>
       <c r="EG75" t="inlineStr"/>
-      <c r="EH75" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+      <c r="EH75" t="inlineStr"/>
       <c r="EI75" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EJ75" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EK75" t="inlineStr"/>
-      <c r="EL75" t="inlineStr"/>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK75" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -35331,146 +35331,146 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
+        <v>7</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5</v>
+      </c>
+      <c r="L76" t="n">
+        <v>12</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>12</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="n">
+        <v>9</v>
+      </c>
+      <c r="U76" t="n">
+        <v>10</v>
+      </c>
+      <c r="V76" t="n">
+        <v>21</v>
+      </c>
+      <c r="W76" t="n">
         <v>6</v>
       </c>
-      <c r="K76" t="n">
-        <v>10</v>
-      </c>
-      <c r="L76" t="n">
-        <v>16</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>4</v>
-      </c>
-      <c r="R76" t="n">
+      <c r="X76" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
         <v>7</v>
       </c>
-      <c r="S76" t="n">
-        <v>9</v>
-      </c>
-      <c r="T76" t="n">
-        <v>7</v>
-      </c>
-      <c r="U76" t="n">
-        <v>13</v>
-      </c>
-      <c r="V76" t="n">
-        <v>14</v>
-      </c>
-      <c r="W76" t="n">
-        <v>15</v>
-      </c>
-      <c r="X76" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AF76" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL76" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN76" t="n">
         <v>1.83</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AS76" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AU76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW76" t="n">
         <v>2</v>
@@ -35479,22 +35479,22 @@
         <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB76" t="n">
-        <v>2522</v>
+        <v>955</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -35512,19 +35512,19 @@
         <v>3</v>
       </c>
       <c r="BJ76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO76" t="n">
         <v>1</v>
@@ -35533,7 +35533,7 @@
         <v>0</v>
       </c>
       <c r="BQ76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR76" t="n">
         <v>0</v>
@@ -35542,31 +35542,31 @@
         <v>1</v>
       </c>
       <c r="BT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU76" t="n">
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BW76" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="BX76" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="BY76" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ76" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="CA76" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="CB76" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
@@ -35593,16 +35593,16 @@
         <v>1</v>
       </c>
       <c r="CK76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL76" t="n">
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO76" t="n">
         <v>0</v>
@@ -35614,73 +35614,73 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS76" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CV76" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY76" t="n">
         <v>4</v>
       </c>
-      <c r="CY76" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ76" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="DA76" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="DB76" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="DC76" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.1</v>
+        <v>0.78</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="DF76" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG76" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH76" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="DI76" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="DJ76" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="DK76" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="DL76" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="DO76" t="n">
         <v>19</v>
@@ -35695,7 +35695,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -35704,72 +35704,72 @@
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW76" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="DX76" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EE76" t="inlineStr"/>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EE76" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
       <c r="EF76" t="inlineStr"/>
       <c r="EG76" t="inlineStr"/>
-      <c r="EH76" t="inlineStr"/>
+      <c r="EH76" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EI76" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EK76" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EL76" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EK76" t="inlineStr"/>
+      <c r="EL76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -36098,7 +36098,7 @@
         <v>74</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE77" t="n">
         <v>1.2</v>
@@ -36554,7 +36554,7 @@
         <v>92</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE78" t="n">
         <v>1.4</v>
@@ -37498,7 +37498,7 @@
         <v>92</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE80" t="n">
         <v>1</v>
@@ -38429,7 +38429,7 @@
         <v>1.89</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF82" t="n">
         <v>1.67</v>
@@ -41207,7 +41207,7 @@
         <v>3.26</v>
       </c>
       <c r="DO88" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41622,7 +41622,7 @@
         <v>59</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE89" t="n">
         <v>1.67</v>
@@ -42513,7 +42513,7 @@
         <v>1.7</v>
       </c>
       <c r="DE91" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF91" t="n">
         <v>1.86</v>
@@ -43422,7 +43422,7 @@
         <v>79</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE93" t="n">
         <v>1.67</v>
@@ -43897,7 +43897,7 @@
         <v>1.44</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF94" t="n">
         <v>1.29</v>
@@ -45254,7 +45254,7 @@
         <v>79</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE97" t="n">
         <v>1.2</v>
@@ -45847,40 +45847,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K99" t="n">
         <v>6</v>
       </c>
       <c r="L99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M99" t="n">
         <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -45892,125 +45892,117 @@
         <v>4</v>
       </c>
       <c r="R99" t="n">
+        <v>3</v>
+      </c>
+      <c r="S99" t="n">
+        <v>7</v>
+      </c>
+      <c r="T99" t="n">
+        <v>7</v>
+      </c>
+      <c r="U99" t="n">
+        <v>11</v>
+      </c>
+      <c r="V99" t="n">
+        <v>10</v>
+      </c>
+      <c r="W99" t="n">
+        <v>14</v>
+      </c>
+      <c r="X99" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD99" t="n">
         <v>4</v>
-      </c>
-      <c r="S99" t="n">
-        <v>14</v>
-      </c>
-      <c r="T99" t="n">
-        <v>10</v>
-      </c>
-      <c r="U99" t="n">
-        <v>18</v>
-      </c>
-      <c r="V99" t="n">
-        <v>14</v>
-      </c>
-      <c r="W99" t="n">
-        <v>10</v>
-      </c>
-      <c r="X99" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>JYSK park</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>Ansvej 104, Silkeborg</t>
-        </is>
-      </c>
-      <c r="AC99" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>2</v>
       </c>
       <c r="AE99" t="n">
         <v>2.37</v>
       </c>
       <c r="AF99" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL99" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AN99" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AU99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
         <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY99" t="n">
         <v>0</v>
       </c>
       <c r="AZ99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB99" t="n">
-        <v>-1</v>
+        <v>2516</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -46025,19 +46017,19 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BJ99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BM99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN99" t="n">
         <v>9</v>
@@ -46046,43 +46038,43 @@
         <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ99" t="n">
         <v>2</v>
       </c>
       <c r="BR99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BW99" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="BX99" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="BY99" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="CB99" t="n">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="CC99" t="n">
         <v>0</v>
@@ -46109,16 +46101,16 @@
         <v>1</v>
       </c>
       <c r="CK99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL99" t="n">
         <v>0</v>
       </c>
       <c r="CM99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO99" t="n">
         <v>0</v>
@@ -46130,82 +46122,82 @@
         <v>1</v>
       </c>
       <c r="CR99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
         <v>16</v>
       </c>
-      <c r="CS99" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
+      <c r="CV99" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY99" t="n">
         <v>12</v>
       </c>
-      <c r="CV99" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX99" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY99" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ99" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="DA99" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="DB99" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="DC99" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="DE99" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="DF99" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DG99" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DH99" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="DI99" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="DJ99" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="DK99" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="DN99" t="n">
-        <v>2.78</v>
+        <v>4.05</v>
       </c>
       <c r="DO99" t="n">
         <v>19</v>
       </c>
       <c r="DP99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR99" t="b">
         <v>0</v>
@@ -46224,82 +46216,82 @@
       </c>
       <c r="DW99" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="DX99" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EF99" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EI99" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EJ99" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -46319,40 +46311,40 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K100" t="n">
         <v>6</v>
       </c>
       <c r="L100" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M100" t="n">
         <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -46364,117 +46356,125 @@
         <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U100" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V100" t="n">
+        <v>14</v>
+      </c>
+      <c r="W100" t="n">
         <v>10</v>
       </c>
-      <c r="W100" t="n">
-        <v>14</v>
-      </c>
       <c r="X100" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y100" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z100" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
       <c r="AC100" t="n">
         <v>2</v>
       </c>
       <c r="AD100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE100" t="n">
         <v>2.37</v>
       </c>
       <c r="AF100" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AJ100" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL100" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AN100" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AU100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW100" t="n">
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>2516</v>
+        <v>-1</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -46489,19 +46489,19 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK100" t="n">
         <v>3</v>
       </c>
-      <c r="BJ100" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK100" t="n">
-        <v>5</v>
-      </c>
       <c r="BL100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BM100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN100" t="n">
         <v>9</v>
@@ -46510,43 +46510,43 @@
         <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ100" t="n">
         <v>2</v>
       </c>
       <c r="BR100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BW100" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="BX100" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="BY100" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BZ100" t="n">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="CB100" t="n">
-        <v>2.28</v>
+        <v>3.24</v>
       </c>
       <c r="CC100" t="n">
         <v>0</v>
@@ -46573,16 +46573,16 @@
         <v>1</v>
       </c>
       <c r="CK100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL100" t="n">
         <v>0</v>
       </c>
       <c r="CM100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO100" t="n">
         <v>0</v>
@@ -46594,82 +46594,82 @@
         <v>1</v>
       </c>
       <c r="CR100" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
         <v>12</v>
       </c>
-      <c r="CS100" t="n">
+      <c r="CV100" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC100" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD100" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE100" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI100" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ100" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK100" t="n">
         <v>19</v>
       </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV100" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ100" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA100" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB100" t="n">
-        <v>38</v>
-      </c>
-      <c r="DC100" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD100" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DE100" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DF100" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG100" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DH100" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DI100" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DJ100" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK100" t="n">
-        <v>25</v>
-      </c>
       <c r="DL100" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="DN100" t="n">
-        <v>4.05</v>
+        <v>2.78</v>
       </c>
       <c r="DO100" t="n">
         <v>19</v>
       </c>
       <c r="DP100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR100" t="b">
         <v>0</v>
@@ -46688,82 +46688,82 @@
       </c>
       <c r="DW100" t="inlineStr">
         <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="DX100" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="DY100" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="DZ100" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EA100" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EB100" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EC100" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="ED100" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="DX100" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="DY100" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="DZ100" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EA100" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EB100" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EC100" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="ED100" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EE100" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EF100" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EG100" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EK100" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.38</t>
         </is>
       </c>
     </row>
@@ -47105,7 +47105,7 @@
         <v>2.4</v>
       </c>
       <c r="DE101" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DF101" t="n">
         <v>2.25</v>
@@ -47561,7 +47561,7 @@
         <v>1.56</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF102" t="n">
         <v>1.38</v>
@@ -48583,170 +48583,170 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
         <v>45998.54166666666</v>
       </c>
       <c r="G105" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L105" t="n">
         <v>11</v>
       </c>
       <c r="M105" t="n">
+        <v>2</v>
+      </c>
+      <c r="N105" t="n">
         <v>4</v>
       </c>
-      <c r="N105" t="n">
-        <v>1</v>
-      </c>
       <c r="O105" t="n">
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S105" t="n">
         <v>7</v>
       </c>
       <c r="T105" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U105" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V105" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="W105" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="X105" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y105" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="Z105" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD105" t="n">
         <v>4</v>
       </c>
-      <c r="AD105" t="n">
-        <v>3</v>
-      </c>
       <c r="AE105" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="AF105" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG105" t="n">
-        <v>4</v>
+        <v>1.66</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AI105" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AJ105" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AK105" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AL105" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AM105" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AO105" t="n">
-        <v>2.37</v>
+        <v>2.87</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AR105" t="n">
         <v>2.18</v>
       </c>
       <c r="AS105" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="AT105" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AU105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ105" t="n">
         <v>4</v>
       </c>
-      <c r="AW105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ105" t="n">
-        <v>1</v>
-      </c>
       <c r="BA105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB105" t="n">
-        <v>986</v>
+        <v>-1</v>
       </c>
       <c r="BC105" t="n">
         <v>0</v>
       </c>
       <c r="BD105" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE105" t="n">
         <v>0</v>
@@ -48761,73 +48761,73 @@
         <v>1</v>
       </c>
       <c r="BI105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BJ105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK105" t="n">
         <v>2</v>
       </c>
       <c r="BL105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM105" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BN105" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BO105" t="n">
         <v>2</v>
       </c>
       <c r="BP105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BT105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU105" t="n">
         <v>1</v>
       </c>
       <c r="BV105" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="BW105" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="BX105" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="BY105" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="BZ105" t="n">
-        <v>2.37</v>
+        <v>1.16</v>
       </c>
       <c r="CA105" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="CB105" t="n">
-        <v>3.57</v>
+        <v>3.16</v>
       </c>
       <c r="CC105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD105" t="n">
         <v>0</v>
       </c>
       <c r="CE105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF105" t="n">
         <v>0</v>
@@ -48851,13 +48851,13 @@
         <v>0</v>
       </c>
       <c r="CM105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP105" t="n">
         <v>0</v>
@@ -48866,73 +48866,73 @@
         <v>1</v>
       </c>
       <c r="CR105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CS105" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV105" t="n">
         <v>16</v>
       </c>
-      <c r="CT105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU105" t="n">
-        <v>5</v>
-      </c>
-      <c r="CV105" t="n">
-        <v>11</v>
-      </c>
       <c r="CW105" t="n">
         <v>1</v>
       </c>
       <c r="CX105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CY105" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CZ105" t="n">
         <v>63</v>
       </c>
       <c r="DA105" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="DB105" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC105" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="DE105" t="n">
-        <v>0.89</v>
+        <v>1.67</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
       </c>
       <c r="DG105" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DH105" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="DI105" t="n">
-        <v>1.12</v>
+        <v>2.06</v>
       </c>
       <c r="DJ105" t="n">
         <v>38</v>
       </c>
       <c r="DK105" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="DL105" t="n">
-        <v>1.81</v>
+        <v>1.22</v>
       </c>
       <c r="DM105" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="DN105" t="n">
-        <v>3.06</v>
+        <v>2.56</v>
       </c>
       <c r="DO105" t="n">
         <v>19</v>
@@ -48953,79 +48953,71 @@
         <v>1</v>
       </c>
       <c r="DU105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW105" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="DX105" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DY105" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="DZ105" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="EA105" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EB105" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC105" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="ED105" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EE105" t="inlineStr">
         <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EF105" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EG105" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr"/>
+      <c r="EG105" t="inlineStr"/>
       <c r="EH105" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI105" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="EJ105" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EK105" t="inlineStr"/>
@@ -49047,146 +49039,146 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
         <v>45998.54166666666</v>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K106" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L106" t="n">
         <v>11</v>
       </c>
       <c r="M106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
+        <v>10</v>
+      </c>
+      <c r="R106" t="n">
         <v>3</v>
-      </c>
-      <c r="R106" t="n">
-        <v>5</v>
       </c>
       <c r="S106" t="n">
         <v>7</v>
       </c>
       <c r="T106" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U106" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V106" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="W106" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="X106" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y106" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="Z106" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF106" t="n">
         <v>4</v>
       </c>
-      <c r="AE106" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AG106" t="n">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="AH106" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AI106" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AJ106" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="AK106" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AL106" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AM106" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN106" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AO106" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AR106" t="n">
         <v>2.18</v>
       </c>
       <c r="AS106" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="AT106" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AU106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW106" t="n">
         <v>0</v>
@@ -49195,22 +49187,22 @@
         <v>1</v>
       </c>
       <c r="AY106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA106" t="n">
         <v>4</v>
       </c>
-      <c r="BA106" t="n">
-        <v>2</v>
-      </c>
       <c r="BB106" t="n">
-        <v>-1</v>
+        <v>986</v>
       </c>
       <c r="BC106" t="n">
         <v>0</v>
       </c>
       <c r="BD106" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE106" t="n">
         <v>0</v>
@@ -49225,178 +49217,178 @@
         <v>1</v>
       </c>
       <c r="BI106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK106" t="n">
         <v>2</v>
       </c>
       <c r="BL106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BM106" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BN106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>82</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM106" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR106" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS106" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU106" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV106" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX106" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY106" t="n">
         <v>8</v>
-      </c>
-      <c r="BO106" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP106" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ106" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR106" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS106" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT106" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU106" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV106" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW106" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX106" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY106" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ106" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CA106" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB106" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CC106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR106" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS106" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU106" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV106" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX106" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY106" t="n">
-        <v>6</v>
       </c>
       <c r="CZ106" t="n">
         <v>63</v>
       </c>
       <c r="DA106" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="DB106" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC106" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.67</v>
+        <v>0.89</v>
       </c>
       <c r="DF106" t="n">
         <v>1.5</v>
       </c>
       <c r="DG106" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DH106" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="DI106" t="n">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="DJ106" t="n">
         <v>38</v>
       </c>
       <c r="DK106" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="DL106" t="n">
-        <v>1.22</v>
+        <v>1.81</v>
       </c>
       <c r="DM106" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="DN106" t="n">
-        <v>2.56</v>
+        <v>3.06</v>
       </c>
       <c r="DO106" t="n">
         <v>19</v>
@@ -49417,71 +49409,79 @@
         <v>1</v>
       </c>
       <c r="DU106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW106" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="DX106" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DY106" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="DZ106" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="EA106" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="EB106" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC106" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="ED106" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="EE106" t="inlineStr">
         <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF106" t="inlineStr"/>
-      <c r="EG106" t="inlineStr"/>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EG106" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
       <c r="EH106" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EI106" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EJ106" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK106" t="inlineStr"/>
@@ -49814,7 +49814,7 @@
         <v>69</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DE107" t="n">
         <v>2.33</v>
@@ -50270,7 +50270,7 @@
         <v>69</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DE108" t="n">
         <v>1.2</v>
@@ -53614,6 +53614,894 @@
           <t>3.29</t>
         </is>
       </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>20</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>46066.75</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>2</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="n">
+        <v>7</v>
+      </c>
+      <c r="L116" t="n">
+        <v>9</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>2</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>4</v>
+      </c>
+      <c r="R116" t="n">
+        <v>3</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3</v>
+      </c>
+      <c r="T116" t="n">
+        <v>11</v>
+      </c>
+      <c r="U116" t="n">
+        <v>7</v>
+      </c>
+      <c r="V116" t="n">
+        <v>14</v>
+      </c>
+      <c r="W116" t="n">
+        <v>11</v>
+      </c>
+      <c r="X116" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr"/>
+      <c r="AC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>2521</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ116" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM116" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN116" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>41</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>71</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>103</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>109</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY116" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ116" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA116" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB116" t="n">
+        <v>56</v>
+      </c>
+      <c r="DC116" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD116" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE116" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF116" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG116" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DH116" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DI116" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="DJ116" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK116" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL116" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DM116" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DN116" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="DO116" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ116" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV116" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW116" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="DX116" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="DY116" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DZ116" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="EA116" t="inlineStr">
+        <is>
+          <t>4.58</t>
+        </is>
+      </c>
+      <c r="EB116" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EC116" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="ED116" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EE116" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr"/>
+      <c r="EG116" t="inlineStr"/>
+      <c r="EH116" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr"/>
+      <c r="EJ116" t="inlineStr"/>
+      <c r="EK116" t="inlineStr"/>
+      <c r="EL116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>20</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Nordsjælland</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>46067.66666666666</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" t="n">
+        <v>3</v>
+      </c>
+      <c r="J117" t="n">
+        <v>4</v>
+      </c>
+      <c r="K117" t="n">
+        <v>6</v>
+      </c>
+      <c r="L117" t="n">
+        <v>10</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>2</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>6</v>
+      </c>
+      <c r="R117" t="n">
+        <v>5</v>
+      </c>
+      <c r="S117" t="n">
+        <v>9</v>
+      </c>
+      <c r="T117" t="n">
+        <v>9</v>
+      </c>
+      <c r="U117" t="n">
+        <v>15</v>
+      </c>
+      <c r="V117" t="n">
+        <v>14</v>
+      </c>
+      <c r="W117" t="n">
+        <v>17</v>
+      </c>
+      <c r="X117" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>Parken</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>Øster Allé 50, København</t>
+        </is>
+      </c>
+      <c r="AC117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>986</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>92</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>104</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>92</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU117" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV117" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX117" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY117" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ117" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA117" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB117" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC117" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD117" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DE117" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DF117" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG117" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH117" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DI117" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DJ117" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK117" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL117" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DM117" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN117" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="DO117" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU117" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV117" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW117" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="DX117" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="DY117" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="DZ117" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EA117" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="EB117" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EC117" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="ED117" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EE117" t="inlineStr"/>
+      <c r="EF117" t="inlineStr"/>
+      <c r="EG117" t="inlineStr"/>
+      <c r="EH117" t="inlineStr"/>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="EJ117" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EK117" t="inlineStr"/>
+      <c r="EL117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL117" headerRowCount="1">
-  <autoFilter ref="A1:EL117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL121" headerRowCount="1">
+  <autoFilter ref="A1:EL121"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL117"/>
+  <dimension ref="A1:EL121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE2" t="n">
         <v>1.5</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE3" t="n">
         <v>1.2</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -3150,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4057,7 +4057,7 @@
         <v>1.7</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         <v>0.76</v>
       </c>
       <c r="DO8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE10" t="n">
         <v>1.4</v>
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5919,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6345,7 +6345,7 @@
         <v>1.8</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF12" t="n">
         <v>0</v>
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6831,7 +6831,7 @@
         <v>2.01</v>
       </c>
       <c r="DO13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7254,7 +7254,7 @@
         <v>100</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE14" t="n">
         <v>1.5</v>
@@ -7287,7 +7287,7 @@
         <v>3.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7751,7 +7751,7 @@
         <v>2.69</v>
       </c>
       <c r="DO15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8169,7 +8169,7 @@
         <v>1.4</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>0.91</v>
       </c>
       <c r="DO16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8630,7 +8630,7 @@
         <v>100</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE17" t="n">
         <v>1.2</v>
@@ -8663,7 +8663,7 @@
         <v>2.96</v>
       </c>
       <c r="DO17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9089,7 +9089,7 @@
         <v>2.2</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9119,7 +9119,7 @@
         <v>1.58</v>
       </c>
       <c r="DO18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP18" t="b">
         <v>0</v>
@@ -9583,7 +9583,7 @@
         <v>3.11</v>
       </c>
       <c r="DO19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10001,7 +10001,7 @@
         <v>1.3</v>
       </c>
       <c r="DE20" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF20" t="n">
         <v>3</v>
@@ -10031,7 +10031,7 @@
         <v>2.67</v>
       </c>
       <c r="DO20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10454,7 +10454,7 @@
         <v>100</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE21" t="n">
         <v>1.2</v>
@@ -10487,7 +10487,7 @@
         <v>3.19</v>
       </c>
       <c r="DO21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10951,7 +10951,7 @@
         <v>3.1</v>
       </c>
       <c r="DO22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11407,7 +11407,7 @@
         <v>3.75</v>
       </c>
       <c r="DO23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11855,7 +11855,7 @@
         <v>2.85</v>
       </c>
       <c r="DO24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12278,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE25" t="n">
         <v>0.9</v>
@@ -12311,7 +12311,7 @@
         <v>2.63</v>
       </c>
       <c r="DO25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13206,7 +13206,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE27" t="n">
         <v>1.2</v>
@@ -13239,7 +13239,7 @@
         <v>2.72</v>
       </c>
       <c r="DO27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13681,7 +13681,7 @@
         <v>1.1</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DF28" t="n">
         <v>2</v>
@@ -13711,7 +13711,7 @@
         <v>1.98</v>
       </c>
       <c r="DO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14134,10 +14134,10 @@
         <v>100</v>
       </c>
       <c r="DD29" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DF29" t="n">
         <v>1.5</v>
@@ -14167,7 +14167,7 @@
         <v>2.35</v>
       </c>
       <c r="DO29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14601,7 +14601,7 @@
         <v>1.4</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF30" t="n">
         <v>3</v>
@@ -14631,7 +14631,7 @@
         <v>1.96</v>
       </c>
       <c r="DO30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15070,10 +15070,10 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE31" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15103,7 +15103,7 @@
         <v>2.43</v>
       </c>
       <c r="DO31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15567,7 +15567,7 @@
         <v>2.68</v>
       </c>
       <c r="DO32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15679,70 +15679,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>12</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>21</v>
+      </c>
+      <c r="V33" t="n">
         <v>11</v>
       </c>
-      <c r="L33" t="n">
-        <v>14</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>15</v>
-      </c>
-      <c r="U33" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>18</v>
-      </c>
       <c r="W33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -15752,97 +15752,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO33" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB33" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -15857,64 +15857,64 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK33" t="n">
         <v>3</v>
       </c>
-      <c r="BK33" t="n">
-        <v>1</v>
-      </c>
       <c r="BL33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO33" t="n">
         <v>0</v>
       </c>
       <c r="BP33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR33" t="n">
         <v>1</v>
       </c>
       <c r="BS33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU33" t="n">
         <v>1</v>
       </c>
       <c r="BV33" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW33" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX33" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY33" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA33" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -15947,7 +15947,7 @@
         <v>0</v>
       </c>
       <c r="CM33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
@@ -15962,141 +15962,141 @@
         <v>1</v>
       </c>
       <c r="CR33" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS33" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY33" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DE33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DF33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ33" t="n">
+        <v>17</v>
+      </c>
+      <c r="DK33" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DM33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DN33" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="DO33" t="n">
         <v>20</v>
       </c>
-      <c r="CT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV33" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>15</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>5</v>
-      </c>
-      <c r="CZ33" t="n">
-        <v>67</v>
-      </c>
-      <c r="DA33" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB33" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC33" t="n">
-        <v>67</v>
-      </c>
-      <c r="DD33" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DE33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="DF33" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DH33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DI33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ33" t="n">
-        <v>33</v>
-      </c>
-      <c r="DK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="DM33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DN33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="DO33" t="n">
-        <v>19</v>
-      </c>
       <c r="DP33" t="b">
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW33" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="DX33" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EF33" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="EI33" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ33" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EK33" t="inlineStr"/>
@@ -16143,70 +16143,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L34" t="n">
+        <v>14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>18</v>
+      </c>
+      <c r="W34" t="n">
         <v>10</v>
       </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>12</v>
-      </c>
-      <c r="R34" t="n">
-        <v>5</v>
-      </c>
-      <c r="S34" t="n">
-        <v>9</v>
-      </c>
-      <c r="T34" t="n">
-        <v>6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>21</v>
-      </c>
-      <c r="V34" t="n">
-        <v>11</v>
-      </c>
-      <c r="W34" t="n">
-        <v>11</v>
-      </c>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16216,97 +16216,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16321,271 +16321,271 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ34" t="n">
         <v>3</v>
       </c>
-      <c r="BJ34" t="n">
-        <v>2</v>
-      </c>
       <c r="BK34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB34" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR34" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY34" t="n">
         <v>5</v>
       </c>
-      <c r="BO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ34" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT34" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV34" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW34" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX34" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY34" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB34" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS34" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV34" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW34" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX34" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY34" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA34" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB34" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC34" t="n">
         <v>67</v>
       </c>
-      <c r="DC34" t="n">
-        <v>100</v>
-      </c>
       <c r="DD34" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DF34" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ34" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK34" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL34" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN34" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW34" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="DX34" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="DZ34" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EA34" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EB34" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC34" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="ED34" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EE34" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EG34" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EH34" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ34" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="DZ34" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EA34" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EB34" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EC34" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="ED34" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EE34" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EF34" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EG34" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EH34" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EJ34" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EK34" t="inlineStr"/>
@@ -16926,10 +16926,10 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE35" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF35" t="n">
         <v>2</v>
@@ -16959,7 +16959,7 @@
         <v>2.46</v>
       </c>
       <c r="DO35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17423,7 +17423,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17887,7 +17887,7 @@
         <v>3.08</v>
       </c>
       <c r="DO37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18343,7 +18343,7 @@
         <v>2.88</v>
       </c>
       <c r="DO38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18815,7 +18815,7 @@
         <v>3.56</v>
       </c>
       <c r="DO39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19263,7 +19263,7 @@
         <v>3.29</v>
       </c>
       <c r="DO40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19702,7 +19702,7 @@
         <v>100</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE41" t="n">
         <v>1.2</v>
@@ -19735,7 +19735,7 @@
         <v>3.25</v>
       </c>
       <c r="DO41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20625,7 +20625,7 @@
         <v>1.7</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -20655,7 +20655,7 @@
         <v>2.97</v>
       </c>
       <c r="DO43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21078,7 +21078,7 @@
         <v>71</v>
       </c>
       <c r="DD44" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE44" t="n">
         <v>0.9</v>
@@ -21111,7 +21111,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21567,7 +21567,7 @@
         <v>3.76</v>
       </c>
       <c r="DO45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22006,10 +22006,10 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE46" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF46" t="n">
         <v>1</v>
@@ -22039,7 +22039,7 @@
         <v>2.56</v>
       </c>
       <c r="DO46" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22465,7 +22465,7 @@
         <v>1.8</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -22495,7 +22495,7 @@
         <v>2.95</v>
       </c>
       <c r="DO47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22959,7 +22959,7 @@
         <v>2.69</v>
       </c>
       <c r="DO48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23362,7 +23362,7 @@
         <v>88</v>
       </c>
       <c r="DD49" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE49" t="n">
         <v>0.2</v>
@@ -23395,7 +23395,7 @@
         <v>2.22</v>
       </c>
       <c r="DO49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23826,7 +23826,7 @@
         <v>100</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE50" t="n">
         <v>1</v>
@@ -23859,7 +23859,7 @@
         <v>2.69</v>
       </c>
       <c r="DO50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24315,7 +24315,7 @@
         <v>3.7</v>
       </c>
       <c r="DO51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24763,7 +24763,7 @@
         <v>3.05</v>
       </c>
       <c r="DO52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25197,7 +25197,7 @@
         <v>1.3</v>
       </c>
       <c r="DE53" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DF53" t="n">
         <v>1.33</v>
@@ -25227,7 +25227,7 @@
         <v>3.35</v>
       </c>
       <c r="DO53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25653,7 +25653,7 @@
         <v>2.2</v>
       </c>
       <c r="DE54" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF54" t="n">
         <v>1.75</v>
@@ -25683,7 +25683,7 @@
         <v>3.92</v>
       </c>
       <c r="DO54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26570,7 +26570,7 @@
         <v>65</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE56" t="n">
         <v>1.5</v>
@@ -26603,7 +26603,7 @@
         <v>2.8</v>
       </c>
       <c r="DO56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27014,7 +27014,7 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE57" t="n">
         <v>1</v>
@@ -27047,7 +27047,7 @@
         <v>2.67</v>
       </c>
       <c r="DO57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27503,7 +27503,7 @@
         <v>2.65</v>
       </c>
       <c r="DO58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27937,7 +27937,7 @@
         <v>1.8</v>
       </c>
       <c r="DE59" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF59" t="n">
         <v>1.5</v>
@@ -27967,7 +27967,7 @@
         <v>2.98</v>
       </c>
       <c r="DO59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28431,7 +28431,7 @@
         <v>2.73</v>
       </c>
       <c r="DO60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28871,7 +28871,7 @@
         <v>3.65</v>
       </c>
       <c r="DO61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29282,7 +29282,7 @@
         <v>80</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE62" t="n">
         <v>1.2</v>
@@ -29315,7 +29315,7 @@
         <v>3.02</v>
       </c>
       <c r="DO62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -29763,7 +29763,7 @@
         <v>2.43</v>
       </c>
       <c r="DO63" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -30653,7 +30653,7 @@
         <v>2.2</v>
       </c>
       <c r="DE65" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DF65" t="n">
         <v>2</v>
@@ -30683,7 +30683,7 @@
         <v>3.44</v>
       </c>
       <c r="DO65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31109,7 +31109,7 @@
         <v>1.3</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DF66" t="n">
         <v>1.25</v>
@@ -31139,7 +31139,7 @@
         <v>3.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31578,10 +31578,10 @@
         <v>68</v>
       </c>
       <c r="DD67" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE67" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF67" t="n">
         <v>1.4</v>
@@ -31611,7 +31611,7 @@
         <v>3.08</v>
       </c>
       <c r="DO67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32059,7 +32059,7 @@
         <v>3.16</v>
       </c>
       <c r="DO68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32930,7 +32930,7 @@
         <v>100</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE70" t="n">
         <v>1.2</v>
@@ -32963,7 +32963,7 @@
         <v>2.44</v>
       </c>
       <c r="DO70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
@@ -33381,7 +33381,7 @@
         <v>1.7</v>
       </c>
       <c r="DE71" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF71" t="n">
         <v>2</v>
@@ -33411,7 +33411,7 @@
         <v>3.14</v>
       </c>
       <c r="DO71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -33883,7 +33883,7 @@
         <v>3.26</v>
       </c>
       <c r="DO72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34298,7 +34298,7 @@
         <v>80</v>
       </c>
       <c r="DD73" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE73" t="n">
         <v>1</v>
@@ -34331,7 +34331,7 @@
         <v>2.18</v>
       </c>
       <c r="DO73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34763,7 +34763,7 @@
         <v>3.72</v>
       </c>
       <c r="DO74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -34875,146 +34875,146 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>5</v>
+      </c>
+      <c r="R75" t="n">
+        <v>12</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="n">
+        <v>9</v>
+      </c>
+      <c r="U75" t="n">
+        <v>10</v>
+      </c>
+      <c r="V75" t="n">
+        <v>21</v>
+      </c>
+      <c r="W75" t="n">
         <v>6</v>
       </c>
-      <c r="K75" t="n">
-        <v>10</v>
-      </c>
-      <c r="L75" t="n">
-        <v>16</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>4</v>
-      </c>
-      <c r="R75" t="n">
+      <c r="X75" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
         <v>7</v>
       </c>
-      <c r="S75" t="n">
-        <v>9</v>
-      </c>
-      <c r="T75" t="n">
-        <v>7</v>
-      </c>
-      <c r="U75" t="n">
-        <v>13</v>
-      </c>
-      <c r="V75" t="n">
-        <v>14</v>
-      </c>
-      <c r="W75" t="n">
-        <v>15</v>
-      </c>
-      <c r="X75" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
-      <c r="AC75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AF75" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL75" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AM75" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN75" t="n">
         <v>1.83</v>
       </c>
       <c r="AO75" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AR75" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AS75" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AU75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW75" t="n">
         <v>2</v>
@@ -35023,22 +35023,22 @@
         <v>0</v>
       </c>
       <c r="AY75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB75" t="n">
-        <v>2522</v>
+        <v>955</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -35056,19 +35056,19 @@
         <v>3</v>
       </c>
       <c r="BJ75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO75" t="n">
         <v>1</v>
@@ -35077,7 +35077,7 @@
         <v>0</v>
       </c>
       <c r="BQ75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR75" t="n">
         <v>0</v>
@@ -35086,31 +35086,31 @@
         <v>1</v>
       </c>
       <c r="BT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU75" t="n">
         <v>1</v>
       </c>
       <c r="BV75" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BW75" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="BX75" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="BY75" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ75" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="CA75" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="CB75" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="CC75" t="n">
         <v>0</v>
@@ -35137,16 +35137,16 @@
         <v>1</v>
       </c>
       <c r="CK75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL75" t="n">
         <v>0</v>
       </c>
       <c r="CM75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO75" t="n">
         <v>0</v>
@@ -35158,76 +35158,76 @@
         <v>1</v>
       </c>
       <c r="CR75" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS75" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CT75" t="n">
         <v>1</v>
       </c>
       <c r="CU75" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CV75" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CW75" t="n">
         <v>1</v>
       </c>
       <c r="CX75" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY75" t="n">
         <v>4</v>
       </c>
-      <c r="CY75" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ75" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="DA75" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="DB75" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="DC75" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.89</v>
+        <v>1.8</v>
       </c>
       <c r="DF75" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG75" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH75" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="DI75" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="DJ75" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="DK75" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="DL75" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="DO75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35239,7 +35239,7 @@
         <v>1</v>
       </c>
       <c r="DS75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT75" t="b">
         <v>0</v>
@@ -35248,72 +35248,72 @@
         <v>0</v>
       </c>
       <c r="DV75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW75" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="DX75" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EE75" t="inlineStr"/>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EE75" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
       <c r="EF75" t="inlineStr"/>
       <c r="EG75" t="inlineStr"/>
-      <c r="EH75" t="inlineStr"/>
+      <c r="EH75" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EI75" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EJ75" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EK75" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EL75" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EK75" t="inlineStr"/>
+      <c r="EL75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -35331,146 +35331,146 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>6</v>
+      </c>
+      <c r="K76" t="n">
+        <v>10</v>
+      </c>
+      <c r="L76" t="n">
+        <v>16</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
         <v>4</v>
       </c>
-      <c r="I76" t="n">
-        <v>4</v>
-      </c>
-      <c r="J76" t="n">
+      <c r="R76" t="n">
         <v>7</v>
       </c>
-      <c r="K76" t="n">
+      <c r="S76" t="n">
+        <v>9</v>
+      </c>
+      <c r="T76" t="n">
+        <v>7</v>
+      </c>
+      <c r="U76" t="n">
+        <v>13</v>
+      </c>
+      <c r="V76" t="n">
+        <v>14</v>
+      </c>
+      <c r="W76" t="n">
+        <v>15</v>
+      </c>
+      <c r="X76" t="n">
         <v>5</v>
       </c>
-      <c r="L76" t="n">
-        <v>12</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>5</v>
-      </c>
-      <c r="R76" t="n">
-        <v>12</v>
-      </c>
-      <c r="S76" t="n">
-        <v>5</v>
-      </c>
-      <c r="T76" t="n">
-        <v>9</v>
-      </c>
-      <c r="U76" t="n">
-        <v>10</v>
-      </c>
-      <c r="V76" t="n">
-        <v>21</v>
-      </c>
-      <c r="W76" t="n">
-        <v>6</v>
-      </c>
-      <c r="X76" t="n">
-        <v>11</v>
-      </c>
       <c r="Y76" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z76" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AF76" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AL76" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AN76" t="n">
         <v>1.83</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AS76" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AU76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW76" t="n">
         <v>2</v>
@@ -35479,22 +35479,22 @@
         <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB76" t="n">
-        <v>955</v>
+        <v>2522</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -35512,178 +35512,178 @@
         <v>3</v>
       </c>
       <c r="BJ76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK76" t="n">
         <v>3</v>
       </c>
-      <c r="BK76" t="n">
+      <c r="BL76" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV76" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX76" t="n">
         <v>4</v>
       </c>
-      <c r="BL76" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM76" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN76" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV76" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW76" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX76" t="n">
-        <v>63</v>
-      </c>
-      <c r="BY76" t="n">
-        <v>102</v>
-      </c>
-      <c r="BZ76" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CA76" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CB76" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="CC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM76" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS76" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU76" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV76" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX76" t="n">
+      <c r="CY76" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ76" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA76" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB76" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC76" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD76" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE76" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DF76" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG76" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH76" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI76" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK76" t="n">
         <v>9</v>
       </c>
-      <c r="CY76" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ76" t="n">
-        <v>27</v>
-      </c>
-      <c r="DA76" t="n">
-        <v>72</v>
-      </c>
-      <c r="DB76" t="n">
-        <v>9</v>
-      </c>
-      <c r="DC76" t="n">
-        <v>45</v>
-      </c>
-      <c r="DD76" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DE76" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF76" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DG76" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DH76" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI76" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ76" t="n">
-        <v>74</v>
-      </c>
-      <c r="DK76" t="n">
-        <v>29</v>
-      </c>
       <c r="DL76" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="DO76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -35695,7 +35695,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -35704,72 +35704,72 @@
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW76" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="DX76" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EE76" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EE76" t="inlineStr"/>
       <c r="EF76" t="inlineStr"/>
       <c r="EG76" t="inlineStr"/>
-      <c r="EH76" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+      <c r="EH76" t="inlineStr"/>
       <c r="EI76" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EK76" t="inlineStr"/>
-      <c r="EL76" t="inlineStr"/>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK76" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -36131,7 +36131,7 @@
         <v>2.73</v>
       </c>
       <c r="DO77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -36587,7 +36587,7 @@
         <v>3.31</v>
       </c>
       <c r="DO78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP78" t="b">
         <v>0</v>
@@ -37026,10 +37026,10 @@
         <v>80</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE79" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF79" t="n">
         <v>1.67</v>
@@ -37059,7 +37059,7 @@
         <v>3.34</v>
       </c>
       <c r="DO79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37531,7 +37531,7 @@
         <v>3.11</v>
       </c>
       <c r="DO80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -37962,7 +37962,7 @@
         <v>79</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE81" t="n">
         <v>0.9</v>
@@ -37995,7 +37995,7 @@
         <v>2.66</v>
       </c>
       <c r="DO81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38426,7 +38426,7 @@
         <v>75</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE82" t="n">
         <v>0.2</v>
@@ -38459,7 +38459,7 @@
         <v>2.34</v>
       </c>
       <c r="DO82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -38903,7 +38903,7 @@
         <v>2.73</v>
       </c>
       <c r="DO83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -39337,7 +39337,7 @@
         <v>1.1</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF84" t="n">
         <v>1.67</v>
@@ -39367,7 +39367,7 @@
         <v>3.22</v>
       </c>
       <c r="DO84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -39801,7 +39801,7 @@
         <v>2.4</v>
       </c>
       <c r="DE85" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF85" t="n">
         <v>2.43</v>
@@ -39831,7 +39831,7 @@
         <v>3.51</v>
       </c>
       <c r="DO85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40254,10 +40254,10 @@
         <v>100</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE86" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DF86" t="n">
         <v>1.43</v>
@@ -40287,7 +40287,7 @@
         <v>2.75</v>
       </c>
       <c r="DO86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40399,143 +40399,143 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>6</v>
+      </c>
+      <c r="R87" t="n">
         <v>3</v>
       </c>
-      <c r="I87" t="n">
-        <v>3</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>8</v>
-      </c>
-      <c r="L87" t="n">
-        <v>9</v>
-      </c>
-      <c r="M87" t="n">
-        <v>2</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>2</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6</v>
-      </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T87" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U87" t="n">
         <v>11</v>
       </c>
       <c r="V87" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W87" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X87" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y87" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="Z87" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>1</v>
       </c>
       <c r="AE87" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="AF87" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG87" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL87" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AN87" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AP87" t="n">
         <v>1.82</v>
       </c>
-      <c r="AO87" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP87" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AQ87" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
         <v>0</v>
@@ -40544,25 +40544,25 @@
         <v>0</v>
       </c>
       <c r="AX87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA87" t="n">
         <v>0</v>
       </c>
       <c r="BB87" t="n">
-        <v>2526</v>
+        <v>3647</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -40580,22 +40580,22 @@
         <v>1</v>
       </c>
       <c r="BJ87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL87" t="n">
         <v>4</v>
       </c>
       <c r="BM87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN87" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP87" t="n">
         <v>1</v>
@@ -40607,7 +40607,7 @@
         <v>0</v>
       </c>
       <c r="BS87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT87" t="n">
         <v>0</v>
@@ -40616,25 +40616,25 @@
         <v>1</v>
       </c>
       <c r="BV87" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW87" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BX87" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="BY87" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="BZ87" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="CA87" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="CB87" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="CC87" t="n">
         <v>0</v>
@@ -40667,10 +40667,10 @@
         <v>0</v>
       </c>
       <c r="CM87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO87" t="n">
         <v>0</v>
@@ -40682,76 +40682,76 @@
         <v>1</v>
       </c>
       <c r="CR87" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="CS87" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
         <v>10</v>
       </c>
-      <c r="CT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU87" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV87" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX87" t="n">
+      <c r="CY87" t="n">
         <v>7</v>
       </c>
-      <c r="CY87" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ87" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="DA87" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC87" t="n">
         <v>79</v>
       </c>
-      <c r="DB87" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC87" t="n">
-        <v>64</v>
-      </c>
       <c r="DD87" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DF87" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="DG87" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DH87" t="n">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="DI87" t="n">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="DJ87" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="DK87" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="DL87" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="DN87" t="n">
-        <v>2.68</v>
+        <v>3.26</v>
       </c>
       <c r="DO87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -40760,7 +40760,7 @@
         <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS87" t="b">
         <v>0</v>
@@ -40776,66 +40776,66 @@
       </c>
       <c r="DW87" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="DX87" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="DY87" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="DZ87" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EA87" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="DY87" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="DZ87" t="inlineStr">
-        <is>
-          <t>3.84</t>
-        </is>
-      </c>
-      <c r="EA87" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EB87" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EC87" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="ED87" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EE87" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EF87" t="inlineStr"/>
-      <c r="EG87" t="inlineStr"/>
+      <c r="EG87" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
       <c r="EH87" t="inlineStr">
         <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EI87" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ87" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr"/>
+      <c r="EJ87" t="inlineStr"/>
       <c r="EK87" t="inlineStr"/>
       <c r="EL87" t="inlineStr"/>
     </row>
@@ -40855,143 +40855,143 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
+        <v>8</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2</v>
+      </c>
+      <c r="R88" t="n">
         <v>6</v>
       </c>
-      <c r="L88" t="n">
-        <v>10</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>6</v>
-      </c>
-      <c r="R88" t="n">
-        <v>3</v>
-      </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T88" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U88" t="n">
         <v>11</v>
       </c>
       <c r="V88" t="n">
+        <v>21</v>
+      </c>
+      <c r="W88" t="n">
         <v>14</v>
       </c>
-      <c r="W88" t="n">
-        <v>9</v>
-      </c>
       <c r="X88" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y88" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="Z88" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Vejle Stadion</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Roms Hule 3, Vejle</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD88" t="n">
         <v>1</v>
       </c>
       <c r="AE88" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="AF88" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AO88" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AU88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV88" t="n">
         <v>0</v>
@@ -41000,25 +41000,25 @@
         <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA88" t="n">
         <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>3647</v>
+        <v>2526</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
@@ -41036,175 +41036,175 @@
         <v>1</v>
       </c>
       <c r="BJ88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL88" t="n">
         <v>4</v>
       </c>
       <c r="BM88" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS88" t="n">
         <v>3</v>
       </c>
-      <c r="BN88" t="n">
+      <c r="BT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV88" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW88" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX88" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY88" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ88" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA88" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB88" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN88" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR88" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS88" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
         <v>7</v>
       </c>
-      <c r="BO88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV88" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW88" t="n">
+      <c r="CY88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ88" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA88" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC88" t="n">
         <v>64</v>
       </c>
-      <c r="BX88" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY88" t="n">
-        <v>153</v>
-      </c>
-      <c r="BZ88" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CA88" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB88" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CC88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP88" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR88" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS88" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU88" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV88" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX88" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY88" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ88" t="n">
-        <v>79</v>
-      </c>
-      <c r="DA88" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB88" t="n">
+      <c r="DD88" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE88" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DF88" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG88" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH88" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI88" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ88" t="n">
         <v>57</v>
       </c>
-      <c r="DC88" t="n">
-        <v>79</v>
-      </c>
-      <c r="DD88" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DE88" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DF88" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DG88" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DH88" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI88" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DJ88" t="n">
+      <c r="DK88" t="n">
         <v>22</v>
       </c>
-      <c r="DK88" t="n">
-        <v>0</v>
-      </c>
       <c r="DL88" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="DM88" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="DN88" t="n">
-        <v>3.26</v>
+        <v>2.68</v>
       </c>
       <c r="DO88" t="n">
         <v>20</v>
@@ -41216,7 +41216,7 @@
         <v>1</v>
       </c>
       <c r="DR88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS88" t="b">
         <v>0</v>
@@ -41232,66 +41232,66 @@
       </c>
       <c r="DW88" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="DX88" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EC88" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED88" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EE88" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EF88" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EG88" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr"/>
+      <c r="EG88" t="inlineStr"/>
       <c r="EH88" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EI88" t="inlineStr"/>
-      <c r="EJ88" t="inlineStr"/>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EK88" t="inlineStr"/>
       <c r="EL88" t="inlineStr"/>
     </row>
@@ -41625,7 +41625,7 @@
         <v>1.4</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DF89" t="n">
         <v>1.67</v>
@@ -41655,7 +41655,7 @@
         <v>2.65</v>
       </c>
       <c r="DO89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42095,7 +42095,7 @@
         <v>3.62</v>
       </c>
       <c r="DO90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42543,7 +42543,7 @@
         <v>3.1</v>
       </c>
       <c r="DO91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -42969,7 +42969,7 @@
         <v>1.1</v>
       </c>
       <c r="DE92" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF92" t="n">
         <v>1.43</v>
@@ -42999,7 +42999,7 @@
         <v>2.83</v>
       </c>
       <c r="DO92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43425,7 +43425,7 @@
         <v>1.3</v>
       </c>
       <c r="DE93" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF93" t="n">
         <v>1.43</v>
@@ -43455,7 +43455,7 @@
         <v>3.71</v>
       </c>
       <c r="DO93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -43894,7 +43894,7 @@
         <v>93</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DE94" t="n">
         <v>0.2</v>
@@ -43927,7 +43927,7 @@
         <v>2.31</v>
       </c>
       <c r="DO94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44383,7 +44383,7 @@
         <v>2.79</v>
       </c>
       <c r="DO95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -44814,10 +44814,10 @@
         <v>57</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DF96" t="n">
         <v>1.86</v>
@@ -44847,7 +44847,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45287,7 +45287,7 @@
         <v>2.56</v>
       </c>
       <c r="DO97" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -45702,7 +45702,7 @@
         <v>69</v>
       </c>
       <c r="DD98" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DE98" t="n">
         <v>1.4</v>
@@ -45735,7 +45735,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46191,7 +46191,7 @@
         <v>4.05</v>
       </c>
       <c r="DO99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
@@ -46663,7 +46663,7 @@
         <v>2.78</v>
       </c>
       <c r="DO100" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP100" t="b">
         <v>0</v>
@@ -47135,7 +47135,7 @@
         <v>3.44</v>
       </c>
       <c r="DO101" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -47558,7 +47558,7 @@
         <v>94</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DE102" t="n">
         <v>0.2</v>
@@ -47591,7 +47591,7 @@
         <v>2.62</v>
       </c>
       <c r="DO102" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48039,7 +48039,7 @@
         <v>2.76</v>
       </c>
       <c r="DO103" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48454,7 +48454,7 @@
         <v>69</v>
       </c>
       <c r="DD104" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DE104" t="n">
         <v>1.2</v>
@@ -48487,7 +48487,7 @@
         <v>2.57</v>
       </c>
       <c r="DO104" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -48583,146 +48583,146 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
         <v>45998.54166666666</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J105" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K105" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L105" t="n">
         <v>11</v>
       </c>
       <c r="M105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" t="n">
+        <v>10</v>
+      </c>
+      <c r="R105" t="n">
         <v>3</v>
-      </c>
-      <c r="R105" t="n">
-        <v>5</v>
       </c>
       <c r="S105" t="n">
         <v>7</v>
       </c>
       <c r="T105" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U105" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V105" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="W105" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="X105" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y105" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="Z105" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF105" t="n">
         <v>4</v>
       </c>
-      <c r="AE105" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AF105" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AG105" t="n">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AI105" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AJ105" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="AK105" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AL105" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AM105" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AO105" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AR105" t="n">
         <v>2.18</v>
       </c>
       <c r="AS105" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="AT105" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AU105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW105" t="n">
         <v>0</v>
@@ -48731,22 +48731,22 @@
         <v>1</v>
       </c>
       <c r="AY105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA105" t="n">
         <v>4</v>
       </c>
-      <c r="BA105" t="n">
-        <v>2</v>
-      </c>
       <c r="BB105" t="n">
-        <v>-1</v>
+        <v>986</v>
       </c>
       <c r="BC105" t="n">
         <v>0</v>
       </c>
       <c r="BD105" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE105" t="n">
         <v>0</v>
@@ -48761,181 +48761,181 @@
         <v>1</v>
       </c>
       <c r="BI105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK105" t="n">
         <v>2</v>
       </c>
       <c r="BL105" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BM105" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BN105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>82</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX105" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY105" t="n">
         <v>8</v>
-      </c>
-      <c r="BO105" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ105" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR105" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS105" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT105" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV105" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW105" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX105" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY105" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ105" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CA105" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB105" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CC105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR105" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS105" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU105" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV105" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX105" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY105" t="n">
-        <v>6</v>
       </c>
       <c r="CZ105" t="n">
         <v>63</v>
       </c>
       <c r="DA105" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="DB105" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC105" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.67</v>
+        <v>0.8</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
       </c>
       <c r="DG105" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DH105" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="DI105" t="n">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="DJ105" t="n">
         <v>38</v>
       </c>
       <c r="DK105" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="DL105" t="n">
-        <v>1.22</v>
+        <v>1.81</v>
       </c>
       <c r="DM105" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="DN105" t="n">
-        <v>2.56</v>
+        <v>3.06</v>
       </c>
       <c r="DO105" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -48953,71 +48953,79 @@
         <v>1</v>
       </c>
       <c r="DU105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW105" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="DX105" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DY105" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="DZ105" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="EA105" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="EB105" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC105" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="ED105" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="EE105" t="inlineStr">
         <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF105" t="inlineStr"/>
-      <c r="EG105" t="inlineStr"/>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EG105" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
       <c r="EH105" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EI105" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EJ105" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK105" t="inlineStr"/>
@@ -49039,170 +49047,170 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
         <v>45998.54166666666</v>
       </c>
       <c r="G106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J106" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K106" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L106" t="n">
         <v>11</v>
       </c>
       <c r="M106" t="n">
+        <v>2</v>
+      </c>
+      <c r="N106" t="n">
         <v>4</v>
       </c>
-      <c r="N106" t="n">
-        <v>1</v>
-      </c>
       <c r="O106" t="n">
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S106" t="n">
         <v>7</v>
       </c>
       <c r="T106" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U106" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V106" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="W106" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="X106" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y106" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="Z106" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD106" t="n">
         <v>4</v>
       </c>
-      <c r="AD106" t="n">
-        <v>3</v>
-      </c>
       <c r="AE106" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="AF106" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG106" t="n">
-        <v>4</v>
+        <v>1.66</v>
       </c>
       <c r="AH106" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AI106" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AJ106" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AK106" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AL106" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AM106" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AN106" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AO106" t="n">
-        <v>2.37</v>
+        <v>2.87</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AR106" t="n">
         <v>2.18</v>
       </c>
       <c r="AS106" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="AT106" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AU106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ106" t="n">
         <v>4</v>
       </c>
-      <c r="AW106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ106" t="n">
-        <v>1</v>
-      </c>
       <c r="BA106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB106" t="n">
-        <v>986</v>
+        <v>-1</v>
       </c>
       <c r="BC106" t="n">
         <v>0</v>
       </c>
       <c r="BD106" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE106" t="n">
         <v>0</v>
@@ -49217,73 +49225,73 @@
         <v>1</v>
       </c>
       <c r="BI106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BJ106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK106" t="n">
         <v>2</v>
       </c>
       <c r="BL106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM106" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BN106" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BO106" t="n">
         <v>2</v>
       </c>
       <c r="BP106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BT106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU106" t="n">
         <v>1</v>
       </c>
       <c r="BV106" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="BW106" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="BX106" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="BY106" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="BZ106" t="n">
-        <v>2.37</v>
+        <v>1.16</v>
       </c>
       <c r="CA106" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="CB106" t="n">
-        <v>3.57</v>
+        <v>3.16</v>
       </c>
       <c r="CC106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD106" t="n">
         <v>0</v>
       </c>
       <c r="CE106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF106" t="n">
         <v>0</v>
@@ -49307,13 +49315,13 @@
         <v>0</v>
       </c>
       <c r="CM106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP106" t="n">
         <v>0</v>
@@ -49322,76 +49330,76 @@
         <v>1</v>
       </c>
       <c r="CR106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CS106" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU106" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV106" t="n">
         <v>16</v>
       </c>
-      <c r="CT106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU106" t="n">
-        <v>5</v>
-      </c>
-      <c r="CV106" t="n">
-        <v>11</v>
-      </c>
       <c r="CW106" t="n">
         <v>1</v>
       </c>
       <c r="CX106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CY106" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CZ106" t="n">
         <v>63</v>
       </c>
       <c r="DA106" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="DB106" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC106" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="DD106" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE106" t="n">
         <v>1.8</v>
-      </c>
-      <c r="DE106" t="n">
-        <v>0.89</v>
       </c>
       <c r="DF106" t="n">
         <v>1.5</v>
       </c>
       <c r="DG106" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DH106" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="DI106" t="n">
-        <v>1.12</v>
+        <v>2.06</v>
       </c>
       <c r="DJ106" t="n">
         <v>38</v>
       </c>
       <c r="DK106" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="DL106" t="n">
-        <v>1.81</v>
+        <v>1.22</v>
       </c>
       <c r="DM106" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="DN106" t="n">
-        <v>3.06</v>
+        <v>2.56</v>
       </c>
       <c r="DO106" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -49409,79 +49417,71 @@
         <v>1</v>
       </c>
       <c r="DU106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW106" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="DX106" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DY106" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="DZ106" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="EA106" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EB106" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC106" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="ED106" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EE106" t="inlineStr">
         <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EF106" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EG106" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr"/>
+      <c r="EG106" t="inlineStr"/>
       <c r="EH106" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI106" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="EJ106" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EK106" t="inlineStr"/>
@@ -49817,7 +49817,7 @@
         <v>1.4</v>
       </c>
       <c r="DE107" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DF107" t="n">
         <v>1.38</v>
@@ -49847,7 +49847,7 @@
         <v>2.84</v>
       </c>
       <c r="DO107" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50303,7 +50303,7 @@
         <v>3.27</v>
       </c>
       <c r="DO108" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -50729,7 +50729,7 @@
         <v>1.1</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DF109" t="n">
         <v>1</v>
@@ -50759,7 +50759,7 @@
         <v>3.17</v>
       </c>
       <c r="DO109" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51215,7 +51215,7 @@
         <v>3.24</v>
       </c>
       <c r="DO110" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -51679,7 +51679,7 @@
         <v>2.95</v>
       </c>
       <c r="DO111" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52143,7 +52143,7 @@
         <v>3.75</v>
       </c>
       <c r="DO112" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52599,7 +52599,7 @@
         <v>3.1</v>
       </c>
       <c r="DO113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP113" t="b">
         <v>0</v>
@@ -53071,7 +53071,7 @@
         <v>2.43</v>
       </c>
       <c r="DO114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -53511,7 +53511,7 @@
         <v>3.43</v>
       </c>
       <c r="DO115" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -54502,6 +54502,1846 @@
       </c>
       <c r="EK117" t="inlineStr"/>
       <c r="EL117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>20</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>46068.54166666666</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" t="n">
+        <v>4</v>
+      </c>
+      <c r="K118" t="n">
+        <v>11</v>
+      </c>
+      <c r="L118" t="n">
+        <v>15</v>
+      </c>
+      <c r="M118" t="n">
+        <v>3</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1</v>
+      </c>
+      <c r="R118" t="n">
+        <v>5</v>
+      </c>
+      <c r="S118" t="n">
+        <v>8</v>
+      </c>
+      <c r="T118" t="n">
+        <v>14</v>
+      </c>
+      <c r="U118" t="n">
+        <v>9</v>
+      </c>
+      <c r="V118" t="n">
+        <v>19</v>
+      </c>
+      <c r="W118" t="n">
+        <v>19</v>
+      </c>
+      <c r="X118" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>10</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>86</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU118" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV118" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW118" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX118" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY118" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ118" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA118" t="n">
+        <v>95</v>
+      </c>
+      <c r="DB118" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC118" t="n">
+        <v>73</v>
+      </c>
+      <c r="DD118" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DF118" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DG118" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DH118" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DI118" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DJ118" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK118" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL118" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DM118" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DN118" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DO118" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU118" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV118" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW118" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DX118" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DY118" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="DZ118" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="EA118" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EB118" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC118" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="ED118" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EE118" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EF118" t="inlineStr"/>
+      <c r="EG118" t="inlineStr"/>
+      <c r="EH118" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EI118" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EJ118" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EK118" t="inlineStr"/>
+      <c r="EL118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>20</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>46068.625</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>4</v>
+      </c>
+      <c r="K119" t="n">
+        <v>6</v>
+      </c>
+      <c r="L119" t="n">
+        <v>10</v>
+      </c>
+      <c r="M119" t="n">
+        <v>2</v>
+      </c>
+      <c r="N119" t="n">
+        <v>2</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>6</v>
+      </c>
+      <c r="R119" t="n">
+        <v>10</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="n">
+        <v>8</v>
+      </c>
+      <c r="U119" t="n">
+        <v>11</v>
+      </c>
+      <c r="V119" t="n">
+        <v>18</v>
+      </c>
+      <c r="W119" t="n">
+        <v>11</v>
+      </c>
+      <c r="X119" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>Nature Energy Park</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>Højstrupvej 7B, Odense</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>955</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>49</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU119" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV119" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX119" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY119" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ119" t="n">
+        <v>61</v>
+      </c>
+      <c r="DA119" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB119" t="n">
+        <v>39</v>
+      </c>
+      <c r="DC119" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD119" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DG119" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH119" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DI119" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="DJ119" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK119" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL119" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM119" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN119" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="DO119" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW119" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="DX119" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="DY119" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="DZ119" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="EA119" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EB119" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="ED119" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EF119" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="EH119" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EI119" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EJ119" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EK119" t="inlineStr"/>
+      <c r="EL119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>20</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Viborg</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Brøndby</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>46068.70833333334</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>3</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3</v>
+      </c>
+      <c r="L120" t="n">
+        <v>6</v>
+      </c>
+      <c r="M120" t="n">
+        <v>4</v>
+      </c>
+      <c r="N120" t="n">
+        <v>1</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>6</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2</v>
+      </c>
+      <c r="S120" t="n">
+        <v>8</v>
+      </c>
+      <c r="T120" t="n">
+        <v>6</v>
+      </c>
+      <c r="U120" t="n">
+        <v>14</v>
+      </c>
+      <c r="V120" t="n">
+        <v>8</v>
+      </c>
+      <c r="W120" t="n">
+        <v>17</v>
+      </c>
+      <c r="X120" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>Energi Viborg Arena</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>Stadion Allé 7, Viborg</t>
+        </is>
+      </c>
+      <c r="AC120" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>2526</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU120" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV120" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW120" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX120" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY120" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ120" t="n">
+        <v>56</v>
+      </c>
+      <c r="DA120" t="n">
+        <v>78</v>
+      </c>
+      <c r="DB120" t="n">
+        <v>56</v>
+      </c>
+      <c r="DC120" t="n">
+        <v>78</v>
+      </c>
+      <c r="DD120" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE120" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF120" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG120" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DH120" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DI120" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DJ120" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK120" t="n">
+        <v>22</v>
+      </c>
+      <c r="DL120" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DM120" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DN120" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DO120" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP120" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV120" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW120" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="DX120" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="DY120" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="DZ120" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="EA120" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EB120" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EC120" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="ED120" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EE120" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EF120" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EG120" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EH120" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EI120" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EJ120" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EK120" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL120" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>20</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SønderjyskE</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>46069.75</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" t="n">
+        <v>3</v>
+      </c>
+      <c r="K121" t="n">
+        <v>3</v>
+      </c>
+      <c r="L121" t="n">
+        <v>6</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1</v>
+      </c>
+      <c r="N121" t="n">
+        <v>4</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>6</v>
+      </c>
+      <c r="R121" t="n">
+        <v>3</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="n">
+        <v>6</v>
+      </c>
+      <c r="U121" t="n">
+        <v>16</v>
+      </c>
+      <c r="V121" t="n">
+        <v>9</v>
+      </c>
+      <c r="W121" t="n">
+        <v>9</v>
+      </c>
+      <c r="X121" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>Sydbank Park</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Stadionvej 7, Haderslev</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>2519</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>74</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>78</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU121" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV121" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX121" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY121" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ121" t="n">
+        <v>73</v>
+      </c>
+      <c r="DA121" t="n">
+        <v>89</v>
+      </c>
+      <c r="DB121" t="n">
+        <v>56</v>
+      </c>
+      <c r="DC121" t="n">
+        <v>89</v>
+      </c>
+      <c r="DD121" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE121" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DF121" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DG121" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DH121" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DI121" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ121" t="n">
+        <v>28</v>
+      </c>
+      <c r="DK121" t="n">
+        <v>11</v>
+      </c>
+      <c r="DL121" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DM121" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN121" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="DO121" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW121" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="DX121" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="DY121" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DZ121" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EA121" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="EB121" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EC121" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="ED121" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EE121" t="inlineStr"/>
+      <c r="EF121" t="inlineStr"/>
+      <c r="EG121" t="inlineStr"/>
+      <c r="EH121" t="inlineStr"/>
+      <c r="EI121" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EJ121" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EK121" t="inlineStr"/>
+      <c r="EL121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL121" headerRowCount="1">
-  <autoFilter ref="A1:EL121"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL123" headerRowCount="1">
+  <autoFilter ref="A1:EL123"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL121"/>
+  <dimension ref="A1:EL123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1777,7 +1777,7 @@
         <v>1.6</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -4977,7 +4977,7 @@
         <v>1.3</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE10" t="n">
         <v>1.4</v>
@@ -6342,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE12" t="n">
         <v>1.5</v>
@@ -7257,7 +7257,7 @@
         <v>0.8</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7751,7 +7751,7 @@
         <v>2.69</v>
       </c>
       <c r="DO15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -11825,7 +11825,7 @@
         <v>1.7</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF24" t="n">
         <v>1.5</v>
@@ -12278,7 +12278,7 @@
         <v>75</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE25" t="n">
         <v>0.9</v>
@@ -12742,10 +12742,10 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF26" t="n">
         <v>0</v>
@@ -12775,7 +12775,7 @@
         <v>4.08</v>
       </c>
       <c r="DO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -15070,7 +15070,7 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE31" t="n">
         <v>2.2</v>
@@ -15567,7 +15567,7 @@
         <v>2.68</v>
       </c>
       <c r="DO32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15679,70 +15679,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L33" t="n">
+        <v>14</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>15</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" t="n">
         <v>10</v>
       </c>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>12</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>9</v>
-      </c>
-      <c r="T33" t="n">
-        <v>6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>21</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>11</v>
-      </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -15752,97 +15752,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB33" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -15857,178 +15857,178 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ33" t="n">
         <v>3</v>
       </c>
-      <c r="BJ33" t="n">
-        <v>2</v>
-      </c>
       <c r="BK33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY33" t="n">
         <v>5</v>
       </c>
-      <c r="BO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB33" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS33" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA33" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB33" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC33" t="n">
         <v>67</v>
       </c>
-      <c r="DC33" t="n">
-        <v>100</v>
-      </c>
       <c r="DD33" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="DF33" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG33" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH33" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI33" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ33" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL33" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN33" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO33" t="n">
         <v>20</v>
@@ -16037,91 +16037,91 @@
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW33" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="DX33" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="DZ33" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EA33" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EB33" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC33" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EG33" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EH33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="DZ33" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EA33" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EB33" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EC33" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="ED33" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EE33" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EF33" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EG33" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EH33" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EJ33" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EK33" t="inlineStr"/>
@@ -16143,70 +16143,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>12</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>21</v>
+      </c>
+      <c r="V34" t="n">
         <v>11</v>
       </c>
-      <c r="L34" t="n">
-        <v>14</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>15</v>
-      </c>
-      <c r="U34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>18</v>
-      </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16216,97 +16216,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO34" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB34" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16321,64 +16321,64 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK34" t="n">
         <v>3</v>
       </c>
-      <c r="BK34" t="n">
-        <v>1</v>
-      </c>
       <c r="BL34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO34" t="n">
         <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR34" t="n">
         <v>1</v>
       </c>
       <c r="BS34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW34" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX34" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY34" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -16411,7 +16411,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -16426,73 +16426,73 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS34" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CY34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB34" t="n">
         <v>67</v>
       </c>
-      <c r="DA34" t="n">
+      <c r="DC34" t="n">
         <v>100</v>
       </c>
-      <c r="DB34" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC34" t="n">
-        <v>67</v>
-      </c>
       <c r="DD34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DE34" t="n">
         <v>0.8</v>
       </c>
-      <c r="DE34" t="n">
-        <v>0.9</v>
-      </c>
       <c r="DF34" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG34" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DJ34" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK34" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO34" t="n">
         <v>20</v>
@@ -16501,66 +16501,66 @@
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW34" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="DX34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
@@ -16580,12 +16580,12 @@
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EK34" t="inlineStr"/>
@@ -17393,7 +17393,7 @@
         <v>2.2</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF36" t="n">
         <v>0.5</v>
@@ -17854,7 +17854,7 @@
         <v>75</v>
       </c>
       <c r="DD37" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE37" t="n">
         <v>1.4</v>
@@ -19702,7 +19702,7 @@
         <v>100</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE41" t="n">
         <v>1.2</v>
@@ -19735,7 +19735,7 @@
         <v>3.25</v>
       </c>
       <c r="DO41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20153,7 +20153,7 @@
         <v>1.4</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF42" t="n">
         <v>1.5</v>
@@ -21537,7 +21537,7 @@
         <v>1.7</v>
       </c>
       <c r="DE45" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF45" t="n">
         <v>1.5</v>
@@ -22462,7 +22462,7 @@
         <v>34</v>
       </c>
       <c r="DD47" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE47" t="n">
         <v>1.8</v>
@@ -23365,7 +23365,7 @@
         <v>0.8</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF49" t="n">
         <v>1.5</v>
@@ -23826,7 +23826,7 @@
         <v>100</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE50" t="n">
         <v>1</v>
@@ -26573,7 +26573,7 @@
         <v>2</v>
       </c>
       <c r="DE56" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF56" t="n">
         <v>1.75</v>
@@ -27473,7 +27473,7 @@
         <v>1.1</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF58" t="n">
         <v>1.5</v>
@@ -27934,7 +27934,7 @@
         <v>88</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE59" t="n">
         <v>2.2</v>
@@ -29282,7 +29282,7 @@
         <v>80</v>
       </c>
       <c r="DD62" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE62" t="n">
         <v>1.2</v>
@@ -29419,22 +29419,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -29443,16 +29443,16 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -29461,120 +29461,128 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V63" t="n">
         <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X63" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y63" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z63" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AF63" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AN63" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AU63" t="n">
         <v>3</v>
       </c>
       <c r="AV63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX63" t="n">
         <v>0</v>
       </c>
       <c r="AY63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB63" t="n">
-        <v>2521</v>
+        <v>986</v>
       </c>
       <c r="BC63" t="n">
         <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="BE63" t="n">
         <v>0</v>
@@ -29589,181 +29597,181 @@
         <v>1</v>
       </c>
       <c r="BI63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK63" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU63" t="n">
         <v>3</v>
       </c>
-      <c r="BL63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV63" t="n">
-        <v>53</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>63</v>
-      </c>
-      <c r="BX63" t="n">
-        <v>84</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ63" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CA63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CB63" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM63" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS63" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU63" t="n">
-        <v>12</v>
-      </c>
       <c r="CV63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW63" t="n">
         <v>1</v>
       </c>
       <c r="CX63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ63" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA63" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DB63" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="DC63" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DF63" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG63" t="n">
         <v>1.2</v>
       </c>
       <c r="DH63" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="DI63" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ63" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK63" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="DL63" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="DM63" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="DN63" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="DO63" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -29784,70 +29792,86 @@
         <v>0</v>
       </c>
       <c r="DV63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW63" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="DX63" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="DY63" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="DZ63" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EA63" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EB63" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EC63" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="ED63" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EE63" t="inlineStr"/>
-      <c r="EF63" t="inlineStr"/>
-      <c r="EG63" t="inlineStr"/>
-      <c r="EH63" t="inlineStr"/>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EE63" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF63" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG63" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH63" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EI63" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EJ63" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK63" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EL63" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.34</t>
         </is>
       </c>
     </row>
@@ -29867,22 +29891,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>3</v>
@@ -29891,16 +29915,16 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -29909,128 +29933,120 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V64" t="n">
         <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y64" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z64" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE64" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF64" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL64" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AM64" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AN64" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AO64" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AS64" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AU64" t="n">
         <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX64" t="n">
         <v>0</v>
       </c>
       <c r="AY64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB64" t="n">
-        <v>986</v>
+        <v>2521</v>
       </c>
       <c r="BC64" t="n">
         <v>0</v>
       </c>
       <c r="BD64" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="BE64" t="n">
         <v>0</v>
@@ -30045,37 +30061,37 @@
         <v>1</v>
       </c>
       <c r="BI64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL64" t="n">
         <v>2</v>
       </c>
       <c r="BM64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN64" t="n">
         <v>5</v>
       </c>
-      <c r="BN64" t="n">
-        <v>6</v>
-      </c>
       <c r="BO64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP64" t="n">
         <v>0</v>
       </c>
       <c r="BQ64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT64" t="n">
         <v>2</v>
@@ -30084,25 +30100,25 @@
         <v>1</v>
       </c>
       <c r="BV64" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BW64" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="BX64" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BY64" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="BZ64" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="CB64" t="n">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="CC64" t="n">
         <v>0</v>
@@ -30135,7 +30151,7 @@
         <v>0</v>
       </c>
       <c r="CM64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
@@ -30150,73 +30166,73 @@
         <v>1</v>
       </c>
       <c r="CR64" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CS64" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT64" t="n">
         <v>1</v>
       </c>
       <c r="CU64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CV64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW64" t="n">
         <v>1</v>
       </c>
       <c r="CX64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ64" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="DA64" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DB64" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="DC64" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="DD64" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DF64" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DG64" t="n">
         <v>1.2</v>
       </c>
       <c r="DH64" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="DI64" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ64" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK64" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="DL64" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="DM64" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="DN64" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="DO64" t="n">
         <v>20</v>
@@ -30240,86 +30256,70 @@
         <v>0</v>
       </c>
       <c r="DV64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW64" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="DX64" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY64" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="DZ64" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EA64" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EB64" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EC64" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED64" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EE64" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EF64" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EG64" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EH64" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EE64" t="inlineStr"/>
+      <c r="EF64" t="inlineStr"/>
+      <c r="EG64" t="inlineStr"/>
+      <c r="EH64" t="inlineStr"/>
       <c r="EI64" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EJ64" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EK64" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL64" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -32029,7 +32029,7 @@
         <v>1.1</v>
       </c>
       <c r="DE68" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF68" t="n">
         <v>1.4</v>
@@ -32163,12 +32163,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -32178,25 +32178,25 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
+        <v>9</v>
+      </c>
+      <c r="K69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" t="n">
-        <v>3</v>
-      </c>
       <c r="L69" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -32205,102 +32205,102 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T69" t="n">
         <v>10</v>
       </c>
       <c r="U69" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V69" t="n">
+        <v>18</v>
+      </c>
+      <c r="W69" t="n">
+        <v>6</v>
+      </c>
+      <c r="X69" t="n">
         <v>13</v>
       </c>
-      <c r="W69" t="n">
-        <v>10</v>
-      </c>
-      <c r="X69" t="n">
-        <v>11</v>
-      </c>
       <c r="Y69" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="Z69" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU69" t="n">
         <v>3</v>
       </c>
-      <c r="AD69" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN69" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO69" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP69" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ69" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU69" t="n">
-        <v>1</v>
-      </c>
       <c r="AV69" t="n">
         <v>1</v>
       </c>
@@ -32311,22 +32311,22 @@
         <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA69" t="n">
         <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>986</v>
+        <v>2523</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="BE69" t="n">
         <v>0</v>
@@ -32335,46 +32335,46 @@
         <v>-1</v>
       </c>
       <c r="BG69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH69" t="n">
         <v>1</v>
       </c>
       <c r="BI69" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BJ69" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK69" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM69" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BN69" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR69" t="n">
         <v>1</v>
       </c>
       <c r="BS69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
@@ -32383,136 +32383,136 @@
         <v>17</v>
       </c>
       <c r="BW69" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BX69" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>40</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR69" t="n">
         <v>35</v>
       </c>
-      <c r="BY69" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ69" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB69" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>16</v>
-      </c>
       <c r="CS69" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU69" t="n">
         <v>14</v>
       </c>
-      <c r="CT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU69" t="n">
-        <v>12</v>
-      </c>
       <c r="CV69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW69" t="n">
         <v>1</v>
       </c>
       <c r="CX69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CY69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ69" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA69" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="DB69" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="DC69" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="DF69" t="n">
         <v>1.2</v>
       </c>
       <c r="DG69" t="n">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="DH69" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="DI69" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="DJ69" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK69" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="DL69" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="DN69" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="DO69" t="n">
         <v>20</v>
@@ -32521,10 +32521,10 @@
         <v>1</v>
       </c>
       <c r="DQ69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS69" t="b">
         <v>0</v>
@@ -32536,46 +32536,46 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW69" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="DX69" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="DZ69" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EA69" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EB69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EC69" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="ED69" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EE69" t="inlineStr"/>
@@ -32584,12 +32584,12 @@
       <c r="EH69" t="inlineStr"/>
       <c r="EI69" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EJ69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EK69" t="inlineStr"/>
@@ -32611,12 +32611,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -32626,25 +32626,25 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" t="n">
         <v>3</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>9</v>
       </c>
-      <c r="K70" t="n">
-        <v>6</v>
-      </c>
-      <c r="L70" t="n">
-        <v>15</v>
-      </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -32653,101 +32653,101 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R70" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="n">
         <v>10</v>
       </c>
       <c r="U70" t="n">
+        <v>14</v>
+      </c>
+      <c r="V70" t="n">
+        <v>13</v>
+      </c>
+      <c r="W70" t="n">
         <v>10</v>
       </c>
-      <c r="V70" t="n">
-        <v>18</v>
-      </c>
-      <c r="W70" t="n">
-        <v>6</v>
-      </c>
       <c r="X70" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y70" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="Z70" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AK70" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL70" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AM70" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN70" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AO70" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AS70" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AU70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV70" t="n">
         <v>1</v>
@@ -32759,22 +32759,22 @@
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
       </c>
       <c r="BB70" t="n">
-        <v>2523</v>
+        <v>986</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -32783,46 +32783,46 @@
         <v>-1</v>
       </c>
       <c r="BG70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH70" t="n">
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BJ70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM70" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BN70" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR70" t="n">
         <v>1</v>
       </c>
       <c r="BS70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU70" t="n">
         <v>1</v>
@@ -32831,22 +32831,22 @@
         <v>17</v>
       </c>
       <c r="BW70" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BX70" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BY70" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BZ70" t="n">
-        <v>0.89</v>
+        <v>1.49</v>
       </c>
       <c r="CA70" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CC70" t="n">
         <v>0</v>
@@ -32873,16 +32873,16 @@
         <v>1</v>
       </c>
       <c r="CK70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL70" t="n">
         <v>0</v>
       </c>
       <c r="CM70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO70" t="n">
         <v>0</v>
@@ -32894,73 +32894,73 @@
         <v>1</v>
       </c>
       <c r="CR70" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="CS70" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT70" t="n">
         <v>1</v>
       </c>
       <c r="CU70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV70" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY70" t="n">
         <v>7</v>
       </c>
-      <c r="CW70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX70" t="n">
+      <c r="CZ70" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB70" t="n">
         <v>9</v>
       </c>
-      <c r="CY70" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ70" t="n">
-        <v>80</v>
-      </c>
-      <c r="DA70" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB70" t="n">
-        <v>80</v>
-      </c>
       <c r="DC70" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="DF70" t="n">
         <v>1.2</v>
       </c>
       <c r="DG70" t="n">
-        <v>0.4</v>
+        <v>1.17</v>
       </c>
       <c r="DH70" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="DI70" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="DJ70" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK70" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="DL70" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="DM70" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="DN70" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="DO70" t="n">
         <v>20</v>
@@ -32969,10 +32969,10 @@
         <v>1</v>
       </c>
       <c r="DQ70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS70" t="b">
         <v>0</v>
@@ -32984,46 +32984,46 @@
         <v>0</v>
       </c>
       <c r="DV70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW70" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="DX70" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DY70" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="DZ70" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EA70" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EB70" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="DY70" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="DZ70" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="EA70" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EB70" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EC70" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="ED70" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EE70" t="inlineStr"/>
@@ -33032,12 +33032,12 @@
       <c r="EH70" t="inlineStr"/>
       <c r="EI70" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EJ70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EK70" t="inlineStr"/>
@@ -33853,7 +33853,7 @@
         <v>2.4</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF72" t="n">
         <v>2.33</v>
@@ -37026,7 +37026,7 @@
         <v>80</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE79" t="n">
         <v>1.5</v>
@@ -38429,7 +38429,7 @@
         <v>2</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF82" t="n">
         <v>1.67</v>
@@ -38870,7 +38870,7 @@
         <v>84</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE83" t="n">
         <v>1.2</v>
@@ -38903,7 +38903,7 @@
         <v>2.73</v>
       </c>
       <c r="DO83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -40254,7 +40254,7 @@
         <v>100</v>
       </c>
       <c r="DD86" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE86" t="n">
         <v>0.8</v>
@@ -40721,7 +40721,7 @@
         <v>1.1</v>
       </c>
       <c r="DE87" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF87" t="n">
         <v>0.71</v>
@@ -40751,7 +40751,7 @@
         <v>3.26</v>
       </c>
       <c r="DO87" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -43897,7 +43897,7 @@
         <v>1.6</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF94" t="n">
         <v>1.29</v>
@@ -44350,7 +44350,7 @@
         <v>86</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE95" t="n">
         <v>1</v>
@@ -45847,40 +45847,40 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K99" t="n">
         <v>6</v>
       </c>
       <c r="L99" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M99" t="n">
         <v>2</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -45892,117 +45892,125 @@
         <v>4</v>
       </c>
       <c r="R99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U99" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V99" t="n">
+        <v>14</v>
+      </c>
+      <c r="W99" t="n">
         <v>10</v>
       </c>
-      <c r="W99" t="n">
-        <v>14</v>
-      </c>
       <c r="X99" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y99" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Z99" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
       <c r="AC99" t="n">
         <v>2</v>
       </c>
       <c r="AD99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE99" t="n">
         <v>2.37</v>
       </c>
       <c r="AF99" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL99" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AN99" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="AO99" t="n">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AS99" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AT99" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AU99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW99" t="n">
         <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
         <v>0</v>
       </c>
       <c r="AZ99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>2516</v>
+        <v>-1</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -46017,19 +46025,19 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK99" t="n">
         <v>3</v>
       </c>
-      <c r="BJ99" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK99" t="n">
-        <v>5</v>
-      </c>
       <c r="BL99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BM99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN99" t="n">
         <v>9</v>
@@ -46038,43 +46046,43 @@
         <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ99" t="n">
         <v>2</v>
       </c>
       <c r="BR99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BW99" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="BX99" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="BY99" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.06</v>
+        <v>1.46</v>
       </c>
       <c r="CB99" t="n">
-        <v>2.28</v>
+        <v>3.24</v>
       </c>
       <c r="CC99" t="n">
         <v>0</v>
@@ -46101,16 +46109,16 @@
         <v>1</v>
       </c>
       <c r="CK99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL99" t="n">
         <v>0</v>
       </c>
       <c r="CM99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO99" t="n">
         <v>0</v>
@@ -46122,82 +46130,82 @@
         <v>1</v>
       </c>
       <c r="CR99" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS99" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU99" t="n">
         <v>12</v>
       </c>
-      <c r="CS99" t="n">
+      <c r="CV99" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW99" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX99" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY99" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ99" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>82</v>
+      </c>
+      <c r="DB99" t="n">
+        <v>44</v>
+      </c>
+      <c r="DC99" t="n">
+        <v>76</v>
+      </c>
+      <c r="DD99" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE99" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK99" t="n">
         <v>19</v>
       </c>
-      <c r="CT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU99" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV99" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW99" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX99" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY99" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ99" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA99" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB99" t="n">
-        <v>38</v>
-      </c>
-      <c r="DC99" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD99" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DE99" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DF99" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG99" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DH99" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DI99" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DJ99" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK99" t="n">
-        <v>25</v>
-      </c>
       <c r="DL99" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="DN99" t="n">
-        <v>4.05</v>
+        <v>2.78</v>
       </c>
       <c r="DO99" t="n">
         <v>20</v>
       </c>
       <c r="DP99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR99" t="b">
         <v>0</v>
@@ -46216,82 +46224,82 @@
       </c>
       <c r="DW99" t="inlineStr">
         <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="DX99" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="DZ99" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EG99" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="DX99" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="DY99" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="DZ99" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="EA99" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EB99" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EC99" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="ED99" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EE99" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EF99" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EG99" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
       <c r="EH99" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EI99" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="EJ99" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.38</t>
         </is>
       </c>
     </row>
@@ -46311,40 +46319,40 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45991.54166666666</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K100" t="n">
         <v>6</v>
       </c>
       <c r="L100" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M100" t="n">
         <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -46356,125 +46364,117 @@
         <v>4</v>
       </c>
       <c r="R100" t="n">
+        <v>3</v>
+      </c>
+      <c r="S100" t="n">
+        <v>7</v>
+      </c>
+      <c r="T100" t="n">
+        <v>7</v>
+      </c>
+      <c r="U100" t="n">
+        <v>11</v>
+      </c>
+      <c r="V100" t="n">
+        <v>10</v>
+      </c>
+      <c r="W100" t="n">
+        <v>14</v>
+      </c>
+      <c r="X100" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD100" t="n">
         <v>4</v>
-      </c>
-      <c r="S100" t="n">
-        <v>14</v>
-      </c>
-      <c r="T100" t="n">
-        <v>10</v>
-      </c>
-      <c r="U100" t="n">
-        <v>18</v>
-      </c>
-      <c r="V100" t="n">
-        <v>14</v>
-      </c>
-      <c r="W100" t="n">
-        <v>10</v>
-      </c>
-      <c r="X100" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>JYSK park</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>Ansvej 104, Silkeborg</t>
-        </is>
-      </c>
-      <c r="AC100" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>2</v>
       </c>
       <c r="AE100" t="n">
         <v>2.37</v>
       </c>
       <c r="AF100" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI100" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AJ100" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL100" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW100" t="n">
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB100" t="n">
-        <v>-1</v>
+        <v>2516</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -46489,19 +46489,19 @@
         <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BJ100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BM100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN100" t="n">
         <v>9</v>
@@ -46510,43 +46510,43 @@
         <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ100" t="n">
         <v>2</v>
       </c>
       <c r="BR100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BW100" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="BX100" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="BY100" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="BZ100" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="CB100" t="n">
-        <v>3.24</v>
+        <v>2.28</v>
       </c>
       <c r="CC100" t="n">
         <v>0</v>
@@ -46573,16 +46573,16 @@
         <v>1</v>
       </c>
       <c r="CK100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL100" t="n">
         <v>0</v>
       </c>
       <c r="CM100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO100" t="n">
         <v>0</v>
@@ -46594,82 +46594,82 @@
         <v>1</v>
       </c>
       <c r="CR100" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
         <v>16</v>
       </c>
-      <c r="CS100" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
+      <c r="CV100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY100" t="n">
         <v>12</v>
       </c>
-      <c r="CV100" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY100" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ100" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="DA100" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="DB100" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="DC100" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="DD100" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="DE100" t="n">
-        <v>0.9</v>
+        <v>1.45</v>
       </c>
       <c r="DF100" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DG100" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DH100" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="DI100" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="DJ100" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="DK100" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="DN100" t="n">
-        <v>2.78</v>
+        <v>4.05</v>
       </c>
       <c r="DO100" t="n">
         <v>20</v>
       </c>
       <c r="DP100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR100" t="b">
         <v>0</v>
@@ -46688,82 +46688,82 @@
       </c>
       <c r="DW100" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="DX100" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EC100" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="ED100" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EE100" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EF100" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EK100" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EL100" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -47558,10 +47558,10 @@
         <v>94</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF102" t="n">
         <v>1.38</v>
@@ -47591,7 +47591,7 @@
         <v>2.62</v>
       </c>
       <c r="DO102" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48583,170 +48583,170 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
         <v>45998.54166666666</v>
       </c>
       <c r="G105" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L105" t="n">
         <v>11</v>
       </c>
       <c r="M105" t="n">
+        <v>2</v>
+      </c>
+      <c r="N105" t="n">
         <v>4</v>
       </c>
-      <c r="N105" t="n">
-        <v>1</v>
-      </c>
       <c r="O105" t="n">
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S105" t="n">
         <v>7</v>
       </c>
       <c r="T105" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U105" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="V105" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="W105" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="X105" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y105" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="Z105" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD105" t="n">
         <v>4</v>
       </c>
-      <c r="AD105" t="n">
-        <v>3</v>
-      </c>
       <c r="AE105" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="AF105" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG105" t="n">
-        <v>4</v>
+        <v>1.66</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AI105" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AJ105" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AK105" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AL105" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AM105" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AO105" t="n">
-        <v>2.37</v>
+        <v>2.87</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AR105" t="n">
         <v>2.18</v>
       </c>
       <c r="AS105" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="AT105" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AU105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ105" t="n">
         <v>4</v>
       </c>
-      <c r="AW105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ105" t="n">
-        <v>1</v>
-      </c>
       <c r="BA105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB105" t="n">
-        <v>986</v>
+        <v>-1</v>
       </c>
       <c r="BC105" t="n">
         <v>0</v>
       </c>
       <c r="BD105" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BE105" t="n">
         <v>0</v>
@@ -48761,73 +48761,73 @@
         <v>1</v>
       </c>
       <c r="BI105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BJ105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK105" t="n">
         <v>2</v>
       </c>
       <c r="BL105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BM105" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BN105" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BO105" t="n">
         <v>2</v>
       </c>
       <c r="BP105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BT105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU105" t="n">
         <v>1</v>
       </c>
       <c r="BV105" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="BW105" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="BX105" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="BY105" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="BZ105" t="n">
-        <v>2.37</v>
+        <v>1.16</v>
       </c>
       <c r="CA105" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="CB105" t="n">
-        <v>3.57</v>
+        <v>3.16</v>
       </c>
       <c r="CC105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD105" t="n">
         <v>0</v>
       </c>
       <c r="CE105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF105" t="n">
         <v>0</v>
@@ -48851,13 +48851,13 @@
         <v>0</v>
       </c>
       <c r="CM105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP105" t="n">
         <v>0</v>
@@ -48866,73 +48866,73 @@
         <v>1</v>
       </c>
       <c r="CR105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CS105" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV105" t="n">
         <v>16</v>
       </c>
-      <c r="CT105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU105" t="n">
-        <v>5</v>
-      </c>
-      <c r="CV105" t="n">
-        <v>11</v>
-      </c>
       <c r="CW105" t="n">
         <v>1</v>
       </c>
       <c r="CX105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="CY105" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="CZ105" t="n">
         <v>63</v>
       </c>
       <c r="DA105" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="DB105" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC105" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="DD105" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DE105" t="n">
         <v>1.8</v>
-      </c>
-      <c r="DE105" t="n">
-        <v>0.8</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
       </c>
       <c r="DG105" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DH105" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="DI105" t="n">
-        <v>1.12</v>
+        <v>2.06</v>
       </c>
       <c r="DJ105" t="n">
         <v>38</v>
       </c>
       <c r="DK105" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="DL105" t="n">
-        <v>1.81</v>
+        <v>1.22</v>
       </c>
       <c r="DM105" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="DN105" t="n">
-        <v>3.06</v>
+        <v>2.56</v>
       </c>
       <c r="DO105" t="n">
         <v>20</v>
@@ -48953,79 +48953,71 @@
         <v>1</v>
       </c>
       <c r="DU105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW105" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="DX105" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DY105" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="DZ105" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="EA105" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EB105" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EC105" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="ED105" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EE105" t="inlineStr">
         <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EF105" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EG105" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF105" t="inlineStr"/>
+      <c r="EG105" t="inlineStr"/>
       <c r="EH105" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI105" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="EJ105" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EK105" t="inlineStr"/>
@@ -49047,146 +49039,146 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
         <v>45998.54166666666</v>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K106" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L106" t="n">
         <v>11</v>
       </c>
       <c r="M106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
+        <v>10</v>
+      </c>
+      <c r="R106" t="n">
         <v>3</v>
-      </c>
-      <c r="R106" t="n">
-        <v>5</v>
       </c>
       <c r="S106" t="n">
         <v>7</v>
       </c>
       <c r="T106" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U106" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V106" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="W106" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="X106" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y106" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="Z106" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF106" t="n">
         <v>4</v>
       </c>
-      <c r="AE106" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AG106" t="n">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="AH106" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AI106" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AJ106" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="AK106" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AL106" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AM106" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN106" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AO106" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AR106" t="n">
         <v>2.18</v>
       </c>
       <c r="AS106" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="AT106" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AU106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW106" t="n">
         <v>0</v>
@@ -49195,22 +49187,22 @@
         <v>1</v>
       </c>
       <c r="AY106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA106" t="n">
         <v>4</v>
       </c>
-      <c r="BA106" t="n">
-        <v>2</v>
-      </c>
       <c r="BB106" t="n">
-        <v>-1</v>
+        <v>986</v>
       </c>
       <c r="BC106" t="n">
         <v>0</v>
       </c>
       <c r="BD106" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="BE106" t="n">
         <v>0</v>
@@ -49225,178 +49217,178 @@
         <v>1</v>
       </c>
       <c r="BI106" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK106" t="n">
         <v>2</v>
       </c>
       <c r="BL106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BM106" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BN106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT106" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV106" t="n">
+        <v>82</v>
+      </c>
+      <c r="BW106" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX106" t="n">
+        <v>129</v>
+      </c>
+      <c r="BY106" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ106" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CA106" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB106" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="CC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM106" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP106" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR106" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS106" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU106" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV106" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW106" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX106" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY106" t="n">
         <v>8</v>
-      </c>
-      <c r="BO106" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP106" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ106" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR106" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS106" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT106" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU106" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV106" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW106" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX106" t="n">
-        <v>69</v>
-      </c>
-      <c r="BY106" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ106" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CA106" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB106" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CC106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP106" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR106" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS106" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU106" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV106" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW106" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX106" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY106" t="n">
-        <v>6</v>
       </c>
       <c r="CZ106" t="n">
         <v>63</v>
       </c>
       <c r="DA106" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="DB106" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC106" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="DF106" t="n">
         <v>1.5</v>
       </c>
       <c r="DG106" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DH106" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="DI106" t="n">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="DJ106" t="n">
         <v>38</v>
       </c>
       <c r="DK106" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="DL106" t="n">
-        <v>1.22</v>
+        <v>1.81</v>
       </c>
       <c r="DM106" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="DN106" t="n">
-        <v>2.56</v>
+        <v>3.06</v>
       </c>
       <c r="DO106" t="n">
         <v>20</v>
@@ -49417,71 +49409,79 @@
         <v>1</v>
       </c>
       <c r="DU106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW106" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="DX106" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DY106" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="DZ106" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="EA106" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="EB106" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC106" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="ED106" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="EE106" t="inlineStr">
         <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EF106" t="inlineStr"/>
-      <c r="EG106" t="inlineStr"/>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EF106" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EG106" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
       <c r="EH106" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EI106" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EJ106" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK106" t="inlineStr"/>
@@ -51182,7 +51182,7 @@
         <v>73</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DE110" t="n">
         <v>1.2</v>
@@ -52113,7 +52113,7 @@
         <v>2.4</v>
       </c>
       <c r="DE112" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DF112" t="n">
         <v>2.33</v>
@@ -53945,7 +53945,7 @@
         <v>1.4</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF116" t="n">
         <v>1.22</v>
@@ -54423,7 +54423,7 @@
         <v>3.21</v>
       </c>
       <c r="DO117" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP117" t="b">
         <v>1</v>
@@ -55294,7 +55294,7 @@
         <v>78</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DE119" t="n">
         <v>1.8</v>
@@ -56342,6 +56342,910 @@
       </c>
       <c r="EK121" t="inlineStr"/>
       <c r="EL121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>21</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Nordsjælland</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>46073.75</v>
+      </c>
+      <c r="G122" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" t="n">
+        <v>3</v>
+      </c>
+      <c r="I122" t="n">
+        <v>6</v>
+      </c>
+      <c r="J122" t="n">
+        <v>5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3</v>
+      </c>
+      <c r="L122" t="n">
+        <v>8</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>7</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6</v>
+      </c>
+      <c r="S122" t="n">
+        <v>4</v>
+      </c>
+      <c r="T122" t="n">
+        <v>10</v>
+      </c>
+      <c r="U122" t="n">
+        <v>11</v>
+      </c>
+      <c r="V122" t="n">
+        <v>16</v>
+      </c>
+      <c r="W122" t="n">
+        <v>7</v>
+      </c>
+      <c r="X122" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>Right to Dream Park</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Idrætsvænget 2, Farum</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>6</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV122" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX122" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY122" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ122" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA122" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB122" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC122" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD122" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DE122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DF122" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DH122" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI122" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DJ122" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK122" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL122" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DM122" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN122" t="n">
+        <v>3</v>
+      </c>
+      <c r="DO122" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW122" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="DX122" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DZ122" t="inlineStr">
+        <is>
+          <t>5.55</t>
+        </is>
+      </c>
+      <c r="EA122" t="inlineStr">
+        <is>
+          <t>8.74</t>
+        </is>
+      </c>
+      <c r="EB122" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EC122" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="ED122" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="EE122" t="inlineStr"/>
+      <c r="EF122" t="inlineStr"/>
+      <c r="EG122" t="inlineStr"/>
+      <c r="EH122" t="inlineStr"/>
+      <c r="EI122" t="inlineStr"/>
+      <c r="EJ122" t="inlineStr"/>
+      <c r="EK122" t="inlineStr"/>
+      <c r="EL122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>21</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>46074.54166666666</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="n">
+        <v>4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>4</v>
+      </c>
+      <c r="K123" t="n">
+        <v>4</v>
+      </c>
+      <c r="L123" t="n">
+        <v>8</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2</v>
+      </c>
+      <c r="N123" t="n">
+        <v>3</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>9</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="n">
+        <v>7</v>
+      </c>
+      <c r="U123" t="n">
+        <v>19</v>
+      </c>
+      <c r="V123" t="n">
+        <v>13</v>
+      </c>
+      <c r="W123" t="n">
+        <v>10</v>
+      </c>
+      <c r="X123" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>Nature Energy Park</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>Højstrupvej 7B, Odense</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>71</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>125</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU123" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV123" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW123" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX123" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY123" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ123" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA123" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB123" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC123" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD123" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DE123" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DF123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG123" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH123" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DI123" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ123" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK123" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL123" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM123" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DN123" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="DO123" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU123" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV123" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW123" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="DX123" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="DY123" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="DZ123" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="EA123" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EB123" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EC123" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="ED123" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EE123" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EF123" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EG123" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EH123" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EJ123" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK123" t="inlineStr"/>
+      <c r="EL123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL123" headerRowCount="1">
-  <autoFilter ref="A1:EL123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL127" headerRowCount="1">
+  <autoFilter ref="A1:EL127"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL123"/>
+  <dimension ref="A1:EL127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE7" t="n">
         <v>0.8</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4502,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE8" t="n">
         <v>0.9</v>
@@ -4535,7 +4535,7 @@
         <v>0.76</v>
       </c>
       <c r="DO8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5433,7 +5433,7 @@
         <v>1.36</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5886,10 +5886,10 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE11" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5919,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6801,7 +6801,7 @@
         <v>2.4</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF13" t="n">
         <v>1</v>
@@ -6831,7 +6831,7 @@
         <v>2.01</v>
       </c>
       <c r="DO13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7287,7 +7287,7 @@
         <v>3.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8166,7 +8166,7 @@
         <v>50</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE16" t="n">
         <v>0.8</v>
@@ -8199,7 +8199,7 @@
         <v>0.91</v>
       </c>
       <c r="DO16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8663,7 +8663,7 @@
         <v>2.96</v>
       </c>
       <c r="DO17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9086,10 +9086,10 @@
         <v>50</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9119,7 +9119,7 @@
         <v>1.58</v>
       </c>
       <c r="DO18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP18" t="b">
         <v>0</v>
@@ -9550,10 +9550,10 @@
         <v>100</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE19" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF19" t="n">
         <v>3</v>
@@ -9583,7 +9583,7 @@
         <v>3.11</v>
       </c>
       <c r="DO19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10031,7 +10031,7 @@
         <v>2.67</v>
       </c>
       <c r="DO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10457,7 +10457,7 @@
         <v>1.6</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF21" t="n">
         <v>0</v>
@@ -10487,7 +10487,7 @@
         <v>3.19</v>
       </c>
       <c r="DO21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>2.4</v>
       </c>
       <c r="DE22" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF22" t="n">
         <v>2</v>
@@ -10951,7 +10951,7 @@
         <v>3.1</v>
       </c>
       <c r="DO22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11374,7 +11374,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE23" t="n">
         <v>1.2</v>
@@ -11407,7 +11407,7 @@
         <v>3.75</v>
       </c>
       <c r="DO23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11822,7 +11822,7 @@
         <v>100</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE24" t="n">
         <v>0.27</v>
@@ -11855,7 +11855,7 @@
         <v>2.85</v>
       </c>
       <c r="DO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12311,7 +12311,7 @@
         <v>2.63</v>
       </c>
       <c r="DO25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -13209,7 +13209,7 @@
         <v>0.8</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF27" t="n">
         <v>0</v>
@@ -13239,7 +13239,7 @@
         <v>2.72</v>
       </c>
       <c r="DO27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13681,7 +13681,7 @@
         <v>1.1</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF28" t="n">
         <v>2</v>
@@ -13711,7 +13711,7 @@
         <v>1.98</v>
       </c>
       <c r="DO28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14167,7 +14167,7 @@
         <v>2.35</v>
       </c>
       <c r="DO29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14598,7 +14598,7 @@
         <v>100</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE30" t="n">
         <v>1.5</v>
@@ -14631,7 +14631,7 @@
         <v>1.96</v>
       </c>
       <c r="DO30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15103,7 +15103,7 @@
         <v>2.43</v>
       </c>
       <c r="DO31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -16031,7 +16031,7 @@
         <v>2.55</v>
       </c>
       <c r="DO33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16495,7 +16495,7 @@
         <v>3.63</v>
       </c>
       <c r="DO34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16959,7 +16959,7 @@
         <v>2.46</v>
       </c>
       <c r="DO35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17390,7 +17390,7 @@
         <v>75</v>
       </c>
       <c r="DD36" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE36" t="n">
         <v>0.27</v>
@@ -17423,7 +17423,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17857,7 +17857,7 @@
         <v>1.73</v>
       </c>
       <c r="DE37" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF37" t="n">
         <v>0</v>
@@ -17887,7 +17887,7 @@
         <v>3.08</v>
       </c>
       <c r="DO37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -18313,7 +18313,7 @@
         <v>1.1</v>
       </c>
       <c r="DE38" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF38" t="n">
         <v>1.33</v>
@@ -18343,7 +18343,7 @@
         <v>2.88</v>
       </c>
       <c r="DO38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18782,10 +18782,10 @@
         <v>84</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF39" t="n">
         <v>1.5</v>
@@ -18815,7 +18815,7 @@
         <v>3.56</v>
       </c>
       <c r="DO39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19230,10 +19230,10 @@
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE40" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF40" t="n">
         <v>1.33</v>
@@ -19263,7 +19263,7 @@
         <v>3.29</v>
       </c>
       <c r="DO40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -20150,7 +20150,7 @@
         <v>84</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE42" t="n">
         <v>1.45</v>
@@ -20183,7 +20183,7 @@
         <v>3.26</v>
       </c>
       <c r="DO42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20622,10 +20622,10 @@
         <v>50</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF43" t="n">
         <v>2</v>
@@ -20655,7 +20655,7 @@
         <v>2.97</v>
       </c>
       <c r="DO43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -21111,7 +21111,7 @@
         <v>2.35</v>
       </c>
       <c r="DO44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21534,7 +21534,7 @@
         <v>75</v>
       </c>
       <c r="DD45" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE45" t="n">
         <v>1.45</v>
@@ -21567,7 +21567,7 @@
         <v>3.76</v>
       </c>
       <c r="DO45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -22039,7 +22039,7 @@
         <v>2.56</v>
       </c>
       <c r="DO46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22465,7 +22465,7 @@
         <v>1.73</v>
       </c>
       <c r="DE47" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF47" t="n">
         <v>1</v>
@@ -22495,7 +22495,7 @@
         <v>2.95</v>
       </c>
       <c r="DO47" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -22926,7 +22926,7 @@
         <v>84</v>
       </c>
       <c r="DD48" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE48" t="n">
         <v>1.2</v>
@@ -22959,7 +22959,7 @@
         <v>2.69</v>
       </c>
       <c r="DO48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23395,7 +23395,7 @@
         <v>2.22</v>
       </c>
       <c r="DO49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23829,7 +23829,7 @@
         <v>1.36</v>
       </c>
       <c r="DE50" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF50" t="n">
         <v>1.5</v>
@@ -23859,7 +23859,7 @@
         <v>2.69</v>
       </c>
       <c r="DO50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -24285,7 +24285,7 @@
         <v>2.4</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF51" t="n">
         <v>2</v>
@@ -24315,7 +24315,7 @@
         <v>3.7</v>
       </c>
       <c r="DO51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP51" t="b">
         <v>1</v>
@@ -24733,7 +24733,7 @@
         <v>1.1</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF52" t="n">
         <v>1</v>
@@ -24763,7 +24763,7 @@
         <v>3.05</v>
       </c>
       <c r="DO52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25227,7 +25227,7 @@
         <v>3.35</v>
       </c>
       <c r="DO53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25650,7 +25650,7 @@
         <v>71</v>
       </c>
       <c r="DD54" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE54" t="n">
         <v>1.5</v>
@@ -25683,7 +25683,7 @@
         <v>3.92</v>
       </c>
       <c r="DO54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26114,7 +26114,7 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE55" t="n">
         <v>1.2</v>
@@ -26147,7 +26147,7 @@
         <v>2.73</v>
       </c>
       <c r="DO55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -26603,7 +26603,7 @@
         <v>2.8</v>
       </c>
       <c r="DO56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -27017,7 +27017,7 @@
         <v>1.6</v>
       </c>
       <c r="DE57" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF57" t="n">
         <v>0.75</v>
@@ -27047,7 +27047,7 @@
         <v>2.67</v>
       </c>
       <c r="DO57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -27470,7 +27470,7 @@
         <v>75</v>
       </c>
       <c r="DD58" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE58" t="n">
         <v>0.27</v>
@@ -27503,7 +27503,7 @@
         <v>2.65</v>
       </c>
       <c r="DO58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -27967,7 +27967,7 @@
         <v>2.98</v>
       </c>
       <c r="DO59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28398,7 +28398,7 @@
         <v>90</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE60" t="n">
         <v>1.2</v>
@@ -28431,7 +28431,7 @@
         <v>2.73</v>
       </c>
       <c r="DO60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -28871,7 +28871,7 @@
         <v>3.65</v>
       </c>
       <c r="DO61" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -29285,7 +29285,7 @@
         <v>1.36</v>
       </c>
       <c r="DE62" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF62" t="n">
         <v>1.8</v>
@@ -29315,7 +29315,7 @@
         <v>3.02</v>
       </c>
       <c r="DO62" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -30202,10 +30202,10 @@
         <v>78</v>
       </c>
       <c r="DD64" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF64" t="n">
         <v>1.5</v>
@@ -30235,7 +30235,7 @@
         <v>2.43</v>
       </c>
       <c r="DO64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30650,7 +30650,7 @@
         <v>90</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE65" t="n">
         <v>0.8</v>
@@ -30683,7 +30683,7 @@
         <v>3.44</v>
       </c>
       <c r="DO65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -31109,7 +31109,7 @@
         <v>1.3</v>
       </c>
       <c r="DE66" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF66" t="n">
         <v>1.25</v>
@@ -31139,7 +31139,7 @@
         <v>3.16</v>
       </c>
       <c r="DO66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -31611,7 +31611,7 @@
         <v>3.08</v>
       </c>
       <c r="DO67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP67" t="b">
         <v>1</v>
@@ -32026,7 +32026,7 @@
         <v>82</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE68" t="n">
         <v>1.45</v>
@@ -32059,7 +32059,7 @@
         <v>3.16</v>
       </c>
       <c r="DO68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -32163,12 +32163,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -32178,25 +32178,25 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>6</v>
+      </c>
+      <c r="K69" t="n">
         <v>3</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>9</v>
       </c>
-      <c r="K69" t="n">
-        <v>6</v>
-      </c>
-      <c r="L69" t="n">
-        <v>15</v>
-      </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -32205,101 +32205,101 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T69" t="n">
         <v>10</v>
       </c>
       <c r="U69" t="n">
+        <v>14</v>
+      </c>
+      <c r="V69" t="n">
+        <v>13</v>
+      </c>
+      <c r="W69" t="n">
         <v>10</v>
       </c>
-      <c r="V69" t="n">
-        <v>18</v>
-      </c>
-      <c r="W69" t="n">
-        <v>6</v>
-      </c>
       <c r="X69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y69" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="Z69" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AF69" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AG69" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL69" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AM69" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN69" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AO69" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR69" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AS69" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AU69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV69" t="n">
         <v>1</v>
@@ -32311,22 +32311,22 @@
         <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA69" t="n">
         <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>2523</v>
+        <v>986</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="BE69" t="n">
         <v>0</v>
@@ -32335,46 +32335,46 @@
         <v>-1</v>
       </c>
       <c r="BG69" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH69" t="n">
         <v>1</v>
       </c>
       <c r="BI69" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BJ69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL69" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM69" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BN69" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR69" t="n">
         <v>1</v>
       </c>
       <c r="BS69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
@@ -32383,22 +32383,22 @@
         <v>17</v>
       </c>
       <c r="BW69" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BX69" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BY69" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BZ69" t="n">
-        <v>0.89</v>
+        <v>1.49</v>
       </c>
       <c r="CA69" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="CB69" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CC69" t="n">
         <v>0</v>
@@ -32425,16 +32425,16 @@
         <v>1</v>
       </c>
       <c r="CK69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL69" t="n">
         <v>0</v>
       </c>
       <c r="CM69" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO69" t="n">
         <v>0</v>
@@ -32446,85 +32446,85 @@
         <v>1</v>
       </c>
       <c r="CR69" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="CS69" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT69" t="n">
         <v>1</v>
       </c>
       <c r="CU69" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV69" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX69" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY69" t="n">
         <v>7</v>
       </c>
-      <c r="CW69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX69" t="n">
+      <c r="CZ69" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA69" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB69" t="n">
         <v>9</v>
       </c>
-      <c r="CY69" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ69" t="n">
-        <v>80</v>
-      </c>
-      <c r="DA69" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB69" t="n">
-        <v>80</v>
-      </c>
       <c r="DC69" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="DD69" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="DF69" t="n">
         <v>1.2</v>
       </c>
       <c r="DG69" t="n">
-        <v>0.4</v>
+        <v>1.17</v>
       </c>
       <c r="DH69" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="DI69" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="DJ69" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK69" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="DL69" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="DN69" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="DO69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP69" t="b">
         <v>1</v>
       </c>
       <c r="DQ69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS69" t="b">
         <v>0</v>
@@ -32536,46 +32536,46 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW69" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="DX69" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DY69" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="DZ69" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EA69" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EB69" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="DY69" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="DZ69" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="EA69" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EB69" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EC69" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="ED69" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EE69" t="inlineStr"/>
@@ -32584,12 +32584,12 @@
       <c r="EH69" t="inlineStr"/>
       <c r="EI69" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EJ69" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EK69" t="inlineStr"/>
@@ -32611,12 +32611,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -32626,25 +32626,25 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
+        <v>9</v>
+      </c>
+      <c r="K70" t="n">
         <v>6</v>
       </c>
-      <c r="K70" t="n">
-        <v>3</v>
-      </c>
       <c r="L70" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -32653,102 +32653,102 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T70" t="n">
         <v>10</v>
       </c>
       <c r="U70" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V70" t="n">
+        <v>18</v>
+      </c>
+      <c r="W70" t="n">
+        <v>6</v>
+      </c>
+      <c r="X70" t="n">
         <v>13</v>
       </c>
-      <c r="W70" t="n">
-        <v>10</v>
-      </c>
-      <c r="X70" t="n">
-        <v>11</v>
-      </c>
       <c r="Y70" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="Z70" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU70" t="n">
         <v>3</v>
       </c>
-      <c r="AD70" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ70" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR70" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT70" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU70" t="n">
-        <v>1</v>
-      </c>
       <c r="AV70" t="n">
         <v>1</v>
       </c>
@@ -32759,22 +32759,22 @@
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
       </c>
       <c r="BB70" t="n">
-        <v>986</v>
+        <v>2523</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -32783,46 +32783,46 @@
         <v>-1</v>
       </c>
       <c r="BG70" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH70" t="n">
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BJ70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL70" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM70" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BN70" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR70" t="n">
         <v>1</v>
       </c>
       <c r="BS70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU70" t="n">
         <v>1</v>
@@ -32831,148 +32831,148 @@
         <v>17</v>
       </c>
       <c r="BW70" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BX70" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>40</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB70" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR70" t="n">
         <v>35</v>
       </c>
-      <c r="BY70" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ70" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA70" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB70" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP70" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>16</v>
-      </c>
       <c r="CS70" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU70" t="n">
         <v>14</v>
       </c>
-      <c r="CT70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU70" t="n">
-        <v>12</v>
-      </c>
       <c r="CV70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW70" t="n">
         <v>1</v>
       </c>
       <c r="CX70" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CY70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ70" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA70" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="DB70" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="DC70" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="DE70" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="DF70" t="n">
         <v>1.2</v>
       </c>
       <c r="DG70" t="n">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="DH70" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="DI70" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="DJ70" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK70" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="DL70" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="DM70" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="DN70" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="DO70" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP70" t="b">
         <v>1</v>
       </c>
       <c r="DQ70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS70" t="b">
         <v>0</v>
@@ -32984,46 +32984,46 @@
         <v>0</v>
       </c>
       <c r="DV70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW70" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="DX70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY70" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="DZ70" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EA70" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EB70" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EC70" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="ED70" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EE70" t="inlineStr"/>
@@ -33032,12 +33032,12 @@
       <c r="EH70" t="inlineStr"/>
       <c r="EI70" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EJ70" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EK70" t="inlineStr"/>
@@ -33378,7 +33378,7 @@
         <v>82</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE71" t="n">
         <v>2.2</v>
@@ -33411,7 +33411,7 @@
         <v>3.14</v>
       </c>
       <c r="DO71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP71" t="b">
         <v>1</v>
@@ -33883,7 +33883,7 @@
         <v>3.26</v>
       </c>
       <c r="DO72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -34301,7 +34301,7 @@
         <v>2</v>
       </c>
       <c r="DE73" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF73" t="n">
         <v>1.4</v>
@@ -34331,7 +34331,7 @@
         <v>2.18</v>
       </c>
       <c r="DO73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34730,7 +34730,7 @@
         <v>83</v>
       </c>
       <c r="DD74" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE74" t="n">
         <v>1.2</v>
@@ -34763,7 +34763,7 @@
         <v>3.72</v>
       </c>
       <c r="DO74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP74" t="b">
         <v>1</v>
@@ -35197,7 +35197,7 @@
         <v>0.8</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF75" t="n">
         <v>1.17</v>
@@ -35227,7 +35227,7 @@
         <v>2.51</v>
       </c>
       <c r="DO75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -35683,7 +35683,7 @@
         <v>2.66</v>
       </c>
       <c r="DO76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -36098,10 +36098,10 @@
         <v>74</v>
       </c>
       <c r="DD77" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE77" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF77" t="n">
         <v>1.8</v>
@@ -36131,7 +36131,7 @@
         <v>2.73</v>
       </c>
       <c r="DO77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP77" t="b">
         <v>0</v>
@@ -36557,7 +36557,7 @@
         <v>1.3</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF78" t="n">
         <v>1.2</v>
@@ -36587,7 +36587,7 @@
         <v>3.31</v>
       </c>
       <c r="DO78" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP78" t="b">
         <v>0</v>
@@ -37059,7 +37059,7 @@
         <v>3.34</v>
       </c>
       <c r="DO79" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -37501,7 +37501,7 @@
         <v>1.3</v>
       </c>
       <c r="DE80" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF80" t="n">
         <v>1.17</v>
@@ -37531,7 +37531,7 @@
         <v>3.11</v>
       </c>
       <c r="DO80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -37995,7 +37995,7 @@
         <v>2.66</v>
       </c>
       <c r="DO81" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -38459,7 +38459,7 @@
         <v>2.34</v>
       </c>
       <c r="DO82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39334,7 +39334,7 @@
         <v>75</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE84" t="n">
         <v>1.5</v>
@@ -39367,7 +39367,7 @@
         <v>3.22</v>
       </c>
       <c r="DO84" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -39831,7 +39831,7 @@
         <v>3.51</v>
       </c>
       <c r="DO85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -40287,7 +40287,7 @@
         <v>2.75</v>
       </c>
       <c r="DO86" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -41177,7 +41177,7 @@
         <v>0.8</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF88" t="n">
         <v>1</v>
@@ -41207,7 +41207,7 @@
         <v>2.68</v>
       </c>
       <c r="DO88" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -41622,10 +41622,10 @@
         <v>59</v>
       </c>
       <c r="DD89" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE89" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF89" t="n">
         <v>1.67</v>
@@ -41655,7 +41655,7 @@
         <v>2.65</v>
       </c>
       <c r="DO89" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP89" t="b">
         <v>1</v>
@@ -42062,10 +42062,10 @@
         <v>64</v>
       </c>
       <c r="DD90" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE90" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF90" t="n">
         <v>2.29</v>
@@ -42095,7 +42095,7 @@
         <v>3.62</v>
       </c>
       <c r="DO90" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -42510,7 +42510,7 @@
         <v>79</v>
       </c>
       <c r="DD91" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE91" t="n">
         <v>1.2</v>
@@ -42543,7 +42543,7 @@
         <v>3.1</v>
       </c>
       <c r="DO91" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -42966,7 +42966,7 @@
         <v>86</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE92" t="n">
         <v>2.2</v>
@@ -42999,7 +42999,7 @@
         <v>2.83</v>
       </c>
       <c r="DO92" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43455,7 +43455,7 @@
         <v>3.71</v>
       </c>
       <c r="DO93" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -43927,7 +43927,7 @@
         <v>2.31</v>
       </c>
       <c r="DO94" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -44353,7 +44353,7 @@
         <v>1.73</v>
       </c>
       <c r="DE95" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF95" t="n">
         <v>1.29</v>
@@ -44383,7 +44383,7 @@
         <v>2.79</v>
       </c>
       <c r="DO95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -44817,7 +44817,7 @@
         <v>2</v>
       </c>
       <c r="DE96" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF96" t="n">
         <v>1.86</v>
@@ -44847,7 +44847,7 @@
         <v>2.86</v>
       </c>
       <c r="DO96" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP96" t="b">
         <v>1</v>
@@ -45254,7 +45254,7 @@
         <v>79</v>
       </c>
       <c r="DD97" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE97" t="n">
         <v>1.2</v>
@@ -45287,7 +45287,7 @@
         <v>2.56</v>
       </c>
       <c r="DO97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP97" t="b">
         <v>0</v>
@@ -45705,7 +45705,7 @@
         <v>2</v>
       </c>
       <c r="DE98" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF98" t="n">
         <v>2</v>
@@ -45735,7 +45735,7 @@
         <v>2.93</v>
       </c>
       <c r="DO98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
@@ -46166,7 +46166,7 @@
         <v>76</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE99" t="n">
         <v>0.9</v>
@@ -46199,7 +46199,7 @@
         <v>2.78</v>
       </c>
       <c r="DO99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP99" t="b">
         <v>0</v>
@@ -46630,7 +46630,7 @@
         <v>75</v>
       </c>
       <c r="DD100" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE100" t="n">
         <v>1.45</v>
@@ -46663,7 +46663,7 @@
         <v>4.05</v>
       </c>
       <c r="DO100" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP100" t="b">
         <v>1</v>
@@ -47135,7 +47135,7 @@
         <v>3.44</v>
       </c>
       <c r="DO101" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -48006,10 +48006,10 @@
         <v>94</v>
       </c>
       <c r="DD103" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE103" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF103" t="n">
         <v>2</v>
@@ -48039,7 +48039,7 @@
         <v>2.76</v>
       </c>
       <c r="DO103" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP103" t="b">
         <v>1</v>
@@ -48487,7 +48487,7 @@
         <v>2.57</v>
       </c>
       <c r="DO104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -48905,7 +48905,7 @@
         <v>1.6</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF105" t="n">
         <v>1.5</v>
@@ -48935,7 +48935,7 @@
         <v>2.56</v>
       </c>
       <c r="DO105" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -49391,7 +49391,7 @@
         <v>3.06</v>
       </c>
       <c r="DO106" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -49814,7 +49814,7 @@
         <v>69</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE107" t="n">
         <v>2.2</v>
@@ -49847,7 +49847,7 @@
         <v>2.84</v>
       </c>
       <c r="DO107" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -50273,7 +50273,7 @@
         <v>1.3</v>
       </c>
       <c r="DE108" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF108" t="n">
         <v>1.63</v>
@@ -50303,7 +50303,7 @@
         <v>3.27</v>
       </c>
       <c r="DO108" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -50759,7 +50759,7 @@
         <v>3.17</v>
       </c>
       <c r="DO109" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51185,7 +51185,7 @@
         <v>1.73</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DF110" t="n">
         <v>1.67</v>
@@ -51215,7 +51215,7 @@
         <v>3.24</v>
       </c>
       <c r="DO110" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -51646,10 +51646,10 @@
         <v>73</v>
       </c>
       <c r="DD111" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DF111" t="n">
         <v>1.22</v>
@@ -51679,7 +51679,7 @@
         <v>2.95</v>
       </c>
       <c r="DO111" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -52143,7 +52143,7 @@
         <v>3.75</v>
       </c>
       <c r="DO112" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -52566,7 +52566,7 @@
         <v>73</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DE113" t="n">
         <v>0.9</v>
@@ -52599,7 +52599,7 @@
         <v>3.1</v>
       </c>
       <c r="DO113" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP113" t="b">
         <v>0</v>
@@ -53041,7 +53041,7 @@
         <v>1.1</v>
       </c>
       <c r="DE114" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DF114" t="n">
         <v>1.22</v>
@@ -53071,7 +53071,7 @@
         <v>2.43</v>
       </c>
       <c r="DO114" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -53478,7 +53478,7 @@
         <v>84</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DE115" t="n">
         <v>1.2</v>
@@ -53511,7 +53511,7 @@
         <v>3.43</v>
       </c>
       <c r="DO115" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -53942,7 +53942,7 @@
         <v>73</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DE116" t="n">
         <v>0.27</v>
@@ -53975,7 +53975,7 @@
         <v>2.52</v>
       </c>
       <c r="DO116" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -54871,7 +54871,7 @@
         <v>2.76</v>
       </c>
       <c r="DO118" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -55297,7 +55297,7 @@
         <v>1.36</v>
       </c>
       <c r="DE119" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DF119" t="n">
         <v>1.56</v>
@@ -55327,7 +55327,7 @@
         <v>2.92</v>
       </c>
       <c r="DO119" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -55791,7 +55791,7 @@
         <v>2.94</v>
       </c>
       <c r="DO120" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP120" t="b">
         <v>1</v>
@@ -56263,7 +56263,7 @@
         <v>2.68</v>
       </c>
       <c r="DO121" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -56832,7 +56832,7 @@
         <v>2</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -56847,13 +56847,13 @@
         <v>6</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T123" t="n">
         <v>7</v>
       </c>
       <c r="U123" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V123" t="n">
         <v>13</v>
@@ -56865,10 +56865,10 @@
         <v>19</v>
       </c>
       <c r="Y123" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z123" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
@@ -56884,7 +56884,7 @@
         <v>2</v>
       </c>
       <c r="AD123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE123" t="n">
         <v>4.29</v>
@@ -57004,13 +57004,13 @@
         <v>1</v>
       </c>
       <c r="BR123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS123" t="n">
         <v>2</v>
       </c>
       <c r="BT123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU123" t="n">
         <v>1</v>
@@ -57028,13 +57028,13 @@
         <v>125</v>
       </c>
       <c r="BZ123" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="CA123" t="n">
         <v>1.76</v>
       </c>
       <c r="CB123" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="CC123" t="n">
         <v>0</v>
@@ -57176,37 +57176,37 @@
       </c>
       <c r="DW123" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="DX123" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY123" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="DZ123" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="EA123" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EB123" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EC123" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="ED123" t="inlineStr">
@@ -57231,21 +57231,1837 @@
       </c>
       <c r="EH123" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EI123" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
-      <c r="EJ123" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EI123" t="inlineStr"/>
+      <c r="EJ123" t="inlineStr"/>
       <c r="EK123" t="inlineStr"/>
       <c r="EL123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>21</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>46075.54166666666</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>14</v>
+      </c>
+      <c r="K124" t="n">
+        <v>3</v>
+      </c>
+      <c r="L124" t="n">
+        <v>17</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>6</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6</v>
+      </c>
+      <c r="S124" t="n">
+        <v>21</v>
+      </c>
+      <c r="T124" t="n">
+        <v>11</v>
+      </c>
+      <c r="U124" t="n">
+        <v>27</v>
+      </c>
+      <c r="V124" t="n">
+        <v>17</v>
+      </c>
+      <c r="W124" t="n">
+        <v>6</v>
+      </c>
+      <c r="X124" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA124" t="inlineStr"/>
+      <c r="AB124" t="inlineStr"/>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>3649</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>56</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>121</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU124" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV124" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX124" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY124" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ124" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA124" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB124" t="n">
+        <v>65</v>
+      </c>
+      <c r="DC124" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD124" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DE124" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DF124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG124" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH124" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI124" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DJ124" t="n">
+        <v>35</v>
+      </c>
+      <c r="DK124" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL124" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DM124" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DN124" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DO124" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU124" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV124" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW124" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DX124" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="DY124" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DZ124" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="EA124" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="EB124" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EC124" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="ED124" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EE124" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EF124" t="inlineStr"/>
+      <c r="EG124" t="inlineStr"/>
+      <c r="EH124" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EI124" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EJ124" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EK124" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL124" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>21</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>46075.625</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>4</v>
+      </c>
+      <c r="I125" t="n">
+        <v>4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>6</v>
+      </c>
+      <c r="K125" t="n">
+        <v>6</v>
+      </c>
+      <c r="L125" t="n">
+        <v>12</v>
+      </c>
+      <c r="M125" t="n">
+        <v>3</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1</v>
+      </c>
+      <c r="R125" t="n">
+        <v>9</v>
+      </c>
+      <c r="S125" t="n">
+        <v>7</v>
+      </c>
+      <c r="T125" t="n">
+        <v>8</v>
+      </c>
+      <c r="U125" t="n">
+        <v>8</v>
+      </c>
+      <c r="V125" t="n">
+        <v>17</v>
+      </c>
+      <c r="W125" t="n">
+        <v>8</v>
+      </c>
+      <c r="X125" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>955</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>47</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>109</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU125" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV125" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY125" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ125" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA125" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB125" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC125" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD125" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE125" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DF125" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DG125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DH125" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DI125" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DJ125" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK125" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL125" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DM125" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DN125" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DO125" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS125" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV125" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW125" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="DX125" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="DY125" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="DZ125" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="EA125" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EB125" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EC125" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="ED125" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="EE125" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EF125" t="inlineStr"/>
+      <c r="EG125" t="inlineStr"/>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EI125" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EJ125" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EK125" t="inlineStr"/>
+      <c r="EL125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>21</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Viborg</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>46075.70833333334</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2</v>
+      </c>
+      <c r="I126" t="n">
+        <v>7</v>
+      </c>
+      <c r="J126" t="n">
+        <v>6</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" t="n">
+        <v>7</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>2</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>9</v>
+      </c>
+      <c r="R126" t="n">
+        <v>4</v>
+      </c>
+      <c r="S126" t="n">
+        <v>6</v>
+      </c>
+      <c r="T126" t="n">
+        <v>7</v>
+      </c>
+      <c r="U126" t="n">
+        <v>15</v>
+      </c>
+      <c r="V126" t="n">
+        <v>11</v>
+      </c>
+      <c r="W126" t="n">
+        <v>15</v>
+      </c>
+      <c r="X126" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>2516</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY126" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ126" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB126" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC126" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD126" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DE126" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF126" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DG126" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH126" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DI126" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ126" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK126" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL126" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DM126" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN126" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="DO126" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV126" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW126" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DX126" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DY126" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="DZ126" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="EA126" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="EB126" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EC126" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="ED126" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EE126" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EF126" t="inlineStr"/>
+      <c r="EG126" t="inlineStr"/>
+      <c r="EH126" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EI126" t="inlineStr"/>
+      <c r="EJ126" t="inlineStr"/>
+      <c r="EK126" t="inlineStr"/>
+      <c r="EL126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>21</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Brøndby</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>SønderjyskE</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>46076.75</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>5</v>
+      </c>
+      <c r="K127" t="n">
+        <v>6</v>
+      </c>
+      <c r="L127" t="n">
+        <v>11</v>
+      </c>
+      <c r="M127" t="n">
+        <v>2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>4</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>2</v>
+      </c>
+      <c r="R127" t="n">
+        <v>4</v>
+      </c>
+      <c r="S127" t="n">
+        <v>13</v>
+      </c>
+      <c r="T127" t="n">
+        <v>13</v>
+      </c>
+      <c r="U127" t="n">
+        <v>15</v>
+      </c>
+      <c r="V127" t="n">
+        <v>17</v>
+      </c>
+      <c r="W127" t="n">
+        <v>17</v>
+      </c>
+      <c r="X127" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Brøndby Stadion</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>Brøndby Stadion 8, Brøndby</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>57</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>60</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>70</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>40</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>21</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW127" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="DX127" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="ED127" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EE127" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF127" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EG127" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EH127" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EI127" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EJ127" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK127" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL127" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -59121,7 +59121,7 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R128" t="n">
         <v>4</v>
@@ -59133,7 +59133,7 @@
         <v>11</v>
       </c>
       <c r="U128" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V128" t="n">
         <v>15</v>
@@ -59308,13 +59308,13 @@
         <v>79</v>
       </c>
       <c r="BZ128" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="CA128" t="n">
         <v>1.47</v>
       </c>
       <c r="CB128" t="n">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="CC128" t="n">
         <v>0</v>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL133" headerRowCount="1">
-  <autoFilter ref="A1:EL133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL134" headerRowCount="1">
+  <autoFilter ref="A1:EL134"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL133"/>
+  <dimension ref="A1:EL134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE3" t="n">
         <v>1.09</v>
@@ -2697,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -4505,7 +4505,7 @@
         <v>2.27</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
         <v>100</v>
       </c>
       <c r="DD14" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE14" t="n">
         <v>1.45</v>
@@ -12281,7 +12281,7 @@
         <v>1.36</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -13206,7 +13206,7 @@
         <v>100</v>
       </c>
       <c r="DD27" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE27" t="n">
         <v>1.18</v>
@@ -15679,70 +15679,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L33" t="n">
+        <v>14</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>15</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" t="n">
         <v>10</v>
       </c>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>12</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>9</v>
-      </c>
-      <c r="T33" t="n">
-        <v>6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>21</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>11</v>
-      </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -15752,97 +15752,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB33" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -15857,271 +15857,271 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ33" t="n">
         <v>3</v>
       </c>
-      <c r="BJ33" t="n">
-        <v>2</v>
-      </c>
       <c r="BK33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY33" t="n">
         <v>5</v>
       </c>
-      <c r="BO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB33" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS33" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA33" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB33" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC33" t="n">
         <v>67</v>
       </c>
-      <c r="DC33" t="n">
-        <v>100</v>
-      </c>
       <c r="DD33" t="n">
-        <v>2.27</v>
+        <v>0.92</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.73</v>
+        <v>1.25</v>
       </c>
       <c r="DF33" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG33" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH33" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI33" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ33" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL33" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN33" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW33" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="DX33" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="DZ33" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EA33" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EB33" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC33" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EG33" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EH33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="DZ33" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EA33" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EB33" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EC33" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="ED33" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EE33" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EF33" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EG33" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EH33" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EJ33" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EK33" t="inlineStr"/>
@@ -16143,70 +16143,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>12</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>21</v>
+      </c>
+      <c r="V34" t="n">
         <v>11</v>
       </c>
-      <c r="L34" t="n">
-        <v>14</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>15</v>
-      </c>
-      <c r="U34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>18</v>
-      </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16216,97 +16216,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO34" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB34" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16321,64 +16321,64 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK34" t="n">
         <v>3</v>
       </c>
-      <c r="BK34" t="n">
-        <v>1</v>
-      </c>
       <c r="BL34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO34" t="n">
         <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR34" t="n">
         <v>1</v>
       </c>
       <c r="BS34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW34" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX34" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY34" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -16411,7 +16411,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -16426,73 +16426,73 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS34" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CY34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB34" t="n">
         <v>67</v>
       </c>
-      <c r="DA34" t="n">
+      <c r="DC34" t="n">
         <v>100</v>
       </c>
-      <c r="DB34" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC34" t="n">
-        <v>67</v>
-      </c>
       <c r="DD34" t="n">
-        <v>1</v>
+        <v>2.27</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="DF34" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG34" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DJ34" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK34" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO34" t="n">
         <v>22</v>
@@ -16501,66 +16501,66 @@
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW34" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="DX34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
@@ -16580,12 +16580,12 @@
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EK34" t="inlineStr"/>
@@ -21081,7 +21081,7 @@
         <v>2.09</v>
       </c>
       <c r="DE44" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF44" t="n">
         <v>2.33</v>
@@ -23362,7 +23362,7 @@
         <v>88</v>
       </c>
       <c r="DD49" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE49" t="n">
         <v>0.27</v>
@@ -28841,7 +28841,7 @@
         <v>2.27</v>
       </c>
       <c r="DE61" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF61" t="n">
         <v>2.2</v>
@@ -31578,7 +31578,7 @@
         <v>68</v>
       </c>
       <c r="DD67" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE67" t="n">
         <v>1.45</v>
@@ -32163,12 +32163,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -32178,25 +32178,25 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
+        <v>9</v>
+      </c>
+      <c r="K69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" t="n">
-        <v>3</v>
-      </c>
       <c r="L69" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -32205,102 +32205,102 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T69" t="n">
         <v>10</v>
       </c>
       <c r="U69" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V69" t="n">
+        <v>18</v>
+      </c>
+      <c r="W69" t="n">
+        <v>6</v>
+      </c>
+      <c r="X69" t="n">
         <v>13</v>
       </c>
-      <c r="W69" t="n">
-        <v>10</v>
-      </c>
-      <c r="X69" t="n">
-        <v>11</v>
-      </c>
       <c r="Y69" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="Z69" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU69" t="n">
         <v>3</v>
       </c>
-      <c r="AD69" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ69" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AN69" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AO69" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AP69" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ69" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU69" t="n">
-        <v>1</v>
-      </c>
       <c r="AV69" t="n">
         <v>1</v>
       </c>
@@ -32311,22 +32311,22 @@
         <v>0</v>
       </c>
       <c r="AY69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA69" t="n">
         <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>986</v>
+        <v>2523</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="BE69" t="n">
         <v>0</v>
@@ -32335,46 +32335,46 @@
         <v>-1</v>
       </c>
       <c r="BG69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH69" t="n">
         <v>1</v>
       </c>
       <c r="BI69" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BJ69" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BK69" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BL69" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM69" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BN69" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR69" t="n">
         <v>1</v>
       </c>
       <c r="BS69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BU69" t="n">
         <v>1</v>
@@ -32383,103 +32383,103 @@
         <v>17</v>
       </c>
       <c r="BW69" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BX69" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>40</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR69" t="n">
         <v>35</v>
       </c>
-      <c r="BY69" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ69" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA69" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB69" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>16</v>
-      </c>
       <c r="CS69" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU69" t="n">
         <v>14</v>
       </c>
-      <c r="CT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU69" t="n">
-        <v>12</v>
-      </c>
       <c r="CV69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CW69" t="n">
         <v>1</v>
       </c>
       <c r="CX69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CY69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ69" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA69" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="DB69" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="DC69" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="DD69" t="n">
         <v>1.73</v>
@@ -32491,28 +32491,28 @@
         <v>1.2</v>
       </c>
       <c r="DG69" t="n">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="DH69" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="DI69" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="DJ69" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK69" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="DL69" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="DN69" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="DO69" t="n">
         <v>22</v>
@@ -32521,10 +32521,10 @@
         <v>1</v>
       </c>
       <c r="DQ69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS69" t="b">
         <v>0</v>
@@ -32536,46 +32536,46 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW69" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="DX69" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="DZ69" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EA69" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EB69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EC69" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="ED69" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="EE69" t="inlineStr"/>
@@ -32584,12 +32584,12 @@
       <c r="EH69" t="inlineStr"/>
       <c r="EI69" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EJ69" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EK69" t="inlineStr"/>
@@ -32611,12 +32611,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -32626,25 +32626,25 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" t="n">
         <v>3</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>9</v>
       </c>
-      <c r="K70" t="n">
-        <v>6</v>
-      </c>
-      <c r="L70" t="n">
-        <v>15</v>
-      </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -32653,101 +32653,101 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R70" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="n">
         <v>10</v>
       </c>
       <c r="U70" t="n">
+        <v>14</v>
+      </c>
+      <c r="V70" t="n">
+        <v>13</v>
+      </c>
+      <c r="W70" t="n">
         <v>10</v>
       </c>
-      <c r="V70" t="n">
-        <v>18</v>
-      </c>
-      <c r="W70" t="n">
-        <v>6</v>
-      </c>
       <c r="X70" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y70" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="Z70" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AF70" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AG70" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AK70" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL70" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AM70" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AN70" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AO70" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AS70" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AU70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV70" t="n">
         <v>1</v>
@@ -32759,22 +32759,22 @@
         <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
       </c>
       <c r="BB70" t="n">
-        <v>2523</v>
+        <v>986</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -32783,46 +32783,46 @@
         <v>-1</v>
       </c>
       <c r="BG70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH70" t="n">
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BJ70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL70" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM70" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BN70" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR70" t="n">
         <v>1</v>
       </c>
       <c r="BS70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BU70" t="n">
         <v>1</v>
@@ -32831,22 +32831,22 @@
         <v>17</v>
       </c>
       <c r="BW70" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BX70" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="BY70" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BZ70" t="n">
-        <v>0.89</v>
+        <v>1.49</v>
       </c>
       <c r="CA70" t="n">
-        <v>1.79</v>
+        <v>1.18</v>
       </c>
       <c r="CB70" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CC70" t="n">
         <v>0</v>
@@ -32873,16 +32873,16 @@
         <v>1</v>
       </c>
       <c r="CK70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL70" t="n">
         <v>0</v>
       </c>
       <c r="CM70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN70" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO70" t="n">
         <v>0</v>
@@ -32894,73 +32894,73 @@
         <v>1</v>
       </c>
       <c r="CR70" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="CS70" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="CT70" t="n">
         <v>1</v>
       </c>
       <c r="CU70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV70" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX70" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY70" t="n">
         <v>7</v>
       </c>
-      <c r="CW70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX70" t="n">
+      <c r="CZ70" t="n">
+        <v>45</v>
+      </c>
+      <c r="DA70" t="n">
+        <v>54</v>
+      </c>
+      <c r="DB70" t="n">
         <v>9</v>
       </c>
-      <c r="CY70" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ70" t="n">
-        <v>80</v>
-      </c>
-      <c r="DA70" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB70" t="n">
-        <v>80</v>
-      </c>
       <c r="DC70" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="DD70" t="n">
         <v>1.73</v>
       </c>
       <c r="DE70" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF70" t="n">
         <v>1.2</v>
       </c>
       <c r="DG70" t="n">
-        <v>0.4</v>
+        <v>1.17</v>
       </c>
       <c r="DH70" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="DI70" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="DJ70" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK70" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="DL70" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="DM70" t="n">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="DN70" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="DO70" t="n">
         <v>22</v>
@@ -32969,10 +32969,10 @@
         <v>1</v>
       </c>
       <c r="DQ70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS70" t="b">
         <v>0</v>
@@ -32984,46 +32984,46 @@
         <v>0</v>
       </c>
       <c r="DV70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW70" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="DX70" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="DY70" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="DZ70" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="EA70" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="EB70" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="DY70" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="DZ70" t="inlineStr">
-        <is>
-          <t>3.72</t>
-        </is>
-      </c>
-      <c r="EA70" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="EB70" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="EC70" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="ED70" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EE70" t="inlineStr"/>
@@ -33032,12 +33032,12 @@
       <c r="EH70" t="inlineStr"/>
       <c r="EI70" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EJ70" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EK70" t="inlineStr"/>
@@ -34875,146 +34875,146 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
         <v>4</v>
       </c>
-      <c r="I75" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="R75" t="n">
         <v>7</v>
       </c>
-      <c r="K75" t="n">
+      <c r="S75" t="n">
+        <v>9</v>
+      </c>
+      <c r="T75" t="n">
+        <v>7</v>
+      </c>
+      <c r="U75" t="n">
+        <v>13</v>
+      </c>
+      <c r="V75" t="n">
+        <v>14</v>
+      </c>
+      <c r="W75" t="n">
+        <v>15</v>
+      </c>
+      <c r="X75" t="n">
         <v>5</v>
       </c>
-      <c r="L75" t="n">
-        <v>12</v>
-      </c>
-      <c r="M75" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>5</v>
-      </c>
-      <c r="R75" t="n">
-        <v>12</v>
-      </c>
-      <c r="S75" t="n">
-        <v>5</v>
-      </c>
-      <c r="T75" t="n">
-        <v>9</v>
-      </c>
-      <c r="U75" t="n">
-        <v>10</v>
-      </c>
-      <c r="V75" t="n">
-        <v>21</v>
-      </c>
-      <c r="W75" t="n">
-        <v>6</v>
-      </c>
-      <c r="X75" t="n">
-        <v>11</v>
-      </c>
       <c r="Y75" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z75" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AF75" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AJ75" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AL75" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AM75" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AN75" t="n">
         <v>1.83</v>
       </c>
       <c r="AO75" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AR75" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AS75" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AU75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW75" t="n">
         <v>2</v>
@@ -35023,22 +35023,22 @@
         <v>0</v>
       </c>
       <c r="AY75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB75" t="n">
-        <v>955</v>
+        <v>2522</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -35056,175 +35056,175 @@
         <v>3</v>
       </c>
       <c r="BJ75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK75" t="n">
         <v>3</v>
       </c>
-      <c r="BK75" t="n">
+      <c r="BL75" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>116</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV75" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX75" t="n">
         <v>4</v>
       </c>
-      <c r="BL75" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV75" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW75" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX75" t="n">
-        <v>63</v>
-      </c>
-      <c r="BY75" t="n">
-        <v>102</v>
-      </c>
-      <c r="BZ75" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CA75" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CB75" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="CC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM75" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU75" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV75" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX75" t="n">
+      <c r="CY75" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ75" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA75" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB75" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC75" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG75" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH75" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DI75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK75" t="n">
         <v>9</v>
       </c>
-      <c r="CY75" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ75" t="n">
-        <v>27</v>
-      </c>
-      <c r="DA75" t="n">
-        <v>72</v>
-      </c>
-      <c r="DB75" t="n">
-        <v>9</v>
-      </c>
-      <c r="DC75" t="n">
-        <v>45</v>
-      </c>
-      <c r="DD75" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE75" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="DF75" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DG75" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DH75" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI75" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DJ75" t="n">
-        <v>74</v>
-      </c>
-      <c r="DK75" t="n">
-        <v>29</v>
-      </c>
       <c r="DL75" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="DO75" t="n">
         <v>22</v>
@@ -35239,7 +35239,7 @@
         <v>1</v>
       </c>
       <c r="DS75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT75" t="b">
         <v>0</v>
@@ -35248,72 +35248,72 @@
         <v>0</v>
       </c>
       <c r="DV75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW75" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="DX75" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="EE75" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EE75" t="inlineStr"/>
       <c r="EF75" t="inlineStr"/>
       <c r="EG75" t="inlineStr"/>
-      <c r="EH75" t="inlineStr">
-        <is>
-          <t>2.22</t>
-        </is>
-      </c>
+      <c r="EH75" t="inlineStr"/>
       <c r="EI75" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EJ75" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EK75" t="inlineStr"/>
-      <c r="EL75" t="inlineStr"/>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EK75" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL75" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -35331,146 +35331,146 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45956.54166666666</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
+        <v>7</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5</v>
+      </c>
+      <c r="L76" t="n">
+        <v>12</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>12</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="n">
+        <v>9</v>
+      </c>
+      <c r="U76" t="n">
+        <v>10</v>
+      </c>
+      <c r="V76" t="n">
+        <v>21</v>
+      </c>
+      <c r="W76" t="n">
         <v>6</v>
       </c>
-      <c r="K76" t="n">
-        <v>10</v>
-      </c>
-      <c r="L76" t="n">
-        <v>16</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>4</v>
-      </c>
-      <c r="R76" t="n">
+      <c r="X76" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
         <v>7</v>
       </c>
-      <c r="S76" t="n">
-        <v>9</v>
-      </c>
-      <c r="T76" t="n">
-        <v>7</v>
-      </c>
-      <c r="U76" t="n">
-        <v>13</v>
-      </c>
-      <c r="V76" t="n">
-        <v>14</v>
-      </c>
-      <c r="W76" t="n">
-        <v>15</v>
-      </c>
-      <c r="X76" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AF76" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AL76" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN76" t="n">
         <v>1.83</v>
       </c>
       <c r="AO76" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AS76" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AU76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW76" t="n">
         <v>2</v>
@@ -35479,22 +35479,22 @@
         <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB76" t="n">
-        <v>2522</v>
+        <v>955</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -35512,19 +35512,19 @@
         <v>3</v>
       </c>
       <c r="BJ76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BK76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO76" t="n">
         <v>1</v>
@@ -35533,7 +35533,7 @@
         <v>0</v>
       </c>
       <c r="BQ76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR76" t="n">
         <v>0</v>
@@ -35542,31 +35542,31 @@
         <v>1</v>
       </c>
       <c r="BT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU76" t="n">
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="BW76" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="BX76" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="BY76" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ76" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="CA76" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="CB76" t="n">
-        <v>3.06</v>
+        <v>3.78</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
@@ -35593,16 +35593,16 @@
         <v>1</v>
       </c>
       <c r="CK76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL76" t="n">
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO76" t="n">
         <v>0</v>
@@ -35614,73 +35614,73 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS76" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CV76" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY76" t="n">
         <v>4</v>
       </c>
-      <c r="CY76" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ76" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="DA76" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="DB76" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="DC76" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="DD76" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.73</v>
+        <v>1.91</v>
       </c>
       <c r="DF76" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DG76" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH76" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="DI76" t="n">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="DJ76" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="DK76" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="DL76" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="DO76" t="n">
         <v>22</v>
@@ -35695,7 +35695,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -35704,72 +35704,72 @@
         <v>0</v>
       </c>
       <c r="DV76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW76" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="DX76" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EE76" t="inlineStr"/>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="EE76" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
       <c r="EF76" t="inlineStr"/>
       <c r="EG76" t="inlineStr"/>
-      <c r="EH76" t="inlineStr"/>
+      <c r="EH76" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
       <c r="EI76" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EK76" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EL76" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EK76" t="inlineStr"/>
+      <c r="EL76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -37965,7 +37965,7 @@
         <v>1.73</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF81" t="n">
         <v>1</v>
@@ -40399,143 +40399,143 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" t="n">
+        <v>9</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
         <v>6</v>
       </c>
-      <c r="L87" t="n">
-        <v>10</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>6</v>
-      </c>
-      <c r="R87" t="n">
-        <v>3</v>
-      </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U87" t="n">
         <v>11</v>
       </c>
       <c r="V87" t="n">
+        <v>21</v>
+      </c>
+      <c r="W87" t="n">
         <v>14</v>
       </c>
-      <c r="W87" t="n">
-        <v>9</v>
-      </c>
       <c r="X87" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Y87" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="Z87" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Vejle Stadion</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Roms Hule 3, Vejle</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD87" t="n">
         <v>1</v>
       </c>
       <c r="AE87" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="AF87" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG87" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL87" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AN87" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AO87" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR87" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AS87" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="AT87" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AU87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV87" t="n">
         <v>0</v>
@@ -40544,25 +40544,25 @@
         <v>0</v>
       </c>
       <c r="AX87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA87" t="n">
         <v>0</v>
       </c>
       <c r="BB87" t="n">
-        <v>3647</v>
+        <v>2526</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -40580,175 +40580,175 @@
         <v>1</v>
       </c>
       <c r="BJ87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL87" t="n">
         <v>4</v>
       </c>
       <c r="BM87" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS87" t="n">
         <v>3</v>
       </c>
-      <c r="BN87" t="n">
+      <c r="BT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV87" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW87" t="n">
+        <v>58</v>
+      </c>
+      <c r="BX87" t="n">
+        <v>104</v>
+      </c>
+      <c r="BY87" t="n">
+        <v>94</v>
+      </c>
+      <c r="BZ87" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA87" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB87" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN87" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR87" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS87" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV87" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW87" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX87" t="n">
         <v>7</v>
       </c>
-      <c r="BO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV87" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW87" t="n">
+      <c r="CY87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ87" t="n">
+        <v>43</v>
+      </c>
+      <c r="DA87" t="n">
+        <v>79</v>
+      </c>
+      <c r="DB87" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC87" t="n">
         <v>64</v>
       </c>
-      <c r="BX87" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY87" t="n">
-        <v>153</v>
-      </c>
-      <c r="BZ87" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CA87" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB87" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR87" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS87" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU87" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV87" t="n">
-        <v>9</v>
-      </c>
-      <c r="CW87" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX87" t="n">
-        <v>10</v>
-      </c>
-      <c r="CY87" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ87" t="n">
-        <v>79</v>
-      </c>
-      <c r="DA87" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB87" t="n">
+      <c r="DD87" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DE87" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DI87" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ87" t="n">
         <v>57</v>
       </c>
-      <c r="DC87" t="n">
-        <v>79</v>
-      </c>
-      <c r="DD87" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE87" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="DF87" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="DG87" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DH87" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI87" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DJ87" t="n">
+      <c r="DK87" t="n">
         <v>22</v>
       </c>
-      <c r="DK87" t="n">
-        <v>0</v>
-      </c>
       <c r="DL87" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="DN87" t="n">
-        <v>3.26</v>
+        <v>2.68</v>
       </c>
       <c r="DO87" t="n">
         <v>22</v>
@@ -40760,7 +40760,7 @@
         <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS87" t="b">
         <v>0</v>
@@ -40776,66 +40776,66 @@
       </c>
       <c r="DW87" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="DX87" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EB87" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EC87" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="ED87" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EE87" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="EF87" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EG87" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr"/>
+      <c r="EG87" t="inlineStr"/>
       <c r="EH87" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EI87" t="inlineStr"/>
-      <c r="EJ87" t="inlineStr"/>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EK87" t="inlineStr"/>
       <c r="EL87" t="inlineStr"/>
     </row>
@@ -40855,143 +40855,143 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>45970.54166666666</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" t="n">
+        <v>6</v>
+      </c>
+      <c r="L88" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>6</v>
+      </c>
+      <c r="R88" t="n">
         <v>3</v>
       </c>
-      <c r="I88" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" t="n">
-        <v>8</v>
-      </c>
-      <c r="L88" t="n">
-        <v>9</v>
-      </c>
-      <c r="M88" t="n">
-        <v>2</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>2</v>
-      </c>
-      <c r="R88" t="n">
-        <v>6</v>
-      </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T88" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U88" t="n">
         <v>11</v>
       </c>
       <c r="V88" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W88" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X88" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y88" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="Z88" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
         <v>1</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="AF88" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG88" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AL88" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AN88" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AP88" t="n">
         <v>1.82</v>
       </c>
-      <c r="AO88" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP88" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AQ88" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AU88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV88" t="n">
         <v>0</v>
@@ -41000,25 +41000,25 @@
         <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA88" t="n">
         <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>2526</v>
+        <v>3647</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="BE88" t="n">
         <v>0</v>
@@ -41036,22 +41036,22 @@
         <v>1</v>
       </c>
       <c r="BJ88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BL88" t="n">
         <v>4</v>
       </c>
       <c r="BM88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BN88" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BO88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP88" t="n">
         <v>1</v>
@@ -41063,7 +41063,7 @@
         <v>0</v>
       </c>
       <c r="BS88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT88" t="n">
         <v>0</v>
@@ -41072,25 +41072,25 @@
         <v>1</v>
       </c>
       <c r="BV88" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BW88" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BX88" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="BY88" t="n">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="BZ88" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="CA88" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="CB88" t="n">
-        <v>3.37</v>
+        <v>3.01</v>
       </c>
       <c r="CC88" t="n">
         <v>0</v>
@@ -41123,10 +41123,10 @@
         <v>0</v>
       </c>
       <c r="CM88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO88" t="n">
         <v>0</v>
@@ -41138,73 +41138,73 @@
         <v>1</v>
       </c>
       <c r="CR88" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="CS88" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV88" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW88" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX88" t="n">
         <v>10</v>
       </c>
-      <c r="CT88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU88" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV88" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW88" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX88" t="n">
+      <c r="CY88" t="n">
         <v>7</v>
       </c>
-      <c r="CY88" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ88" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="DA88" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB88" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC88" t="n">
         <v>79</v>
       </c>
-      <c r="DB88" t="n">
-        <v>29</v>
-      </c>
-      <c r="DC88" t="n">
-        <v>64</v>
-      </c>
       <c r="DD88" t="n">
         <v>1</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="DF88" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="DG88" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="DH88" t="n">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="DI88" t="n">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="DJ88" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="DK88" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="DL88" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="DM88" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="DN88" t="n">
-        <v>2.68</v>
+        <v>3.26</v>
       </c>
       <c r="DO88" t="n">
         <v>22</v>
@@ -41216,7 +41216,7 @@
         <v>1</v>
       </c>
       <c r="DR88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS88" t="b">
         <v>0</v>
@@ -41232,66 +41232,66 @@
       </c>
       <c r="DW88" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="DX88" t="inlineStr">
         <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="DY88" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="DZ88" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="EA88" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EB88" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="ED88" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EE88" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr">
+        <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="DY88" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="DZ88" t="inlineStr">
-        <is>
-          <t>3.84</t>
-        </is>
-      </c>
-      <c r="EA88" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EB88" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="EC88" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="ED88" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EE88" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="EF88" t="inlineStr"/>
-      <c r="EG88" t="inlineStr"/>
+      <c r="EG88" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
       <c r="EH88" t="inlineStr">
         <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="EI88" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EJ88" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr"/>
+      <c r="EJ88" t="inlineStr"/>
       <c r="EK88" t="inlineStr"/>
       <c r="EL88" t="inlineStr"/>
     </row>
@@ -46169,7 +46169,7 @@
         <v>1</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF99" t="n">
         <v>1.25</v>
@@ -48454,7 +48454,7 @@
         <v>69</v>
       </c>
       <c r="DD104" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE104" t="n">
         <v>1.09</v>
@@ -50863,37 +50863,37 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
         <v>46061.54166666666</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" t="n">
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K110" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L110" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N110" t="n">
         <v>1</v>
@@ -50905,101 +50905,101 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
       </c>
       <c r="T110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U110" t="n">
+        <v>13</v>
+      </c>
+      <c r="V110" t="n">
         <v>11</v>
       </c>
-      <c r="V110" t="n">
-        <v>14</v>
-      </c>
       <c r="W110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X110" t="n">
         <v>11</v>
       </c>
       <c r="Y110" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="Z110" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>JYSK park</t>
+          <t>Right to Dream Park</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>Ansvej 104, Silkeborg</t>
+          <t>Idrætsvænget 2, Farum</t>
         </is>
       </c>
       <c r="AC110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD110" t="n">
         <v>1</v>
       </c>
       <c r="AE110" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF110" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AG110" t="n">
-        <v>2.15</v>
+        <v>4.7</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI110" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AJ110" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AK110" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL110" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AM110" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AN110" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AO110" t="n">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.26</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AS110" t="n">
         <v>3.34</v>
       </c>
       <c r="AT110" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AU110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV110" t="n">
         <v>0</v>
@@ -51008,25 +51008,25 @@
         <v>0</v>
       </c>
       <c r="AX110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY110" t="n">
         <v>1</v>
       </c>
       <c r="AZ110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA110" t="n">
         <v>0</v>
       </c>
       <c r="BB110" t="n">
-        <v>2526</v>
+        <v>986</v>
       </c>
       <c r="BC110" t="n">
         <v>0</v>
       </c>
       <c r="BD110" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BE110" t="n">
         <v>0</v>
@@ -51041,64 +51041,64 @@
         <v>1</v>
       </c>
       <c r="BI110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ110" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BK110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT110" t="n">
         <v>3</v>
       </c>
-      <c r="BL110" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM110" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN110" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT110" t="n">
-        <v>2</v>
-      </c>
       <c r="BU110" t="n">
         <v>1</v>
       </c>
       <c r="BV110" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="BW110" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="BX110" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="BY110" t="n">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="BZ110" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="CA110" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="CB110" t="n">
-        <v>2.68</v>
+        <v>2.49</v>
       </c>
       <c r="CC110" t="n">
         <v>0</v>
@@ -51131,10 +51131,10 @@
         <v>0</v>
       </c>
       <c r="CM110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO110" t="n">
         <v>0</v>
@@ -51146,73 +51146,73 @@
         <v>1</v>
       </c>
       <c r="CR110" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CS110" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="CT110" t="n">
         <v>1</v>
       </c>
       <c r="CU110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CV110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
         <v>10</v>
       </c>
-      <c r="CW110" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX110" t="n">
-        <v>13</v>
-      </c>
       <c r="CY110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CZ110" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DA110" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DB110" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="DC110" t="n">
         <v>73</v>
       </c>
       <c r="DD110" t="n">
-        <v>1</v>
+        <v>1.73</v>
       </c>
       <c r="DE110" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="DF110" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="DG110" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="DH110" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="DI110" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="DJ110" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="DK110" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DL110" t="n">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="DM110" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="DN110" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="DO110" t="n">
         <v>22</v>
@@ -51221,10 +51221,10 @@
         <v>1</v>
       </c>
       <c r="DQ110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS110" t="b">
         <v>0</v>
@@ -51236,76 +51236,76 @@
         <v>0</v>
       </c>
       <c r="DV110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW110" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="DX110" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="DY110" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="DZ110" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="EA110" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="EB110" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EC110" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="ED110" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EE110" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF110" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EG110" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EH110" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EI110" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EJ110" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EK110" t="inlineStr"/>
@@ -51327,37 +51327,37 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
         <v>46061.54166666666</v>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K111" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L111" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N111" t="n">
         <v>1</v>
@@ -51369,101 +51369,101 @@
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
       </c>
       <c r="T111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U111" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V111" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="X111" t="n">
         <v>11</v>
       </c>
       <c r="Y111" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="Z111" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Right to Dream Park</t>
+          <t>JYSK park</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Idrætsvænget 2, Farum</t>
+          <t>Ansvej 104, Silkeborg</t>
         </is>
       </c>
       <c r="AC111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD111" t="n">
         <v>1</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="AF111" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AG111" t="n">
-        <v>4.7</v>
+        <v>2.15</v>
       </c>
       <c r="AH111" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AI111" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AJ111" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="AK111" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL111" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="AM111" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AN111" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AO111" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.26</v>
       </c>
       <c r="AR111" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AS111" t="n">
         <v>3.34</v>
       </c>
       <c r="AT111" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AU111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV111" t="n">
         <v>0</v>
@@ -51472,25 +51472,25 @@
         <v>0</v>
       </c>
       <c r="AX111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY111" t="n">
         <v>1</v>
       </c>
       <c r="AZ111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA111" t="n">
         <v>0</v>
       </c>
       <c r="BB111" t="n">
-        <v>986</v>
+        <v>2526</v>
       </c>
       <c r="BC111" t="n">
         <v>0</v>
       </c>
       <c r="BD111" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BE111" t="n">
         <v>0</v>
@@ -51505,22 +51505,22 @@
         <v>1</v>
       </c>
       <c r="BI111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ111" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK111" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL111" t="n">
         <v>4</v>
       </c>
-      <c r="BJ111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL111" t="n">
-        <v>1</v>
-      </c>
       <c r="BM111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN111" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BO111" t="n">
         <v>0</v>
@@ -51529,7 +51529,7 @@
         <v>0</v>
       </c>
       <c r="BQ111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR111" t="n">
         <v>1</v>
@@ -51538,68 +51538,68 @@
         <v>0</v>
       </c>
       <c r="BT111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN111" t="n">
         <v>3</v>
       </c>
-      <c r="BU111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV111" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW111" t="n">
-        <v>42</v>
-      </c>
-      <c r="BX111" t="n">
-        <v>124</v>
-      </c>
-      <c r="BY111" t="n">
-        <v>86</v>
-      </c>
-      <c r="BZ111" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CA111" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="CB111" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM111" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN111" t="n">
-        <v>0</v>
-      </c>
       <c r="CO111" t="n">
         <v>0</v>
       </c>
@@ -51610,73 +51610,73 @@
         <v>1</v>
       </c>
       <c r="CR111" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CS111" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="CT111" t="n">
         <v>1</v>
       </c>
       <c r="CU111" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CV111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CW111" t="n">
         <v>1</v>
       </c>
       <c r="CX111" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CY111" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CZ111" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DA111" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DB111" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="DC111" t="n">
         <v>73</v>
       </c>
       <c r="DD111" t="n">
-        <v>1.73</v>
+        <v>1</v>
       </c>
       <c r="DE111" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="DF111" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="DG111" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DH111" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI111" t="n">
         <v>1.33</v>
       </c>
-      <c r="DH111" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DI111" t="n">
-        <v>1.61</v>
-      </c>
       <c r="DJ111" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="DK111" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DL111" t="n">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="DM111" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="DN111" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="DO111" t="n">
         <v>22</v>
@@ -51685,10 +51685,10 @@
         <v>1</v>
       </c>
       <c r="DQ111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS111" t="b">
         <v>0</v>
@@ -51700,76 +51700,76 @@
         <v>0</v>
       </c>
       <c r="DV111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW111" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="DX111" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="DY111" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="DZ111" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="EA111" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EB111" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EC111" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="ED111" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EE111" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EF111" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EG111" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EH111" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EI111" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EJ111" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EK111" t="inlineStr"/>
@@ -52569,7 +52569,7 @@
         <v>1.64</v>
       </c>
       <c r="DE113" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF113" t="n">
         <v>1.78</v>
@@ -54838,7 +54838,7 @@
         <v>73</v>
       </c>
       <c r="DD118" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE118" t="n">
         <v>2.27</v>
@@ -57599,7 +57599,7 @@
         <v>2.53</v>
       </c>
       <c r="DO124" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP124" t="b">
         <v>1</v>
@@ -59079,12 +59079,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
@@ -59100,16 +59100,16 @@
         <v>3</v>
       </c>
       <c r="J128" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
         <v>1</v>
@@ -59121,98 +59121,98 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S128" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T128" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U128" t="n">
         <v>22</v>
       </c>
       <c r="V128" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W128" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X128" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Y128" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z128" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
         <v>1</v>
       </c>
       <c r="AE128" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AF128" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AG128" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AI128" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ128" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL128" t="n">
         <v>2.4</v>
       </c>
-      <c r="AK128" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL128" t="n">
-        <v>2.53</v>
-      </c>
       <c r="AM128" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AO128" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AR128" t="n">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="AS128" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AT128" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AU128" t="n">
         <v>3</v>
@@ -59221,28 +59221,28 @@
         <v>1</v>
       </c>
       <c r="AW128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX128" t="n">
         <v>1</v>
       </c>
       <c r="AY128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB128" t="n">
-        <v>2526</v>
+        <v>3649</v>
       </c>
       <c r="BC128" t="n">
         <v>0</v>
       </c>
       <c r="BD128" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE128" t="n">
         <v>0</v>
@@ -59257,64 +59257,64 @@
         <v>1</v>
       </c>
       <c r="BI128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ128" t="n">
         <v>1</v>
       </c>
       <c r="BK128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BN128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO128" t="n">
         <v>0</v>
       </c>
       <c r="BP128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU128" t="n">
         <v>1</v>
       </c>
       <c r="BV128" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="BW128" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="BX128" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BY128" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="BZ128" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="CB128" t="n">
-        <v>3.7</v>
+        <v>3.99</v>
       </c>
       <c r="CC128" t="n">
         <v>0</v>
@@ -59341,7 +59341,7 @@
         <v>1</v>
       </c>
       <c r="CK128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL128" t="n">
         <v>0</v>
@@ -59350,13 +59350,13 @@
         <v>1</v>
       </c>
       <c r="CN128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO128" t="n">
         <v>0</v>
       </c>
       <c r="CP128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ128" t="n">
         <v>1</v>
@@ -59365,16 +59365,16 @@
         <v>16</v>
       </c>
       <c r="CS128" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CT128" t="n">
         <v>1</v>
       </c>
       <c r="CU128" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="CV128" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CW128" t="n">
         <v>1</v>
@@ -59386,49 +59386,49 @@
         <v>11</v>
       </c>
       <c r="CZ128" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC128" t="n">
         <v>80</v>
       </c>
-      <c r="DA128" t="n">
-        <v>85</v>
-      </c>
-      <c r="DB128" t="n">
-        <v>65</v>
-      </c>
-      <c r="DC128" t="n">
-        <v>90</v>
-      </c>
       <c r="DD128" t="n">
-        <v>1.73</v>
+        <v>0.92</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="DF128" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="DG128" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="DH128" t="n">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="DI128" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="DJ128" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="DK128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="DL128" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DM128" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="DN128" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="DO128" t="n">
         <v>22</v>
@@ -59456,37 +59456,37 @@
       </c>
       <c r="DW128" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="DX128" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="DY128" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="DZ128" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EA128" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EB128" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC128" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED128" t="inlineStr">
@@ -59496,26 +59496,26 @@
       </c>
       <c r="EE128" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EF128" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EG128" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EF128" t="inlineStr"/>
+      <c r="EG128" t="inlineStr"/>
       <c r="EH128" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EI128" t="inlineStr"/>
-      <c r="EJ128" t="inlineStr"/>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
       <c r="EK128" t="inlineStr"/>
       <c r="EL128" t="inlineStr"/>
     </row>
@@ -59535,40 +59535,40 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F129" s="2" t="n">
         <v>46082.66666666666</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>6</v>
       </c>
       <c r="K129" t="n">
+        <v>2</v>
+      </c>
+      <c r="L129" t="n">
         <v>8</v>
       </c>
-      <c r="L129" t="n">
-        <v>14</v>
-      </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -59577,104 +59577,104 @@
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S129" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T129" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="U129" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V129" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W129" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X129" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="Y129" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="Z129" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>Sydbank Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>Stadionvej 7, Haderslev</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE129" t="n">
-        <v>2.19</v>
+        <v>1.49</v>
       </c>
       <c r="AF129" t="n">
-        <v>3.4</v>
+        <v>4.83</v>
       </c>
       <c r="AG129" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH129" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AI129" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AJ129" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AK129" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL129" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AM129" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AN129" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AO129" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AP129" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.25</v>
       </c>
       <c r="AR129" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AS129" t="n">
         <v>3.4</v>
       </c>
       <c r="AT129" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AU129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW129" t="n">
         <v>0</v>
@@ -59689,16 +59689,16 @@
         <v>0</v>
       </c>
       <c r="BA129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB129" t="n">
-        <v>2519</v>
+        <v>-1</v>
       </c>
       <c r="BC129" t="n">
         <v>0</v>
       </c>
       <c r="BD129" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BE129" t="n">
         <v>0</v>
@@ -59713,184 +59713,184 @@
         <v>1</v>
       </c>
       <c r="BI129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR129" t="n">
         <v>5</v>
       </c>
-      <c r="BM129" t="n">
+      <c r="BS129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>49</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX129" t="n">
         <v>6</v>
       </c>
-      <c r="BN129" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV129" t="n">
-        <v>45</v>
-      </c>
-      <c r="BW129" t="n">
-        <v>72</v>
-      </c>
-      <c r="BX129" t="n">
-        <v>71</v>
-      </c>
-      <c r="BY129" t="n">
-        <v>102</v>
-      </c>
-      <c r="BZ129" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CA129" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CB129" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP129" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR129" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS129" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU129" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV129" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW129" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX129" t="n">
-        <v>14</v>
-      </c>
       <c r="CY129" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CZ129" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DA129" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="DB129" t="n">
         <v>45</v>
       </c>
       <c r="DC129" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="DD129" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="DF129" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="DG129" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DH129" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DI129" t="n">
         <v>1.57</v>
       </c>
-      <c r="DI129" t="n">
-        <v>1.29</v>
-      </c>
       <c r="DJ129" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DK129" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="DL129" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="DM129" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="DN129" t="n">
-        <v>2.77</v>
+        <v>3.56</v>
       </c>
       <c r="DO129" t="n">
         <v>22</v>
       </c>
       <c r="DP129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ129" t="b">
         <v>0</v>
@@ -59912,58 +59912,74 @@
       </c>
       <c r="DW129" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="DX129" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="DY129" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="DZ129" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="EA129" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="EB129" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EC129" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="ED129" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="EE129" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EF129" t="inlineStr"/>
-      <c r="EG129" t="inlineStr"/>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF129" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EG129" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
       <c r="EH129" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EI129" t="inlineStr"/>
-      <c r="EJ129" t="inlineStr"/>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EI129" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
       <c r="EK129" t="inlineStr"/>
       <c r="EL129" t="inlineStr"/>
     </row>
@@ -60305,7 +60321,7 @@
         <v>1.18</v>
       </c>
       <c r="DE130" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DF130" t="n">
         <v>1.3</v>
@@ -60455,12 +60471,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F131" s="2" t="n">
@@ -60470,149 +60486,149 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" t="n">
+        <v>6</v>
+      </c>
+      <c r="K131" t="n">
+        <v>8</v>
+      </c>
+      <c r="L131" t="n">
+        <v>14</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
         <v>3</v>
       </c>
-      <c r="J131" t="n">
-        <v>2</v>
-      </c>
-      <c r="K131" t="n">
-        <v>4</v>
-      </c>
-      <c r="L131" t="n">
-        <v>6</v>
-      </c>
-      <c r="M131" t="n">
-        <v>1</v>
-      </c>
-      <c r="N131" t="n">
-        <v>1</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>5</v>
-      </c>
       <c r="R131" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T131" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="U131" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V131" t="n">
+        <v>13</v>
+      </c>
+      <c r="W131" t="n">
+        <v>12</v>
+      </c>
+      <c r="X131" t="n">
         <v>8</v>
       </c>
-      <c r="W131" t="n">
-        <v>18</v>
-      </c>
-      <c r="X131" t="n">
-        <v>13</v>
-      </c>
       <c r="Y131" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z131" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>Vejle Stadion</t>
+          <t>Sydbank Park</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>Roms Hule 3, Vejle</t>
+          <t>Stadionvej 7, Haderslev</t>
         </is>
       </c>
       <c r="AC131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>1</v>
       </c>
       <c r="AE131" t="n">
-        <v>5.6</v>
+        <v>2.19</v>
       </c>
       <c r="AF131" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AG131" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="AH131" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AI131" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AJ131" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AK131" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AL131" t="n">
-        <v>1.85</v>
+        <v>2.43</v>
       </c>
       <c r="AM131" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AN131" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AO131" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AR131" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="AS131" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="AT131" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AU131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW131" t="n">
         <v>0</v>
       </c>
       <c r="AX131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB131" t="n">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="BC131" t="n">
         <v>0</v>
@@ -60633,178 +60649,178 @@
         <v>1</v>
       </c>
       <c r="BI131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ131" t="n">
         <v>3</v>
       </c>
       <c r="BK131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM131" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BN131" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BO131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ131" t="n">
         <v>0</v>
       </c>
       <c r="BR131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU131" t="n">
         <v>1</v>
       </c>
       <c r="BV131" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BW131" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="BX131" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="BY131" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU131" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV131" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW131" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX131" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY131" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ131" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA131" t="n">
         <v>90</v>
       </c>
-      <c r="BZ131" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CA131" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="CB131" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI131" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ131" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN131" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP131" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ131" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR131" t="n">
-        <v>24</v>
-      </c>
-      <c r="CS131" t="n">
-        <v>33</v>
-      </c>
-      <c r="CT131" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU131" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV131" t="n">
-        <v>18</v>
-      </c>
-      <c r="CW131" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX131" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY131" t="n">
-        <v>5</v>
-      </c>
-      <c r="CZ131" t="n">
-        <v>65</v>
-      </c>
-      <c r="DA131" t="n">
-        <v>100</v>
-      </c>
       <c r="DB131" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="DC131" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="DD131" t="n">
-        <v>1</v>
+        <v>2.09</v>
       </c>
       <c r="DE131" t="n">
-        <v>2.27</v>
+        <v>1.09</v>
       </c>
       <c r="DF131" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="DG131" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="DH131" t="n">
-        <v>0.67</v>
+        <v>1.57</v>
       </c>
       <c r="DI131" t="n">
-        <v>2.24</v>
+        <v>1.29</v>
       </c>
       <c r="DJ131" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="DK131" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="DL131" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="DM131" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="DN131" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="DO131" t="n">
         <v>22</v>
@@ -60813,10 +60829,10 @@
         <v>1</v>
       </c>
       <c r="DQ131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS131" t="b">
         <v>0</v>
@@ -60828,72 +60844,64 @@
         <v>0</v>
       </c>
       <c r="DV131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW131" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="DX131" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="DY131" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="DZ131" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EA131" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EB131" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EC131" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="ED131" t="inlineStr">
         <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="EE131" t="inlineStr"/>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EE131" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
       <c r="EF131" t="inlineStr"/>
       <c r="EG131" t="inlineStr"/>
-      <c r="EH131" t="inlineStr"/>
-      <c r="EI131" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="EJ131" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EK131" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EL131" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
+      <c r="EH131" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EI131" t="inlineStr"/>
+      <c r="EJ131" t="inlineStr"/>
+      <c r="EK131" t="inlineStr"/>
+      <c r="EL131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -60911,12 +60919,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F132" s="2" t="n">
@@ -60932,16 +60940,16 @@
         <v>3</v>
       </c>
       <c r="J132" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L132" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N132" t="n">
         <v>1</v>
@@ -60953,98 +60961,98 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S132" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T132" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U132" t="n">
         <v>22</v>
       </c>
       <c r="V132" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W132" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X132" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Y132" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z132" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD132" t="n">
         <v>1</v>
       </c>
       <c r="AE132" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AF132" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AG132" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AH132" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AI132" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ132" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AK132" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL132" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AM132" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AN132" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AO132" t="n">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AR132" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="AS132" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AT132" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AU132" t="n">
         <v>3</v>
@@ -61053,28 +61061,28 @@
         <v>1</v>
       </c>
       <c r="AW132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX132" t="n">
         <v>1</v>
       </c>
       <c r="AY132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB132" t="n">
-        <v>3649</v>
+        <v>2526</v>
       </c>
       <c r="BC132" t="n">
         <v>0</v>
       </c>
       <c r="BD132" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE132" t="n">
         <v>0</v>
@@ -61089,64 +61097,64 @@
         <v>1</v>
       </c>
       <c r="BI132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN132" t="n">
         <v>4</v>
       </c>
-      <c r="BJ132" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK132" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM132" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN132" t="n">
-        <v>5</v>
-      </c>
       <c r="BO132" t="n">
         <v>0</v>
       </c>
       <c r="BP132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU132" t="n">
         <v>1</v>
       </c>
       <c r="BV132" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="BW132" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="BX132" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BY132" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="BZ132" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="CA132" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="CB132" t="n">
-        <v>3.99</v>
+        <v>3.7</v>
       </c>
       <c r="CC132" t="n">
         <v>0</v>
@@ -61173,7 +61181,7 @@
         <v>1</v>
       </c>
       <c r="CK132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL132" t="n">
         <v>0</v>
@@ -61182,13 +61190,13 @@
         <v>1</v>
       </c>
       <c r="CN132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO132" t="n">
         <v>0</v>
       </c>
       <c r="CP132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ132" t="n">
         <v>1</v>
@@ -61197,16 +61205,16 @@
         <v>16</v>
       </c>
       <c r="CS132" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CT132" t="n">
         <v>1</v>
       </c>
       <c r="CU132" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="CV132" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CW132" t="n">
         <v>1</v>
@@ -61218,49 +61226,49 @@
         <v>11</v>
       </c>
       <c r="CZ132" t="n">
+        <v>80</v>
+      </c>
+      <c r="DA132" t="n">
+        <v>85</v>
+      </c>
+      <c r="DB132" t="n">
         <v>65</v>
       </c>
-      <c r="DA132" t="n">
+      <c r="DC132" t="n">
         <v>90</v>
       </c>
-      <c r="DB132" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC132" t="n">
-        <v>80</v>
-      </c>
       <c r="DD132" t="n">
-        <v>1</v>
+        <v>1.73</v>
       </c>
       <c r="DE132" t="n">
-        <v>0.73</v>
+        <v>1.09</v>
       </c>
       <c r="DF132" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="DG132" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="DH132" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="DI132" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="DJ132" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="DK132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="DL132" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DM132" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DN132" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="DO132" t="n">
         <v>22</v>
@@ -61288,37 +61296,37 @@
       </c>
       <c r="DW132" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="DX132" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="DY132" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="DZ132" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EA132" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EB132" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EC132" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="ED132" t="inlineStr">
@@ -61328,26 +61336,26 @@
       </c>
       <c r="EE132" t="inlineStr">
         <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EF132" t="inlineStr"/>
-      <c r="EG132" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF132" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EG132" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
       <c r="EH132" t="inlineStr">
         <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EI132" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="EJ132" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EI132" t="inlineStr"/>
+      <c r="EJ132" t="inlineStr"/>
       <c r="EK132" t="inlineStr"/>
       <c r="EL132" t="inlineStr"/>
     </row>
@@ -61367,143 +61375,143 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F133" s="2" t="n">
         <v>46082.66666666666</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J133" t="n">
+        <v>2</v>
+      </c>
+      <c r="K133" t="n">
+        <v>4</v>
+      </c>
+      <c r="L133" t="n">
         <v>6</v>
       </c>
-      <c r="K133" t="n">
-        <v>2</v>
-      </c>
-      <c r="L133" t="n">
+      <c r="M133" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>5</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6</v>
+      </c>
+      <c r="S133" t="n">
+        <v>6</v>
+      </c>
+      <c r="T133" t="n">
+        <v>2</v>
+      </c>
+      <c r="U133" t="n">
+        <v>11</v>
+      </c>
+      <c r="V133" t="n">
         <v>8</v>
       </c>
-      <c r="M133" t="n">
-        <v>2</v>
-      </c>
-      <c r="N133" t="n">
-        <v>5</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>4</v>
-      </c>
-      <c r="R133" t="n">
-        <v>4</v>
-      </c>
-      <c r="S133" t="n">
-        <v>9</v>
-      </c>
-      <c r="T133" t="n">
-        <v>5</v>
-      </c>
-      <c r="U133" t="n">
+      <c r="W133" t="n">
+        <v>18</v>
+      </c>
+      <c r="X133" t="n">
         <v>13</v>
       </c>
-      <c r="V133" t="n">
-        <v>9</v>
-      </c>
-      <c r="W133" t="n">
-        <v>15</v>
-      </c>
-      <c r="X133" t="n">
-        <v>21</v>
-      </c>
       <c r="Y133" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="Z133" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD133" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE133" t="n">
-        <v>1.49</v>
+        <v>5.6</v>
       </c>
       <c r="AF133" t="n">
-        <v>4.83</v>
+        <v>4.3</v>
       </c>
       <c r="AG133" t="n">
-        <v>6</v>
+        <v>1.56</v>
       </c>
       <c r="AH133" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AI133" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AJ133" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AK133" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AL133" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AM133" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AN133" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AO133" t="n">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AR133" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="AS133" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="AT133" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="AU133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV133" t="n">
         <v>0</v>
@@ -61512,25 +61520,25 @@
         <v>0</v>
       </c>
       <c r="AX133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA133" t="n">
         <v>0</v>
       </c>
       <c r="BB133" t="n">
-        <v>-1</v>
+        <v>2516</v>
       </c>
       <c r="BC133" t="n">
         <v>0</v>
       </c>
       <c r="BD133" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BE133" t="n">
         <v>0</v>
@@ -61545,190 +61553,190 @@
         <v>1</v>
       </c>
       <c r="BI133" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM133" t="n">
         <v>4</v>
       </c>
       <c r="BN133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU133" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV133" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW133" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX133" t="n">
         <v>4</v>
       </c>
-      <c r="BO133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ133" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR133" t="n">
+      <c r="CY133" t="n">
         <v>5</v>
       </c>
-      <c r="BS133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT133" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU133" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV133" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW133" t="n">
-        <v>27</v>
-      </c>
-      <c r="BX133" t="n">
-        <v>91</v>
-      </c>
-      <c r="BY133" t="n">
-        <v>49</v>
-      </c>
-      <c r="BZ133" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CA133" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB133" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI133" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ133" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP133" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ133" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR133" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS133" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT133" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU133" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV133" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW133" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX133" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY133" t="n">
-        <v>11</v>
-      </c>
       <c r="CZ133" t="n">
+        <v>65</v>
+      </c>
+      <c r="DA133" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB133" t="n">
         <v>50</v>
       </c>
-      <c r="DA133" t="n">
-        <v>80</v>
-      </c>
-      <c r="DB133" t="n">
-        <v>45</v>
-      </c>
       <c r="DC133" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="DD133" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE133" t="n">
         <v>2.27</v>
       </c>
-      <c r="DE133" t="n">
-        <v>1.45</v>
-      </c>
       <c r="DF133" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="DG133" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="DH133" t="n">
-        <v>2.14</v>
+        <v>0.67</v>
       </c>
       <c r="DI133" t="n">
-        <v>1.57</v>
+        <v>2.24</v>
       </c>
       <c r="DJ133" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="DK133" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="DL133" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="DM133" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="DN133" t="n">
-        <v>3.56</v>
+        <v>3.14</v>
       </c>
       <c r="DO133" t="n">
         <v>22</v>
       </c>
       <c r="DP133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS133" t="b">
         <v>0</v>
@@ -61740,80 +61748,528 @@
         <v>0</v>
       </c>
       <c r="DV133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW133" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="DX133" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DY133" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="DZ133" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EA133" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EB133" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EC133" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="ED133" t="inlineStr">
         <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="EE133" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EF133" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EG133" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EH133" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EE133" t="inlineStr"/>
+      <c r="EF133" t="inlineStr"/>
+      <c r="EG133" t="inlineStr"/>
+      <c r="EH133" t="inlineStr"/>
       <c r="EI133" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EJ133" t="inlineStr">
         <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL133" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Fredericia</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>46094.75</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
+      <c r="I134" t="n">
+        <v>3</v>
+      </c>
+      <c r="J134" t="n">
+        <v>3</v>
+      </c>
+      <c r="K134" t="n">
+        <v>6</v>
+      </c>
+      <c r="L134" t="n">
+        <v>9</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>3</v>
+      </c>
+      <c r="R134" t="n">
+        <v>3</v>
+      </c>
+      <c r="S134" t="n">
+        <v>7</v>
+      </c>
+      <c r="T134" t="n">
+        <v>9</v>
+      </c>
+      <c r="U134" t="n">
+        <v>10</v>
+      </c>
+      <c r="V134" t="n">
+        <v>12</v>
+      </c>
+      <c r="W134" t="n">
+        <v>11</v>
+      </c>
+      <c r="X134" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>56</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Monjasa Park</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>Vestre Ringvej 102, Fredericia</t>
+        </is>
+      </c>
+      <c r="AC134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>2521</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>128</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU134" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV134" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW134" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX134" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY134" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ134" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA134" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB134" t="n">
+        <v>53</v>
+      </c>
+      <c r="DC134" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD134" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DE134" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DF134" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DG134" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DH134" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI134" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DJ134" t="n">
+        <v>41</v>
+      </c>
+      <c r="DK134" t="n">
+        <v>21</v>
+      </c>
+      <c r="DL134" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DM134" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DN134" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO134" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR134" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV134" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW134" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="DX134" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="DY134" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="DZ134" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EA134" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EB134" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EC134" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="ED134" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EE134" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EF134" t="inlineStr"/>
+      <c r="EG134" t="inlineStr"/>
+      <c r="EH134" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EI134" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ134" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="EK133" t="inlineStr"/>
-      <c r="EL133" t="inlineStr"/>
+      <c r="EK134" t="inlineStr"/>
+      <c r="EL134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL138" headerRowCount="1">
-  <autoFilter ref="A1:EL138"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL139" headerRowCount="1">
+  <autoFilter ref="A1:EL139"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL138"/>
+  <dimension ref="A1:EL139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4977,7 +4977,7 @@
         <v>1.18</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5919,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -7751,7 +7751,7 @@
         <v>2.69</v>
       </c>
       <c r="DO15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8663,7 +8663,7 @@
         <v>0.91</v>
       </c>
       <c r="DO17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -11407,7 +11407,7 @@
         <v>3.75</v>
       </c>
       <c r="DO23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11825,7 +11825,7 @@
         <v>1.5</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF24" t="n">
         <v>1.5</v>
@@ -11855,7 +11855,7 @@
         <v>2.85</v>
       </c>
       <c r="DO24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -13711,7 +13711,7 @@
         <v>1.98</v>
       </c>
       <c r="DO28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14167,7 +14167,7 @@
         <v>2.35</v>
       </c>
       <c r="DO29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -16031,7 +16031,7 @@
         <v>3.63</v>
       </c>
       <c r="DO33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -17393,7 +17393,7 @@
         <v>2.27</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF36" t="n">
         <v>0.5</v>
@@ -17423,7 +17423,7 @@
         <v>2.75</v>
       </c>
       <c r="DO36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18343,7 +18343,7 @@
         <v>2.88</v>
       </c>
       <c r="DO38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -19279,7 +19279,7 @@
         <v>3.56</v>
       </c>
       <c r="DO40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -22959,7 +22959,7 @@
         <v>2.69</v>
       </c>
       <c r="DO48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -23365,7 +23365,7 @@
         <v>0.92</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF49" t="n">
         <v>1.5</v>
@@ -23395,7 +23395,7 @@
         <v>2.22</v>
       </c>
       <c r="DO49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -24763,7 +24763,7 @@
         <v>3.05</v>
       </c>
       <c r="DO52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -25227,7 +25227,7 @@
         <v>3.35</v>
       </c>
       <c r="DO53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -27473,7 +27473,7 @@
         <v>1</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF58" t="n">
         <v>1.5</v>
@@ -27503,7 +27503,7 @@
         <v>2.65</v>
       </c>
       <c r="DO58" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -30219,7 +30219,7 @@
         <v>2.95</v>
       </c>
       <c r="DO64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP64" t="b">
         <v>1</v>
@@ -30683,7 +30683,7 @@
         <v>3.44</v>
       </c>
       <c r="DO65" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32059,7 +32059,7 @@
         <v>3.16</v>
       </c>
       <c r="DO68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33853,7 +33853,7 @@
         <v>2.08</v>
       </c>
       <c r="DE72" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF72" t="n">
         <v>2.33</v>
@@ -33883,7 +33883,7 @@
         <v>3.26</v>
       </c>
       <c r="DO72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35227,7 +35227,7 @@
         <v>2.66</v>
       </c>
       <c r="DO75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP75" t="b">
         <v>1</v>
@@ -38429,7 +38429,7 @@
         <v>2</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF82" t="n">
         <v>1.67</v>
@@ -38459,7 +38459,7 @@
         <v>2.34</v>
       </c>
       <c r="DO82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
@@ -39367,7 +39367,7 @@
         <v>3.22</v>
       </c>
       <c r="DO84" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -40287,7 +40287,7 @@
         <v>2.75</v>
       </c>
       <c r="DO86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP86" t="b">
         <v>1</v>
@@ -40751,7 +40751,7 @@
         <v>3.26</v>
       </c>
       <c r="DO87" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP87" t="b">
         <v>1</v>
@@ -42999,7 +42999,7 @@
         <v>2.83</v>
       </c>
       <c r="DO92" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -43897,7 +43897,7 @@
         <v>1.73</v>
       </c>
       <c r="DE94" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF94" t="n">
         <v>1.29</v>
@@ -43927,7 +43927,7 @@
         <v>2.31</v>
       </c>
       <c r="DO94" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -46663,7 +46663,7 @@
         <v>2.78</v>
       </c>
       <c r="DO100" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP100" t="b">
         <v>0</v>
@@ -47561,7 +47561,7 @@
         <v>1.5</v>
       </c>
       <c r="DE102" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF102" t="n">
         <v>1.38</v>
@@ -47591,7 +47591,7 @@
         <v>2.62</v>
       </c>
       <c r="DO102" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48935,7 +48935,7 @@
         <v>3.06</v>
       </c>
       <c r="DO105" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP105" t="b">
         <v>1</v>
@@ -50759,7 +50759,7 @@
         <v>3.17</v>
       </c>
       <c r="DO109" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -51215,7 +51215,7 @@
         <v>2.95</v>
       </c>
       <c r="DO110" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP110" t="b">
         <v>1</v>
@@ -53071,7 +53071,7 @@
         <v>2.43</v>
       </c>
       <c r="DO114" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP114" t="b">
         <v>1</v>
@@ -53945,7 +53945,7 @@
         <v>1.27</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF116" t="n">
         <v>1.22</v>
@@ -53975,7 +53975,7 @@
         <v>2.52</v>
       </c>
       <c r="DO116" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -56263,7 +56263,7 @@
         <v>2.68</v>
       </c>
       <c r="DO121" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP121" t="b">
         <v>1</v>
@@ -56681,7 +56681,7 @@
         <v>1.73</v>
       </c>
       <c r="DE122" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="DF122" t="n">
         <v>1.8</v>
@@ -56711,7 +56711,7 @@
         <v>3</v>
       </c>
       <c r="DO122" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP122" t="b">
         <v>1</v>
@@ -58063,7 +58063,7 @@
         <v>2.91</v>
       </c>
       <c r="DO125" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP125" t="b">
         <v>1</v>
@@ -60343,7 +60343,7 @@
         <v>2.47</v>
       </c>
       <c r="DO130" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP130" t="b">
         <v>1</v>
@@ -61727,7 +61727,7 @@
         <v>3.14</v>
       </c>
       <c r="DO133" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="DP133" t="b">
         <v>1</v>
@@ -64110,6 +64110,454 @@
           <t>3.31</t>
         </is>
       </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>46097.75</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2</v>
+      </c>
+      <c r="J139" t="n">
+        <v>7</v>
+      </c>
+      <c r="K139" t="n">
+        <v>4</v>
+      </c>
+      <c r="L139" t="n">
+        <v>11</v>
+      </c>
+      <c r="M139" t="n">
+        <v>2</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>8</v>
+      </c>
+      <c r="R139" t="n">
+        <v>5</v>
+      </c>
+      <c r="S139" t="n">
+        <v>13</v>
+      </c>
+      <c r="T139" t="n">
+        <v>7</v>
+      </c>
+      <c r="U139" t="n">
+        <v>21</v>
+      </c>
+      <c r="V139" t="n">
+        <v>12</v>
+      </c>
+      <c r="W139" t="n">
+        <v>6</v>
+      </c>
+      <c r="X139" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
+      <c r="AC139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>137</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>5</v>
+      </c>
+      <c r="CT139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU139" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV139" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW139" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX139" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY139" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ139" t="n">
+        <v>62</v>
+      </c>
+      <c r="DA139" t="n">
+        <v>91</v>
+      </c>
+      <c r="DB139" t="n">
+        <v>57</v>
+      </c>
+      <c r="DC139" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD139" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DE139" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DF139" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DG139" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DH139" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DI139" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DJ139" t="n">
+        <v>39</v>
+      </c>
+      <c r="DK139" t="n">
+        <v>10</v>
+      </c>
+      <c r="DL139" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM139" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN139" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="DO139" t="n">
+        <v>23</v>
+      </c>
+      <c r="DP139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU139" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV139" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW139" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="DX139" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="DY139" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="DZ139" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="EA139" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="EB139" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EC139" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="ED139" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="EE139" t="inlineStr"/>
+      <c r="EF139" t="inlineStr"/>
+      <c r="EG139" t="inlineStr"/>
+      <c r="EH139" t="inlineStr"/>
+      <c r="EI139" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="EJ139" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="EK139" t="inlineStr"/>
+      <c r="EL139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL139" headerRowCount="1">
-  <autoFilter ref="A1:EL139"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL140" headerRowCount="1">
+  <autoFilter ref="A1:EL140"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL139"/>
+  <dimension ref="A1:EL140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.8" customWidth="1" min="1" max="1"/>
@@ -3609,7 +3609,7 @@
         <v>2.08</v>
       </c>
       <c r="DE6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
         <v>1</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
@@ -7751,7 +7751,7 @@
         <v>2.69</v>
       </c>
       <c r="DO15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7855,170 +7855,162 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>45872.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10</v>
+      </c>
+      <c r="V16" t="n">
+        <v>18</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5</v>
+      </c>
+      <c r="X16" t="n">
         <v>6</v>
       </c>
-      <c r="L16" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5</v>
-      </c>
-      <c r="V16" t="n">
-        <v>17</v>
-      </c>
-      <c r="W16" t="n">
-        <v>11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>14</v>
-      </c>
       <c r="Y16" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="Z16" t="n">
-        <v>68</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Sydbank Park</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Stadionvej 7, Haderslev</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>3.31</v>
+        <v>1.94</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>3.68</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AP16" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AU16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
         <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB16" t="n">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -8033,178 +8025,178 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL16" t="n">
         <v>4</v>
       </c>
-      <c r="BK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>2</v>
-      </c>
       <c r="BM16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>49</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>7</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU16" t="n">
         <v>5</v>
       </c>
-      <c r="BN16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>65</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>136</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR16" t="n">
+      <c r="CV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX16" t="n">
         <v>11</v>
       </c>
-      <c r="CS16" t="n">
-        <v>25</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>8</v>
-      </c>
       <c r="CY16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CZ16" t="n">
         <v>50</v>
       </c>
       <c r="DA16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
         <v>50</v>
       </c>
-      <c r="DC16" t="n">
-        <v>100</v>
-      </c>
       <c r="DD16" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.25</v>
+        <v>0.73</v>
       </c>
       <c r="DF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DI16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>1.69</v>
+        <v>0.91</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.96</v>
+        <v>0.91</v>
       </c>
       <c r="DO16" t="n">
         <v>23</v>
@@ -8213,91 +8205,91 @@
         <v>1</v>
       </c>
       <c r="DQ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU16" t="b">
         <v>0</v>
       </c>
       <c r="DV16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr">
+        <is>
           <t>2.58</t>
         </is>
       </c>
-      <c r="ED16" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="EE16" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EH16" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr"/>
@@ -8319,162 +8311,170 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45872.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="R17" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10</v>
+      </c>
+      <c r="U17" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="n">
-        <v>9</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
+        <v>17</v>
+      </c>
+      <c r="W17" t="n">
+        <v>11</v>
+      </c>
+      <c r="X17" t="n">
         <v>14</v>
       </c>
-      <c r="U17" t="n">
-        <v>10</v>
-      </c>
-      <c r="V17" t="n">
-        <v>18</v>
-      </c>
-      <c r="W17" t="n">
-        <v>5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6</v>
-      </c>
       <c r="Y17" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Sydbank Park</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Stadionvej 7, Haderslev</t>
+        </is>
+      </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.94</v>
+        <v>3.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.68</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AP17" t="n">
         <v>1.85</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
         <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -8489,73 +8489,73 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BM17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BN17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS17" t="n">
         <v>2</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BW17" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="BX17" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="BY17" t="n">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.23</v>
+        <v>0.8</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="CB17" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="CC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -8573,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="CK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
         <v>1</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP17" t="n">
         <v>0</v>
@@ -8594,73 +8594,73 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CS17" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CV17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="CY17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="CZ17" t="n">
         <v>50</v>
       </c>
       <c r="DA17" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB17" t="n">
         <v>50</v>
       </c>
-      <c r="DB17" t="n">
-        <v>0</v>
-      </c>
       <c r="DC17" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ17" t="n">
         <v>50</v>
       </c>
-      <c r="DD17" t="n">
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
         <v>1.27</v>
       </c>
-      <c r="DE17" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL17" t="n">
-        <v>0</v>
-      </c>
       <c r="DM17" t="n">
-        <v>0.91</v>
+        <v>1.69</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.91</v>
+        <v>2.96</v>
       </c>
       <c r="DO17" t="n">
         <v>23</v>
@@ -8669,91 +8669,91 @@
         <v>1</v>
       </c>
       <c r="DQ17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU17" t="b">
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr"/>
@@ -15537,7 +15537,7 @@
         <v>1.18</v>
       </c>
       <c r="DE32" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF32" t="n">
         <v>1.5</v>
@@ -15679,70 +15679,70 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L33" t="n">
+        <v>14</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>15</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" t="n">
         <v>10</v>
       </c>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>12</v>
-      </c>
-      <c r="R33" t="n">
-        <v>5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>9</v>
-      </c>
-      <c r="T33" t="n">
-        <v>6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>21</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>11</v>
-      </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y33" t="n">
         <v>43</v>
@@ -15752,97 +15752,97 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>4.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AP33" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB33" t="n">
-        <v>955</v>
+        <v>3649</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -15857,178 +15857,178 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ33" t="n">
         <v>3</v>
       </c>
-      <c r="BJ33" t="n">
-        <v>2</v>
-      </c>
       <c r="BK33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BM33" t="n">
         <v>5</v>
       </c>
       <c r="BN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>97</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>128</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY33" t="n">
         <v>5</v>
       </c>
-      <c r="BO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>64</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>37</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>119</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>76</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CB33" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="CC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS33" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA33" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB33" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC33" t="n">
         <v>67</v>
       </c>
-      <c r="DC33" t="n">
-        <v>100</v>
-      </c>
       <c r="DD33" t="n">
-        <v>2.08</v>
+        <v>0.92</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.73</v>
+        <v>1.25</v>
       </c>
       <c r="DF33" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DG33" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DH33" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DI33" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ33" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL33" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="DN33" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="DO33" t="n">
         <v>23</v>
@@ -16037,91 +16037,91 @@
         <v>1</v>
       </c>
       <c r="DQ33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW33" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="DX33" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="DZ33" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="EA33" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EB33" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC33" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EG33" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EH33" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
           <t>1.64</t>
-        </is>
-      </c>
-      <c r="DZ33" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="EA33" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="EB33" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EC33" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="ED33" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EE33" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EF33" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EG33" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="EH33" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EJ33" t="inlineStr">
-        <is>
-          <t>1.82</t>
         </is>
       </c>
       <c r="EK33" t="inlineStr"/>
@@ -16143,70 +16143,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45893.5</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>12</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>21</v>
+      </c>
+      <c r="V34" t="n">
         <v>11</v>
       </c>
-      <c r="L34" t="n">
-        <v>14</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>15</v>
-      </c>
-      <c r="U34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V34" t="n">
-        <v>18</v>
-      </c>
       <c r="W34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y34" t="n">
         <v>43</v>
@@ -16216,97 +16216,97 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.14</v>
+        <v>4.57</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AJ34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO34" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>2.5</v>
       </c>
       <c r="AP34" t="n">
         <v>1.98</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AU34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
         <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB34" t="n">
-        <v>3649</v>
+        <v>955</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16321,64 +16321,64 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK34" t="n">
         <v>3</v>
       </c>
-      <c r="BK34" t="n">
-        <v>1</v>
-      </c>
       <c r="BL34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BM34" t="n">
         <v>5</v>
       </c>
       <c r="BN34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BO34" t="n">
         <v>0</v>
       </c>
       <c r="BP34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR34" t="n">
         <v>1</v>
       </c>
       <c r="BS34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="BW34" t="n">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="BX34" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="BY34" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="CA34" t="n">
-        <v>2.04</v>
+        <v>1.31</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -16411,7 +16411,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -16426,73 +16426,73 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CS34" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CV34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CY34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB34" t="n">
         <v>67</v>
       </c>
-      <c r="DA34" t="n">
+      <c r="DC34" t="n">
         <v>100</v>
       </c>
-      <c r="DB34" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC34" t="n">
-        <v>67</v>
-      </c>
       <c r="DD34" t="n">
-        <v>0.92</v>
+        <v>2.08</v>
       </c>
       <c r="DE34" t="n">
-        <v>1.25</v>
+        <v>0.73</v>
       </c>
       <c r="DF34" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DG34" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="DI34" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="DJ34" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK34" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.46</v>
+        <v>2.06</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.55</v>
+        <v>3.63</v>
       </c>
       <c r="DO34" t="n">
         <v>23</v>
@@ -16501,66 +16501,66 @@
         <v>1</v>
       </c>
       <c r="DQ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW34" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="DX34" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
@@ -16580,12 +16580,12 @@
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EK34" t="inlineStr"/>
@@ -18463,162 +18463,170 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45900.5</v>
       </c>
       <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>11</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>5</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="R39" t="n">
         <v>7</v>
       </c>
-      <c r="K39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>13</v>
+      </c>
+      <c r="V39" t="n">
+        <v>10</v>
+      </c>
+      <c r="W39" t="n">
         <v>8</v>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>10</v>
-      </c>
-      <c r="R39" t="n">
-        <v>5</v>
-      </c>
-      <c r="S39" t="n">
-        <v>20</v>
-      </c>
-      <c r="T39" t="n">
-        <v>4</v>
-      </c>
-      <c r="U39" t="n">
-        <v>30</v>
-      </c>
-      <c r="V39" t="n">
-        <v>9</v>
-      </c>
-      <c r="W39" t="n">
-        <v>12</v>
-      </c>
       <c r="X39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Y39" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z39" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>JYSK park</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Ansvej 104, Silkeborg</t>
+        </is>
+      </c>
       <c r="AC39" t="n">
         <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AF39" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AG39" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AJ39" t="n">
         <v>2.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AO39" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AP39" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AU39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -18636,95 +18644,95 @@
         <v>4</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK39" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>67</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>141</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CB39" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM39" t="n">
         <v>3</v>
       </c>
-      <c r="BL39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM39" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN39" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV39" t="n">
-        <v>69</v>
-      </c>
-      <c r="BW39" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>107</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>72</v>
-      </c>
-      <c r="BZ39" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CA39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CB39" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="CC39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM39" t="n">
-        <v>0</v>
-      </c>
       <c r="CN39" t="n">
         <v>0</v>
       </c>
@@ -18738,73 +18746,73 @@
         <v>1</v>
       </c>
       <c r="CR39" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="CS39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CV39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW39" t="n">
         <v>1</v>
       </c>
       <c r="CX39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="CY39" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="CZ39" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="DA39" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB39" t="n">
         <v>67</v>
-      </c>
-      <c r="DB39" t="n">
-        <v>50</v>
       </c>
       <c r="DC39" t="n">
         <v>84</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.27</v>
+        <v>1</v>
       </c>
       <c r="DE39" t="n">
         <v>1.18</v>
       </c>
       <c r="DF39" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DG39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ39" t="n">
+        <v>42</v>
+      </c>
+      <c r="DK39" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL39" t="n">
         <v>1.83</v>
       </c>
-      <c r="DI39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DJ39" t="n">
-        <v>59</v>
-      </c>
-      <c r="DK39" t="n">
-        <v>34</v>
-      </c>
-      <c r="DL39" t="n">
-        <v>1.86</v>
-      </c>
       <c r="DM39" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="DN39" t="n">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="DO39" t="n">
         <v>23</v>
@@ -18816,53 +18824,53 @@
         <v>1</v>
       </c>
       <c r="DR39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU39" t="b">
         <v>0</v>
       </c>
       <c r="DV39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW39" t="inlineStr">
         <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="DX39" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="DY39" t="inlineStr">
+        <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="DX39" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="DY39" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="DZ39" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
@@ -18872,44 +18880,28 @@
       </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EF39" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EG39" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EI39" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EJ39" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EK39" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EL39" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EI39" t="inlineStr"/>
+      <c r="EJ39" t="inlineStr"/>
+      <c r="EK39" t="inlineStr"/>
+      <c r="EL39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18927,170 +18919,162 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45900.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>10</v>
+      </c>
+      <c r="R40" t="n">
+        <v>5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>30</v>
+      </c>
+      <c r="V40" t="n">
         <v>9</v>
       </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" t="n">
+      <c r="W40" t="n">
+        <v>12</v>
+      </c>
+      <c r="X40" t="n">
         <v>11</v>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7</v>
-      </c>
-      <c r="S40" t="n">
-        <v>9</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>13</v>
-      </c>
-      <c r="V40" t="n">
-        <v>10</v>
-      </c>
-      <c r="W40" t="n">
-        <v>8</v>
-      </c>
-      <c r="X40" t="n">
-        <v>7</v>
-      </c>
       <c r="Y40" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="Z40" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>JYSK park</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>Ansvej 104, Silkeborg</t>
-        </is>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="AF40" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="AG40" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AJ40" t="n">
         <v>2.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AO40" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AU40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB40" t="n">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19108,19 +19092,19 @@
         <v>4</v>
       </c>
       <c r="BJ40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL40" t="n">
         <v>1</v>
       </c>
       <c r="BM40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO40" t="n">
         <v>0</v>
@@ -19132,151 +19116,151 @@
         <v>0</v>
       </c>
       <c r="BR40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS40" t="n">
         <v>1</v>
       </c>
       <c r="BT40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
+        <v>69</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>25</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>107</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CB40" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="CC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR40" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS40" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU40" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX40" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY40" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ40" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA40" t="n">
         <v>67</v>
       </c>
-      <c r="BW40" t="n">
-        <v>28</v>
-      </c>
-      <c r="BX40" t="n">
-        <v>141</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CA40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CB40" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM40" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS40" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU40" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV40" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX40" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY40" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ40" t="n">
-        <v>59</v>
-      </c>
-      <c r="DA40" t="n">
-        <v>84</v>
-      </c>
       <c r="DB40" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DC40" t="n">
         <v>84</v>
       </c>
       <c r="DD40" t="n">
-        <v>1</v>
+        <v>2.27</v>
       </c>
       <c r="DE40" t="n">
         <v>1.18</v>
       </c>
       <c r="DF40" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DG40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DH40" t="n">
-        <v>1</v>
+        <v>1.83</v>
       </c>
       <c r="DI40" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="DJ40" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="DK40" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="DL40" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DM40" t="n">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="DN40" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="DO40" t="n">
         <v>23</v>
@@ -19288,53 +19272,53 @@
         <v>1</v>
       </c>
       <c r="DR40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU40" t="b">
         <v>0</v>
       </c>
       <c r="DV40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW40" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="DX40" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
@@ -19344,28 +19328,44 @@
       </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EI40" t="inlineStr"/>
-      <c r="EJ40" t="inlineStr"/>
-      <c r="EK40" t="inlineStr"/>
-      <c r="EL40" t="inlineStr"/>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EI40" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EJ40" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EK40" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL40" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22929,7 +22929,7 @@
         <v>1</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF48" t="n">
         <v>1</v>
@@ -28401,7 +28401,7 @@
         <v>1.5</v>
       </c>
       <c r="DE60" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF60" t="n">
         <v>1.8</v>
@@ -29419,22 +29419,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63" t="n">
         <v>3</v>
@@ -29443,16 +29443,16 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -29461,120 +29461,128 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T63" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V63" t="n">
         <v>16</v>
       </c>
       <c r="W63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X63" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y63" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="Z63" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AF63" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.98</v>
+        <v>2.17</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AN63" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AO63" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AU63" t="n">
         <v>3</v>
       </c>
       <c r="AV63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX63" t="n">
         <v>0</v>
       </c>
       <c r="AY63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB63" t="n">
-        <v>2521</v>
+        <v>986</v>
       </c>
       <c r="BC63" t="n">
         <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="BE63" t="n">
         <v>0</v>
@@ -29589,178 +29597,178 @@
         <v>1</v>
       </c>
       <c r="BI63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK63" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>43</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>47</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>87</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>116</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>30</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU63" t="n">
         <v>3</v>
       </c>
-      <c r="BL63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN63" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT63" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV63" t="n">
-        <v>53</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>63</v>
-      </c>
-      <c r="BX63" t="n">
-        <v>84</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ63" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CA63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CB63" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM63" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS63" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU63" t="n">
-        <v>12</v>
-      </c>
       <c r="CV63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW63" t="n">
         <v>1</v>
       </c>
       <c r="CX63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CY63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ63" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="DA63" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="DB63" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="DC63" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="DD63" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="DF63" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG63" t="n">
         <v>1.2</v>
       </c>
       <c r="DH63" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="DI63" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ63" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="DK63" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="DL63" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="DM63" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="DN63" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="DO63" t="n">
         <v>23</v>
@@ -29784,70 +29792,86 @@
         <v>0</v>
       </c>
       <c r="DV63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW63" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="DX63" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="DY63" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="DZ63" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EA63" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EB63" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EC63" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="ED63" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EE63" t="inlineStr"/>
-      <c r="EF63" t="inlineStr"/>
-      <c r="EG63" t="inlineStr"/>
-      <c r="EH63" t="inlineStr"/>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EE63" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EF63" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EG63" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH63" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="EI63" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EJ63" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK63" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EL63" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.34</t>
         </is>
       </c>
     </row>
@@ -29867,22 +29891,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>45935.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>3</v>
@@ -29891,16 +29915,16 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -29909,128 +29933,120 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V64" t="n">
         <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="X64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y64" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Z64" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Vejle Stadion</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>Roms Hule 3, Vejle</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE64" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF64" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL64" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AM64" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AN64" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AO64" t="n">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AS64" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AU64" t="n">
         <v>3</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX64" t="n">
         <v>0</v>
       </c>
       <c r="AY64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB64" t="n">
-        <v>986</v>
+        <v>2521</v>
       </c>
       <c r="BC64" t="n">
         <v>0</v>
       </c>
       <c r="BD64" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="BE64" t="n">
         <v>0</v>
@@ -30045,37 +30061,37 @@
         <v>1</v>
       </c>
       <c r="BI64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL64" t="n">
         <v>2</v>
       </c>
       <c r="BM64" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN64" t="n">
         <v>5</v>
       </c>
-      <c r="BN64" t="n">
-        <v>6</v>
-      </c>
       <c r="BO64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP64" t="n">
         <v>0</v>
       </c>
       <c r="BQ64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT64" t="n">
         <v>2</v>
@@ -30084,25 +30100,25 @@
         <v>1</v>
       </c>
       <c r="BV64" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BW64" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="BX64" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="BY64" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="BZ64" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="CB64" t="n">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="CC64" t="n">
         <v>0</v>
@@ -30135,7 +30151,7 @@
         <v>0</v>
       </c>
       <c r="CM64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN64" t="n">
         <v>0</v>
@@ -30150,73 +30166,73 @@
         <v>1</v>
       </c>
       <c r="CR64" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CS64" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT64" t="n">
         <v>1</v>
       </c>
       <c r="CU64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="CV64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW64" t="n">
         <v>1</v>
       </c>
       <c r="CX64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CY64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CZ64" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="DA64" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="DB64" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="DC64" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="DD64" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="DE64" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="DF64" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DG64" t="n">
         <v>1.2</v>
       </c>
       <c r="DH64" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="DI64" t="n">
         <v>1.2</v>
       </c>
       <c r="DJ64" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="DK64" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="DL64" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="DM64" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="DN64" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="DO64" t="n">
         <v>23</v>
@@ -30240,86 +30256,70 @@
         <v>0</v>
       </c>
       <c r="DV64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW64" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="DX64" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="DY64" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="DZ64" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EA64" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="EB64" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EC64" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="ED64" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EE64" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="EF64" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EG64" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="EH64" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EE64" t="inlineStr"/>
+      <c r="EF64" t="inlineStr"/>
+      <c r="EG64" t="inlineStr"/>
+      <c r="EH64" t="inlineStr"/>
       <c r="EI64" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EJ64" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EK64" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EL64" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -32485,7 +32485,7 @@
         <v>1.73</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF69" t="n">
         <v>1.2</v>
@@ -38873,7 +38873,7 @@
         <v>1.73</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF83" t="n">
         <v>1.5</v>
@@ -45257,7 +45257,7 @@
         <v>1.27</v>
       </c>
       <c r="DE97" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF97" t="n">
         <v>1.43</v>
@@ -47591,7 +47591,7 @@
         <v>2.62</v>
       </c>
       <c r="DO102" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -48457,7 +48457,7 @@
         <v>0.92</v>
       </c>
       <c r="DE104" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF104" t="n">
         <v>0.88</v>
@@ -53481,7 +53481,7 @@
         <v>2.27</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF115" t="n">
         <v>2.11</v>
@@ -59079,40 +59079,40 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
         <v>46082.66666666666</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
+        <v>4</v>
+      </c>
+      <c r="K128" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" t="n">
         <v>6</v>
       </c>
-      <c r="K128" t="n">
-        <v>2</v>
-      </c>
-      <c r="L128" t="n">
-        <v>8</v>
-      </c>
       <c r="M128" t="n">
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -59121,128 +59121,128 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R128" t="n">
         <v>4</v>
       </c>
       <c r="S128" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T128" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="U128" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="V128" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W128" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="X128" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y128" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="Z128" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Energi Viborg Arena</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Stadion Allé 7, Viborg</t>
         </is>
       </c>
       <c r="AC128" t="n">
         <v>2</v>
       </c>
       <c r="AD128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="AF128" t="n">
-        <v>4.83</v>
+        <v>3.65</v>
       </c>
       <c r="AG128" t="n">
-        <v>6</v>
+        <v>2.78</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI128" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AJ128" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AK128" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL128" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="AM128" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AN128" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AO128" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.25</v>
       </c>
       <c r="AR128" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AS128" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AT128" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AU128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW128" t="n">
         <v>0</v>
       </c>
       <c r="AX128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB128" t="n">
-        <v>-1</v>
+        <v>2526</v>
       </c>
       <c r="BC128" t="n">
         <v>0</v>
       </c>
       <c r="BD128" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BE128" t="n">
         <v>0</v>
@@ -59257,19 +59257,19 @@
         <v>1</v>
       </c>
       <c r="BI128" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BJ128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BN128" t="n">
         <v>4</v>
@@ -59284,37 +59284,37 @@
         <v>2</v>
       </c>
       <c r="BR128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS128" t="n">
         <v>0</v>
       </c>
       <c r="BT128" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BU128" t="n">
         <v>1</v>
       </c>
       <c r="BV128" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="BW128" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BX128" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="BY128" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="BZ128" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="CB128" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="CC128" t="n">
         <v>0</v>
@@ -59341,13 +59341,13 @@
         <v>1</v>
       </c>
       <c r="CK128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL128" t="n">
         <v>0</v>
       </c>
       <c r="CM128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN128" t="n">
         <v>0</v>
@@ -59362,85 +59362,85 @@
         <v>1</v>
       </c>
       <c r="CR128" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="CS128" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CT128" t="n">
         <v>1</v>
       </c>
       <c r="CU128" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CV128" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="CW128" t="n">
         <v>1</v>
       </c>
       <c r="CX128" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CY128" t="n">
         <v>11</v>
       </c>
       <c r="CZ128" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="DA128" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="DB128" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="DC128" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="DD128" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="DE128" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="DF128" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="DG128" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DH128" t="n">
-        <v>2.14</v>
+        <v>1.43</v>
       </c>
       <c r="DI128" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="DJ128" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="DK128" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="DL128" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="DM128" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="DN128" t="n">
-        <v>3.56</v>
+        <v>2.64</v>
       </c>
       <c r="DO128" t="n">
         <v>23</v>
       </c>
       <c r="DP128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS128" t="b">
         <v>0</v>
@@ -59452,56 +59452,56 @@
         <v>0</v>
       </c>
       <c r="DV128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW128" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="DX128" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="DY128" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="DZ128" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="EA128" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EB128" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EC128" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="ED128" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EE128" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EF128" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EG128" t="inlineStr">
@@ -59511,19 +59511,11 @@
       </c>
       <c r="EH128" t="inlineStr">
         <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EI128" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="EJ128" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr"/>
+      <c r="EJ128" t="inlineStr"/>
       <c r="EK128" t="inlineStr"/>
       <c r="EL128" t="inlineStr"/>
     </row>
@@ -59865,7 +59857,7 @@
         <v>2</v>
       </c>
       <c r="DE129" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DF129" t="n">
         <v>2</v>
@@ -59991,37 +59983,37 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F130" s="2" t="n">
         <v>46082.66666666666</v>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I130" t="n">
         <v>3</v>
       </c>
       <c r="J130" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L130" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N130" t="n">
         <v>1</v>
@@ -60033,128 +60025,128 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S130" t="n">
+        <v>6</v>
+      </c>
+      <c r="T130" t="n">
+        <v>2</v>
+      </c>
+      <c r="U130" t="n">
+        <v>11</v>
+      </c>
+      <c r="V130" t="n">
+        <v>8</v>
+      </c>
+      <c r="W130" t="n">
+        <v>18</v>
+      </c>
+      <c r="X130" t="n">
         <v>13</v>
       </c>
-      <c r="T130" t="n">
-        <v>8</v>
-      </c>
-      <c r="U130" t="n">
-        <v>22</v>
-      </c>
-      <c r="V130" t="n">
-        <v>13</v>
-      </c>
-      <c r="W130" t="n">
-        <v>9</v>
-      </c>
-      <c r="X130" t="n">
-        <v>7</v>
-      </c>
       <c r="Y130" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Z130" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>Monjasa Park</t>
+          <t>Vejle Stadion</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>Vestre Ringvej 102, Fredericia</t>
+          <t>Roms Hule 3, Vejle</t>
         </is>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD130" t="n">
         <v>1</v>
       </c>
       <c r="AE130" t="n">
-        <v>2.37</v>
+        <v>5.6</v>
       </c>
       <c r="AF130" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG130" t="n">
-        <v>2.66</v>
+        <v>1.56</v>
       </c>
       <c r="AH130" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AI130" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AJ130" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="AK130" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AL130" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AM130" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AN130" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AO130" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="AP130" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AR130" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AS130" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="AT130" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AU130" t="n">
         <v>3</v>
       </c>
       <c r="AV130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX130" t="n">
         <v>1</v>
       </c>
       <c r="AY130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB130" t="n">
-        <v>3649</v>
+        <v>2516</v>
       </c>
       <c r="BC130" t="n">
         <v>0</v>
       </c>
       <c r="BD130" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BE130" t="n">
         <v>0</v>
@@ -60169,178 +60161,178 @@
         <v>1</v>
       </c>
       <c r="BI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM130" t="n">
         <v>4</v>
       </c>
-      <c r="BJ130" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK130" t="n">
+      <c r="BN130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU130" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV130" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW130" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX130" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY130" t="n">
         <v>5</v>
-      </c>
-      <c r="BL130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM130" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN130" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP130" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS130" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU130" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV130" t="n">
-        <v>51</v>
-      </c>
-      <c r="BW130" t="n">
-        <v>61</v>
-      </c>
-      <c r="BX130" t="n">
-        <v>87</v>
-      </c>
-      <c r="BY130" t="n">
-        <v>93</v>
-      </c>
-      <c r="BZ130" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CA130" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CB130" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="CC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI130" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ130" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM130" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN130" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO130" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP130" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ130" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR130" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS130" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT130" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU130" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV130" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW130" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX130" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY130" t="n">
-        <v>11</v>
       </c>
       <c r="CZ130" t="n">
         <v>65</v>
       </c>
       <c r="DA130" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="DB130" t="n">
         <v>50</v>
       </c>
       <c r="DC130" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="DD130" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DE130" t="n">
-        <v>0.73</v>
+        <v>2.17</v>
       </c>
       <c r="DF130" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="DG130" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="DH130" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DI130" t="n">
-        <v>0.9</v>
+        <v>2.24</v>
       </c>
       <c r="DJ130" t="n">
         <v>35</v>
       </c>
       <c r="DK130" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="DL130" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="DM130" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="DN130" t="n">
-        <v>2.47</v>
+        <v>3.14</v>
       </c>
       <c r="DO130" t="n">
         <v>23</v>
@@ -60368,68 +60360,68 @@
       </c>
       <c r="DW130" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="DX130" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DY130" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="DZ130" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EA130" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EB130" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="EC130" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="ED130" t="inlineStr">
         <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EE130" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="EE130" t="inlineStr"/>
       <c r="EF130" t="inlineStr"/>
       <c r="EG130" t="inlineStr"/>
-      <c r="EH130" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
+      <c r="EH130" t="inlineStr"/>
       <c r="EI130" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EJ130" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EK130" t="inlineStr"/>
-      <c r="EL130" t="inlineStr"/>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EK130" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL130" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -60447,140 +60439,140 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>København</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F131" s="2" t="n">
         <v>46082.66666666666</v>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I131" t="n">
         <v>3</v>
       </c>
       <c r="J131" t="n">
+        <v>6</v>
+      </c>
+      <c r="K131" t="n">
+        <v>6</v>
+      </c>
+      <c r="L131" t="n">
+        <v>12</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
         <v>4</v>
       </c>
-      <c r="K131" t="n">
-        <v>2</v>
-      </c>
-      <c r="L131" t="n">
-        <v>6</v>
-      </c>
-      <c r="M131" t="n">
-        <v>2</v>
-      </c>
-      <c r="N131" t="n">
-        <v>1</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>6</v>
-      </c>
       <c r="R131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S131" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T131" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U131" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="V131" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W131" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="X131" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Y131" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="Z131" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>Energi Viborg Arena</t>
+          <t>Parken</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>Stadion Allé 7, Viborg</t>
+          <t>Øster Allé 50, København</t>
         </is>
       </c>
       <c r="AC131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE131" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AF131" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AG131" t="n">
-        <v>2.78</v>
+        <v>4.6</v>
       </c>
       <c r="AH131" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI131" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AJ131" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="AK131" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL131" t="n">
-        <v>2.53</v>
+        <v>2.01</v>
       </c>
       <c r="AM131" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN131" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AO131" t="n">
         <v>2.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AR131" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="AS131" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="AT131" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AU131" t="n">
         <v>3</v>
@@ -60589,28 +60581,28 @@
         <v>1</v>
       </c>
       <c r="AW131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY131" t="n">
         <v>1</v>
       </c>
       <c r="AZ131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB131" t="n">
-        <v>2526</v>
+        <v>2521</v>
       </c>
       <c r="BC131" t="n">
         <v>0</v>
       </c>
       <c r="BD131" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BE131" t="n">
         <v>0</v>
@@ -60625,22 +60617,22 @@
         <v>1</v>
       </c>
       <c r="BI131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK131" t="n">
         <v>3</v>
       </c>
       <c r="BL131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM131" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BN131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO131" t="n">
         <v>0</v>
@@ -60649,10 +60641,10 @@
         <v>0</v>
       </c>
       <c r="BQ131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS131" t="n">
         <v>0</v>
@@ -60664,37 +60656,37 @@
         <v>1</v>
       </c>
       <c r="BV131" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="BW131" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BX131" t="n">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="BY131" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="BZ131" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="CA131" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="CB131" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="CC131" t="n">
         <v>0</v>
       </c>
       <c r="CD131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE131" t="n">
         <v>0</v>
       </c>
       <c r="CF131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG131" t="n">
         <v>0</v>
@@ -60709,16 +60701,16 @@
         <v>1</v>
       </c>
       <c r="CK131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL131" t="n">
         <v>0</v>
       </c>
       <c r="CM131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO131" t="n">
         <v>0</v>
@@ -60730,73 +60722,73 @@
         <v>1</v>
       </c>
       <c r="CR131" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="CS131" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="CT131" t="n">
         <v>1</v>
       </c>
       <c r="CU131" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="CV131" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="CW131" t="n">
         <v>1</v>
       </c>
       <c r="CX131" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY131" t="n">
         <v>11</v>
       </c>
       <c r="CZ131" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="DA131" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="DB131" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC131" t="n">
         <v>65</v>
       </c>
-      <c r="DC131" t="n">
-        <v>90</v>
-      </c>
       <c r="DD131" t="n">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="DE131" t="n">
         <v>1.25</v>
       </c>
       <c r="DF131" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="DG131" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="DH131" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DI131" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="DJ131" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="DK131" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="DL131" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="DM131" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DN131" t="n">
-        <v>2.64</v>
+        <v>3.28</v>
       </c>
       <c r="DO131" t="n">
         <v>23</v>
@@ -60824,42 +60816,42 @@
       </c>
       <c r="DW131" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="DX131" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="DY131" t="inlineStr">
+        <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="DY131" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
       <c r="DZ131" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EA131" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="EB131" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EC131" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="ED131" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EE131" t="inlineStr">
@@ -60869,12 +60861,12 @@
       </c>
       <c r="EF131" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EG131" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EH131" t="inlineStr">
@@ -60882,10 +60874,26 @@
           <t>1.99</t>
         </is>
       </c>
-      <c r="EI131" t="inlineStr"/>
-      <c r="EJ131" t="inlineStr"/>
-      <c r="EK131" t="inlineStr"/>
-      <c r="EL131" t="inlineStr"/>
+      <c r="EI131" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="EJ131" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EK131" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EL131" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -60903,40 +60911,40 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F132" s="2" t="n">
         <v>46082.66666666666</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>6</v>
       </c>
       <c r="K132" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L132" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -60948,125 +60956,125 @@
         <v>4</v>
       </c>
       <c r="R132" t="n">
+        <v>4</v>
+      </c>
+      <c r="S132" t="n">
+        <v>9</v>
+      </c>
+      <c r="T132" t="n">
         <v>5</v>
       </c>
-      <c r="S132" t="n">
-        <v>14</v>
-      </c>
-      <c r="T132" t="n">
-        <v>8</v>
-      </c>
       <c r="U132" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="V132" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W132" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X132" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="Y132" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Z132" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>Parken</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>Øster Allé 50, København</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AF132" t="n">
-        <v>3.9</v>
+        <v>4.83</v>
       </c>
       <c r="AG132" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AH132" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AI132" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AJ132" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="AK132" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL132" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AM132" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AN132" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO132" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AP132" t="n">
         <v>1.99</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AR132" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AS132" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AT132" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AU132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX132" t="n">
         <v>0</v>
       </c>
       <c r="AY132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB132" t="n">
-        <v>2521</v>
+        <v>-1</v>
       </c>
       <c r="BC132" t="n">
         <v>0</v>
       </c>
       <c r="BD132" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE132" t="n">
         <v>0</v>
@@ -61081,76 +61089,76 @@
         <v>1</v>
       </c>
       <c r="BI132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM132" t="n">
         <v>4</v>
       </c>
-      <c r="BK132" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL132" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM132" t="n">
+      <c r="BN132" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT132" t="n">
         <v>7</v>
       </c>
-      <c r="BN132" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ132" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR132" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT132" t="n">
-        <v>3</v>
-      </c>
       <c r="BU132" t="n">
         <v>1</v>
       </c>
       <c r="BV132" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="BW132" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BX132" t="n">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="BY132" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="BZ132" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="CA132" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="CB132" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="CC132" t="n">
         <v>0</v>
       </c>
       <c r="CD132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE132" t="n">
         <v>0</v>
       </c>
       <c r="CF132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG132" t="n">
         <v>0</v>
@@ -61171,10 +61179,10 @@
         <v>0</v>
       </c>
       <c r="CM132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO132" t="n">
         <v>0</v>
@@ -61186,85 +61194,85 @@
         <v>1</v>
       </c>
       <c r="CR132" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="CS132" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CT132" t="n">
         <v>1</v>
       </c>
       <c r="CU132" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="CV132" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="CW132" t="n">
         <v>1</v>
       </c>
       <c r="CX132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY132" t="n">
         <v>11</v>
       </c>
       <c r="CZ132" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA132" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="DB132" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="DC132" t="n">
         <v>65</v>
       </c>
       <c r="DD132" t="n">
-        <v>1.18</v>
+        <v>2.08</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="DF132" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="DG132" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="DH132" t="n">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="DI132" t="n">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="DJ132" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="DK132" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="DL132" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DM132" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="DN132" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="DO132" t="n">
         <v>23</v>
       </c>
       <c r="DP132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS132" t="b">
         <v>0</v>
@@ -61276,88 +61284,80 @@
         <v>0</v>
       </c>
       <c r="DV132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW132" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="DX132" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="DY132" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="DZ132" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="EA132" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="EB132" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EC132" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="ED132" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="EE132" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF132" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EG132" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EH132" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EI132" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="EJ132" t="inlineStr">
         <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EK132" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EL132" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EK132" t="inlineStr"/>
+      <c r="EL132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -61375,37 +61375,37 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F133" s="2" t="n">
         <v>46082.66666666666</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I133" t="n">
         <v>3</v>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K133" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L133" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
         <v>1</v>
@@ -61417,128 +61417,128 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
+        <v>9</v>
+      </c>
+      <c r="R133" t="n">
         <v>5</v>
       </c>
-      <c r="R133" t="n">
-        <v>6</v>
-      </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T133" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U133" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="V133" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W133" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="X133" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y133" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Z133" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Vejle Stadion</t>
+          <t>Monjasa Park</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>Roms Hule 3, Vejle</t>
+          <t>Vestre Ringvej 102, Fredericia</t>
         </is>
       </c>
       <c r="AC133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
         <v>1</v>
       </c>
       <c r="AE133" t="n">
-        <v>5.6</v>
+        <v>2.37</v>
       </c>
       <c r="AF133" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AG133" t="n">
-        <v>1.56</v>
+        <v>2.66</v>
       </c>
       <c r="AH133" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AI133" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AJ133" t="n">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="AK133" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AL133" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AM133" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AN133" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AO133" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AR133" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AS133" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AT133" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AU133" t="n">
         <v>3</v>
       </c>
       <c r="AV133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX133" t="n">
         <v>1</v>
       </c>
       <c r="AY133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB133" t="n">
-        <v>2516</v>
+        <v>3649</v>
       </c>
       <c r="BC133" t="n">
         <v>0</v>
       </c>
       <c r="BD133" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BE133" t="n">
         <v>0</v>
@@ -61553,25 +61553,25 @@
         <v>1</v>
       </c>
       <c r="BI133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK133" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BL133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP133" t="n">
         <v>1</v>
@@ -61583,7 +61583,7 @@
         <v>0</v>
       </c>
       <c r="BS133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT133" t="n">
         <v>0</v>
@@ -61592,25 +61592,25 @@
         <v>1</v>
       </c>
       <c r="BV133" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="BW133" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="BX133" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="BY133" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="BZ133" t="n">
-        <v>1.37</v>
+        <v>2.38</v>
       </c>
       <c r="CA133" t="n">
-        <v>1.14</v>
+        <v>1.61</v>
       </c>
       <c r="CB133" t="n">
-        <v>2.51</v>
+        <v>3.99</v>
       </c>
       <c r="CC133" t="n">
         <v>0</v>
@@ -61643,7 +61643,7 @@
         <v>0</v>
       </c>
       <c r="CM133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN133" t="n">
         <v>1</v>
@@ -61652,79 +61652,79 @@
         <v>0</v>
       </c>
       <c r="CP133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ133" t="n">
         <v>1</v>
       </c>
       <c r="CR133" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="CS133" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="CT133" t="n">
         <v>1</v>
       </c>
       <c r="CU133" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CV133" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="CW133" t="n">
         <v>1</v>
       </c>
       <c r="CX133" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CY133" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CZ133" t="n">
         <v>65</v>
       </c>
       <c r="DA133" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="DB133" t="n">
         <v>50</v>
       </c>
       <c r="DC133" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="DD133" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DE133" t="n">
-        <v>2.17</v>
+        <v>0.73</v>
       </c>
       <c r="DF133" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="DG133" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="DH133" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DI133" t="n">
-        <v>2.24</v>
+        <v>0.9</v>
       </c>
       <c r="DJ133" t="n">
         <v>35</v>
       </c>
       <c r="DK133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="DL133" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="DM133" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="DN133" t="n">
-        <v>3.14</v>
+        <v>2.47</v>
       </c>
       <c r="DO133" t="n">
         <v>23</v>
@@ -61752,68 +61752,68 @@
       </c>
       <c r="DW133" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="DX133" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="DY133" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="DZ133" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="EA133" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EB133" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC133" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED133" t="inlineStr">
         <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="EE133" t="inlineStr"/>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EE133" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
       <c r="EF133" t="inlineStr"/>
       <c r="EG133" t="inlineStr"/>
-      <c r="EH133" t="inlineStr"/>
+      <c r="EH133" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
       <c r="EI133" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EJ133" t="inlineStr">
         <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="EK133" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EL133" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EK133" t="inlineStr"/>
+      <c r="EL133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -62287,70 +62287,70 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
         <v>46096.54166666666</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>1</v>
       </c>
       <c r="I135" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" t="n">
+        <v>2</v>
+      </c>
+      <c r="L135" t="n">
+        <v>7</v>
+      </c>
+      <c r="M135" t="n">
+        <v>4</v>
+      </c>
+      <c r="N135" t="n">
         <v>3</v>
       </c>
-      <c r="J135" t="n">
-        <v>9</v>
-      </c>
-      <c r="K135" t="n">
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
         <v>4</v>
-      </c>
-      <c r="L135" t="n">
-        <v>13</v>
-      </c>
-      <c r="M135" t="n">
-        <v>1</v>
-      </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>6</v>
       </c>
       <c r="R135" t="n">
         <v>3</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U135" t="n">
         <v>9</v>
       </c>
       <c r="V135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W135" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="X135" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y135" t="n">
         <v>60</v>
@@ -62360,97 +62360,97 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Nature Energy Park</t>
+          <t>MCH Arena</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>Højstrupvej 7B, Odense</t>
+          <t>Kaj Zartows Vej 5, Herning</t>
         </is>
       </c>
       <c r="AC135" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE135" t="n">
-        <v>3.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF135" t="n">
-        <v>3.66</v>
+        <v>5</v>
       </c>
       <c r="AG135" t="n">
-        <v>2.1</v>
+        <v>6.23</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AI135" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AJ135" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="AK135" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL135" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AM135" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AO135" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="AP135" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AR135" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AS135" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AT135" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AU135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV135" t="n">
         <v>0</v>
       </c>
       <c r="AW135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB135" t="n">
-        <v>2523</v>
+        <v>986</v>
       </c>
       <c r="BC135" t="n">
         <v>1</v>
       </c>
       <c r="BD135" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BE135" t="n">
         <v>0</v>
@@ -62465,64 +62465,64 @@
         <v>1</v>
       </c>
       <c r="BI135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ135" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK135" t="n">
         <v>3</v>
       </c>
-      <c r="BK135" t="n">
-        <v>8</v>
-      </c>
       <c r="BL135" t="n">
         <v>1</v>
       </c>
       <c r="BM135" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN135" t="n">
         <v>4</v>
       </c>
-      <c r="BN135" t="n">
-        <v>9</v>
-      </c>
       <c r="BO135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP135" t="n">
         <v>0</v>
       </c>
       <c r="BQ135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT135" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BU135" t="n">
         <v>1</v>
       </c>
       <c r="BV135" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="BW135" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="BX135" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="BY135" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="CB135" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="CC135" t="n">
         <v>0</v>
@@ -62555,10 +62555,10 @@
         <v>0</v>
       </c>
       <c r="CM135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO135" t="n">
         <v>0</v>
@@ -62570,73 +62570,73 @@
         <v>1</v>
       </c>
       <c r="CR135" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="CS135" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="CT135" t="n">
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CV135" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CW135" t="n">
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="CY135" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CZ135" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="DA135" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="DB135" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="DC135" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="DE135" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="DF135" t="n">
-        <v>1.23</v>
+        <v>2.09</v>
       </c>
       <c r="DG135" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="DH135" t="n">
-        <v>1.23</v>
+        <v>2.09</v>
       </c>
       <c r="DI135" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="DJ135" t="n">
         <v>32</v>
       </c>
       <c r="DK135" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="DL135" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="DN135" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="DO135" t="n">
         <v>23</v>
@@ -62645,10 +62645,10 @@
         <v>1</v>
       </c>
       <c r="DQ135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS135" t="b">
         <v>0</v>
@@ -62660,60 +62660,76 @@
         <v>0</v>
       </c>
       <c r="DV135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW135" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="DX135" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="DY135" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DZ135" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="EA135" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="EB135" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC135" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="ED135" t="inlineStr">
         <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EE135" t="inlineStr"/>
-      <c r="EF135" t="inlineStr"/>
-      <c r="EG135" t="inlineStr"/>
-      <c r="EH135" t="inlineStr"/>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="EE135" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF135" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EG135" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="EH135" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
       <c r="EI135" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EJ135" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EK135" t="inlineStr"/>
@@ -62735,40 +62751,40 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F136" s="2" t="n">
         <v>46096.54166666666</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L136" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N136" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -62777,28 +62793,28 @@
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R136" t="n">
         <v>3</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U136" t="n">
         <v>9</v>
       </c>
       <c r="V136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W136" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X136" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y136" t="n">
         <v>60</v>
@@ -62808,97 +62824,97 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>MCH Arena</t>
+          <t>Nature Energy Park</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>Kaj Zartows Vej 5, Herning</t>
+          <t>Højstrupvej 7B, Odense</t>
         </is>
       </c>
       <c r="AC136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU136" t="n">
         <v>3</v>
       </c>
-      <c r="AE136" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF136" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG136" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI136" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AJ136" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AK136" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL136" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM136" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN136" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO136" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AP136" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ136" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR136" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS136" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AT136" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AU136" t="n">
-        <v>1</v>
-      </c>
       <c r="AV136" t="n">
         <v>0</v>
       </c>
       <c r="AW136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB136" t="n">
-        <v>986</v>
+        <v>2523</v>
       </c>
       <c r="BC136" t="n">
         <v>1</v>
       </c>
       <c r="BD136" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BE136" t="n">
         <v>0</v>
@@ -62913,178 +62929,178 @@
         <v>1</v>
       </c>
       <c r="BI136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BK136" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BL136" t="n">
         <v>1</v>
       </c>
       <c r="BM136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN136" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>115</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU136" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV136" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW136" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX136" t="n">
         <v>4</v>
       </c>
-      <c r="BO136" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ136" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR136" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS136" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT136" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU136" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV136" t="n">
-        <v>47</v>
-      </c>
-      <c r="BW136" t="n">
-        <v>47</v>
-      </c>
-      <c r="BX136" t="n">
-        <v>95</v>
-      </c>
-      <c r="BY136" t="n">
-        <v>88</v>
-      </c>
-      <c r="BZ136" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CA136" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="CB136" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="CC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI136" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ136" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN136" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP136" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ136" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR136" t="n">
-        <v>30</v>
-      </c>
-      <c r="CS136" t="n">
-        <v>12</v>
-      </c>
-      <c r="CT136" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU136" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV136" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW136" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX136" t="n">
+      <c r="CY136" t="n">
         <v>11</v>
       </c>
-      <c r="CY136" t="n">
-        <v>7</v>
-      </c>
       <c r="CZ136" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="DA136" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="DB136" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="DC136" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="DD136" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="DE136" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="DF136" t="n">
-        <v>2.09</v>
+        <v>1.23</v>
       </c>
       <c r="DG136" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="DH136" t="n">
-        <v>2.09</v>
+        <v>1.23</v>
       </c>
       <c r="DI136" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="DJ136" t="n">
         <v>32</v>
       </c>
       <c r="DK136" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="DL136" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="DM136" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="DN136" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="DO136" t="n">
         <v>23</v>
@@ -63093,10 +63109,10 @@
         <v>1</v>
       </c>
       <c r="DQ136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS136" t="b">
         <v>0</v>
@@ -63108,76 +63124,60 @@
         <v>0</v>
       </c>
       <c r="DV136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW136" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="DX136" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="DY136" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="DZ136" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="EA136" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EB136" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EC136" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="ED136" t="inlineStr">
         <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="EE136" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EF136" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EG136" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EH136" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="EE136" t="inlineStr"/>
+      <c r="EF136" t="inlineStr"/>
+      <c r="EG136" t="inlineStr"/>
+      <c r="EH136" t="inlineStr"/>
       <c r="EI136" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EJ136" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK136" t="inlineStr"/>
@@ -64449,7 +64449,7 @@
         <v>0.87</v>
       </c>
       <c r="DE139" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DF139" t="n">
         <v>0.86</v>
@@ -64558,6 +64558,470 @@
       </c>
       <c r="EK139" t="inlineStr"/>
       <c r="EL139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Denmark_Superliga_2025-2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Vejle</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>46101.75</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>2</v>
+      </c>
+      <c r="J140" t="n">
+        <v>2</v>
+      </c>
+      <c r="K140" t="n">
+        <v>7</v>
+      </c>
+      <c r="L140" t="n">
+        <v>9</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>1</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>3</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="n">
+        <v>8</v>
+      </c>
+      <c r="U140" t="n">
+        <v>6</v>
+      </c>
+      <c r="V140" t="n">
+        <v>11</v>
+      </c>
+      <c r="W140" t="n">
+        <v>14</v>
+      </c>
+      <c r="X140" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Vejle Stadion</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Roms Hule 3, Vejle</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>74</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>68</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>130</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU140" t="n">
+        <v>7</v>
+      </c>
+      <c r="CV140" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW140" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX140" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY140" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ140" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA140" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB140" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC140" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD140" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE140" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF140" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DG140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DH140" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="DI140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DJ140" t="n">
+        <v>31</v>
+      </c>
+      <c r="DK140" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL140" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DM140" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DN140" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO140" t="n">
+        <v>24</v>
+      </c>
+      <c r="DP140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU140" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV140" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW140" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="DX140" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DY140" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="DZ140" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EA140" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EB140" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EC140" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="ED140" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="EE140" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EF140" t="inlineStr"/>
+      <c r="EG140" t="inlineStr"/>
+      <c r="EH140" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EI140" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EJ140" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EK140" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EL140" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1</v>
+        <v>6696</v>
       </c>
       <c r="BG2" t="n">
         <v>2</v>
@@ -1944,7 +1944,7 @@
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1996,7 +1996,7 @@
         <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>4.65</v>
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-1</v>
+        <v>6288</v>
       </c>
       <c r="BG3" t="n">
         <v>2</v>
@@ -2116,13 +2116,13 @@
         <v>3</v>
       </c>
       <c r="BR3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU3" t="n">
         <v>1</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1</v>
+        <v>10187</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
@@ -3000,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-1</v>
+        <v>4011</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-1</v>
+        <v>8861</v>
       </c>
       <c r="BG6" t="n">
         <v>2</v>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>1.67</v>
@@ -3904,13 +3904,13 @@
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-1</v>
+        <v>19863</v>
       </c>
       <c r="BG7" t="n">
         <v>2</v>
       </c>
       <c r="BH7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI7" t="n">
         <v>2</v>
@@ -3940,13 +3940,13 @@
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS7" t="n">
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU7" t="n">
         <v>1</v>
@@ -4009,10 +4009,10 @@
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
         <v>1</v>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-1</v>
+        <v>8215</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
@@ -4824,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-1</v>
+        <v>22403</v>
       </c>
       <c r="BG9" t="n">
         <v>2</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-1</v>
+        <v>12394</v>
       </c>
       <c r="BG10" t="n">
         <v>2</v>
@@ -5736,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-1</v>
+        <v>3554</v>
       </c>
       <c r="BG11" t="n">
         <v>2</v>
@@ -6192,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-1</v>
+        <v>6711</v>
       </c>
       <c r="BG12" t="n">
         <v>2</v>
@@ -6648,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-1</v>
+        <v>8861</v>
       </c>
       <c r="BG13" t="n">
         <v>2</v>
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-1</v>
+        <v>6288</v>
       </c>
       <c r="BG14" t="n">
         <v>2</v>
@@ -7568,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-1</v>
+        <v>10187</v>
       </c>
       <c r="BG15" t="n">
         <v>2</v>
@@ -8016,7 +8016,7 @@
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-1</v>
+        <v>5751</v>
       </c>
       <c r="BG16" t="n">
         <v>2</v>
@@ -8480,7 +8480,7 @@
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-1</v>
+        <v>4011</v>
       </c>
       <c r="BG17" t="n">
         <v>2</v>
@@ -8936,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-1</v>
+        <v>8432</v>
       </c>
       <c r="BG18" t="n">
         <v>2</v>
@@ -9400,7 +9400,7 @@
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-1</v>
+        <v>21909</v>
       </c>
       <c r="BG19" t="n">
         <v>2</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>-1</v>
+        <v>28812</v>
       </c>
       <c r="BG20" t="n">
         <v>2</v>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>-1</v>
+        <v>5622</v>
       </c>
       <c r="BG21" t="n">
         <v>2</v>
@@ -10768,7 +10768,7 @@
         <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>-1</v>
+        <v>9307</v>
       </c>
       <c r="BG22" t="n">
         <v>2</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>-1</v>
+        <v>3516</v>
       </c>
       <c r="BG23" t="n">
         <v>2</v>
@@ -11672,7 +11672,7 @@
         <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>-1</v>
+        <v>19863</v>
       </c>
       <c r="BG24" t="n">
         <v>2</v>
@@ -12128,7 +12128,7 @@
         <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>-1</v>
+        <v>9270</v>
       </c>
       <c r="BG25" t="n">
         <v>2</v>
@@ -12592,7 +12592,7 @@
         <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>-1</v>
+        <v>6687</v>
       </c>
       <c r="BG26" t="n">
         <v>2</v>
@@ -13056,7 +13056,7 @@
         <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>-1</v>
+        <v>3984</v>
       </c>
       <c r="BG27" t="n">
         <v>2</v>
@@ -13528,7 +13528,7 @@
         <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>-1</v>
+        <v>9779</v>
       </c>
       <c r="BG28" t="n">
         <v>2</v>
@@ -13984,7 +13984,7 @@
         <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>-1</v>
+        <v>6387</v>
       </c>
       <c r="BG29" t="n">
         <v>2</v>
@@ -14448,7 +14448,7 @@
         <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>-1</v>
+        <v>8057</v>
       </c>
       <c r="BG30" t="n">
         <v>2</v>
@@ -14920,7 +14920,7 @@
         <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>-1</v>
+        <v>13073</v>
       </c>
       <c r="BG31" t="n">
         <v>2</v>
@@ -15384,7 +15384,7 @@
         <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>-1</v>
+        <v>27397</v>
       </c>
       <c r="BG32" t="n">
         <v>2</v>
@@ -15848,7 +15848,7 @@
         <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>-1</v>
+        <v>3572</v>
       </c>
       <c r="BG33" t="n">
         <v>2</v>
@@ -16312,7 +16312,7 @@
         <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>-1</v>
+        <v>9379</v>
       </c>
       <c r="BG34" t="n">
         <v>2</v>
@@ -16776,7 +16776,7 @@
         <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>-1</v>
+        <v>8735</v>
       </c>
       <c r="BG35" t="n">
         <v>2</v>
@@ -17240,7 +17240,7 @@
         <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>-1</v>
+        <v>9333</v>
       </c>
       <c r="BG36" t="n">
         <v>2</v>
@@ -17704,7 +17704,7 @@
         <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>-1</v>
+        <v>3175</v>
       </c>
       <c r="BG37" t="n">
         <v>2</v>
@@ -18160,7 +18160,7 @@
         <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>-1</v>
+        <v>7894</v>
       </c>
       <c r="BG38" t="n">
         <v>2</v>
@@ -18624,7 +18624,7 @@
         <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>-1</v>
+        <v>9649</v>
       </c>
       <c r="BG39" t="n">
         <v>2</v>
@@ -19096,7 +19096,7 @@
         <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>-1</v>
+        <v>4513</v>
       </c>
       <c r="BG40" t="n">
         <v>2</v>
@@ -19552,7 +19552,7 @@
         <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>-1</v>
+        <v>10915</v>
       </c>
       <c r="BG41" t="n">
         <v>2</v>
@@ -20000,7 +20000,7 @@
         <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>-1</v>
+        <v>5857</v>
       </c>
       <c r="BG42" t="n">
         <v>2</v>
@@ -20472,7 +20472,7 @@
         <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>-1</v>
+        <v>18552</v>
       </c>
       <c r="BG43" t="n">
         <v>2</v>
@@ -20928,7 +20928,7 @@
         <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>-1</v>
+        <v>4789</v>
       </c>
       <c r="BG44" t="n">
         <v>2</v>
@@ -21384,7 +21384,7 @@
         <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>-1</v>
+        <v>25493</v>
       </c>
       <c r="BG45" t="n">
         <v>2</v>
@@ -21856,7 +21856,7 @@
         <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>-1</v>
+        <v>7655</v>
       </c>
       <c r="BG46" t="n">
         <v>2</v>
@@ -22312,7 +22312,7 @@
         <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>-1</v>
+        <v>4613</v>
       </c>
       <c r="BG47" t="n">
         <v>2</v>
@@ -22776,7 +22776,7 @@
         <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>-1</v>
+        <v>4024</v>
       </c>
       <c r="BG48" t="n">
         <v>2</v>
@@ -23212,7 +23212,7 @@
         <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>-1</v>
+        <v>4749</v>
       </c>
       <c r="BG49" t="n">
         <v>2</v>
@@ -23676,7 +23676,7 @@
         <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>-1</v>
+        <v>9119</v>
       </c>
       <c r="BG50" t="n">
         <v>2</v>
@@ -24132,7 +24132,7 @@
         <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>-1</v>
+        <v>11440</v>
       </c>
       <c r="BG51" t="n">
         <v>2</v>
@@ -24580,7 +24580,7 @@
         <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>-1</v>
+        <v>7477</v>
       </c>
       <c r="BG52" t="n">
         <v>2</v>
@@ -25044,7 +25044,7 @@
         <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>-1</v>
+        <v>28928</v>
       </c>
       <c r="BG53" t="n">
         <v>2</v>
@@ -25500,7 +25500,7 @@
         <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>-1</v>
+        <v>10818</v>
       </c>
       <c r="BG54" t="n">
         <v>2</v>
@@ -25964,7 +25964,7 @@
         <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>-1</v>
+        <v>4508</v>
       </c>
       <c r="BG55" t="n">
         <v>2</v>
@@ -26420,7 +26420,7 @@
         <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>-1</v>
+        <v>8202</v>
       </c>
       <c r="BG56" t="n">
         <v>2</v>
@@ -26864,7 +26864,7 @@
         <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>-1</v>
+        <v>5330</v>
       </c>
       <c r="BG57" t="n">
         <v>-1</v>
@@ -27320,7 +27320,7 @@
         <v>0</v>
       </c>
       <c r="BF58" t="n">
-        <v>-1</v>
+        <v>4690</v>
       </c>
       <c r="BG58" t="n">
         <v>2</v>
@@ -27784,7 +27784,7 @@
         <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>-1</v>
+        <v>4449</v>
       </c>
       <c r="BG59" t="n">
         <v>2</v>
@@ -28248,7 +28248,7 @@
         <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>-1</v>
+        <v>18554</v>
       </c>
       <c r="BG60" t="n">
         <v>2</v>
@@ -28688,7 +28688,7 @@
         <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>-1</v>
+        <v>7964</v>
       </c>
       <c r="BG61" t="n">
         <v>2</v>
@@ -29132,7 +29132,7 @@
         <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>-1</v>
+        <v>9159</v>
       </c>
       <c r="BG62" t="n">
         <v>2</v>
@@ -29580,7 +29580,7 @@
         <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>-1</v>
+        <v>5888</v>
       </c>
       <c r="BG63" t="n">
         <v>2</v>
@@ -30036,7 +30036,7 @@
         <v>0</v>
       </c>
       <c r="BF64" t="n">
-        <v>-1</v>
+        <v>6046</v>
       </c>
       <c r="BG64" t="n">
         <v>2</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="BF65" t="n">
-        <v>-1</v>
+        <v>8849</v>
       </c>
       <c r="BG65" t="n">
         <v>2</v>
@@ -30956,7 +30956,7 @@
         <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>-1</v>
+        <v>30661</v>
       </c>
       <c r="BG66" t="n">
         <v>2</v>
@@ -31428,7 +31428,7 @@
         <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>-1</v>
+        <v>5589</v>
       </c>
       <c r="BG67" t="n">
         <v>2</v>
@@ -31876,7 +31876,7 @@
         <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>-1</v>
+        <v>6429</v>
       </c>
       <c r="BG68" t="n">
         <v>2</v>
@@ -32332,7 +32332,7 @@
         <v>0</v>
       </c>
       <c r="BF69" t="n">
-        <v>-1</v>
+        <v>3712</v>
       </c>
       <c r="BG69" t="n">
         <v>2</v>
@@ -32780,7 +32780,7 @@
         <v>0</v>
       </c>
       <c r="BF70" t="n">
-        <v>-1</v>
+        <v>5560</v>
       </c>
       <c r="BG70" t="n">
         <v>-1</v>
@@ -33228,7 +33228,7 @@
         <v>0</v>
       </c>
       <c r="BF71" t="n">
-        <v>-1</v>
+        <v>25641</v>
       </c>
       <c r="BG71" t="n">
         <v>2</v>
@@ -33700,7 +33700,7 @@
         <v>0</v>
       </c>
       <c r="BF72" t="n">
-        <v>-1</v>
+        <v>9948</v>
       </c>
       <c r="BG72" t="n">
         <v>2</v>
@@ -34148,7 +34148,7 @@
         <v>0</v>
       </c>
       <c r="BF73" t="n">
-        <v>-1</v>
+        <v>4777</v>
       </c>
       <c r="BG73" t="n">
         <v>2</v>
@@ -34580,7 +34580,7 @@
         <v>0</v>
       </c>
       <c r="BF74" t="n">
-        <v>-1</v>
+        <v>8593</v>
       </c>
       <c r="BG74" t="n">
         <v>2</v>
@@ -35044,7 +35044,7 @@
         <v>0</v>
       </c>
       <c r="BF75" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BG75" t="n">
         <v>2</v>
@@ -35500,7 +35500,7 @@
         <v>0</v>
       </c>
       <c r="BF76" t="n">
-        <v>-1</v>
+        <v>3323</v>
       </c>
       <c r="BG76" t="n">
         <v>2</v>
@@ -35948,7 +35948,7 @@
         <v>0</v>
       </c>
       <c r="BF77" t="n">
-        <v>-1</v>
+        <v>3718</v>
       </c>
       <c r="BG77" t="n">
         <v>2</v>
@@ -36404,7 +36404,7 @@
         <v>0</v>
       </c>
       <c r="BF78" t="n">
-        <v>-1</v>
+        <v>20485</v>
       </c>
       <c r="BG78" t="n">
         <v>2</v>
@@ -36876,7 +36876,7 @@
         <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>-1</v>
+        <v>14275</v>
       </c>
       <c r="BG79" t="n">
         <v>2</v>
@@ -37348,7 +37348,7 @@
         <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>-1</v>
+        <v>20760</v>
       </c>
       <c r="BG80" t="n">
         <v>2</v>
@@ -37812,7 +37812,7 @@
         <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>-1</v>
+        <v>5028</v>
       </c>
       <c r="BG81" t="n">
         <v>2</v>
@@ -38276,7 +38276,7 @@
         <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>-1</v>
+        <v>5877</v>
       </c>
       <c r="BG82" t="n">
         <v>2</v>
@@ -38720,7 +38720,7 @@
         <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>-1</v>
+        <v>3117</v>
       </c>
       <c r="BG83" t="n">
         <v>2</v>
@@ -39184,7 +39184,7 @@
         <v>0</v>
       </c>
       <c r="BF84" t="n">
-        <v>-1</v>
+        <v>5146</v>
       </c>
       <c r="BG84" t="n">
         <v>2</v>
@@ -39648,7 +39648,7 @@
         <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>-1</v>
+        <v>11619</v>
       </c>
       <c r="BG85" t="n">
         <v>2</v>
@@ -40104,7 +40104,7 @@
         <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>-1</v>
+        <v>7207</v>
       </c>
       <c r="BG86" t="n">
         <v>2</v>
@@ -40568,7 +40568,7 @@
         <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>-1</v>
+        <v>2057</v>
       </c>
       <c r="BG87" t="n">
         <v>2</v>
@@ -41024,7 +41024,7 @@
         <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>-1</v>
+        <v>7541</v>
       </c>
       <c r="BG88" t="n">
         <v>2</v>
@@ -41472,7 +41472,7 @@
         <v>0</v>
       </c>
       <c r="BF89" t="n">
-        <v>-1</v>
+        <v>4918</v>
       </c>
       <c r="BG89" t="n">
         <v>2</v>
@@ -41912,7 +41912,7 @@
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>-1</v>
+        <v>7386</v>
       </c>
       <c r="BG90" t="n">
         <v>2</v>
@@ -42360,7 +42360,7 @@
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>-1</v>
+        <v>15876</v>
       </c>
       <c r="BG91" t="n">
         <v>2</v>
@@ -42816,7 +42816,7 @@
         <v>0</v>
       </c>
       <c r="BF92" t="n">
-        <v>-1</v>
+        <v>6173</v>
       </c>
       <c r="BG92" t="n">
         <v>2</v>
@@ -43272,7 +43272,7 @@
         <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>-1</v>
+        <v>34442</v>
       </c>
       <c r="BG93" t="n">
         <v>2</v>
@@ -43744,7 +43744,7 @@
         <v>0</v>
       </c>
       <c r="BF94" t="n">
-        <v>-1</v>
+        <v>4467</v>
       </c>
       <c r="BG94" t="n">
         <v>2</v>
@@ -44200,7 +44200,7 @@
         <v>0</v>
       </c>
       <c r="BF95" t="n">
-        <v>-1</v>
+        <v>2373</v>
       </c>
       <c r="BG95" t="n">
         <v>2</v>
@@ -44664,7 +44664,7 @@
         <v>0</v>
       </c>
       <c r="BF96" t="n">
-        <v>-1</v>
+        <v>5355</v>
       </c>
       <c r="BG96" t="n">
         <v>2</v>
@@ -45104,7 +45104,7 @@
         <v>0</v>
       </c>
       <c r="BF97" t="n">
-        <v>-1</v>
+        <v>3513</v>
       </c>
       <c r="BG97" t="n">
         <v>2</v>
@@ -45552,7 +45552,7 @@
         <v>0</v>
       </c>
       <c r="BF98" t="n">
-        <v>-1</v>
+        <v>4125</v>
       </c>
       <c r="BG98" t="n">
         <v>2</v>
@@ -46008,7 +46008,7 @@
         <v>0</v>
       </c>
       <c r="BF99" t="n">
-        <v>-1</v>
+        <v>10289</v>
       </c>
       <c r="BG99" t="n">
         <v>2</v>
@@ -46480,7 +46480,7 @@
         <v>0</v>
       </c>
       <c r="BF100" t="n">
-        <v>-1</v>
+        <v>3165</v>
       </c>
       <c r="BG100" t="n">
         <v>2</v>
@@ -46952,7 +46952,7 @@
         <v>0</v>
       </c>
       <c r="BF101" t="n">
-        <v>-1</v>
+        <v>8870</v>
       </c>
       <c r="BG101" t="n">
         <v>2</v>
@@ -47408,7 +47408,7 @@
         <v>0</v>
       </c>
       <c r="BF102" t="n">
-        <v>-1</v>
+        <v>6722</v>
       </c>
       <c r="BG102" t="n">
         <v>2</v>
@@ -47856,7 +47856,7 @@
         <v>0</v>
       </c>
       <c r="BF103" t="n">
-        <v>-1</v>
+        <v>19078</v>
       </c>
       <c r="BG103" t="n">
         <v>2</v>
@@ -48304,7 +48304,7 @@
         <v>0</v>
       </c>
       <c r="BF104" t="n">
-        <v>-1</v>
+        <v>3348</v>
       </c>
       <c r="BG104" t="n">
         <v>2</v>
@@ -48752,7 +48752,7 @@
         <v>0</v>
       </c>
       <c r="BF105" t="n">
-        <v>-1</v>
+        <v>2167</v>
       </c>
       <c r="BG105" t="n">
         <v>2</v>
@@ -49216,7 +49216,7 @@
         <v>0</v>
       </c>
       <c r="BF106" t="n">
-        <v>-1</v>
+        <v>7699</v>
       </c>
       <c r="BG106" t="n">
         <v>2</v>
@@ -49664,7 +49664,7 @@
         <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>-1</v>
+        <v>7146</v>
       </c>
       <c r="BG107" t="n">
         <v>2</v>
@@ -50120,7 +50120,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>-1</v>
+        <v>19977</v>
       </c>
       <c r="BG108" t="n">
         <v>2</v>
@@ -50576,7 +50576,7 @@
         <v>0</v>
       </c>
       <c r="BF109" t="n">
-        <v>-1</v>
+        <v>7281</v>
       </c>
       <c r="BG109" t="n">
         <v>2</v>

--- a/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
+++ b/data/matches/leagues/Denmark_Superliga_2025-2026.xlsx
@@ -69578,13 +69578,13 @@
         <v>6</v>
       </c>
       <c r="T151" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U151" t="n">
         <v>13</v>
       </c>
       <c r="V151" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W151" t="n">
         <v>11</v>
@@ -69696,7 +69696,7 @@
         <v>0</v>
       </c>
       <c r="BF151" t="n">
-        <v>-1</v>
+        <v>6083</v>
       </c>
       <c r="BG151" t="n">
         <v>2</v>
@@ -69759,10 +69759,10 @@
         <v>1.73</v>
       </c>
       <c r="CA151" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="CB151" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="CC151" t="n">
         <v>0</v>
@@ -69813,7 +69813,7 @@
         <v>18</v>
       </c>
       <c r="CS151" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CT151" t="n">
         <v>1</v>
